--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="6_{07DD5C5E-4B7E-564D-9FFA-3C28EE9E5650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C94B56B-9988-0E4E-A9FD-D4F7485A58AC}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="6_{07DD5C5E-4B7E-564D-9FFA-3C28EE9E5650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5DD8E4C-FA79-834A-BD7F-F01A012B50B1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34540" windowHeight="20120" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="36260" yWindow="-7080" windowWidth="34540" windowHeight="19640" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="248">
   <si>
     <t>Progress stage</t>
   </si>
@@ -195,9 +195,6 @@
     <t>microglia</t>
   </si>
   <si>
-    <t>Finlay_2006_primary_or_equivalent.xlsx</t>
-  </si>
-  <si>
     <t xml:space="preserve">pdf </t>
   </si>
   <si>
@@ -525,9 +522,6 @@
     <t>--&gt; Online database</t>
   </si>
   <si>
-    <t>FINISHED w/TSV</t>
-  </si>
-  <si>
     <t>DOI (or Alt)</t>
   </si>
   <si>
@@ -540,27 +534,12 @@
     <t>mostly secondary</t>
   </si>
   <si>
-    <t>HerculanoHouzel_etal_2015_Table1.xlsx</t>
-  </si>
-  <si>
     <t>HerculanoHouzel_etal_2015_Table1.csv</t>
   </si>
   <si>
     <t>https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf</t>
   </si>
   <si>
-    <t>HerculanoHouzel_etal_2015_Table2.xlsx</t>
-  </si>
-  <si>
-    <t>HerculanoHouzel_etal_2015_Table3.xlsx</t>
-  </si>
-  <si>
-    <t>HerculanoHouzel_etal_2015_Table4.xlsx</t>
-  </si>
-  <si>
-    <t>HerculanoHouzel_etal_2015_Table5.xlsx</t>
-  </si>
-  <si>
     <t>HerculanoHouzel_etal_2015_Table2.csv</t>
   </si>
   <si>
@@ -576,30 +555,15 @@
     <t>cerebral cortex surface area and number of areas (broadly defined)</t>
   </si>
   <si>
-    <t>dossantos_etal_2020_Table1_primary_or_equivalent.csv</t>
-  </si>
-  <si>
-    <t>dossantos_etal_2020_table1.csv</t>
-  </si>
-  <si>
-    <t>dossantos_etal_2017_tables1.csv</t>
-  </si>
-  <si>
     <t>pdf online</t>
   </si>
   <si>
-    <t>HerculanoHouzel_etal_2020_Table1_primary_or_equivalent.csv</t>
-  </si>
-  <si>
     <t>HerculanoHouzel_etal_2020_Table1.csv</t>
   </si>
   <si>
     <t>HerculanoHouzel_etal_2020_Table2.csv</t>
   </si>
   <si>
-    <t>HerculanoHouzel_etal_2020_Table2_primary_or_equivalent.csv</t>
-  </si>
-  <si>
     <t>docx</t>
   </si>
   <si>
@@ -618,9 +582,6 @@
     <t>JardimMesseder_etal_2017_Table1.csv</t>
   </si>
   <si>
-    <t>JardimMesseder_etal_2017_Table1_primary_or_equivalent.csv</t>
-  </si>
-  <si>
     <t>1st Author (no punctuation)</t>
   </si>
   <si>
@@ -738,9 +699,6 @@
     <t>Item number</t>
   </si>
   <si>
-    <t>caspar_etal_2022_table1_snapshot.xlsx</t>
-  </si>
-  <si>
     <t>Changizi_2001_Figure3_snapshot.csv</t>
   </si>
   <si>
@@ -750,9 +708,6 @@
     <t>Heffner_Masterton_1975_TableI_snapshot.xlsx</t>
   </si>
   <si>
-    <t>Caspar_etal_2022_table1.csv</t>
-  </si>
-  <si>
     <t>Item encoded</t>
   </si>
   <si>
@@ -760,6 +715,72 @@
   </si>
   <si>
     <t>DosSantos_etal_2017_TableS1_snapshot.csv</t>
+  </si>
+  <si>
+    <t>DosSantos_etal_2020_Table1_snapshot.csv</t>
+  </si>
+  <si>
+    <t>DosSantos_etal_2020_Table1.csv</t>
+  </si>
+  <si>
+    <t>DosSantos_etal_2017_TableS1.csv</t>
+  </si>
+  <si>
+    <t>Finlay_etal_2006_Table6.1_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>Caspar_etal_2022_Table1_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>Caspar_etal_2022_Table1.csv</t>
+  </si>
+  <si>
+    <t>Finlay_etal_2006_Table6.1.csv</t>
+  </si>
+  <si>
+    <t>Changizi_2001_Figure3.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_TABLE1_snapshot.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2020_TABLE2_snapshot.csv</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table1_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table2_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table3_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table4_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>HerculanoHouzel_etal_2015_Table5_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>JardimMesseder_etal_2017_Table1_snapshot.csv</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fnana.2017.00118</t>
+  </si>
+  <si>
+    <t>TABLE 1 | Summary of the cellular composition of the major brain structures of eight carnivoran species.</t>
+  </si>
+  <si>
+    <t>primary; secondary brain and body mass</t>
+  </si>
+  <si>
+    <t>Online Database</t>
+  </si>
+  <si>
+    <t>added</t>
+  </si>
+  <si>
+    <t>already there</t>
   </si>
 </sst>
 </file>
@@ -831,18 +852,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -858,33 +873,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1200,2099 +1209,2213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25" style="15" customWidth="1"/>
-    <col min="2" max="2" width="17" style="15" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
-    <col min="7" max="7" width="22.1640625" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45" customWidth="1"/>
-    <col min="10" max="10" width="53.83203125" customWidth="1"/>
-    <col min="11" max="11" width="23.1640625" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="53.5" customWidth="1"/>
-    <col min="14" max="14" width="16.1640625" customWidth="1"/>
-    <col min="15" max="15" width="35.33203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" customWidth="1"/>
-    <col min="18" max="18" width="22.1640625" customWidth="1"/>
-    <col min="19" max="19" width="14.33203125" customWidth="1"/>
-    <col min="20" max="20" width="41.1640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.5" customWidth="1"/>
+    <col min="1" max="1" width="25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="20.5" style="8" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="45" style="8" customWidth="1"/>
+    <col min="10" max="10" width="53.83203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="8" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="8" customWidth="1"/>
+    <col min="14" max="14" width="41.5" style="8" customWidth="1"/>
+    <col min="15" max="15" width="16.1640625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="34.1640625" style="8" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="22.1640625" style="8" customWidth="1"/>
+    <col min="20" max="20" width="14.33203125" style="8" customWidth="1"/>
+    <col min="21" max="21" width="41.1640625" style="8" customWidth="1"/>
+    <col min="22" max="22" width="12.33203125" style="8" customWidth="1"/>
+    <col min="23" max="23" width="11" style="8"/>
+    <col min="24" max="24" width="10.6640625" style="8" customWidth="1"/>
+    <col min="25" max="25" width="6.5" style="8" customWidth="1"/>
+    <col min="26" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="I1" s="1" t="s">
+    <row r="1" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="M1" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="str">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="str">
         <f t="shared" ref="A2:A29" si="0">B2 &amp; IF(C2&lt;&gt;"", "_" &amp; C2, "") &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "") &amp; IF(E2&lt;&gt;"", "-" &amp; E2, "")</f>
         <v>_Unpublished_ProjectKaskan</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6" t="str">
+      <c r="B2" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="str">
         <f t="shared" ref="I2:I33" si="1">TRIM(_xlfn.TEXTJOIN("_",FALSE,A2,(SUBSTITUTE(H2," ",""))))</f>
         <v>_Unpublished_ProjectKaskan_</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <f t="shared" ref="J2:J33" si="2">TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, F2, H2), "/", "%2F"), ":", "%3A"), " ", ""))</f>
         <v>_</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="3"/>
-      <c r="P2" t="s">
+      <c r="M2" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N2" s="7"/>
+      <c r="O2" s="9"/>
+      <c r="Q2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="16"/>
-      <c r="U2" t="s">
+      <c r="U2" s="7"/>
+      <c r="V2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="X2" t="s">
+      <c r="W2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="str">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Burger_etal_2019</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D3" s="16">
+      <c r="B3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="7">
         <v>2019</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="I3" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
-      <c r="J3" s="6" t="str">
+      <c r="J3" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="K3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O3" t="str">
-        <f>IF(N3="N", M3, "write file name")</f>
+      <c r="P3" s="8" t="str">
+        <f>IF(O3="N", N3, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="16"/>
-      <c r="U3" t="s">
+      <c r="U3" s="7"/>
+      <c r="V3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="str">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Caspar_etal_2022</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="16">
+      <c r="B4" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="7">
         <v>2022</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" t="s">
-        <v>162</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="K4" s="3"/>
+      <c r="L4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O4" t="s">
-        <v>237</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="P4" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="U4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="str">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Caspar_etal_2022</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="B5" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="7">
         <v>2022</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="6" t="str">
+      <c r="E5" s="12"/>
+      <c r="F5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="str">
         <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,A5,(SUBSTITUTE(H5," ",""))))</f>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
-      <c r="J5" s="6" t="str">
+      <c r="J5" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="15" t="s">
+      <c r="K5" s="13"/>
+      <c r="L5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O5" t="str">
-        <f>IF(N5="N", M5, "write file name")</f>
+      <c r="P5" s="8" t="str">
+        <f>IF(O5="N", N5, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="T5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="U5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="str">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Changizi_2001</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16">
+      <c r="B6" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7">
         <v>2001</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="12"/>
+      <c r="F6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Changizi_2001_Figure3</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" t="s">
-        <v>235</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="K6" s="13"/>
+      <c r="L6" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O6" t="str">
-        <f>IF(N6="N", M6, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="P6" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" t="s">
-        <v>98</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="R6" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="S6" s="5"/>
-      <c r="T6" s="15"/>
-      <c r="U6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="S6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="T6" s="14"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="X6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="str">
+      <c r="W6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Chen_Wiens_2020</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="B7" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="7">
         <v>2020</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I7" s="6" t="str">
+      <c r="I7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
-      <c r="J7" s="6" t="str">
+      <c r="J7" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" t="s">
-        <v>162</v>
-      </c>
-      <c r="M7" s="15" t="s">
+      <c r="K7" s="3"/>
+      <c r="L7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O7" t="str">
-        <f>IF(N7="N", M7, "write file name")</f>
+      <c r="P7" s="8" t="str">
+        <f>IF(O7="N", N7, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="T7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="T7" s="16"/>
-      <c r="U7" t="s">
+      <c r="U7" s="7"/>
+      <c r="V7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="X7" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y7" t="s">
+      <c r="Y7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z7" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="str">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>DosSantos_etal_2017</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="B8" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="7">
         <v>2017</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="6" t="str">
+      <c r="I8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
-      <c r="J8" s="6" t="str">
+      <c r="J8" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
-      <c r="K8" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="N8" s="11" t="s">
+      <c r="K8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="R8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="S8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="T8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="T8" s="18"/>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="10"/>
+      <c r="V8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="W8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="Y8" s="11" t="s">
+      <c r="Z8" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="str">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="str">
         <f t="shared" si="0"/>
         <v>DosSantos_etal_2020</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D9" s="16">
+      <c r="B9" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="7">
         <v>2020</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="6" t="str">
+      <c r="E9" s="7"/>
+      <c r="F9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
-      <c r="J9" s="6" t="str">
+      <c r="J9" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="N9" s="11" t="s">
+      <c r="K9" s="3"/>
+      <c r="L9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q9" s="11" t="s">
+      <c r="P9" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="19"/>
-      <c r="U9" s="11" t="s">
+      <c r="U9" s="7"/>
+      <c r="V9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="V9" s="11" t="s">
+      <c r="W9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="Y9" s="11" t="s">
+      <c r="Z9" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="str">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Finlay_etal_2006</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="16">
+      <c r="B10" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="7">
         <v>2006</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="6" t="str">
+      <c r="E10" s="7"/>
+      <c r="F10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
-      <c r="J10" s="6" t="str">
+      <c r="J10" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" t="s">
-        <v>235</v>
-      </c>
-      <c r="M10" s="15" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" t="str">
-        <f>IF(N10="N", M10, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="R10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" t="s">
-        <v>20</v>
-      </c>
-      <c r="R10" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" s="3" t="s">
+      <c r="U10" s="7"/>
+      <c r="V10" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="T10" s="16"/>
-      <c r="U10" t="s">
-        <v>178</v>
-      </c>
-      <c r="X10" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="Z10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="str">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Heffner_Masterton_1975</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="B11" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="7">
         <v>1975</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="6" t="str">
+      <c r="E11" s="7"/>
+      <c r="F11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Heffner_Masterton_1975_TableI</v>
       </c>
-      <c r="J11" s="6" t="str">
+      <c r="J11" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="K11" s="3"/>
+      <c r="L11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O11" t="s">
-        <v>165</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="P11" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R11" t="s">
-        <v>97</v>
-      </c>
-      <c r="T11" s="16"/>
-      <c r="U11" t="s">
+      <c r="S11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="U11" s="7"/>
+      <c r="V11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="X11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V11" t="s">
-        <v>166</v>
-      </c>
-      <c r="W11" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="Z11" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="str">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Heffner_Masterton_1983</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="16">
+      <c r="B12" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="7">
         <v>1983</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="6" t="str">
+      <c r="E12" s="7"/>
+      <c r="F12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Heffner_Masterton_1983_TableI</v>
       </c>
-      <c r="J12" s="6" t="str">
+      <c r="J12" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M12" s="22"/>
-      <c r="O12" t="str">
-        <f>IF(N12="N", M12, "write file name")</f>
+      <c r="K12" s="3"/>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N12" s="15"/>
+      <c r="P12" s="8" t="str">
+        <f>IF(O12="N", N12, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T12" s="16"/>
-      <c r="U12" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y12" t="s">
+      <c r="U12" s="7"/>
+      <c r="V12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="str">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Heldstab_etal_2016</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="B13" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="7">
         <v>2016</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="6" t="str">
+      <c r="E13" s="7"/>
+      <c r="F13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
-      <c r="J13" s="6" t="str">
+      <c r="J13" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="3"/>
+      <c r="L13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N13" s="15"/>
+      <c r="P13" s="8" t="str">
+        <f>IF(O13="N", N13, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U13" s="7"/>
+      <c r="V13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M13" s="22"/>
-      <c r="O13" t="str">
-        <f>IF(N13="N", M13, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>20</v>
-      </c>
-      <c r="T13" s="16"/>
-      <c r="U13" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y13" t="s">
+      <c r="Z13" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="str">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="B14" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="7">
         <v>2015</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="6" t="str">
+      <c r="E14" s="7"/>
+      <c r="F14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
-      <c r="J14" s="6" t="str">
+      <c r="J14" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M14" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="N14" s="12" t="s">
+      <c r="K14" s="3"/>
+      <c r="L14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O14" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="R14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="S14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S14" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="T14" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="U14" s="11" t="s">
+      <c r="T14" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="V14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y14" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="str">
+      <c r="Z14" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="16">
+      <c r="B15" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="7">
         <v>2015</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="12" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" s="6" t="str">
+      <c r="I15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
-      <c r="J15" s="6" t="str">
+      <c r="J15" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M15" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="N15" s="12" t="s">
+      <c r="K15" s="3"/>
+      <c r="L15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O15" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="P15" s="11" t="s">
+      <c r="P15" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="R15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S15" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="T15" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="U15" s="11" t="s">
+      <c r="T15" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="V15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y15" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="str">
+      <c r="Z15" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="16">
+      <c r="B16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="7">
         <v>2015</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="6" t="str">
+      <c r="E16" s="7"/>
+      <c r="F16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
-      <c r="J16" s="6" t="str">
+      <c r="J16" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M16" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="N16" s="12" t="s">
+      <c r="K16" s="3"/>
+      <c r="L16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O16" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="P16" s="11" t="s">
+      <c r="P16" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="R16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S16" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="U16" s="11" t="s">
+      <c r="T16" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="V16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y16" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="str">
+      <c r="Z16" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D17" s="16">
+      <c r="B17" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="7">
         <v>2015</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="6" t="str">
+      <c r="E17" s="7"/>
+      <c r="F17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
-      <c r="J17" s="6" t="str">
+      <c r="J17" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M17" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="N17" s="12" t="s">
+      <c r="K17" s="3"/>
+      <c r="L17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O17" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="P17" s="11" t="s">
+      <c r="P17" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="R17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="11" t="s">
+      <c r="S17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S17" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="U17" s="11" t="s">
+      <c r="T17" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U17" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="V17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y17" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="str">
+      <c r="Z17" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="B18" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="7">
         <v>2015</v>
       </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="6" t="str">
+      <c r="E18" s="7"/>
+      <c r="F18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
-      <c r="J18" s="6" t="str">
+      <c r="J18" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M18" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="N18" s="12" t="s">
+      <c r="K18" s="3"/>
+      <c r="L18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O18" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="P18" s="11" t="s">
+      <c r="P18" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="R18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S18" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="T18" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="U18" s="11" t="s">
+      <c r="T18" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="V18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y18" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="str">
+      <c r="Z18" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D19" s="16">
+      <c r="B19" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="7">
         <v>2020</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="6" t="str">
+      <c r="E19" s="7"/>
+      <c r="F19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
-      <c r="J19" s="6" t="str">
+      <c r="J19" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M19" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="N19" s="12" t="s">
+      <c r="K19" s="3"/>
+      <c r="L19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O19" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="P19" s="11" t="s">
+      <c r="P19" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="R19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R19" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="T19" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" s="11" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="str">
+      <c r="S19" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z19" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="str">
         <f t="shared" si="0"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="B20" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="7">
         <v>2020</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="6" t="str">
+      <c r="E20" s="7"/>
+      <c r="F20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
-      <c r="J20" s="6" t="str">
+      <c r="J20" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M20" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="N20" s="12" t="s">
+      <c r="K20" s="3"/>
+      <c r="L20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O20" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="P20" s="11" t="s">
+      <c r="P20" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="R20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R20" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="T20" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y20" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="str">
+      <c r="S20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z20" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Iwaniuk_etal_2016</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D21" s="16">
+      <c r="B21" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="7">
         <v>2016</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" s="6" t="str">
+      <c r="E21" s="7"/>
+      <c r="F21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Iwaniuk_etal_2016_Table1</v>
       </c>
-      <c r="J21" s="6" t="str">
+      <c r="J21" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
-      <c r="K21" s="6"/>
-      <c r="L21" t="s">
-        <v>56</v>
-      </c>
-      <c r="M21" s="22"/>
-      <c r="O21" t="str">
-        <f>IF(N21="N", M21, "write file name")</f>
+      <c r="K21" s="3"/>
+      <c r="L21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N21" s="15"/>
+      <c r="P21" s="8" t="str">
+        <f>IF(O21="N", N21, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T21" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="U21" t="s">
+      <c r="U21" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z21" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Y21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="str">
+    </row>
+    <row r="22" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Iwaniuk_etal_2016</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="B22" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="7">
         <v>2016</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I22" s="6" t="str">
+      <c r="E22" s="7"/>
+      <c r="F22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Iwaniuk_etal_2016_Table2</v>
       </c>
-      <c r="J22" s="6" t="str">
+      <c r="J22" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
-      <c r="K22" s="6"/>
-      <c r="L22" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="22"/>
-      <c r="O22" t="str">
-        <f>IF(N22="N", M22, "write file name")</f>
+      <c r="K22" s="3"/>
+      <c r="L22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N22" s="15"/>
+      <c r="P22" s="8" t="str">
+        <f>IF(O22="N", N22, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T22" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="U22" t="s">
+      <c r="U22" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Y22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="str">
+    </row>
+    <row r="23" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Iwaniuk_etal_2016</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="16">
+      <c r="B23" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="7">
         <v>2016</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="6" t="str">
+      <c r="E23" s="7"/>
+      <c r="F23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Iwaniuk_etal_2016_Table3</v>
       </c>
-      <c r="J23" s="6" t="str">
+      <c r="J23" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
-      <c r="K23" s="6"/>
-      <c r="L23" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" s="22"/>
-      <c r="O23" t="str">
-        <f>IF(N23="N", M23, "write file name")</f>
+      <c r="K23" s="3"/>
+      <c r="L23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N23" s="15"/>
+      <c r="P23" s="8" t="str">
+        <f>IF(O23="N", N23, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T23" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="U23" t="s">
+      <c r="U23" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Y23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="str">
+    </row>
+    <row r="24" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Iwaniuk_etal_2016</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="B24" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="7">
         <v>2016</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="6" t="str">
+      <c r="E24" s="7"/>
+      <c r="F24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Iwaniuk_etal_2016_Table4</v>
       </c>
-      <c r="J24" s="6" t="str">
+      <c r="J24" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
-      <c r="K24" s="6"/>
-      <c r="L24" t="s">
-        <v>56</v>
-      </c>
-      <c r="M24" s="22"/>
-      <c r="O24" t="str">
-        <f>IF(N24="N", M24, "write file name")</f>
+      <c r="K24" s="3"/>
+      <c r="L24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N24" s="15"/>
+      <c r="P24" s="8" t="str">
+        <f>IF(O24="N", N24, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T24" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="U24" t="s">
+      <c r="U24" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Y24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="str">
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="str">
         <f t="shared" si="0"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="B25" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="7">
         <v>2017</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" s="6" t="str">
+      <c r="E25" s="7"/>
+      <c r="F25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="3" t="str">
         <f t="shared" si="1"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
-      <c r="J25" s="6" t="str">
+      <c r="J25" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M25" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="N25" s="12" t="s">
+      <c r="K25" s="3"/>
+      <c r="L25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="P25" s="11" t="s">
+      <c r="P25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q25" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="R25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R25" s="11" t="s">
+      <c r="S25" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="T25" s="19"/>
-      <c r="U25" s="11" t="s">
+      <c r="T25" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="V25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Y25" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="str">
+      <c r="Z25" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="16">
+      <c r="C26" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="7">
         <v>2018</v>
       </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I26" s="6" t="str">
+      <c r="E26" s="7"/>
+      <c r="F26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I26" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
-      <c r="J26" s="6" t="str">
+      <c r="J26" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="12" t="s">
+      <c r="K26" s="3"/>
+      <c r="L26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N26" s="15"/>
+      <c r="O26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O26" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="P26" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q26" s="11" t="s">
+      <c r="P26" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="R26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R26" s="11" t="s">
+      <c r="S26" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S26" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="T26" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="str">
+      <c r="T26" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="W26" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z26" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B27" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="16">
+      <c r="C27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="7">
         <v>2018</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="12" t="s">
+      <c r="E27" s="7"/>
+      <c r="F27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="6" t="str">
+      <c r="I27" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
-      <c r="J27" s="6" t="str">
+      <c r="J27" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M27" s="21"/>
-      <c r="N27" s="12" t="s">
+      <c r="K27" s="3"/>
+      <c r="L27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="N27" s="15"/>
+      <c r="O27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O27" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="P27" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q27" s="11" t="s">
+      <c r="P27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="11" t="s">
+      <c r="S27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S27" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="T27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="U27" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y27" s="11" t="s">
+      <c r="T27" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="U27" s="7" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="str">
+      <c r="V27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="W27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z27" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="str">
         <f t="shared" si="0"/>
         <v>ManyPrimates_etal_2022</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="16">
+      <c r="B28" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="7">
         <v>2022</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I28" s="6" t="str">
+      <c r="E28" s="7"/>
+      <c r="F28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" s="3" t="str">
         <f t="shared" si="1"/>
         <v>ManyPrimates_etal_2022_data/species_predictors.xlsx</v>
       </c>
-      <c r="J28" s="6" t="str">
+      <c r="J28" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspecies_predictors.xlsx</v>
       </c>
-      <c r="K28" s="6"/>
-      <c r="L28" t="s">
+      <c r="K28" s="3"/>
+      <c r="L28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N28" s="15"/>
+      <c r="P28" s="8" t="str">
+        <f t="shared" ref="P28:P33" si="3">IF(O28="N", N28, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="U28" s="7"/>
+      <c r="V28" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="M28" s="22"/>
-      <c r="O28" t="str">
-        <f t="shared" ref="O28:O33" si="3">IF(N28="N", M28, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="P28" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>20</v>
-      </c>
-      <c r="R28" t="s">
-        <v>37</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="T28" s="16"/>
-      <c r="U28" t="s">
+      <c r="W28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="X28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="V28" t="s">
-        <v>23</v>
-      </c>
-      <c r="W28" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y28" t="s">
+      <c r="Z28" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="str">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Powell_etal_2017</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D29" s="16">
+      <c r="B29" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="7">
         <v>2017</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="7"/>
+      <c r="F29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I29" s="6" t="str">
+      <c r="I29" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
-      <c r="J29" s="6" t="str">
+      <c r="J29" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M29" s="22"/>
-      <c r="O29" t="str">
+      <c r="K29" s="3"/>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N29" s="15"/>
+      <c r="P29" s="8" t="str">
         <f t="shared" si="3"/>
         <v>write file name</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="T29" s="16"/>
-      <c r="U29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V29" t="s">
+      <c r="T29" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="U29" s="7"/>
+      <c r="V29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="W29" t="s">
+      <c r="X29" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="str">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="str">
         <f>B30 &amp; IF(C30&lt;&gt;"", "_" &amp; C30, "") &amp; IF(D30&lt;&gt;"", "_" &amp; D30, "") &amp; IF(E30&lt;&gt;"", "_" &amp; E30, "")</f>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="16">
+      <c r="B30" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="7">
         <v>2004</v>
       </c>
-      <c r="E30" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="6" t="str">
+      <c r="E30" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
-      <c r="J30" s="6" t="str">
+      <c r="J30" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
-      <c r="K30" s="6"/>
-      <c r="L30" t="s">
-        <v>67</v>
-      </c>
-      <c r="M30" s="22"/>
-      <c r="O30" t="str">
+      <c r="K30" s="3"/>
+      <c r="L30" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N30" s="15"/>
+      <c r="P30" s="8" t="str">
         <f t="shared" si="3"/>
         <v>write file name</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q30" t="s">
-        <v>61</v>
-      </c>
-      <c r="T30" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="U30" t="s">
-        <v>71</v>
-      </c>
-      <c r="V30" t="s">
+      <c r="R30" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W30" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="str">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="str">
         <f>B31 &amp; IF(C31&lt;&gt;"", "_" &amp; C31, "") &amp; IF(D31&lt;&gt;"", "_" &amp; D31, "") &amp; IF(E31&lt;&gt;"", "_" &amp; E31, "")</f>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="16">
+      <c r="B31" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="7">
         <v>2004</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I31" s="6" t="str">
+      <c r="E31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
-      <c r="J31" s="6" t="str">
+      <c r="J31" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
-      <c r="K31" s="6"/>
-      <c r="L31" t="s">
-        <v>67</v>
-      </c>
-      <c r="M31" s="22"/>
-      <c r="O31" t="str">
+      <c r="K31" s="3"/>
+      <c r="L31" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N31" s="15"/>
+      <c r="P31" s="8" t="str">
         <f t="shared" si="3"/>
         <v>write file name</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q31" t="s">
-        <v>61</v>
-      </c>
-      <c r="T31" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="U31" t="s">
-        <v>71</v>
-      </c>
-      <c r="V31" t="s">
+      <c r="R31" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="U31" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="V31" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W31" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="str">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="str">
         <f>B32 &amp; IF(C32&lt;&gt;"", "_" &amp; C32, "") &amp; IF(D32&lt;&gt;"", "_" &amp; D32, "") &amp; IF(E32&lt;&gt;"", "-" &amp; E32, "")</f>
         <v>Winkler_Bryant_2021</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D32" s="16">
+      <c r="B32" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="7">
         <v>2021</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="6" t="s">
+      <c r="E32" s="7"/>
+      <c r="F32" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I32" s="6" t="str">
+      <c r="I32" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Winkler_Bryant_2021_Figure1</v>
       </c>
-      <c r="J32" s="6" t="str">
+      <c r="J32" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M32" s="22"/>
-      <c r="O32" t="str">
+      <c r="K32" s="3"/>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N32" s="15"/>
+      <c r="P32" s="8" t="str">
         <f t="shared" si="3"/>
         <v>write file name</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="U32" s="7"/>
+      <c r="V32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T32" s="16"/>
-      <c r="U32" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y32" t="s">
+      <c r="Z32" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="str">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="str">
         <f>B33 &amp; IF(C33&lt;&gt;"", "_" &amp; C33, "") &amp; IF(D33&lt;&gt;"", "_" &amp; D33, "") &amp; IF(E33&lt;&gt;"", "-" &amp; E33, "")</f>
         <v>Young_etal_2013</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D33" s="16">
+      <c r="B33" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="7">
         <v>2013</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I33" s="6" t="str">
+      <c r="E33" s="7"/>
+      <c r="F33" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="3" t="str">
         <f t="shared" si="1"/>
         <v>Young_etal_2013_Table1</v>
       </c>
-      <c r="J33" s="6" t="str">
+      <c r="J33" s="3" t="str">
         <f t="shared" si="2"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
-      <c r="K33" s="6"/>
-      <c r="L33" t="s">
-        <v>67</v>
-      </c>
-      <c r="M33" s="22"/>
-      <c r="O33" t="str">
+      <c r="K33" s="3"/>
+      <c r="L33" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="N33" s="15"/>
+      <c r="P33" s="8" t="str">
         <f t="shared" si="3"/>
         <v>write file name</v>
       </c>
-      <c r="P33" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q33" t="s">
+      <c r="Q33" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="R33" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="T33" s="16"/>
-      <c r="U33" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s">
+      <c r="U33" s="7"/>
+      <c r="V33" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z33" s="8" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="S4" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
-    <hyperlink ref="S5" r:id="rId2" xr:uid="{0C8D4DAC-C617-2547-BF75-D17B07FAB104}"/>
-    <hyperlink ref="S7" r:id="rId3" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
-    <hyperlink ref="S8" r:id="rId4" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
-    <hyperlink ref="S10" r:id="rId5" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
-    <hyperlink ref="S28" r:id="rId6" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
-    <hyperlink ref="S29" r:id="rId7" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
-    <hyperlink ref="S14" r:id="rId8" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
-    <hyperlink ref="S15:S18" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
-    <hyperlink ref="S27" r:id="rId10" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
-    <hyperlink ref="S26" r:id="rId11" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
+    <hyperlink ref="T4" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
+    <hyperlink ref="T5" r:id="rId2" xr:uid="{0C8D4DAC-C617-2547-BF75-D17B07FAB104}"/>
+    <hyperlink ref="T7" r:id="rId3" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
+    <hyperlink ref="T8" r:id="rId4" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
+    <hyperlink ref="T10" r:id="rId5" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
+    <hyperlink ref="T28" r:id="rId6" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
+    <hyperlink ref="T29" r:id="rId7" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
+    <hyperlink ref="T14" r:id="rId8" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
+    <hyperlink ref="T15:T18" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
+    <hyperlink ref="T27" r:id="rId10" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
+    <hyperlink ref="T26" r:id="rId11" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
+    <hyperlink ref="T25" r:id="rId12" xr:uid="{236492C9-FC3A-614B-84DC-0D56063EE72E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3308,97 +3431,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="B5" t="s">
         <v>78</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="B6" t="s">
         <v>80</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="B7" t="s">
         <v>82</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="B8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="B9" t="s">
         <v>86</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="B10" t="s">
         <v>88</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="B11" t="s">
         <v>90</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3407,15 +3530,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -3424,6 +3538,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3664,26 +3787,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -5593,6 +5593,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -5601,15 +5610,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5856,26 +5856,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17DA8DA6-16B6-C54B-9DC1-33E8AE2A2DCE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32752C55-B6BF-A242-9DFD-CB091070879E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34560" yWindow="-5960" windowWidth="34680" windowHeight="18920" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="280">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -897,6 +897,12 @@
   </si>
   <si>
     <t>Kverkova_etal_2018_TableS5_snapshot.csv</t>
+  </si>
+  <si>
+    <t>Table S1 Physiological and life-history variables</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -1293,9 +1299,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1333,7 +1339,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1439,7 +1445,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1581,7 +1587,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5168,6 +5174,12 @@
       <c r="P45" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="X45" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>279</v>
+      </c>
       <c r="AI45">
         <v>9</v>
       </c>
@@ -5227,6 +5239,9 @@
       <c r="X46" t="s">
         <v>232</v>
       </c>
+      <c r="AA46" t="s">
+        <v>279</v>
+      </c>
       <c r="AI46">
         <v>6</v>
       </c>
@@ -5283,6 +5298,9 @@
       </c>
       <c r="P47" s="20" t="s">
         <v>49</v>
+      </c>
+      <c r="AA47" s="17" t="s">
+        <v>279</v>
       </c>
       <c r="AI47" s="17">
         <v>7</v>
@@ -5861,16 +5879,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E6B17D0-2911-AA42-BCCE-08D385DE0529}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCB6B39-592B-7347-A777-25143F16DD52}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5960" windowWidth="38400" windowHeight="17420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34560" yWindow="-5960" windowWidth="44700" windowHeight="16720" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="301">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -773,9 +773,6 @@
     <t>Smaers, J. B., Steele, J., Case, C. R., Cowper, A., Amunts, K., &amp; Zilles, K. (2011). Primate prefrontal cortex evolution: human brains are the extreme of a lateralized ape trend. Brain Behav Evol, 77(2), 67-78. https://doi.org/10.1159/000323671</t>
   </si>
   <si>
-    <t>10.1159/000323671</t>
-  </si>
-  <si>
     <t>SupplementaryTable1</t>
   </si>
   <si>
@@ -914,12 +911,6 @@
     <t xml:space="preserve">Mota, B., Dos Santos, S. E., Ventura-Antunes, L., Jardim-Messeder, D., Neves, K., Kazu, R. S., Noctor, S., Lambert, K., Bertelsen, M. F., Manger, P. R., Sherwood, C. C., Kaas, J. H., &amp; Herculano-Houzel, S. (2019). White matter volume and white/gray matter ratio in mammalian species as a consequence of the universal scaling of cortical folding. Proc Natl Acad Sci U S A, 116(30), 15253-15261. https://doi.org/10.1073/pnas.1716956116 	</t>
   </si>
   <si>
-    <t>10.1159/000323672</t>
-  </si>
-  <si>
-    <t>10.1159/000323673</t>
-  </si>
-  <si>
     <t>Supplementary Table S1. Morphometrical and cell number data used in this study (“our dataset”).</t>
   </si>
   <si>
@@ -933,6 +924,48 @@
   </si>
   <si>
     <t>Table 1. Cellular composition of the spinal cord</t>
+  </si>
+  <si>
+    <t>Supplementary Table 1: Dataset of individual spinal cord measurements</t>
+  </si>
+  <si>
+    <t>Supplementary Table 1</t>
+  </si>
+  <si>
+    <t>primary (averages)</t>
+  </si>
+  <si>
+    <t>primary (individual)</t>
+  </si>
+  <si>
+    <t>primates and tree shrew</t>
+  </si>
+  <si>
+    <t>total and exposed cortical surface area</t>
+  </si>
+  <si>
+    <t>number spinal cord neurons</t>
+  </si>
+  <si>
+    <t>BMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fu, Y., Rusznak, Z., Herculano-Houzel, S., Watson, C., &amp; Paxinos, G. (2013). Cellular composition characterizing postnatal development and maturation of the mouse brain and spinal cord. Brain Struct Funct, 218(5), 1337-1354. https://doi.org/10.1007/s00429-012-0462-x 	</t>
+  </si>
+  <si>
+    <t>mouse (developmental)</t>
+  </si>
+  <si>
+    <t>Table 1. Aging-dependent changes affecting the female mouse brain and spinal cord between 15 weeks and 25 months of age</t>
+  </si>
+  <si>
+    <t>Species - binomials need to be added</t>
+  </si>
+  <si>
+    <t>Burish_etal_2010_Table1_snapshot.csv</t>
+  </si>
+  <si>
+    <t>Burish_etal_2010_SupplementaryTable1_snapshot.csv</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1139,7 @@
       <sheetName val="FileList"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Files</v>
@@ -1626,7 +1659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.6640625" customWidth="1"/>
@@ -1634,7 +1667,8 @@
     <col min="3" max="3" width="16.83203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="15" style="9" customWidth="1"/>
     <col min="5" max="6" width="2.1640625" style="9" customWidth="1"/>
-    <col min="7" max="8" width="2.1640625" customWidth="1"/>
+    <col min="7" max="7" width="2.1640625" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
     <col min="9" max="9" width="17.1640625" customWidth="1"/>
     <col min="10" max="10" width="31.1640625" customWidth="1"/>
     <col min="11" max="11" width="46.5" customWidth="1"/>
@@ -3936,7 +3970,7 @@
         <v>60</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>62</v>
@@ -3952,10 +3986,10 @@
       </c>
       <c r="W26" s="8"/>
       <c r="X26" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y26" t="s">
         <v>273</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>274</v>
       </c>
       <c r="Z26" t="s">
         <v>106</v>
@@ -4029,7 +4063,7 @@
         <v>60</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>62</v>
@@ -4124,7 +4158,7 @@
         <v>60</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R28" s="3" t="s">
         <v>62</v>
@@ -5198,10 +5232,10 @@
         <v>49</v>
       </c>
       <c r="X45" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA45" t="s">
         <v>278</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>279</v>
       </c>
       <c r="AI45">
         <v>9</v>
@@ -5260,7 +5294,7 @@
         <v>232</v>
       </c>
       <c r="AA46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AI46">
         <v>6</v>
@@ -5320,7 +5354,7 @@
         <v>49</v>
       </c>
       <c r="AA47" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AI47" s="17">
         <v>7</v>
@@ -5350,11 +5384,12 @@
         <v>2011</v>
       </c>
       <c r="F48" s="24"/>
-      <c r="G48" s="15" t="s">
+      <c r="G48" t="str">
+        <f>_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
+        <v>10.1159/000323671</v>
+      </c>
+      <c r="I48" s="15" t="s">
         <v>236</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>237</v>
       </c>
       <c r="J48" s="23" t="str">
         <f t="shared" ref="J48" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
@@ -5376,7 +5411,7 @@
         <v>49</v>
       </c>
       <c r="AI48" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:35" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5400,14 +5435,15 @@
         <v>2011</v>
       </c>
       <c r="F49" s="24"/>
-      <c r="G49" s="15" t="s">
-        <v>236</v>
+      <c r="G49" t="str">
+        <f t="shared" ref="G49:G53" si="68">_xlfn.TEXTAFTER(A49,"https://doi.org/")</f>
+        <v>10.1159/000323671</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J49" s="23" t="str">
-        <f t="shared" ref="J49" si="68">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+        <f t="shared" ref="J49" si="69">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="K49" s="23" t="str">
@@ -5426,47 +5462,48 @@
         <v>49</v>
       </c>
       <c r="AI49" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B50" s="22" t="str">
-        <f t="shared" ref="B50:B53" si="69">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
+        <f t="shared" ref="B50:B53" si="70">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="C50" s="24" t="str">
-        <f t="shared" ref="C50:C53" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C50:C53" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f t="shared" ref="D50:D53" si="71">IF(ISNUMBER(FIND("&amp;", A50)),
+        <f t="shared" ref="D50:D53" si="72">IF(ISNUMBER(FIND("&amp;", A50)),
     IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E50" s="24" t="str">
-        <f t="shared" ref="E50:E52" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+        <f t="shared" ref="E50:E52" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
         <v>1999</v>
       </c>
       <c r="F50" s="24"/>
-      <c r="G50" s="15" t="s">
-        <v>236</v>
+      <c r="G50" t="str">
+        <f t="shared" si="68"/>
+        <v xml:space="preserve">10.1016/s0166-4328(98)00151-x 	</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J50" s="23" t="str">
-        <f t="shared" ref="J50:J52" si="73">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
+        <f t="shared" ref="J50:J52" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_Table1</v>
       </c>
       <c r="K50" s="23" t="str">
         <f>IF(ISBLANK(H50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_Table1</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x	_Table1</v>
       </c>
       <c r="M50" s="15" t="s">
         <v>132</v>
@@ -5477,131 +5514,270 @@
     </row>
     <row r="51" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B51" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Genoud_etal_2018</v>
       </c>
       <c r="C51" s="24" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>Genoud</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="E51" s="24" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2018</v>
       </c>
       <c r="F51" s="24"/>
-      <c r="G51" s="15" t="s">
-        <v>283</v>
+      <c r="G51" t="str">
+        <f t="shared" si="68"/>
+        <v xml:space="preserve">10.1111/brv.12350 	</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="3" t="s">
         <v>227</v>
       </c>
       <c r="J51" s="23" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="K51" s="23" t="str">
-        <f t="shared" ref="K51:K52" si="74">IF(ISBLANK(H51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323672_TableS2</v>
+        <f t="shared" ref="K51:K52" si="75">IF(ISBLANK(H51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1111%2Fbrv.12350	_TableS2</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>132</v>
       </c>
       <c r="X51" t="s">
-        <v>287</v>
+        <v>284</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B52" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Mota_etal_2019</v>
       </c>
       <c r="C52" s="24" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>Mota</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="E52" s="24" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2019</v>
       </c>
       <c r="F52" s="24"/>
-      <c r="G52" s="15" t="s">
-        <v>284</v>
+      <c r="G52" t="str">
+        <f t="shared" si="68"/>
+        <v xml:space="preserve">10.1073/pnas.1716956116 	</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J52" s="23" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="K52" s="23" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159%2F000323673_SupplementaryTableS1</v>
+        <f t="shared" si="75"/>
+        <v>10.1073%2Fpnas.1716956116	_SupplementaryTableS1</v>
       </c>
       <c r="M52" s="15" t="s">
         <v>132</v>
       </c>
       <c r="X52" t="s">
-        <v>285</v>
+        <v>282</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="53" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B53" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="C53" s="24" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>Burish</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="E53" s="24" t="str">
-        <f t="shared" ref="E53" si="75">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
+        <f t="shared" ref="E53" si="76">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
         <v>2010</v>
       </c>
       <c r="F53" s="24"/>
-      <c r="G53" s="15" t="s">
-        <v>284</v>
+      <c r="G53" t="str">
+        <f t="shared" si="68"/>
+        <v xml:space="preserve">10.1159/000319019 </v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J53" s="23" t="str">
-        <f t="shared" ref="J53" si="76">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
+        <f t="shared" ref="J53" si="77">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_Table1</v>
       </c>
       <c r="K53" s="23" t="str">
-        <f t="shared" ref="K53" si="77">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323673_Table1</v>
-      </c>
-      <c r="M53" s="15" t="s">
+        <f t="shared" ref="K53" si="78">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000319019_Table1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>48</v>
+      </c>
+      <c r="N53" s="15" t="str" cm="1">
+        <f t="array" ref="N53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O53" s="15" t="str" cm="1">
+        <f t="array" ref="O53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K53, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P53" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>299</v>
+      </c>
+      <c r="X53" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>293</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="54" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="22" t="str">
+        <f t="shared" ref="B54:B55" si="79">C54 &amp; IF(D54&lt;&gt;"", "_" &amp; D54, "_") &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "")</f>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="C54" s="24" t="str">
+        <f t="shared" ref="C54:C55" si="80">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
+        <v>Burish</v>
+      </c>
+      <c r="D54" s="9" t="str">
+        <f t="shared" ref="D54:D55" si="81">IF(ISNUMBER(FIND("&amp;", A54)),
+    IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
+    ""
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="E54" s="24" t="str">
+        <f t="shared" ref="E54:E55" si="82">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
+        <v>2010</v>
+      </c>
+      <c r="F54" s="24"/>
+      <c r="G54" t="str">
+        <f t="shared" ref="G54:G55" si="83">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
+        <v xml:space="preserve">10.1159/000319019 </v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J54" s="23" t="str">
+        <f t="shared" ref="J54:J55" si="84">TRIM(_xlfn.TEXTJOIN("_",FALSE,B54,(SUBSTITUTE(SUBSTITUTE(I54," ",""), "_", ""))))</f>
+        <v>Burish_etal_2010_SupplementaryTable1</v>
+      </c>
+      <c r="K54" s="23" t="str">
+        <f t="shared" ref="K54:K55" si="85">IF(ISBLANK(H54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000319019_SupplementaryTable1</v>
+      </c>
+      <c r="M54" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>300</v>
+      </c>
+      <c r="X54" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>290</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>293</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>295</v>
+      </c>
+      <c r="B55" s="22" t="str">
+        <f t="shared" si="79"/>
+        <v>Fu_etal_2013</v>
+      </c>
+      <c r="C55" s="24" t="str">
+        <f t="shared" si="80"/>
+        <v>Fu</v>
+      </c>
+      <c r="D55" s="9" t="str">
+        <f t="shared" si="81"/>
+        <v>etal</v>
+      </c>
+      <c r="E55" s="24" t="str">
+        <f t="shared" si="82"/>
+        <v>2013</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="83"/>
+        <v xml:space="preserve">10.1007/s00429-012-0462-x 	</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J55" s="23" t="str">
+        <f t="shared" si="84"/>
+        <v>Fu_etal_2013_Table1</v>
+      </c>
+      <c r="K55" s="23" t="str">
+        <f t="shared" si="85"/>
+        <v>10.1007%2Fs00429-012-0462-x	_Table1</v>
+      </c>
+      <c r="M55" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="X53" t="s">
-        <v>289</v>
+      <c r="X55" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>296</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5635,97 +5811,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" t="s">
         <v>242</v>
-      </c>
-      <c r="B3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" t="s">
         <v>244</v>
-      </c>
-      <c r="B4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s">
         <v>246</v>
-      </c>
-      <c r="B5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" t="s">
         <v>248</v>
-      </c>
-      <c r="B6" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" t="s">
         <v>251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" t="s">
         <v>254</v>
-      </c>
-      <c r="B10" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" t="s">
         <v>256</v>
-      </c>
-      <c r="B11" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" t="s">
         <v>258</v>
-      </c>
-      <c r="B12" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5745,12 +5921,12 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -5758,10 +5934,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" t="s">
         <v>263</v>
-      </c>
-      <c r="C3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -5769,10 +5945,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" t="s">
         <v>265</v>
-      </c>
-      <c r="C4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5780,10 +5956,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" t="s">
         <v>267</v>
-      </c>
-      <c r="C5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5791,10 +5967,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
         <v>269</v>
-      </c>
-      <c r="C6" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5803,26 +5979,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -6065,32 +6221,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6107,4 +6258,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{045E28B8-B49B-3C47-9172-A6003714B92C}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D7FDA6E-33B4-9E41-BE2B-0C7D2203B6D5}"/>
   <bookViews>
-    <workbookView xWindow="43180" yWindow="-1360" windowWidth="34120" windowHeight="12640" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33080" windowHeight="21580" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="315">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -954,6 +954,60 @@
   </si>
   <si>
     <t>Item full name</t>
+  </si>
+  <si>
+    <t>10.1159%2F000323671_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t>notfound</t>
+  </si>
+  <si>
+    <t>10.1159%2F000319019_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000452856_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
+  </si>
+  <si>
+    <t>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
+  </si>
+  <si>
+    <t>10.1007%2Fs004220000205_Figure3.tsv</t>
+  </si>
+  <si>
+    <t>10.1126%2Fscience.aaa9101_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnana.2017.00118_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.1002%2Fcne.24985_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table1.tsv</t>
   </si>
 </sst>
 </file>
@@ -1120,11 +1174,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls driveId="b!LmviqIkNkU-5KarvTLZlFGpsrTudMulFuLAevsyKh2Qj_R6OuvTSQoX9alEEN7rm" itemId="01BSP3E5VBLELHBKLNIBELDTNFUEYQ5KUR">
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="FileList"/>
+      <sheetName val="__file_list"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1344,6 +1396,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1650,7 +1703,7 @@
   <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="77.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" style="9" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="15" style="9" customWidth="1"/>
@@ -1843,9 +1896,8 @@
         <f t="array" ref="N2">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
-      <c r="O2" t="str" cm="1">
-        <f t="array" ref="O2">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K2, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
+      <c r="O2" t="s">
+        <v>307</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>42</v>
@@ -1933,9 +1985,8 @@
         <f t="array" ref="N3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K3, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O3" t="s">
+        <v>298</v>
       </c>
       <c r="P3" t="s">
         <v>53</v>
@@ -2027,9 +2078,8 @@
         <f t="array" ref="N4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O4" t="str" cm="1">
-        <f t="array" ref="O4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K4, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O4" t="s">
+        <v>298</v>
       </c>
       <c r="P4" t="s">
         <v>53</v>
@@ -2119,9 +2169,8 @@
         <f t="array" ref="N5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
-      <c r="O5" t="str" cm="1">
-        <f t="array" ref="O5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K5, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+      <c r="O5" t="s">
+        <v>308</v>
       </c>
       <c r="P5" t="s">
         <v>35</v>
@@ -2204,9 +2253,8 @@
         <f t="array" ref="N6">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
-      <c r="O6" t="str" cm="1">
-        <f t="array" ref="O6">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K6, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+      <c r="O6" t="s">
+        <v>303</v>
       </c>
       <c r="P6" t="s">
         <v>53</v>
@@ -2302,9 +2350,8 @@
         <f t="array" ref="N7">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
-      <c r="O7" t="str" cm="1">
-        <f t="array" ref="O7">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K7, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000452856_TableS1.tsv</v>
+      <c r="O7" t="s">
+        <v>304</v>
       </c>
       <c r="P7" t="s">
         <v>53</v>
@@ -2400,9 +2447,8 @@
         <f t="array" ref="N8">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
-      <c r="O8" t="str" cm="1">
-        <f t="array" ref="O8">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K8, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
+      <c r="O8" t="s">
+        <v>305</v>
       </c>
       <c r="P8" t="s">
         <v>53</v>
@@ -2490,9 +2536,8 @@
         <f t="array" ref="N9">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
-      <c r="O9" t="str" cm="1">
-        <f t="array" ref="O9">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K9, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+      <c r="O9" t="s">
+        <v>306</v>
       </c>
       <c r="P9" t="s">
         <v>35</v>
@@ -2583,9 +2628,8 @@
         <f t="array" ref="N10">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
-      <c r="O10" t="str" cm="1">
-        <f t="array" ref="O10">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K10, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000124401_TableI.tsv</v>
+      <c r="O10" t="s">
+        <v>310</v>
       </c>
       <c r="P10" t="s">
         <v>53</v>
@@ -2673,9 +2717,8 @@
         <f t="array" ref="N11">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O11" t="str" cm="1">
-        <f t="array" ref="O11">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K11, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O11" t="s">
+        <v>298</v>
       </c>
       <c r="P11" t="s">
         <v>35</v>
@@ -2750,9 +2793,8 @@
         <f t="array" ref="N12">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O12" t="str" cm="1">
-        <f t="array" ref="O12">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K12, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O12" t="s">
+        <v>298</v>
       </c>
       <c r="P12" t="s">
         <v>35</v>
@@ -2820,9 +2862,8 @@
         <f t="array" ref="N13">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
-      <c r="O13" t="str" cm="1">
-        <f t="array" ref="O13">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K13, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
+      <c r="O13" t="s">
+        <v>314</v>
       </c>
       <c r="P13" t="s">
         <v>53</v>
@@ -2918,9 +2959,8 @@
         <f t="array" ref="N14">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
-      <c r="O14" t="str" cm="1">
-        <f t="array" ref="O14">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K14, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
+      <c r="O14" t="s">
+        <v>314</v>
       </c>
       <c r="P14" t="s">
         <v>53</v>
@@ -3013,9 +3053,8 @@
         <f t="array" ref="N15">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
-      <c r="O15" t="str" cm="1">
-        <f t="array" ref="O15">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K15, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
+      <c r="O15" t="s">
+        <v>314</v>
       </c>
       <c r="P15" t="s">
         <v>53</v>
@@ -3108,9 +3147,8 @@
         <f t="array" ref="N16">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
-      <c r="O16" t="str" cm="1">
-        <f t="array" ref="O16">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K16, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
+      <c r="O16" t="s">
+        <v>314</v>
       </c>
       <c r="P16" t="s">
         <v>53</v>
@@ -3203,9 +3241,8 @@
         <f t="array" ref="N17">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
-      <c r="O17" t="str" cm="1">
-        <f t="array" ref="O17">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K17, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
+      <c r="O17" t="s">
+        <v>314</v>
       </c>
       <c r="P17" t="s">
         <v>53</v>
@@ -3298,9 +3335,8 @@
         <f t="array" ref="N18">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
-      <c r="O18" t="str" cm="1">
-        <f t="array" ref="O18">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K18, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+      <c r="O18" t="s">
+        <v>313</v>
       </c>
       <c r="P18" t="s">
         <v>53</v>
@@ -3393,9 +3429,8 @@
         <f t="array" ref="N19">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
-      <c r="O19" t="str" cm="1">
-        <f t="array" ref="O19">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K19, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+      <c r="O19" t="s">
+        <v>313</v>
       </c>
       <c r="P19" t="s">
         <v>53</v>
@@ -3490,9 +3525,8 @@
         <f t="array" ref="N20">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O20" t="str" cm="1">
-        <f t="array" ref="O20">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K20, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O20" t="s">
+        <v>298</v>
       </c>
       <c r="P20" t="s">
         <v>35</v>
@@ -3562,9 +3596,8 @@
         <f t="array" ref="N21">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O21" t="str" cm="1">
-        <f t="array" ref="O21">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K21, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O21" t="s">
+        <v>298</v>
       </c>
       <c r="P21" t="s">
         <v>35</v>
@@ -3634,9 +3667,8 @@
         <f t="array" ref="N22">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O22" t="str" cm="1">
-        <f t="array" ref="O22">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K22, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O22" t="s">
+        <v>298</v>
       </c>
       <c r="P22" t="s">
         <v>35</v>
@@ -3706,9 +3738,8 @@
         <f t="array" ref="N23">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O23" t="str" cm="1">
-        <f t="array" ref="O23">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K23, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O23" t="s">
+        <v>298</v>
       </c>
       <c r="P23" t="s">
         <v>35</v>
@@ -3778,9 +3809,8 @@
         <f t="array" ref="N24">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
-      <c r="O24" t="str" cm="1">
-        <f t="array" ref="O24">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K24, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+      <c r="O24" t="s">
+        <v>312</v>
       </c>
       <c r="P24" t="s">
         <v>53</v>
@@ -3876,9 +3906,8 @@
         <f t="array" ref="N25">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
-      <c r="O25" t="str" cm="1">
-        <f t="array" ref="O25">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K25, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+      <c r="O25" t="s">
+        <v>311</v>
       </c>
       <c r="P25" t="s">
         <v>53</v>
@@ -3969,9 +3998,8 @@
         <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
-      <c r="O26" t="str" cm="1">
-        <f t="array" ref="O26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K26, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+      <c r="O26" t="s">
+        <v>311</v>
       </c>
       <c r="P26" t="s">
         <v>53</v>
@@ -4064,9 +4092,8 @@
         <f t="array" ref="N27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
-      <c r="O27" t="str" cm="1">
-        <f t="array" ref="O27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K27, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+      <c r="O27" t="s">
+        <v>311</v>
       </c>
       <c r="P27" t="s">
         <v>53</v>
@@ -4159,9 +4186,8 @@
         <f t="array" ref="N28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O28" t="str" cm="1">
-        <f t="array" ref="O28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K28, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O28" t="s">
+        <v>298</v>
       </c>
       <c r="P28" t="s">
         <v>35</v>
@@ -4244,9 +4270,8 @@
         <f t="array" ref="N29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O29" t="str" cm="1">
-        <f t="array" ref="O29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K29, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O29" t="s">
+        <v>298</v>
       </c>
       <c r="P29" t="s">
         <v>35</v>
@@ -4329,9 +4354,8 @@
         <f t="array" ref="N30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O30" t="str" cm="1">
-        <f t="array" ref="O30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K30, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O30" t="s">
+        <v>298</v>
       </c>
       <c r="P30" t="s">
         <v>35</v>
@@ -4410,9 +4434,8 @@
         <f t="array" ref="N31">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O31" t="str" cm="1">
-        <f t="array" ref="O31">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K31, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O31" t="s">
+        <v>298</v>
       </c>
       <c r="P31" t="s">
         <v>35</v>
@@ -4486,9 +4509,8 @@
         <f t="array" ref="N32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O32" t="str" cm="1">
-        <f t="array" ref="O32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K32, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O32" t="s">
+        <v>298</v>
       </c>
       <c r="P32" t="s">
         <v>35</v>
@@ -4557,9 +4579,8 @@
         <f t="array" ref="N33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O33" t="str" cm="1">
-        <f t="array" ref="O33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K33, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O33" t="s">
+        <v>298</v>
       </c>
       <c r="P33" t="s">
         <v>35</v>
@@ -4622,9 +4643,8 @@
         <f t="array" ref="N34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
-      <c r="O34" t="str" cm="1">
-        <f t="array" ref="O34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K34, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      <c r="O34" t="s">
+        <v>309</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>42</v>
@@ -4675,9 +4695,8 @@
         <f t="array" ref="N35">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K35, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
-      <c r="O35" t="str" cm="1">
-        <f t="array" ref="O35">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K35, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+      <c r="O35" t="s">
+        <v>302</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>42</v>
@@ -4725,9 +4744,8 @@
         <f t="array" ref="N36">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K36, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
-      <c r="O36" t="str" cm="1">
-        <f t="array" ref="O36">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K36, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+      <c r="O36" t="s">
+        <v>302</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>42</v>
@@ -4775,9 +4793,8 @@
         <f t="array" ref="N37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
-      <c r="O37" t="str" cm="1">
-        <f t="array" ref="O37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K37, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+      <c r="O37" t="s">
+        <v>302</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>42</v>
@@ -4825,9 +4842,8 @@
         <f t="array" ref="N38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
-      <c r="O38" t="str" cm="1">
-        <f t="array" ref="O38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K38, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O38" t="s">
+        <v>301</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>42</v>
@@ -4878,9 +4894,8 @@
         <f t="array" ref="N39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="O39" t="str" cm="1">
-        <f t="array" ref="O39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K39, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O39" t="s">
+        <v>301</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>42</v>
@@ -4931,9 +4946,8 @@
         <f t="array" ref="N40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
-      <c r="O40" t="str" cm="1">
-        <f t="array" ref="O40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K40, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O40" t="s">
+        <v>301</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>42</v>
@@ -4981,9 +4995,8 @@
         <f t="array" ref="N41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
-      <c r="O41" t="str" cm="1">
-        <f t="array" ref="O41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K41, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O41" t="s">
+        <v>301</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>42</v>
@@ -5037,9 +5050,8 @@
         <f t="array" ref="N42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
-      <c r="O42" t="str" cm="1">
-        <f t="array" ref="O42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K42, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O42" t="s">
+        <v>301</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>42</v>
@@ -5087,13 +5099,12 @@
         <f t="shared" ref="K43" si="49">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
-      <c r="N43" s="17" t="str" cm="1">
+      <c r="N43" t="str" cm="1">
         <f t="array" ref="N43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O43" s="17" t="str" cm="1">
-        <f t="array" ref="O43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K43, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      <c r="O43" s="17" t="s">
+        <v>301</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>42</v>
@@ -5138,9 +5149,8 @@
         <f t="array" ref="N44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
-      <c r="O44" t="str" cm="1">
-        <f t="array" ref="O44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K44, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      <c r="O44" t="s">
+        <v>300</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>42</v>
@@ -5197,9 +5207,8 @@
         <f t="array" ref="N45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
-      <c r="O45" t="str" cm="1">
-        <f t="array" ref="O45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K45, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      <c r="O45" t="s">
+        <v>300</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>42</v>
@@ -5256,7 +5265,7 @@
         <f>IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
-      <c r="N46" s="17" t="str" cm="1">
+      <c r="N46" t="str" cm="1">
         <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
@@ -5313,13 +5322,12 @@
         <f>IF(ISBLANK(H47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
-      <c r="N47" s="15" t="str" cm="1">
+      <c r="N47" t="str" cm="1">
         <f t="array" ref="N47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O47" s="15" t="str" cm="1">
-        <f t="array" ref="O47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K47, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      <c r="O47" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="P47" s="23" t="s">
         <v>42</v>
@@ -5364,13 +5372,12 @@
         <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
-      <c r="N48" s="15" t="str" cm="1">
+      <c r="N48" t="str" cm="1">
         <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
-      <c r="O48" s="15" t="str" cm="1">
-        <f t="array" ref="O48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K48, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      <c r="O48" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="P48" s="23" t="s">
         <v>42</v>
@@ -5422,13 +5429,12 @@
       <c r="M49" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="N49" s="15" t="str" cm="1">
+      <c r="N49" t="str" cm="1">
         <f t="array" ref="N49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O49" s="15" t="str" cm="1">
-        <f t="array" ref="O49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K49, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O49" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="V49" t="s">
         <v>78</v>
@@ -5474,13 +5480,12 @@
       <c r="M50" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="N50" s="15" t="str" cm="1">
+      <c r="N50" t="str" cm="1">
         <f t="array" ref="N50">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K50, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O50" s="15" t="str" cm="1">
-        <f t="array" ref="O50">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K50, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O50" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="X50" t="s">
         <v>277</v>
@@ -5529,13 +5534,12 @@
       <c r="M51" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="15" t="str" cm="1">
+      <c r="N51" t="str" cm="1">
         <f t="array" ref="N51">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K51, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O51" s="15" t="str" cm="1">
-        <f t="array" ref="O51">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K51, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O51" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="X51" t="s">
         <v>275</v>
@@ -5584,13 +5588,12 @@
       <c r="M52" t="s">
         <v>41</v>
       </c>
-      <c r="N52" s="15" t="str" cm="1">
+      <c r="N52" t="str" cm="1">
         <f t="array" ref="N52">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K52, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
-      <c r="O52" s="15" t="str" cm="1">
-        <f t="array" ref="O52">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K52, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
+      <c r="O52" s="15" t="s">
+        <v>299</v>
       </c>
       <c r="P52" t="s">
         <v>53</v>
@@ -5654,13 +5657,12 @@
       <c r="M53" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="N53" s="15" t="str" cm="1">
+      <c r="N53" t="str" cm="1">
         <f t="array" ref="N53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O53" s="15" t="str" cm="1">
-        <f t="array" ref="O53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K53, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
+      <c r="O53" s="15" t="s">
+        <v>299</v>
       </c>
       <c r="Q53" t="s">
         <v>293</v>
@@ -5716,13 +5718,12 @@
       <c r="M54" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="N54" s="15" t="str" cm="1">
+      <c r="N54" t="str" cm="1">
         <f t="array" ref="N54">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K54, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O54" s="15" t="str" cm="1">
-        <f t="array" ref="O54">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K54, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O54" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="X54" t="s">
         <v>290</v>
@@ -5772,13 +5773,12 @@
       <c r="M55" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="N55" s="15" t="str" cm="1">
+      <c r="N55" t="str" cm="1">
         <f t="array" ref="N55">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K55, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O55" s="15" t="str" cm="1">
-        <f t="array" ref="O55">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K55, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+      <c r="O55" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="X55" t="s">
         <v>295</v>
@@ -5983,6 +5983,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -6225,7 +6234,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -6236,16 +6245,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6264,27 +6272,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D7FDA6E-33B4-9E41-BE2B-0C7D2203B6D5}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0725EF1A-AA76-D147-92BB-751950291942}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33080" windowHeight="21580" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="33080" windowHeight="20280" activeTab="1" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -854,9 +854,6 @@
     <t xml:space="preserve">Ref last </t>
   </si>
   <si>
-    <t>if there are typos or shorthand speces names used, can update based on heading, note, text</t>
-  </si>
-  <si>
     <t>add a column to correct any errors in species designations (e.g., misidentified or combined different species of same genus)</t>
   </si>
   <si>
@@ -1008,6 +1005,9 @@
   </si>
   <si>
     <t>10.1159%2F000437413_Table1.tsv</t>
+  </si>
+  <si>
+    <t>if there are typos or shorthand species names used, can update based on heading, note, text</t>
   </si>
 </sst>
 </file>
@@ -1805,7 +1805,7 @@
         <v>21</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y1" s="6" t="s">
         <v>22</v>
@@ -1897,7 +1897,7 @@
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
       <c r="O2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>42</v>
@@ -1986,7 +1986,7 @@
         <v>notfound</v>
       </c>
       <c r="O3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P3" t="s">
         <v>53</v>
@@ -2079,7 +2079,7 @@
         <v>notfound</v>
       </c>
       <c r="O4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P4" t="s">
         <v>53</v>
@@ -2170,7 +2170,7 @@
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="O5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P5" t="s">
         <v>35</v>
@@ -2254,7 +2254,7 @@
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
       <c r="O6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P6" t="s">
         <v>53</v>
@@ -2351,7 +2351,7 @@
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
       <c r="O7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P7" t="s">
         <v>53</v>
@@ -2448,7 +2448,7 @@
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="O8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P8" t="s">
         <v>53</v>
@@ -2537,7 +2537,7 @@
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
       <c r="O9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P9" t="s">
         <v>35</v>
@@ -2629,7 +2629,7 @@
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
       <c r="O10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P10" t="s">
         <v>53</v>
@@ -2718,7 +2718,7 @@
         <v>notfound</v>
       </c>
       <c r="O11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P11" t="s">
         <v>35</v>
@@ -2794,7 +2794,7 @@
         <v>notfound</v>
       </c>
       <c r="O12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P12" t="s">
         <v>35</v>
@@ -2863,7 +2863,7 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="O13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P13" t="s">
         <v>53</v>
@@ -2960,7 +2960,7 @@
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="O14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P14" t="s">
         <v>53</v>
@@ -3054,7 +3054,7 @@
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="O15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P15" t="s">
         <v>53</v>
@@ -3148,7 +3148,7 @@
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="O16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P16" t="s">
         <v>53</v>
@@ -3242,7 +3242,7 @@
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="O17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P17" t="s">
         <v>53</v>
@@ -3336,7 +3336,7 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="O18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P18" t="s">
         <v>53</v>
@@ -3430,7 +3430,7 @@
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
       <c r="O19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P19" t="s">
         <v>53</v>
@@ -3526,7 +3526,7 @@
         <v>notfound</v>
       </c>
       <c r="O20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P20" t="s">
         <v>35</v>
@@ -3597,7 +3597,7 @@
         <v>notfound</v>
       </c>
       <c r="O21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P21" t="s">
         <v>35</v>
@@ -3668,7 +3668,7 @@
         <v>notfound</v>
       </c>
       <c r="O22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P22" t="s">
         <v>35</v>
@@ -3739,7 +3739,7 @@
         <v>notfound</v>
       </c>
       <c r="O23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P23" t="s">
         <v>35</v>
@@ -3810,7 +3810,7 @@
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="O24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P24" t="s">
         <v>53</v>
@@ -3907,13 +3907,13 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="O25" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P25" t="s">
         <v>53</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R25" s="3" t="s">
         <v>55</v>
@@ -3929,10 +3929,10 @@
       </c>
       <c r="W25" s="8"/>
       <c r="X25" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y25" t="s">
         <v>265</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>266</v>
       </c>
       <c r="Z25" t="s">
         <v>99</v>
@@ -3999,13 +3999,13 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="O26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P26" t="s">
         <v>53</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>55</v>
@@ -4093,13 +4093,13 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="O27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P27" t="s">
         <v>53</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>55</v>
@@ -4187,7 +4187,7 @@
         <v>notfound</v>
       </c>
       <c r="O28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P28" t="s">
         <v>35</v>
@@ -4271,7 +4271,7 @@
         <v>notfound</v>
       </c>
       <c r="O29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P29" t="s">
         <v>35</v>
@@ -4355,7 +4355,7 @@
         <v>notfound</v>
       </c>
       <c r="O30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P30" t="s">
         <v>35</v>
@@ -4435,7 +4435,7 @@
         <v>notfound</v>
       </c>
       <c r="O31" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s">
         <v>35</v>
@@ -4510,7 +4510,7 @@
         <v>notfound</v>
       </c>
       <c r="O32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P32" t="s">
         <v>35</v>
@@ -4580,7 +4580,7 @@
         <v>notfound</v>
       </c>
       <c r="O33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P33" t="s">
         <v>35</v>
@@ -4644,7 +4644,7 @@
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="O34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>42</v>
@@ -4696,7 +4696,7 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="O35" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>42</v>
@@ -4745,7 +4745,7 @@
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="O36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>42</v>
@@ -4794,7 +4794,7 @@
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="O37" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>42</v>
@@ -4843,7 +4843,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="O38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>42</v>
@@ -4895,7 +4895,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
       <c r="O39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>42</v>
@@ -4947,7 +4947,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="O40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>42</v>
@@ -4996,7 +4996,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="O41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>42</v>
@@ -5051,7 +5051,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="O42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>42</v>
@@ -5104,7 +5104,7 @@
         <v>notfound</v>
       </c>
       <c r="O43" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>42</v>
@@ -5150,16 +5150,16 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="O44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="X44" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA44" t="s">
         <v>270</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>271</v>
       </c>
       <c r="AI44">
         <v>9</v>
@@ -5208,7 +5208,7 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="O45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>42</v>
@@ -5217,7 +5217,7 @@
         <v>225</v>
       </c>
       <c r="AA45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AI45">
         <v>6</v>
@@ -5277,7 +5277,7 @@
         <v>42</v>
       </c>
       <c r="AA46" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AI46" s="17">
         <v>7</v>
@@ -5327,7 +5327,7 @@
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="O47" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P47" s="23" t="s">
         <v>42</v>
@@ -5377,7 +5377,7 @@
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
       <c r="O48" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P48" s="23" t="s">
         <v>42</v>
@@ -5388,7 +5388,7 @@
     </row>
     <row r="49" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B49" s="22" t="str">
         <f t="shared" ref="B49:B52" si="68">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
@@ -5434,7 +5434,7 @@
         <v>notfound</v>
       </c>
       <c r="O49" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V49" t="s">
         <v>78</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="50" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B50" s="22" t="str">
         <f t="shared" si="68"/>
@@ -5485,18 +5485,18 @@
         <v>notfound</v>
       </c>
       <c r="O50" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="X50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AC50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B51" s="22" t="str">
         <f t="shared" si="68"/>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J51" s="23" t="str">
         <f t="shared" si="72"/>
@@ -5539,18 +5539,18 @@
         <v>notfound</v>
       </c>
       <c r="O51" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="X51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AC51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B52" s="22" t="str">
         <f t="shared" si="68"/>
@@ -5593,30 +5593,30 @@
         <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="O52" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P52" t="s">
         <v>53</v>
       </c>
       <c r="Q52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="X52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Z52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AC52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AE52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B53" s="22" t="str">
         <f t="shared" ref="B53:B55" si="77">C53 &amp; IF(D53&lt;&gt;"", "_" &amp; D53, "_") &amp; IF(E53&lt;&gt;"", "_" &amp; E53, "_") &amp; IF(F53&lt;&gt;"", "_" &amp; F53, "")</f>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J53" s="23" t="str">
         <f t="shared" ref="J53:J54" si="82">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
@@ -5655,34 +5655,34 @@
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M53" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N53" t="str" cm="1">
         <f t="array" ref="N53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="O53" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q53" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="X53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Z53" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>285</v>
+      </c>
+      <c r="AE53" t="s">
         <v>283</v>
-      </c>
-      <c r="AC53" t="s">
-        <v>286</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B54" s="22" t="str">
         <f t="shared" si="77"/>
@@ -5723,21 +5723,21 @@
         <v>notfound</v>
       </c>
       <c r="O54" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="X54" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z54" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AC54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B55" s="22" t="str">
         <f t="shared" si="77"/>
@@ -5778,10 +5778,10 @@
         <v>notfound</v>
       </c>
       <c r="O55" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="X55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5860,7 +5860,7 @@
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5876,7 +5876,7 @@
         <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -5983,12 +5983,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6235,20 +6237,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6273,18 +6282,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EFEAD8-FD4A-C04E-827C-11F37E67926D}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D15A47-F99B-7246-8B5B-2AFC1BCCAE91}"/>
   <bookViews>
-    <workbookView xWindow="41160" yWindow="-5960" windowWidth="37740" windowHeight="26820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35000" yWindow="-5960" windowWidth="49660" windowHeight="24360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="353">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -854,15 +854,6 @@
     <t>L</t>
   </si>
   <si>
-    <t xml:space="preserve">Iwaniuk, A. N., Pellis, S. M., &amp; Whishaw, I. Q. (1999). Is digital dexterity really related to corticospinal projections?: a re-analysis of the Heffner and Masterton data set using modern comparative statistics. Behav Brain Res, 101(2), 173-187. https://doi.org/10.1016/s0166-4328(98)00151-x 	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genoud, M., Isler, K., &amp; Martin, R. D. (2018). Comparative analyses of basal rate of metabolism in mammals: data selection does matter. Biol Rev Camb Philos Soc, 93(1), 404-438. https://doi.org/10.1111/brv.12350 	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mota, B., Dos Santos, S. E., Ventura-Antunes, L., Jardim-Messeder, D., Neves, K., Kazu, R. S., Noctor, S., Lambert, K., Bertelsen, M. F., Manger, P. R., Sherwood, C. C., Kaas, J. H., &amp; Herculano-Houzel, S. (2019). White matter volume and white/gray matter ratio in mammalian species as a consequence of the universal scaling of cortical folding. Proc Natl Acad Sci U S A, 116(30), 15253-15261. https://doi.org/10.1073/pnas.1716956116 	</t>
-  </si>
-  <si>
     <t>Supplementary Table S1. Morphometrical and cell number data used in this study (“our dataset”).</t>
   </si>
   <si>
@@ -872,9 +863,6 @@
     <t>Table S2. Basal metabolic rate (BMR) database.</t>
   </si>
   <si>
-    <t xml:space="preserve">Burish, M. J., Peebles, J. K., Baldwin, M. K., Tavares, L., Kaas, J. H., &amp; Herculano-Houzel, S. (2010). Cellular scaling rules for primate spinal cords. Brain Behav Evol, 76(1), 45-59. https://doi.org/10.1159/000319019 </t>
-  </si>
-  <si>
     <t>Table 1. Cellular composition of the spinal cord</t>
   </si>
   <si>
@@ -902,9 +890,6 @@
     <t>BMR</t>
   </si>
   <si>
-    <t xml:space="preserve">Fu, Y., Rusznak, Z., Herculano-Houzel, S., Watson, C., &amp; Paxinos, G. (2013). Cellular composition characterizing postnatal development and maturation of the mouse brain and spinal cord. Brain Struct Funct, 218(5), 1337-1354. https://doi.org/10.1007/s00429-012-0462-x 	</t>
-  </si>
-  <si>
     <t>mouse (developmental)</t>
   </si>
   <si>
@@ -920,9 +905,6 @@
     <t>Burish_etal_2010_SupplementaryTable1_snapshot.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">MacLarnon, A. (1996). The scaling of gross dimensions of the spinal cord in primates and other species. J Hum Evol, 30(1), 71-87. https://doi.org/10.1006/jhev.1996.0005 	</t>
-  </si>
-  <si>
     <t>Table 1 Data</t>
   </si>
   <si>
@@ -930,9 +912,6 @@
   </si>
   <si>
     <t>if there are typos or shorthand species names used, can update based on heading, note, text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wimberly, A. N., Slater, G. J., &amp; Granatosky, M. C. (2021). Evolutionary history of quadrupedal walking gaits shows mammalian release from locomotor constraint. Proc Biol Sci, 288(1957), 20210937. https://doi.org/10.1098/rspb.2021.0937 	</t>
   </si>
   <si>
     <t>Files</t>
@@ -1077,15 +1056,9 @@
 study.</t>
   </si>
   <si>
-    <t xml:space="preserve">Granatosky, M. C. (2018). A Review of locomotor diversity in mammals with analyses exploring the influence of substrate use, body mass and intermembral index in primates. Journal of Zoology, 306(4), 207-216. https://doi.org/10.1111/jzo.12608 	</t>
-  </si>
-  <si>
     <t>mammal_gait.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">Wilman, H., Belmaker, J., Simpson, J., de la Rosa, C., Rivadeneira, M. M., &amp; Jetz, W. (2014). EltonTraits 1.0: Species‐level foraging attributes of the world's birds and mammals. Ecology, 95(7), 2027-2027. https://doi.org/10.1890/13-1917.1 	</t>
-  </si>
-  <si>
     <t>MamFuncDat.txt</t>
   </si>
   <si>
@@ -1096,6 +1069,36 @@
   </si>
   <si>
     <t>reference list</t>
+  </si>
+  <si>
+    <t>Iwaniuk, A. N., Pellis, S. M., &amp; Whishaw, I. Q. (1999). Is digital dexterity really related to corticospinal projections?: a re-analysis of the Heffner and Masterton data set using modern comparative statistics. Behav Brain Res, 101(2), 173-187. https://doi.org/10.1016/s0166-4328(98)00151-x</t>
+  </si>
+  <si>
+    <t>Genoud, M., Isler, K., &amp; Martin, R. D. (2018). Comparative analyses of basal rate of metabolism in mammals: data selection does matter. Biol Rev Camb Philos Soc, 93(1), 404-438. https://doi.org/10.1111/brv.12350</t>
+  </si>
+  <si>
+    <t>Mota, B., Dos Santos, S. E., Ventura-Antunes, L., Jardim-Messeder, D., Neves, K., Kazu, R. S., Noctor, S., Lambert, K., Bertelsen, M. F., Manger, P. R., Sherwood, C. C., Kaas, J. H., &amp; Herculano-Houzel, S. (2019). White matter volume and white/gray matter ratio in mammalian species as a consequence of the universal scaling of cortical folding. Proc Natl Acad Sci U S A, 116(30), 15253-15261. https://doi.org/10.1073/pnas.1716956116</t>
+  </si>
+  <si>
+    <t>Burish, M. J., Peebles, J. K., Baldwin, M. K., Tavares, L., Kaas, J. H., &amp; Herculano-Houzel, S. (2010). Cellular scaling rules for primate spinal cords. Brain Behav Evol, 76(1), 45-59. https://doi.org/10.1159/000319019</t>
+  </si>
+  <si>
+    <t>Fu, Y., Rusznak, Z., Herculano-Houzel, S., Watson, C., &amp; Paxinos, G. (2013). Cellular composition characterizing postnatal development and maturation of the mouse brain and spinal cord. Brain Struct Funct, 218(5), 1337-1354. https://doi.org/10.1007/s00429-012-0462-x</t>
+  </si>
+  <si>
+    <t>MacLarnon, A. (1996). The scaling of gross dimensions of the spinal cord in primates and other species. J Hum Evol, 30(1), 71-87. https://doi.org/10.1006/jhev.1996.0005</t>
+  </si>
+  <si>
+    <t>Wimberly, A. N., Slater, G. J., &amp; Granatosky, M. C. (2021). Evolutionary history of quadrupedal walking gaits shows mammalian release from locomotor constraint. Proc Biol Sci, 288(1957), 20210937. https://doi.org/10.1098/rspb.2021.0937</t>
+  </si>
+  <si>
+    <t>Granatosky, M. C. (2018). A Review of locomotor diversity in mammals with analyses exploring the influence of substrate use, body mass and intermembral index in primates. Journal of Zoology, 306(4), 207-216. https://doi.org/10.1111/jzo.12608</t>
+  </si>
+  <si>
+    <t>Wilman, H., Belmaker, J., Simpson, J., de la Rosa, C., Rivadeneira, M. M., &amp; Jetz, W. (2014). EltonTraits 1.0: Species‐level foraging attributes of the world's birds and mammals. Ecology, 95(7), 2027-2027. https://doi.org/10.1890/13-1917.1</t>
+  </si>
+  <si>
+    <t>end</t>
   </si>
 </sst>
 </file>
@@ -1545,1627 +1548,1696 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AK59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="7" width="2.1640625" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" customWidth="1"/>
-    <col min="10" max="10" width="31.1640625" customWidth="1"/>
-    <col min="11" max="11" width="46.5" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="49.83203125" customWidth="1"/>
-    <col min="15" max="18" width="14.1640625" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" customWidth="1"/>
-    <col min="21" max="21" width="22.1640625" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" customWidth="1"/>
-    <col min="23" max="23" width="15.33203125" customWidth="1"/>
-    <col min="24" max="24" width="39.5" customWidth="1"/>
-    <col min="25" max="25" width="11.1640625" customWidth="1"/>
-    <col min="26" max="26" width="5" customWidth="1"/>
-    <col min="27" max="27" width="7.5" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" customWidth="1"/>
-    <col min="29" max="29" width="6.5" customWidth="1"/>
-    <col min="30" max="30" width="11" customWidth="1"/>
-    <col min="31" max="33" width="10.83203125" customWidth="1"/>
-    <col min="34" max="34" width="12.5" customWidth="1"/>
-    <col min="35" max="35" width="2.83203125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
+    <col min="2" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="8" width="2.1640625" customWidth="1"/>
+    <col min="9" max="9" width="37.5" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" customWidth="1"/>
+    <col min="11" max="11" width="31.1640625" customWidth="1"/>
+    <col min="12" max="12" width="46.5" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="15" max="15" width="49.83203125" customWidth="1"/>
+    <col min="16" max="19" width="14.1640625" customWidth="1"/>
+    <col min="20" max="20" width="13.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" customWidth="1"/>
+    <col min="22" max="22" width="22.1640625" customWidth="1"/>
+    <col min="23" max="23" width="14.33203125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="39.5" customWidth="1"/>
+    <col min="26" max="26" width="11.1640625" customWidth="1"/>
+    <col min="27" max="27" width="5" customWidth="1"/>
+    <col min="28" max="28" width="7.5" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" customWidth="1"/>
+    <col min="30" max="30" width="6.5" customWidth="1"/>
+    <col min="31" max="31" width="11" customWidth="1"/>
+    <col min="32" max="34" width="10.83203125" customWidth="1"/>
+    <col min="35" max="35" width="12.5" customWidth="1"/>
+    <col min="36" max="36" width="2.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="11" t="s">
-        <v>295</v>
-      </c>
       <c r="X1" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AK1" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="2" t="str">
-        <f t="shared" ref="B2" si="0">C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
+      <c r="B2" t="str">
+        <f>RIGHT(A2,1)</f>
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f t="shared" ref="C2" si="0">D2 &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "_") &amp; IF(G2&lt;&gt;"", "_" &amp; G2, "")</f>
         <v>Burger_etal_2019</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="D2" s="2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
         <v>Burger</v>
       </c>
-      <c r="D2" s="2" t="str">
-        <f t="shared" ref="D2:D48" si="1">IF(ISNUMBER(FIND("&amp;", A2)),
+      <c r="E2" s="2" t="str">
+        <f t="shared" ref="E2:E48" si="1">IF(ISNUMBER(FIND("&amp;", A2)),
     IF(LEN(A2)-LEN(SUBSTITUTE(A2, ",", ""))&gt;=6, "etal", MID(A2, SEARCH("&amp; ", A2)+2, SEARCH(",", A2, SEARCH("&amp; ", A2)+2) - SEARCH("&amp; ", A2)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
+      <c r="F2" s="2" t="str">
+        <f t="shared" ref="F2" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
         <v>2019</v>
       </c>
-      <c r="G2" t="str">
-        <f t="shared" ref="G2:G37" si="3">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
+      <c r="H2" t="str">
+        <f t="shared" ref="H2:H37" si="3">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <f t="shared" ref="J2:J44" si="4">TRIM(_xlfn.TEXTJOIN("_",FALSE,B2,(SUBSTITUTE(SUBSTITUTE(I2," ",""), "_", ""))))</f>
+      <c r="K2" s="1" t="str">
+        <f t="shared" ref="K2:K44" si="4">TRIM(_xlfn.TEXTJOIN("_",FALSE,C2,(SUBSTITUTE(SUBSTITUTE(J2," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
-      <c r="K2" s="8" t="str">
-        <f>IF(ISBLANK(H2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G2, SUBSTITUTE(I2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(I2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L2" s="8" t="str">
+        <f>IF(ISBLANK(I2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>41</v>
       </c>
-      <c r="N2" t="str">
-        <f t="array" ref="N2">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O2" t="str">
+        <f t="array" ref="O2">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>44</v>
       </c>
-      <c r="R2" t="str">
-        <f>IF(Q2="N", P2, "write file name")</f>
+      <c r="S2" t="str">
+        <f>IF(R2="N", Q2, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>45</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>46</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="2"/>
-      <c r="X2" t="s">
+      <c r="X2" s="2"/>
+      <c r="Y2" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>50</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>37</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>17</v>
       </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="2" t="str">
-        <f t="shared" ref="B3:B44" si="5">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
+      <c r="B3" t="str">
+        <f t="shared" ref="B3:B59" si="5">RIGHT(A3,1)</f>
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" ref="C3:C44" si="6">D3 &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "_") &amp; IF(G3&lt;&gt;"", "_" &amp; G3, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
-      <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:C44" si="6">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D44" si="7">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
-      <c r="D3" s="2" t="str">
+      <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <f t="shared" ref="E3:E44" si="7">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:F44" si="8">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>2022</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <f t="shared" si="3"/>
         <v>10.7554/eLife.77875</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="1" t="str">
+      <c r="K3" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
-      <c r="K3" s="1" t="str">
-        <f t="shared" ref="K3:K44" si="8">IF(ISBLANK(H3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G3, SUBSTITUTE(I3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H3, SUBSTITUTE(I3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L3" s="1" t="str">
+        <f t="shared" ref="L3:L44" si="9">IF(ISBLANK(I3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
-      <c r="L3" s="1"/>
-      <c r="M3" t="s">
+      <c r="M3" s="1"/>
+      <c r="N3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" t="str">
-        <f t="array" ref="N3">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O3" t="str">
+        <f t="array" ref="O3">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>55</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>56</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>57</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>46</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>58</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>61</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>63</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>64</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>7</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B4" t="str">
         <f t="shared" si="5"/>
-        <v>Caspar_etal_2022</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Caspar_etal_2022</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Caspar</v>
       </c>
-      <c r="D4" s="2" t="str">
+      <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F4" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2022</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <f t="shared" si="3"/>
         <v>10.7554/eLife.77875</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="1" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
-      <c r="K4" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L4" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" t="s">
+      <c r="M4" s="1"/>
+      <c r="N4" t="s">
         <v>41</v>
       </c>
-      <c r="N4" t="str">
-        <f t="array" ref="N4">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O4" t="str">
+        <f t="array" ref="O4">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>44</v>
       </c>
-      <c r="R4" t="str">
-        <f>IF(Q4="N", P4, "write file name")</f>
+      <c r="S4" t="str">
+        <f>IF(R4="N", Q4, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>67</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>46</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>68</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>71</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>64</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>5</v>
       </c>
-      <c r="AJ4">
+      <c r="AK4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" t="str">
         <f t="shared" si="5"/>
-        <v>Changizi__2001</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Changizi__2001</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Changizi</v>
       </c>
-      <c r="D5" s="2" t="str">
+      <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E5" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F5" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2001</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <f t="shared" si="3"/>
         <v>10.1007/s004220000205</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="1" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Changizi__2001_Figure3</v>
       </c>
-      <c r="K5" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L5" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" t="s">
+      <c r="M5" s="1"/>
+      <c r="N5" t="s">
         <v>74</v>
       </c>
-      <c r="N5" t="str">
-        <f t="array" ref="N5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O5" t="str">
+        <f t="array" ref="O5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>35</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>55</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>57</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>77</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>78</v>
       </c>
-      <c r="V5" s="3"/>
-      <c r="W5" s="2"/>
-      <c r="X5" t="s">
+      <c r="W5" s="3"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" t="s">
         <v>79</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>36</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>80</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" t="str">
         <f t="shared" si="5"/>
-        <v>Chen_Wiens_2020</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Chen_Wiens_2020</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Chen</v>
       </c>
-      <c r="D6" s="2" t="str">
+      <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Wiens</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F6" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2020</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" t="str">
+      <c r="G6" s="2"/>
+      <c r="H6" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
-      <c r="K6" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L6" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" t="s">
+      <c r="M6" s="1"/>
+      <c r="N6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" t="str">
-        <f t="array" ref="N6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O6" t="str">
+        <f t="array" ref="O6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>53</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>44</v>
       </c>
-      <c r="R6" t="str">
-        <f>IF(Q6="N", P6, "write file name")</f>
+      <c r="S6" t="str">
+        <f>IF(R6="N", Q6, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>67</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>46</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>68</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="W6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="2"/>
-      <c r="X6" t="s">
+      <c r="X6" s="2"/>
+      <c r="Y6" t="s">
         <v>86</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>87</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>88</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>89</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>10</v>
       </c>
-      <c r="AJ6">
+      <c r="AK6">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" t="str">
         <f t="shared" si="5"/>
-        <v>DosSantos_etal_2017</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>DosSantos_etal_2017</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>DosSantos</v>
       </c>
-      <c r="D7" s="2" t="str">
+      <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2017</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000452856</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="4"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
-      <c r="K7" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L7" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>41</v>
       </c>
-      <c r="N7" t="str">
-        <f t="array" ref="N7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O7" t="str">
+        <f t="array" ref="O7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>53</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>55</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>94</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>95</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>96</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>68</v>
       </c>
-      <c r="V7" s="3" t="s">
+      <c r="W7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" t="s">
+      <c r="X7" s="2"/>
+      <c r="Y7" t="s">
         <v>98</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>99</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>100</v>
       </c>
       <c r="AA7" t="s">
         <v>100</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AB7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE7" t="s">
         <v>101</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>102</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>0</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="2" t="str">
+      <c r="B8" t="str">
         <f t="shared" si="5"/>
-        <v>DosSantos_etal_2020</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>DosSantos</v>
       </c>
-      <c r="D8" s="2" t="str">
+      <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F8" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2020</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <f t="shared" si="3"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="1" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="4"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
-      <c r="K8" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L8" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
-      <c r="L8" s="1"/>
-      <c r="M8" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" t="s">
         <v>41</v>
       </c>
-      <c r="N8" t="str">
-        <f t="array" ref="N8">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O8" t="str">
+        <f t="array" ref="O8">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>53</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>55</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>105</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>106</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>46</v>
       </c>
-      <c r="W8" s="2"/>
-      <c r="X8" t="s">
+      <c r="X8" s="2"/>
+      <c r="Y8" t="s">
         <v>98</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>107</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>100</v>
       </c>
       <c r="AA8" t="s">
         <v>100</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AB8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE8" t="s">
         <v>108</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>4</v>
       </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="2" t="str">
+      <c r="B9" t="str">
         <f t="shared" si="5"/>
-        <v>Finlay_etal_2006</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Finlay_etal_2006</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Finlay</v>
       </c>
-      <c r="D9" s="2" t="str">
+      <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2006</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" t="str">
+      <c r="G9" s="2"/>
+      <c r="H9" t="str">
         <f t="shared" si="3"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="1" t="str">
+      <c r="K9" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
-      <c r="K9" s="1" t="str">
-        <f>IF(ISBLANK(H9),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G9, SUBSTITUTE(I9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H9, SUBSTITUTE(I9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L9" s="1" t="str">
+        <f>IF(ISBLANK(I9),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H9, SUBSTITUTE(J9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I9, SUBSTITUTE(J9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
-      <c r="L9" s="1"/>
-      <c r="M9" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" t="s">
         <v>74</v>
       </c>
-      <c r="N9" t="str">
-        <f t="array" ref="N9">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O9" t="str">
+        <f t="array" ref="O9">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>55</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>112</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>113</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>46</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>58</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="W9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="W9" s="2"/>
-      <c r="X9" t="s">
+      <c r="X9" s="2"/>
+      <c r="Y9" t="s">
         <v>115</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="Z9" t="s">
         <v>36</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>116</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>37</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>3</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="2" t="str">
-        <f>C10 &amp; IF(D10&lt;&gt;"", "_" &amp; D10, "_") &amp; IF(E10&lt;&gt;"", "_" &amp; E10, "_") &amp; IF(F10&lt;&gt;"", "_" &amp; F10, "")</f>
+      <c r="B10" t="str">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>D10 &amp; IF(E10&lt;&gt;"", "_" &amp; E10, "_") &amp; IF(F10&lt;&gt;"", "_" &amp; F10, "_") &amp; IF(G10&lt;&gt;"", "_" &amp; G10, "")</f>
         <v>Heffner_Masterton_1975</v>
       </c>
-      <c r="C10" s="2" t="str">
-        <f t="shared" si="6"/>
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Heffner</v>
       </c>
-      <c r="D10" s="2" t="str">
+      <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Masterton</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F10" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>1975</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" t="str">
+      <c r="G10" s="2"/>
+      <c r="H10" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000124401</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="1" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heffner_Masterton_1975_TableI</v>
       </c>
-      <c r="K10" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L10" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" t="s">
+      <c r="M10" s="1"/>
+      <c r="N10" t="s">
         <v>41</v>
       </c>
-      <c r="N10" t="str">
-        <f t="array" ref="N10">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O10" t="str">
+        <f t="array" ref="O10">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>55</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>120</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>57</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>46</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>78</v>
       </c>
-      <c r="W10" s="2"/>
-      <c r="X10" t="s">
+      <c r="X10" s="2"/>
+      <c r="Y10" t="s">
         <v>121</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Z10" t="s">
         <v>122</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>123</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="s">
         <v>37</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>7</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="2" t="str">
+      <c r="B11" t="str">
         <f t="shared" si="5"/>
-        <v>Heffner_Masterton_1983</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Heffner_Masterton_1983</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Heffner</v>
       </c>
-      <c r="D11" s="2" t="str">
+      <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Masterton</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F11" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>1983</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" t="str">
+      <c r="G11" s="2"/>
+      <c r="H11" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000121494</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="1" t="str">
+      <c r="K11" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heffner_Masterton_1983_TableI</v>
       </c>
-      <c r="K11" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L11" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="1"/>
+      <c r="N11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N11" t="str">
-        <f t="array" ref="N11">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O11" t="str">
+        <f t="array" ref="O11">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="4"/>
-      <c r="R11" t="str">
-        <f>IF(Q11="N", P11, "write file name")</f>
+      <c r="Q11" s="4"/>
+      <c r="S11" t="str">
+        <f>IF(R11="N", Q11, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>57</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>46</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>78</v>
       </c>
-      <c r="W11" s="2"/>
-      <c r="X11" t="s">
+      <c r="X11" s="2"/>
+      <c r="Y11" t="s">
         <v>121</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AE11" t="s">
         <v>37</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AG11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="2" t="str">
+      <c r="B12" t="str">
         <f t="shared" si="5"/>
-        <v>Heldstab_etal_2016</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Heldstab_etal_2016</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Heldstab</v>
       </c>
-      <c r="D12" s="2" t="str">
+      <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F12" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2016</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" t="str">
+      <c r="G12" s="2"/>
+      <c r="H12" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/srep24528</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="1" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
-      <c r="K12" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L12" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="1"/>
+      <c r="N12" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N12" t="str">
-        <f t="array" ref="N12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O12" t="str">
+        <f t="array" ref="O12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="4"/>
-      <c r="R12" t="str">
-        <f>IF(Q12="N", P12, "write file name")</f>
+      <c r="Q12" s="4"/>
+      <c r="S12" t="str">
+        <f>IF(R12="N", Q12, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>57</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>46</v>
       </c>
-      <c r="W12" s="2"/>
-      <c r="X12" t="s">
+      <c r="X12" s="2"/>
+      <c r="Y12" t="s">
         <v>128</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="2" t="str">
+      <c r="B13" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D13" s="2" t="str">
+      <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F13" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="1" t="str">
+      <c r="K13" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
-      <c r="K13" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L13" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
-      <c r="L13" s="1"/>
-      <c r="M13" t="s">
+      <c r="M13" s="1"/>
+      <c r="N13" t="s">
         <v>41</v>
       </c>
-      <c r="N13" t="str">
-        <f t="array" ref="N13">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O13" t="str">
+        <f t="array" ref="O13">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>53</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="Q13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>131</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>57</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>46</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
         <v>58</v>
       </c>
-      <c r="V13" s="3" t="s">
+      <c r="W13" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="X13" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>98</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>100</v>
       </c>
       <c r="AA13" t="s">
         <v>100</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AB13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE13" t="s">
         <v>134</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>9</v>
       </c>
-      <c r="AJ13">
+      <c r="AK13">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="2" t="str">
+      <c r="B14" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D14" s="2" t="str">
+      <c r="E14" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A14)),
     IF(LEN(A14)-LEN(SUBSTITUTE(A14, ",", ""))&gt;=6, "etal", MID(A14, SEARCH("&amp; ", A14)+2, SEARCH(",", A14, SEARCH("&amp; ", A14)+2) - SEARCH("&amp; ", A14)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F14" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" t="str">
+      <c r="G14" s="2"/>
+      <c r="H14" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
-      <c r="K14" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L14" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
-      <c r="L14" s="1"/>
-      <c r="M14" t="s">
+      <c r="M14" s="1"/>
+      <c r="N14" t="s">
         <v>41</v>
       </c>
-      <c r="N14" t="str">
-        <f t="array" ref="N14">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O14" t="str">
+        <f t="array" ref="O14">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>53</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="Q14" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>137</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>57</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>46</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
         <v>58</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="X14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>98</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>100</v>
       </c>
       <c r="AA14" t="s">
         <v>100</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AB14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE14" t="s">
         <v>134</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>9</v>
       </c>
-      <c r="AJ14">
+      <c r="AK14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="2" t="str">
+      <c r="B15" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D15" s="2" t="str">
+      <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" t="str">
+      <c r="G15" s="2"/>
+      <c r="H15" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="K15" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
-      <c r="K15" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L15" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
-      <c r="L15" s="1"/>
-      <c r="M15" t="s">
+      <c r="M15" s="1"/>
+      <c r="N15" t="s">
         <v>41</v>
       </c>
-      <c r="N15" t="str">
-        <f t="array" ref="N15">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O15" t="str">
+        <f t="array" ref="O15">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>53</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>141</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>57</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>46</v>
       </c>
-      <c r="U15" t="s">
+      <c r="V15" t="s">
         <v>58</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="X15" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>98</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>100</v>
       </c>
       <c r="AA15" t="s">
         <v>100</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AB15" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE15" t="s">
         <v>134</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>9</v>
       </c>
-      <c r="AJ15">
+      <c r="AK15">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>129</v>
       </c>
-      <c r="B16" s="2" t="str">
+      <c r="B16" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D16" s="2" t="str">
+      <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F16" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" t="str">
+      <c r="G16" s="2"/>
+      <c r="H16" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J16" s="1" t="str">
+      <c r="K16" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
-      <c r="K16" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L16" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
-      <c r="L16" s="1"/>
-      <c r="M16" t="s">
+      <c r="M16" s="1"/>
+      <c r="N16" t="s">
         <v>41</v>
       </c>
-      <c r="N16" t="str">
-        <f t="array" ref="N16">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O16" t="str">
+        <f t="array" ref="O16">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>53</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>145</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>57</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>46</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
         <v>58</v>
       </c>
-      <c r="V16" s="3" t="s">
+      <c r="W16" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="X16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>98</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>100</v>
       </c>
       <c r="AA16" t="s">
         <v>100</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AB16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE16" t="s">
         <v>134</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>8</v>
       </c>
-      <c r="AJ16">
+      <c r="AK16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="2" t="str">
+      <c r="B17" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D17" s="2" t="str">
+      <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F17" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" t="str">
+      <c r="G17" s="2"/>
+      <c r="H17" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="1" t="str">
+      <c r="K17" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
-      <c r="K17" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L17" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" t="s">
+      <c r="M17" s="1"/>
+      <c r="N17" t="s">
         <v>41</v>
       </c>
-      <c r="N17" t="str">
-        <f t="array" ref="N17">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O17" t="str">
+        <f t="array" ref="O17">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>53</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="Q17" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>149</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>57</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>46</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
         <v>58</v>
       </c>
-      <c r="V17" s="3" t="s">
+      <c r="W17" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="X17" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
         <v>98</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>100</v>
       </c>
       <c r="AA17" t="s">
         <v>100</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AB17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE17" t="s">
         <v>134</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>9</v>
       </c>
-      <c r="AJ17">
+      <c r="AK17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="2" t="str">
+      <c r="B18" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2020</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D18" s="2" t="str">
+      <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F18" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2020</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" t="str">
+      <c r="G18" s="2"/>
+      <c r="H18" t="str">
         <f t="shared" si="3"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J18" s="1" t="str">
+      <c r="K18" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
-      <c r="K18" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L18" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
-      <c r="L18" s="1"/>
-      <c r="M18" t="s">
+      <c r="M18" s="1"/>
+      <c r="N18" t="s">
         <v>41</v>
       </c>
-      <c r="N18" t="str">
-        <f t="array" ref="N18">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O18" t="str">
+        <f t="array" ref="O18">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>53</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="Q18" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>154</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>57</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>46</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
         <v>78</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="X18" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>156</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>100</v>
       </c>
       <c r="AA18" t="s">
         <v>100</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AB18" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE18" t="s">
         <v>157</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -3173,90 +3245,94 @@
       <c r="AJ18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AK18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="2" t="str">
+      <c r="B19" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2020</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D19" s="2" t="str">
+      <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F19" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2020</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" t="str">
+      <c r="G19" s="2"/>
+      <c r="H19" t="str">
         <f t="shared" si="3"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J19" s="1" t="str">
+      <c r="K19" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
-      <c r="K19" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L19" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
-      <c r="L19" s="1"/>
-      <c r="M19" t="s">
+      <c r="M19" s="1"/>
+      <c r="N19" t="s">
         <v>41</v>
       </c>
-      <c r="N19" t="str">
-        <f t="array" ref="N19">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O19" t="str">
+        <f t="array" ref="O19">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>53</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="Q19" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>160</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>57</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>46</v>
       </c>
-      <c r="U19" t="s">
+      <c r="V19" t="s">
         <v>78</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="X19" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
         <v>162</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>100</v>
       </c>
       <c r="AA19" t="s">
         <v>100</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AB19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE19" t="s">
         <v>157</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -3264,2410 +3340,2573 @@
       <c r="AJ19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AK19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="2" t="str">
+      <c r="B20" t="str">
         <f t="shared" si="5"/>
-        <v>Iwaniuk_etal_2001</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D20" s="2" t="str">
+      <c r="E20" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A20)),
     IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F20" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2001</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="1" t="str">
+      <c r="K20" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
-      <c r="K20" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L20" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
-      <c r="L20" s="1"/>
-      <c r="M20" t="s">
+      <c r="M20" s="1"/>
+      <c r="N20" t="s">
         <v>164</v>
       </c>
-      <c r="N20" t="str">
-        <f t="array" ref="N20">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O20" t="str">
+        <f t="array" ref="O20">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>35</v>
       </c>
-      <c r="P20" s="4"/>
-      <c r="R20" t="str">
-        <f>IF(Q20="N", P20, "write file name")</f>
+      <c r="Q20" s="4"/>
+      <c r="S20" t="str">
+        <f>IF(R20="N", Q20, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>57</v>
       </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>46</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="X20" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
         <v>166</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="2" t="str">
+      <c r="B21" t="str">
         <f t="shared" si="5"/>
-        <v>Iwaniuk_etal_2001</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D21" s="2" t="str">
+      <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F21" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2001</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J21" s="1" t="str">
+      <c r="K21" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
-      <c r="K21" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L21" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
-      <c r="L21" s="1"/>
-      <c r="M21" t="s">
+      <c r="M21" s="1"/>
+      <c r="N21" t="s">
         <v>164</v>
       </c>
-      <c r="N21" t="str">
-        <f t="array" ref="N21">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O21" t="str">
+        <f t="array" ref="O21">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>35</v>
       </c>
-      <c r="P21" s="4"/>
-      <c r="R21" t="str">
-        <f>IF(Q21="N", P21, "write file name")</f>
+      <c r="Q21" s="4"/>
+      <c r="S21" t="str">
+        <f>IF(R21="N", Q21, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>57</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>46</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="X21" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
         <v>166</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="2" t="str">
+      <c r="B22" t="str">
         <f t="shared" si="5"/>
-        <v>Iwaniuk_etal_2001</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D22" s="2" t="str">
+      <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F22" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2001</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="K22" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
-      <c r="K22" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L22" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
-      <c r="L22" s="1"/>
-      <c r="M22" t="s">
+      <c r="M22" s="1"/>
+      <c r="N22" t="s">
         <v>164</v>
       </c>
-      <c r="N22" t="str">
-        <f t="array" ref="N22">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O22" t="str">
+        <f t="array" ref="O22">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>35</v>
       </c>
-      <c r="P22" s="4"/>
-      <c r="R22" t="str">
-        <f>IF(Q22="N", P22, "write file name")</f>
+      <c r="Q22" s="4"/>
+      <c r="S22" t="str">
+        <f>IF(R22="N", Q22, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>57</v>
       </c>
-      <c r="T22" t="s">
+      <c r="U22" t="s">
         <v>46</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="X22" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>166</v>
       </c>
-      <c r="AD22" t="s">
+      <c r="AE22" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="2" t="str">
+      <c r="B23" t="str">
         <f t="shared" si="5"/>
-        <v>Iwaniuk_etal_2001</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D23" s="2" t="str">
+      <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F23" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2001</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="K23" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
-      <c r="K23" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L23" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
-      <c r="L23" s="1"/>
-      <c r="M23" t="s">
+      <c r="M23" s="1"/>
+      <c r="N23" t="s">
         <v>164</v>
       </c>
-      <c r="N23" t="str">
-        <f t="array" ref="N23">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O23" t="str">
+        <f t="array" ref="O23">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="4"/>
-      <c r="R23" t="str">
-        <f>IF(Q23="N", P23, "write file name")</f>
+      <c r="Q23" s="4"/>
+      <c r="S23" t="str">
+        <f>IF(R23="N", Q23, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>57</v>
       </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
         <v>46</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="X23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>166</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AE23" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="2" t="str">
+      <c r="B24" t="str">
         <f t="shared" si="5"/>
-        <v>JardimMesseder_etal_2017</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>JardimMesseder_etal_2017</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>JardimMesseder</v>
       </c>
-      <c r="D24" s="2" t="str">
+      <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F24" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2017</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="1" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="4"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
-      <c r="K24" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L24" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
-      <c r="L24" s="1"/>
-      <c r="M24" t="s">
+      <c r="M24" s="1"/>
+      <c r="N24" t="s">
         <v>41</v>
       </c>
-      <c r="N24" t="str">
-        <f t="array" ref="N24">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O24" t="str">
+        <f t="array" ref="O24">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>53</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="Q24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>173</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>57</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>46</v>
       </c>
-      <c r="U24" t="s">
+      <c r="V24" t="s">
         <v>58</v>
       </c>
-      <c r="V24" s="3" t="s">
+      <c r="W24" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="X24" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>98</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Z24" t="s">
         <v>99</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>100</v>
       </c>
       <c r="AA24" t="s">
         <v>100</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AB24" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE24" t="s">
         <v>176</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>2</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>177</v>
       </c>
-      <c r="B25" s="2" t="str">
-        <f t="shared" ref="B25" si="9">C25 &amp; IF(D25&lt;&gt;"", "_" &amp; D25, "_") &amp; IF(E25&lt;&gt;"", "_" &amp; E25, "_") &amp; IF(F25&lt;&gt;"", "_" &amp; F25, "")</f>
+      <c r="B25" t="str">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="str">
+        <f t="shared" ref="C25" si="10">D25 &amp; IF(E25&lt;&gt;"", "_" &amp; E25, "_") &amp; IF(F25&lt;&gt;"", "_" &amp; F25, "_") &amp; IF(G25&lt;&gt;"", "_" &amp; G25, "")</f>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="C25" s="2" t="str">
-        <f t="shared" ref="C25" si="10">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A25,","), "-", ""), " ", "")</f>
+      <c r="D25" s="2" t="str">
+        <f t="shared" ref="D25" si="11">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A25,","), "-", ""), " ", "")</f>
         <v>Kverkova</v>
       </c>
-      <c r="D25" s="2" t="str">
+      <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <f t="shared" ref="E25" si="11">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, "("), ")")</f>
+      <c r="F25" s="2" t="str">
+        <f t="shared" ref="F25" si="12">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, "("), ")")</f>
         <v>2018</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" t="str">
-        <f t="shared" ref="G25" si="12">_xlfn.TEXTAFTER(A25,"https://doi.org/")</f>
+      <c r="G25" s="2"/>
+      <c r="H25" t="str">
+        <f t="shared" ref="H25" si="13">_xlfn.TEXTAFTER(A25,"https://doi.org/")</f>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="1" t="str">
-        <f t="shared" ref="J25" si="13">TRIM(_xlfn.TEXTJOIN("_",FALSE,B25,(SUBSTITUTE(SUBSTITUTE(I25," ",""), "_", ""))))</f>
+      <c r="K25" s="1" t="str">
+        <f t="shared" ref="K25" si="14">TRIM(_xlfn.TEXTJOIN("_",FALSE,C25,(SUBSTITUTE(SUBSTITUTE(J25," ",""), "_", ""))))</f>
         <v>Kverkova_etal_2018_Table1</v>
       </c>
-      <c r="K25" s="1" t="str">
-        <f t="shared" ref="K25" si="14">IF(ISBLANK(H25),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G25, SUBSTITUTE(I25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H25, SUBSTITUTE(I25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L25" s="1" t="str">
+        <f t="shared" ref="L25" si="15">IF(ISBLANK(I25),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H25, SUBSTITUTE(J25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I25, SUBSTITUTE(J25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" t="s">
+      <c r="M25" s="1"/>
+      <c r="N25" t="s">
         <v>41</v>
       </c>
-      <c r="N25" t="str">
-        <f t="array" ref="N25">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O25" t="str">
+        <f t="array" ref="O25">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="Q25" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="R25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>178</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>179</v>
       </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>46</v>
       </c>
-      <c r="V25" s="3"/>
-      <c r="W25" s="2" t="s">
+      <c r="W25" s="3"/>
+      <c r="X25" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>265</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Z25" t="s">
         <v>99</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>100</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" t="s">
         <v>183</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>1</v>
       </c>
-      <c r="AJ25">
+      <c r="AK25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>177</v>
       </c>
-      <c r="B26" s="2" t="str">
+      <c r="B26" t="str">
         <f t="shared" si="5"/>
-        <v>Kverkova_etal_2018</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Kverkova</v>
       </c>
-      <c r="D26" s="2" t="str">
+      <c r="E26" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A26)),
     IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=6, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F26" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2018</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" t="str">
+      <c r="G26" s="2"/>
+      <c r="H26" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J26" s="1" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
-      <c r="K26" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L26" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
-      <c r="L26" s="1"/>
-      <c r="M26" t="s">
+      <c r="M26" s="1"/>
+      <c r="N26" t="s">
         <v>41</v>
       </c>
-      <c r="N26" t="str">
-        <f t="array" ref="N26">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O26" t="str">
+        <f t="array" ref="O26">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>53</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="Q26" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="R26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>178</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>179</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>46</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V26" t="s">
         <v>58</v>
       </c>
-      <c r="V26" s="3" t="s">
+      <c r="W26" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="X26" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>156</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>182</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>100</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>183</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>1</v>
       </c>
-      <c r="AJ26">
+      <c r="AK26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>177</v>
       </c>
-      <c r="B27" s="2" t="str">
+      <c r="B27" t="str">
         <f t="shared" si="5"/>
-        <v>Kverkova_etal_2018</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Kverkova</v>
       </c>
-      <c r="D27" s="2" t="str">
+      <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F27" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2018</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" t="str">
+      <c r="G27" s="2"/>
+      <c r="H27" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="1" t="str">
+      <c r="K27" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
-      <c r="K27" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L27" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
-      <c r="L27" s="1"/>
-      <c r="M27" t="s">
+      <c r="M27" s="1"/>
+      <c r="N27" t="s">
         <v>41</v>
       </c>
-      <c r="N27" t="str">
-        <f t="array" ref="N27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O27" t="str">
+        <f t="array" ref="O27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>53</v>
       </c>
-      <c r="P27" s="4" t="s">
+      <c r="Q27" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>185</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>186</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>46</v>
       </c>
-      <c r="U27" t="s">
+      <c r="V27" t="s">
         <v>58</v>
       </c>
-      <c r="V27" s="3" t="s">
+      <c r="W27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="X27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>162</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>99</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>100</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
         <v>183</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>1</v>
       </c>
-      <c r="AJ27">
+      <c r="AK27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>188</v>
       </c>
-      <c r="B28" s="2" t="str">
+      <c r="B28" t="str">
         <f t="shared" si="5"/>
-        <v>ManyPrimates__2022</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>ManyPrimates__2022</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>ManyPrimates</v>
       </c>
-      <c r="D28" s="2" t="str">
+      <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E28" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F28" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2022</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" t="str">
+      <c r="G28" s="2"/>
+      <c r="H28" t="str">
         <f t="shared" si="3"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J28" s="1" t="str">
+      <c r="K28" s="1" t="str">
         <f t="shared" si="4"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
-      <c r="K28" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L28" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
-      <c r="L28" s="1"/>
-      <c r="M28" t="s">
+      <c r="M28" s="1"/>
+      <c r="N28" t="s">
         <v>190</v>
       </c>
-      <c r="N28" t="str">
-        <f t="array" ref="N28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O28" t="str">
+        <f t="array" ref="O28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>35</v>
       </c>
-      <c r="P28" s="4"/>
-      <c r="R28" t="str">
-        <f t="shared" ref="R28:R33" si="15">IF(Q28="N", P28, "write file name")</f>
+      <c r="Q28" s="4"/>
+      <c r="S28" t="str">
+        <f t="shared" ref="S28:S33" si="16">IF(R28="N", Q28, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>67</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>46</v>
       </c>
-      <c r="U28" t="s">
+      <c r="V28" t="s">
         <v>68</v>
       </c>
-      <c r="V28" s="3" t="s">
+      <c r="W28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="W28" s="2"/>
-      <c r="X28" t="s">
+      <c r="X28" s="2"/>
+      <c r="Y28" t="s">
         <v>192</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>49</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>193</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="2" t="str">
+      <c r="B29" t="str">
         <f t="shared" si="5"/>
-        <v>Powell_etal_2017</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Powell</v>
       </c>
-      <c r="D29" s="2" t="str">
+      <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F29" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2017</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" t="str">
+      <c r="G29" s="2"/>
+      <c r="H29" t="str">
         <f t="shared" si="3"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="1" t="str">
+      <c r="K29" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
-      <c r="K29" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L29" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="5" t="s">
+      <c r="M29" s="1"/>
+      <c r="N29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N29" t="str">
-        <f t="array" ref="N29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O29" t="str">
+        <f t="array" ref="O29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>35</v>
       </c>
-      <c r="P29" s="4"/>
-      <c r="R29" t="str">
-        <f t="shared" si="15"/>
+      <c r="Q29" s="4"/>
+      <c r="S29" t="str">
+        <f t="shared" si="16"/>
         <v>write file name</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>67</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>46</v>
       </c>
-      <c r="U29" t="s">
+      <c r="V29" t="s">
         <v>68</v>
       </c>
-      <c r="V29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="W29" s="2"/>
-      <c r="X29" t="s">
+      <c r="X29" s="2"/>
+      <c r="Y29" t="s">
         <v>198</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" t="s">
         <v>49</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>48</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AE29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>199</v>
       </c>
-      <c r="B30" s="2" t="str">
+      <c r="B30" t="str">
         <f t="shared" si="5"/>
-        <v>Sherwood_etal_2004_I</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Sherwood</v>
       </c>
-      <c r="D30" s="2" t="str">
+      <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F30" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2004</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000075672</v>
       </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="K30" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
-      <c r="K30" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L30" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
-      <c r="L30" s="1"/>
-      <c r="M30" t="s">
+      <c r="M30" s="1"/>
+      <c r="N30" t="s">
         <v>190</v>
       </c>
-      <c r="N30" t="str">
-        <f t="array" ref="N30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O30" t="str">
+        <f t="array" ref="O30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>35</v>
       </c>
-      <c r="P30" s="4"/>
-      <c r="R30" t="str">
-        <f t="shared" si="15"/>
+      <c r="Q30" s="4"/>
+      <c r="S30" t="str">
+        <f t="shared" si="16"/>
         <v>write file name</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>57</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
         <v>201</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="X30" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>203</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>99</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sherwood_etal_2004_I</v>
+      <c r="B31" t="str">
+        <f>RIGHT(A31,1)</f>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Sherwood</v>
       </c>
-      <c r="D31" s="2" t="str">
+      <c r="E31" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A31)),
     IF(LEN(A31)-LEN(SUBSTITUTE(A31, ",", ""))&gt;=6, "etal", MID(A31, SEARCH("&amp; ", A31)+2, SEARCH(",", A31, SEARCH("&amp; ", A31)+2) - SEARCH("&amp; ", A31)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F31" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2004</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000075672</v>
       </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="K31" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
-      <c r="K31" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L31" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
-      <c r="L31" s="1"/>
-      <c r="M31" t="s">
+      <c r="M31" s="1"/>
+      <c r="N31" t="s">
         <v>190</v>
       </c>
-      <c r="N31" t="str">
-        <f t="array" ref="N31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O31" t="str">
+        <f t="array" ref="O31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>35</v>
       </c>
-      <c r="P31" s="4"/>
-      <c r="R31" t="str">
-        <f t="shared" si="15"/>
+      <c r="Q31" s="4"/>
+      <c r="S31" t="str">
+        <f t="shared" si="16"/>
         <v>write file name</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
         <v>57</v>
       </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
         <v>201</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="X31" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>203</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>99</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="2" t="str">
+      <c r="B32" t="str">
         <f t="shared" si="5"/>
-        <v>Winkler_Bryant_2021</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Winkler</v>
       </c>
-      <c r="D32" s="2" t="str">
+      <c r="E32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Bryant</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F32" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2021</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" t="str">
+      <c r="G32" s="2"/>
+      <c r="H32" t="str">
         <f t="shared" si="3"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J32" s="1" t="str">
+      <c r="K32" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Winkler_Bryant_2021_Figure1</v>
       </c>
-      <c r="K32" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L32" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="5" t="s">
+      <c r="M32" s="1"/>
+      <c r="N32" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N32" t="str">
-        <f t="array" ref="N32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O32" t="str">
+        <f t="array" ref="O32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>35</v>
       </c>
-      <c r="P32" s="4"/>
-      <c r="R32" t="str">
-        <f t="shared" si="15"/>
+      <c r="Q32" s="4"/>
+      <c r="S32" t="str">
+        <f t="shared" si="16"/>
         <v>write file name</v>
       </c>
-      <c r="S32" t="s">
+      <c r="T32" t="s">
         <v>57</v>
       </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>207</v>
       </c>
-      <c r="W32" s="2"/>
-      <c r="X32" t="s">
+      <c r="X32" s="2"/>
+      <c r="Y32" t="s">
         <v>208</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="2" t="str">
+      <c r="B33" t="str">
         <f t="shared" si="5"/>
-        <v>Young_etal_2013</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Young</v>
       </c>
-      <c r="D33" s="2" t="str">
+      <c r="E33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F33" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2013</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" t="str">
+      <c r="G33" s="2"/>
+      <c r="H33" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J33" s="1" t="str">
+      <c r="K33" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Young_etal_2013_Table1</v>
       </c>
-      <c r="K33" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L33" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
-      <c r="L33" s="1"/>
-      <c r="M33" t="s">
+      <c r="M33" s="1"/>
+      <c r="N33" t="s">
         <v>190</v>
       </c>
-      <c r="N33" t="str">
-        <f t="array" ref="N33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O33" t="str">
+        <f t="array" ref="O33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>35</v>
       </c>
-      <c r="P33" s="4"/>
-      <c r="R33" t="str">
-        <f t="shared" si="15"/>
+      <c r="Q33" s="4"/>
+      <c r="S33" t="str">
+        <f t="shared" si="16"/>
         <v>write file name</v>
       </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
         <v>113</v>
       </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
         <v>46</v>
       </c>
-      <c r="W33" s="2"/>
-      <c r="X33" t="s">
+      <c r="X33" s="2"/>
+      <c r="Y33" t="s">
         <v>210</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="2" t="str">
+      <c r="B34" t="str">
         <f t="shared" si="5"/>
-        <v>Mota_etal_2015</v>
+        <v>1</v>
       </c>
       <c r="C34" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Mota</v>
       </c>
-      <c r="D34" s="2" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F34" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2015</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <f t="shared" si="3"/>
         <v>10.1126/science.aaa9101</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J34" s="1" t="str">
+      <c r="K34" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
-      <c r="K34" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L34" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
-      <c r="N34" t="str">
-        <f t="array" ref="N34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O34" t="str">
+        <f t="array" ref="O34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH34">
+      <c r="AI34">
         <v>10</v>
       </c>
-      <c r="AJ34">
+      <c r="AK34">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="2" t="str">
+      <c r="B35" t="str">
         <f t="shared" si="5"/>
-        <v>HerculanoHouzel_etal_2013</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D35" s="2" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F35" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2013</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J35" s="1" t="str">
+      <c r="K35" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
-      <c r="K35" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L35" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
-      <c r="N35" t="str">
-        <f t="array" ref="N35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O35" t="str">
+        <f t="array" ref="O35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH35" t="s">
+      <c r="AI35" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>212</v>
       </c>
-      <c r="B36" s="2" t="str">
-        <f t="shared" ref="B36" si="16">C36 &amp; IF(D36&lt;&gt;"", "_" &amp; D36, "_") &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "")</f>
+      <c r="B36" t="str">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="str">
+        <f t="shared" ref="C36" si="17">D36 &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "_") &amp; IF(G36&lt;&gt;"", "_" &amp; G36, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f t="shared" ref="C36" si="17">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
+      <c r="D36" s="2" t="str">
+        <f t="shared" ref="D36" si="18">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D36" s="2" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" ref="E36" si="18">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
+      <c r="F36" s="2" t="str">
+        <f t="shared" ref="F36" si="19">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
         <v>2013</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J36" s="1" t="str">
-        <f t="shared" ref="J36" si="19">TRIM(_xlfn.TEXTJOIN("_",FALSE,B36,(SUBSTITUTE(SUBSTITUTE(I36," ",""), "_", ""))))</f>
+      <c r="K36" s="1" t="str">
+        <f t="shared" ref="K36" si="20">TRIM(_xlfn.TEXTJOIN("_",FALSE,C36,(SUBSTITUTE(SUBSTITUTE(J36," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
-      <c r="K36" s="1" t="str">
-        <f t="shared" ref="K36" si="20">IF(ISBLANK(H36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L36" s="1" t="str">
+        <f t="shared" ref="L36" si="21">IF(ISBLANK(I36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(J36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I36, SUBSTITUTE(J36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
-      <c r="N36" t="str">
-        <f t="array" ref="N36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O36" t="str">
+        <f t="array" ref="O36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH36" t="s">
+      <c r="AI36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>212</v>
       </c>
-      <c r="B37" s="2" t="str">
-        <f t="shared" ref="B37" si="21">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
+      <c r="B37" t="str">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="str">
+        <f t="shared" ref="C37" si="22">D37 &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "_") &amp; IF(G37&lt;&gt;"", "_" &amp; G37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="C37" s="2" t="str">
-        <f t="shared" ref="C37" si="22">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+      <c r="D37" s="2" t="str">
+        <f t="shared" ref="D37" si="23">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D37" s="2" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" ref="E37" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+      <c r="F37" s="2" t="str">
+        <f t="shared" ref="F37" si="24">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
         <v>2013</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J37" s="1" t="str">
-        <f t="shared" ref="J37" si="24">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
+      <c r="K37" s="1" t="str">
+        <f t="shared" ref="K37" si="25">TRIM(_xlfn.TEXTJOIN("_",FALSE,C37,(SUBSTITUTE(SUBSTITUTE(J37," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
-      <c r="K37" s="1" t="str">
-        <f t="shared" ref="K37" si="25">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L37" s="1" t="str">
+        <f t="shared" ref="L37" si="26">IF(ISBLANK(I37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(J37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I37, SUBSTITUTE(J37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
-      <c r="N37" t="str">
-        <f t="array" ref="N37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O37" t="str">
+        <f t="array" ref="O37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
-      <c r="O37" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" t="s">
+      <c r="AI37" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>217</v>
       </c>
-      <c r="B38" s="2" t="str">
-        <f t="shared" ref="B38" si="26">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
+      <c r="B38" t="str">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C38" s="2" t="str">
+        <f t="shared" ref="C38" si="27">D38 &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "_") &amp; IF(G38&lt;&gt;"", "_" &amp; G38, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C38" s="2" t="str">
-        <f t="shared" ref="C38" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
+      <c r="D38" s="2" t="str">
+        <f t="shared" ref="D38" si="28">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D38" s="2" t="str">
+      <c r="E38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
+      <c r="F38" s="2" t="str">
+        <f t="shared" ref="F38" si="29">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="G38" t="str">
-        <f t="shared" ref="G38" si="29">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
+      <c r="H38" t="str">
+        <f t="shared" ref="H38" si="30">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J38" s="1" t="str">
-        <f t="shared" ref="J38" si="30">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
+      <c r="K38" s="1" t="str">
+        <f t="shared" ref="K38" si="31">TRIM(_xlfn.TEXTJOIN("_",FALSE,C38,(SUBSTITUTE(SUBSTITUTE(J38," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Table2</v>
       </c>
-      <c r="K38" s="1" t="str">
-        <f t="shared" ref="K38" si="31">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L38" s="1" t="str">
+        <f t="shared" ref="L38" si="32">IF(ISBLANK(I38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(J38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I38, SUBSTITUTE(J38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
-      <c r="N38" t="str">
-        <f t="array" ref="N38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O38" t="str">
+        <f t="array" ref="O38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>6</v>
       </c>
-      <c r="AJ38">
+      <c r="AK38">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="2" t="str">
+      <c r="B39" t="str">
         <f t="shared" si="5"/>
-        <v>Isler_etal_2008</v>
+        <v>4</v>
       </c>
       <c r="C39" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Isler</v>
       </c>
-      <c r="D39" s="2" t="str">
+      <c r="E39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F39" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2008</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <f>_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="K39" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
-      <c r="K39" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L39" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
-      <c r="N39" t="str">
-        <f t="array" ref="N39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O39" t="str">
+        <f t="array" ref="O39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="P39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>3</v>
       </c>
-      <c r="AJ39">
+      <c r="AK39">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="2" t="str">
+      <c r="B40" t="str">
         <f t="shared" si="5"/>
-        <v>Isler_etal_2008</v>
+        <v>4</v>
       </c>
       <c r="C40" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Isler</v>
       </c>
-      <c r="D40" s="2" t="str">
+      <c r="E40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F40" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2008</v>
       </c>
-      <c r="G40" t="str">
+      <c r="H40" t="str">
         <f>_xlfn.TEXTAFTER(A40,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J40" s="1" t="str">
+      <c r="K40" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="K40" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L40" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
-      <c r="N40" t="str">
-        <f t="array" ref="N40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O40" t="str">
+        <f t="array" ref="O40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="P40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH40" t="s">
+      <c r="AI40" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="2" t="str">
-        <f t="shared" ref="B41" si="32">C41 &amp; IF(D41&lt;&gt;"", "_" &amp; D41, "_") &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "")</f>
+      <c r="B41" t="str">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C41" s="2" t="str">
+        <f t="shared" ref="C41" si="33">D41 &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "_") &amp; IF(G41&lt;&gt;"", "_" &amp; G41, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C41" s="2" t="str">
-        <f t="shared" ref="C41" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
+      <c r="D41" s="2" t="str">
+        <f t="shared" ref="D41" si="34">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D41" s="2" t="str">
+      <c r="E41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" ref="E41" si="34">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
+      <c r="F41" s="2" t="str">
+        <f t="shared" ref="F41" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="G41" t="str">
-        <f t="shared" ref="G41" si="35">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
+      <c r="H41" t="str">
+        <f t="shared" ref="H41" si="36">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J41" s="1" t="str">
-        <f t="shared" ref="J41" si="36">TRIM(_xlfn.TEXTJOIN("_",FALSE,B41,(SUBSTITUTE(SUBSTITUTE(I41," ",""), "_", ""))))</f>
+      <c r="K41" s="1" t="str">
+        <f t="shared" ref="K41" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,C41,(SUBSTITUTE(SUBSTITUTE(J41," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS2</v>
       </c>
-      <c r="K41" s="1" t="str">
-        <f t="shared" ref="K41" si="37">IF(ISBLANK(H41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L41" s="1" t="str">
+        <f t="shared" ref="L41" si="38">IF(ISBLANK(I41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(J41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I41, SUBSTITUTE(J41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
-      <c r="N41" t="str">
-        <f t="array" ref="N41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O41" t="str">
+        <f t="array" ref="O41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>8</v>
       </c>
-      <c r="AJ41">
+      <c r="AK41">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>217</v>
       </c>
-      <c r="B42" s="2" t="str">
-        <f t="shared" ref="B42" si="38">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
+      <c r="B42" t="str">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C42" s="2" t="str">
+        <f t="shared" ref="C42" si="39">D42 &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "_") &amp; IF(G42&lt;&gt;"", "_" &amp; G42, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C42" s="2" t="str">
-        <f t="shared" ref="C42" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
+      <c r="D42" s="2" t="str">
+        <f t="shared" ref="D42" si="40">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D42" s="2" t="str">
+      <c r="E42" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A42)),
     IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=6, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E42" s="2" t="str">
-        <f t="shared" ref="E42" si="40">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
+      <c r="F42" s="2" t="str">
+        <f t="shared" ref="F42" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="G42" t="str">
-        <f t="shared" ref="G42" si="41">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
+      <c r="H42" t="str">
+        <f t="shared" ref="H42" si="42">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J42" s="1" t="str">
-        <f t="shared" ref="J42" si="42">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
+      <c r="K42" s="1" t="str">
+        <f t="shared" ref="K42" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,C42,(SUBSTITUTE(SUBSTITUTE(J42," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS3</v>
       </c>
-      <c r="K42" s="1" t="str">
-        <f t="shared" ref="K42" si="43">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L42" s="1" t="str">
+        <f t="shared" ref="L42" si="44">IF(ISBLANK(I42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(J42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I42, SUBSTITUTE(J42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
-      <c r="N42" t="str">
-        <f t="array" ref="N42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O42" t="str">
+        <f t="array" ref="O42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
-      <c r="O42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>7</v>
       </c>
-      <c r="AJ42" s="6">
+      <c r="AK42" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="7" t="str">
-        <f t="shared" ref="B43" si="44">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
+      <c r="B43" t="str">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C43" s="7" t="str">
+        <f t="shared" ref="C43" si="45">D43 &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "_") &amp; IF(G43&lt;&gt;"", "_" &amp; G43, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C43" s="7" t="str">
-        <f t="shared" ref="C43" si="45">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
+      <c r="D43" s="7" t="str">
+        <f t="shared" ref="D43" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D43" s="2" t="str">
+      <c r="E43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E43" s="7" t="str">
-        <f t="shared" ref="E43" si="46">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
+      <c r="F43" s="7" t="str">
+        <f t="shared" ref="F43" si="47">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6" t="str">
-        <f t="shared" ref="G43" si="47">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
+      <c r="G43" s="7"/>
+      <c r="H43" s="6" t="str">
+        <f t="shared" ref="H43" si="48">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="J43" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="J43" s="6" t="str">
-        <f t="shared" ref="J43" si="48">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
+      <c r="K43" s="6" t="str">
+        <f t="shared" ref="K43" si="49">TRIM(_xlfn.TEXTJOIN("_",FALSE,C43,(SUBSTITUTE(SUBSTITUTE(J43," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
-      <c r="K43" s="8" t="str">
-        <f t="shared" ref="K43" si="49">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L43" s="8" t="str">
+        <f t="shared" ref="L43" si="50">IF(ISBLANK(I43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(J43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I43, SUBSTITUTE(J43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
-      <c r="N43" t="str">
-        <f t="array" ref="N43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O43" t="str">
+        <f t="array" ref="O43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O43" s="6" t="s">
+      <c r="P43" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>223</v>
       </c>
-      <c r="B44" s="2" t="str">
+      <c r="B44" t="str">
         <f t="shared" si="5"/>
-        <v>Lewitus_etal_2014</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2" t="str">
         <f t="shared" si="6"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f t="shared" si="7"/>
         <v>Lewitus</v>
       </c>
-      <c r="D44" s="2" t="str">
+      <c r="E44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E44" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F44" s="2" t="str">
+        <f t="shared" si="8"/>
         <v>2014</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
         <f>_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J44" s="1" t="str">
+      <c r="K44" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Lewitus_etal_2014_TableS1</v>
       </c>
-      <c r="K44" s="1" t="str">
-        <f t="shared" si="8"/>
+      <c r="L44" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
-      <c r="N44" t="str">
-        <f t="array" ref="N44">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O44" t="str">
+        <f t="array" ref="O44">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
-      <c r="O44" s="1" t="s">
+      <c r="P44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W44" t="s">
+      <c r="X44" t="s">
         <v>269</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AA44" t="s">
         <v>270</v>
       </c>
-      <c r="AH44">
+      <c r="AI44">
         <v>9</v>
       </c>
-      <c r="AJ44">
+      <c r="AK44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="2" t="str">
-        <f t="shared" ref="B45" si="50">C45 &amp; IF(D45&lt;&gt;"", "_" &amp; D45, "_") &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "")</f>
+      <c r="B45" t="str">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C45" s="2" t="str">
+        <f t="shared" ref="C45" si="51">D45 &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "_") &amp; IF(G45&lt;&gt;"", "_" &amp; G45, "")</f>
         <v>Lewitus_etal_2014</v>
       </c>
-      <c r="C45" s="2" t="str">
-        <f t="shared" ref="C45" si="51">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
+      <c r="D45" s="2" t="str">
+        <f t="shared" ref="D45" si="52">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
-      <c r="D45" s="2" t="str">
+      <c r="E45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E45" s="2" t="str">
-        <f t="shared" ref="E45" si="52">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
+      <c r="F45" s="2" t="str">
+        <f t="shared" ref="F45" si="53">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
         <v>2014</v>
       </c>
-      <c r="G45" t="str">
+      <c r="H45" t="str">
         <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J45" s="1" t="str">
-        <f t="shared" ref="J45" si="53">TRIM(_xlfn.TEXTJOIN("_",FALSE,B45,(SUBSTITUTE(SUBSTITUTE(I45," ",""), "_", ""))))</f>
+      <c r="K45" s="1" t="str">
+        <f t="shared" ref="K45" si="54">TRIM(_xlfn.TEXTJOIN("_",FALSE,C45,(SUBSTITUTE(SUBSTITUTE(J45," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
-      <c r="K45" s="1" t="str">
-        <f t="shared" ref="K45" si="54">IF(ISBLANK(H45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L45" s="1" t="str">
+        <f t="shared" ref="L45" si="55">IF(ISBLANK(I45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
-      <c r="N45" t="str">
-        <f t="array" ref="N45">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O45" t="str">
+        <f t="array" ref="O45">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
-      <c r="O45" s="1" t="s">
+      <c r="P45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W45" t="s">
+      <c r="X45" t="s">
         <v>225</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AA45" t="s">
         <v>270</v>
       </c>
-      <c r="AH45">
+      <c r="AI45">
         <v>6</v>
       </c>
-      <c r="AJ45" s="6">
+      <c r="AK45" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B46" s="7" t="str">
-        <f t="shared" ref="B46" si="55">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
+      <c r="B46" t="str">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C46" s="7" t="str">
+        <f t="shared" ref="C46" si="56">D46 &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "_") &amp; IF(G46&lt;&gt;"", "_" &amp; G46, "")</f>
         <v>Lewitus_etal_2013</v>
       </c>
-      <c r="C46" s="7" t="str">
-        <f t="shared" ref="C46" si="56">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+      <c r="D46" s="7" t="str">
+        <f t="shared" ref="D46" si="57">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
-      <c r="D46" s="2" t="str">
+      <c r="E46" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=6, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E46" s="7" t="str">
-        <f t="shared" ref="E46" si="57">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+      <c r="F46" s="7" t="str">
+        <f t="shared" ref="F46" si="58">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2013</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="6" t="str">
+      <c r="G46" s="7"/>
+      <c r="H46" s="6" t="str">
         <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
         <v>10.3389/fnhum.2013.00424</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="J46" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="J46" s="6" t="str">
-        <f t="shared" ref="J46" si="58">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
+      <c r="K46" s="6" t="str">
+        <f t="shared" ref="K46" si="59">TRIM(_xlfn.TEXTJOIN("_",FALSE,C46,(SUBSTITUTE(SUBSTITUTE(J46," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
-      <c r="K46" s="8" t="str">
-        <f>IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L46" s="8" t="str">
+        <f>IF(ISBLANK(I46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(J46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I46, SUBSTITUTE(J46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
-      <c r="N46" t="str">
-        <f t="array" ref="N46">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O46" t="str">
+        <f t="array" ref="O46">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
-      <c r="O46" s="6" t="s">
+      <c r="P46" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Z46" s="6" t="s">
+      <c r="AA46" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="AH46" s="6">
+      <c r="AI46" s="6">
         <v>7</v>
       </c>
-      <c r="AJ46" s="6">
+      <c r="AK46" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B47" s="9" t="str">
-        <f t="shared" ref="B47" si="59">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
+      <c r="B47" t="str">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="str">
+        <f t="shared" ref="C47" si="60">D47 &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "_") &amp; IF(G47&lt;&gt;"", "_" &amp; G47, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C47" s="9" t="str">
-        <f t="shared" ref="C47" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+      <c r="D47" s="9" t="str">
+        <f t="shared" ref="D47" si="61">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D47" s="2" t="str">
+      <c r="E47" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E47" s="9" t="str">
-        <f t="shared" ref="E47" si="61">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+      <c r="F47" s="9" t="str">
+        <f t="shared" ref="F47" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F47" s="9"/>
-      <c r="G47" t="str">
+      <c r="G47" s="9"/>
+      <c r="H47" t="str">
         <f>_xlfn.TEXTAFTER(A47,"https://doi.org/")</f>
         <v>10.1159/000323671</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="J47" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="J47" s="5" t="str">
-        <f t="shared" ref="J47" si="62">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
+      <c r="K47" s="5" t="str">
+        <f t="shared" ref="K47" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,C47,(SUBSTITUTE(SUBSTITUTE(J47," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
-      <c r="K47" s="5" t="str">
-        <f>IF(ISBLANK(H47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L47" s="5" t="str">
+        <f>IF(ISBLANK(I47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(J47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I47, SUBSTITUTE(J47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
-      <c r="N47" t="str">
-        <f t="array" ref="N47">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O47" t="str">
+        <f t="array" ref="O47">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="P47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AH47" s="5" t="s">
+      <c r="AI47" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="9" t="str">
-        <f t="shared" ref="B48" si="63">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
+      <c r="B48" t="str">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="str">
+        <f t="shared" ref="C48" si="64">D48 &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "_") &amp; IF(G48&lt;&gt;"", "_" &amp; G48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C48" s="9" t="str">
-        <f t="shared" ref="C48" si="64">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+      <c r="D48" s="9" t="str">
+        <f t="shared" ref="D48" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D48" s="2" t="str">
+      <c r="E48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E48" s="9" t="str">
-        <f t="shared" ref="E48" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+      <c r="F48" s="9" t="str">
+        <f t="shared" ref="F48" si="66">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F48" s="9"/>
-      <c r="G48" t="str">
-        <f t="shared" ref="G48:G53" si="66">_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
+      <c r="G48" s="9"/>
+      <c r="H48" t="str">
+        <f>_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
         <v>10.1159/000323671</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="J48" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="J48" s="5" t="str">
-        <f t="shared" ref="J48" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
+      <c r="K48" s="5" t="str">
+        <f t="shared" ref="K48" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,C48,(SUBSTITUTE(SUBSTITUTE(J48," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
-      <c r="K48" s="5" t="str">
-        <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L48" s="5" t="str">
+        <f>IF(ISBLANK(I48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(J48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I48, SUBSTITUTE(J48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
-      <c r="N48" t="str">
-        <f t="array" ref="N48">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O48" t="str">
+        <f t="array" ref="O48">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
-      <c r="O48" s="5" t="s">
+      <c r="P48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AH48" s="5" t="s">
+      <c r="AI48" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>271</v>
-      </c>
-      <c r="B49" s="9" t="str">
-        <f t="shared" ref="B49:B53" si="68">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
+        <v>343</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="5"/>
+        <v>x</v>
+      </c>
+      <c r="C49" s="9" t="str">
+        <f t="shared" ref="C49:C53" si="68">D49 &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "_") &amp; IF(G49&lt;&gt;"", "_" &amp; G49, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
-      <c r="C49" s="9" t="str">
-        <f t="shared" ref="C49:C53" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+      <c r="D49" s="9" t="str">
+        <f t="shared" ref="D49:D53" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
-      <c r="D49" s="2" t="str">
-        <f t="shared" ref="D49:D53" si="70">IF(ISNUMBER(FIND("&amp;", A49)),
+      <c r="E49" s="2" t="str">
+        <f t="shared" ref="E49:E53" si="70">IF(ISNUMBER(FIND("&amp;", A49)),
     IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=6, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E49" s="9" t="str">
-        <f t="shared" ref="E49:E52" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+      <c r="F49" s="9" t="str">
+        <f t="shared" ref="F49:F52" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
         <v>1999</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1016/s0166-4328(98)00151-x 	</v>
-      </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="1" t="s">
+      <c r="G49" s="9"/>
+      <c r="H49" t="str">
+        <f>_xlfn.TEXTAFTER(A49,"https://doi.org/")</f>
+        <v>10.1016/s0166-4328(98)00151-x</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J49" s="5" t="str">
-        <f t="shared" ref="J49:J52" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+      <c r="K49" s="5" t="str">
+        <f t="shared" ref="K49:K52" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,C49,(SUBSTITUTE(SUBSTITUTE(J49," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_Table1</v>
       </c>
-      <c r="K49" s="5" t="str">
-        <f>IF(ISBLANK(H49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x	_Table1</v>
-      </c>
-      <c r="M49" s="5" t="s">
+      <c r="L49" s="5" t="str">
+        <f>IF(ISBLANK(I49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(J49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I49, SUBSTITUTE(J49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
+      </c>
+      <c r="N49" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N49" t="str">
-        <f t="array" ref="N49">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O49" t="str">
+        <f t="array" ref="O49">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="T49" t="s">
+      <c r="U49" t="s">
         <v>46</v>
       </c>
-      <c r="U49" t="s">
+      <c r="V49" t="s">
         <v>78</v>
       </c>
-      <c r="W49" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>271</v>
-      </c>
-      <c r="B50" s="9" t="str">
-        <f t="shared" ref="B50" si="73">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
+        <v>343</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="5"/>
+        <v>x</v>
+      </c>
+      <c r="C50" s="9" t="str">
+        <f t="shared" ref="C50" si="73">D50 &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "_") &amp; IF(G50&lt;&gt;"", "_" &amp; G50, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
-      <c r="C50" s="9" t="str">
-        <f t="shared" ref="C50" si="74">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+      <c r="D50" s="9" t="str">
+        <f t="shared" ref="D50" si="74">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
-      <c r="D50" s="2" t="str">
-        <f t="shared" ref="D50" si="75">IF(ISNUMBER(FIND("&amp;", A50)),
+      <c r="E50" s="2" t="str">
+        <f t="shared" ref="E50" si="75">IF(ISNUMBER(FIND("&amp;", A50)),
     IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E50" s="9" t="str">
-        <f t="shared" ref="E50" si="76">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+      <c r="F50" s="9" t="str">
+        <f t="shared" ref="F50" si="76">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
         <v>1999</v>
       </c>
-      <c r="F50" s="9"/>
-      <c r="G50" t="str">
-        <f t="shared" ref="G50" si="77">_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
-        <v xml:space="preserve">10.1016/s0166-4328(98)00151-x 	</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="J50" s="5" t="str">
-        <f t="shared" ref="J50" si="78">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
+      <c r="G50" s="9"/>
+      <c r="H50" t="str">
+        <f t="shared" ref="H50" si="77">_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
+        <v>10.1016/s0166-4328(98)00151-x</v>
+      </c>
+      <c r="I50" s="5"/>
+      <c r="J50" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K50" s="5" t="str">
+        <f t="shared" ref="K50" si="78">TRIM(_xlfn.TEXTJOIN("_",FALSE,C50,(SUBSTITUTE(SUBSTITUTE(J50," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_References</v>
       </c>
-      <c r="K50" s="5" t="str">
-        <f>IF(ISBLANK(H50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x	_References</v>
-      </c>
-      <c r="M50" s="5" t="s">
+      <c r="L50" s="5" t="str">
+        <f>IF(ISBLANK(I50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(J50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I50, SUBSTITUTE(J50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
+      </c>
+      <c r="N50" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N50" t="str">
-        <f t="array" ref="N50">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O50" t="str">
+        <f t="array" ref="O50">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="T50" t="s">
-        <v>351</v>
-      </c>
       <c r="U50" t="s">
+        <v>342</v>
+      </c>
+      <c r="V50" t="s">
         <v>78</v>
       </c>
-      <c r="W50" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X50" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>272</v>
-      </c>
-      <c r="B51" s="9" t="str">
+        <v>344</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="9" t="str">
         <f t="shared" si="68"/>
         <v>Genoud_etal_2018</v>
       </c>
-      <c r="C51" s="9" t="str">
+      <c r="D51" s="9" t="str">
         <f t="shared" si="69"/>
         <v>Genoud</v>
       </c>
-      <c r="D51" s="2" t="str">
+      <c r="E51" s="2" t="str">
         <f t="shared" si="70"/>
         <v>etal</v>
       </c>
-      <c r="E51" s="9" t="str">
+      <c r="F51" s="9" t="str">
         <f t="shared" si="71"/>
         <v>2018</v>
       </c>
-      <c r="F51" s="9"/>
-      <c r="G51" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1111/brv.12350 	</v>
-      </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="1" t="s">
+      <c r="G51" s="9"/>
+      <c r="H51" t="str">
+        <f>_xlfn.TEXTAFTER(A51,"https://doi.org/")</f>
+        <v>10.1111/brv.12350</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J51" s="5" t="str">
+      <c r="K51" s="5" t="str">
         <f t="shared" si="72"/>
         <v>Genoud_etal_2018_TableS2</v>
       </c>
-      <c r="K51" s="5" t="str">
-        <f t="shared" ref="K51:K52" si="79">IF(ISBLANK(H51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1111%2Fbrv.12350	_TableS2</v>
-      </c>
-      <c r="M51" s="5" t="s">
+      <c r="L51" s="5" t="str">
+        <f t="shared" ref="L51:L52" si="79">IF(ISBLANK(I51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1111%2Fbrv.12350_TableS2</v>
+      </c>
+      <c r="N51" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N51" t="str">
-        <f t="array" ref="N51">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O51" t="str">
+        <f t="array" ref="O51">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="W51" t="s">
-        <v>276</v>
-      </c>
-      <c r="AB51" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X51" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>273</v>
-      </c>
-      <c r="B52" s="9" t="str">
+        <v>345</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C52" s="9" t="str">
         <f t="shared" si="68"/>
         <v>Mota_etal_2019</v>
       </c>
-      <c r="C52" s="9" t="str">
+      <c r="D52" s="9" t="str">
         <f t="shared" si="69"/>
         <v>Mota</v>
       </c>
-      <c r="D52" s="2" t="str">
+      <c r="E52" s="2" t="str">
         <f t="shared" si="70"/>
         <v>etal</v>
       </c>
-      <c r="E52" s="9" t="str">
+      <c r="F52" s="9" t="str">
         <f t="shared" si="71"/>
         <v>2019</v>
       </c>
-      <c r="F52" s="9"/>
-      <c r="G52" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1073/pnas.1716956116 	</v>
-      </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J52" s="5" t="str">
+      <c r="G52" s="9"/>
+      <c r="H52" t="str">
+        <f>_xlfn.TEXTAFTER(A52,"https://doi.org/")</f>
+        <v>10.1073/pnas.1716956116</v>
+      </c>
+      <c r="I52" s="5"/>
+      <c r="J52" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K52" s="5" t="str">
         <f t="shared" si="72"/>
         <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
-      <c r="K52" s="5" t="str">
+      <c r="L52" s="5" t="str">
         <f t="shared" si="79"/>
-        <v>10.1073%2Fpnas.1716956116	_SupplementaryTableS1</v>
-      </c>
-      <c r="M52" s="5" t="s">
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+      </c>
+      <c r="N52" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N52" t="str">
-        <f t="array" ref="N52">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O52" t="str">
+        <f t="array" ref="O52">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="W52" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB52" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X52" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>277</v>
-      </c>
-      <c r="B53" s="9" t="str">
+        <v>346</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C53" s="9" t="str">
         <f t="shared" si="68"/>
         <v>Burish_etal_2010</v>
       </c>
-      <c r="C53" s="9" t="str">
+      <c r="D53" s="9" t="str">
         <f t="shared" si="69"/>
         <v>Burish</v>
       </c>
-      <c r="D53" s="2" t="str">
+      <c r="E53" s="2" t="str">
         <f t="shared" si="70"/>
         <v>etal</v>
       </c>
-      <c r="E53" s="9" t="str">
-        <f t="shared" ref="E53" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
+      <c r="F53" s="9" t="str">
+        <f t="shared" ref="F53" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
         <v>2010</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1159/000319019 </v>
-      </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="1" t="s">
+      <c r="G53" s="9"/>
+      <c r="H53" t="str">
+        <f>_xlfn.TEXTAFTER(A53,"https://doi.org/")</f>
+        <v>10.1159/000319019</v>
+      </c>
+      <c r="I53" s="5"/>
+      <c r="J53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J53" s="5" t="str">
-        <f t="shared" ref="J53" si="81">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
+      <c r="K53" s="5" t="str">
+        <f t="shared" ref="K53" si="81">TRIM(_xlfn.TEXTJOIN("_",FALSE,C53,(SUBSTITUTE(SUBSTITUTE(J53," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_Table1</v>
       </c>
-      <c r="K53" s="5" t="str">
-        <f t="shared" ref="K53" si="82">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L53" s="5" t="str">
+        <f t="shared" ref="L53" si="82">IF(ISBLANK(I53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000319019_Table1</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>41</v>
       </c>
-      <c r="N53" t="str">
-        <f t="array" ref="N53">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O53" t="str">
+        <f t="array" ref="O53">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
-      <c r="O53" t="s">
+      <c r="P53" t="s">
         <v>53</v>
       </c>
-      <c r="P53" t="s">
-        <v>291</v>
-      </c>
-      <c r="W53" t="s">
-        <v>278</v>
-      </c>
-      <c r="Y53" t="s">
+      <c r="Q53" t="s">
+        <v>286</v>
+      </c>
+      <c r="X53" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC53" t="s">
         <v>281</v>
       </c>
-      <c r="AB53" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD53" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE53" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>277</v>
-      </c>
-      <c r="B54" s="9" t="str">
-        <f t="shared" ref="B54:B59" si="83">C54 &amp; IF(D54&lt;&gt;"", "_" &amp; D54, "_") &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "")</f>
+        <v>346</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C54" s="9" t="str">
+        <f t="shared" ref="C54:C59" si="83">D54 &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "_") &amp; IF(G54&lt;&gt;"", "_" &amp; G54, "")</f>
         <v>Burish_etal_2010</v>
       </c>
-      <c r="C54" s="9" t="str">
-        <f t="shared" ref="C54:C59" si="84">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
+      <c r="D54" s="9" t="str">
+        <f t="shared" ref="D54:D59" si="84">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
         <v>Burish</v>
       </c>
-      <c r="D54" s="2" t="str">
-        <f t="shared" ref="D54:D59" si="85">IF(ISNUMBER(FIND("&amp;", A54)),
+      <c r="E54" s="2" t="str">
+        <f t="shared" ref="E54:E59" si="85">IF(ISNUMBER(FIND("&amp;", A54)),
     IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E54" s="9" t="str">
-        <f t="shared" ref="E54:E59" si="86">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
+      <c r="F54" s="9" t="str">
+        <f t="shared" ref="F54:F59" si="86">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
         <v>2010</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" t="str">
-        <f t="shared" ref="G54:G59" si="87">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
-        <v xml:space="preserve">10.1159/000319019 </v>
-      </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="J54" s="5" t="str">
-        <f t="shared" ref="J54:J55" si="88">TRIM(_xlfn.TEXTJOIN("_",FALSE,B54,(SUBSTITUTE(SUBSTITUTE(I54," ",""), "_", ""))))</f>
+      <c r="G54" s="9"/>
+      <c r="H54" t="str">
+        <f t="shared" ref="H54:H59" si="87">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
+        <v>10.1159/000319019</v>
+      </c>
+      <c r="I54" s="5"/>
+      <c r="J54" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K54" s="5" t="str">
+        <f t="shared" ref="K54:K55" si="88">TRIM(_xlfn.TEXTJOIN("_",FALSE,C54,(SUBSTITUTE(SUBSTITUTE(J54," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
-      <c r="K54" s="5" t="str">
-        <f t="shared" ref="K54:K55" si="89">IF(ISBLANK(H54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L54" s="5" t="str">
+        <f t="shared" ref="L54:L55" si="89">IF(ISBLANK(I54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="N54" t="str">
-        <f t="array" ref="N54">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N54" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="O54" t="str">
+        <f t="array" ref="O54">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
-      <c r="P54" t="s">
-        <v>292</v>
-      </c>
-      <c r="W54" t="s">
+      <c r="Q54" t="s">
+        <v>287</v>
+      </c>
+      <c r="X54" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE54" t="s">
         <v>279</v>
       </c>
-      <c r="Y54" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB54" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD54" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>287</v>
-      </c>
-      <c r="B55" s="9" t="str">
+        <v>347</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="5"/>
+        <v>x</v>
+      </c>
+      <c r="C55" s="9" t="str">
         <f t="shared" si="83"/>
         <v>Fu_etal_2013</v>
       </c>
-      <c r="C55" s="9" t="str">
+      <c r="D55" s="9" t="str">
         <f t="shared" si="84"/>
         <v>Fu</v>
       </c>
-      <c r="D55" s="2" t="str">
+      <c r="E55" s="2" t="str">
         <f t="shared" si="85"/>
         <v>etal</v>
       </c>
-      <c r="E55" s="9" t="str">
+      <c r="F55" s="9" t="str">
         <f t="shared" si="86"/>
         <v>2013</v>
       </c>
-      <c r="G55" t="str">
+      <c r="H55" t="str">
         <f t="shared" si="87"/>
-        <v xml:space="preserve">10.1007/s00429-012-0462-x 	</v>
-      </c>
-      <c r="I55" s="1" t="s">
+        <v>10.1007/s00429-012-0462-x</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J55" s="5" t="str">
+      <c r="K55" s="5" t="str">
         <f t="shared" si="88"/>
         <v>Fu_etal_2013_Table1</v>
       </c>
-      <c r="K55" s="5" t="str">
+      <c r="L55" s="5" t="str">
         <f t="shared" si="89"/>
-        <v>10.1007%2Fs00429-012-0462-x	_Table1</v>
-      </c>
-      <c r="M55" s="5" t="s">
+        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
+      </c>
+      <c r="N55" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N55" t="str">
-        <f t="array" ref="N55">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O55" t="str">
+        <f t="array" ref="O55">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="W55" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X55" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>293</v>
-      </c>
-      <c r="B56" s="9" t="str">
+        <v>348</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C56" s="9" t="str">
         <f t="shared" si="83"/>
         <v>MacLarnon__1996</v>
       </c>
-      <c r="C56" s="9" t="str">
+      <c r="D56" s="9" t="str">
         <f t="shared" si="84"/>
         <v>MacLarnon</v>
       </c>
-      <c r="D56" s="2" t="str">
+      <c r="E56" s="2" t="str">
         <f t="shared" si="85"/>
         <v/>
       </c>
-      <c r="E56" s="9" t="str">
+      <c r="F56" s="9" t="str">
         <f t="shared" si="86"/>
         <v>1996</v>
       </c>
-      <c r="G56" t="str">
+      <c r="H56" t="str">
         <f t="shared" si="87"/>
-        <v xml:space="preserve">10.1006/jhev.1996.0005 	</v>
-      </c>
-      <c r="I56" s="1" t="s">
+        <v>10.1006/jhev.1996.0005</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J56" s="5" t="str">
-        <f t="shared" ref="J56:J59" si="90">TRIM(_xlfn.TEXTJOIN("_",FALSE,B56,(SUBSTITUTE(SUBSTITUTE(I56," ",""), "_", ""))))</f>
+      <c r="K56" s="5" t="str">
+        <f t="shared" ref="K56:K59" si="90">TRIM(_xlfn.TEXTJOIN("_",FALSE,C56,(SUBSTITUTE(SUBSTITUTE(J56," ",""), "_", ""))))</f>
         <v>MacLarnon__1996_Table1</v>
       </c>
-      <c r="K56" s="5" t="str">
-        <f t="shared" ref="K56:K59" si="91">IF(ISBLANK(H56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1006%2Fjhev.1996.0005	_Table1</v>
-      </c>
-      <c r="M56" s="5" t="s">
+      <c r="L56" s="5" t="str">
+        <f t="shared" ref="L56:L59" si="91">IF(ISBLANK(I56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+      </c>
+      <c r="N56" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N56" t="str">
-        <f t="array" ref="N56">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O56" t="str">
+        <f t="array" ref="O56">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="W56" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X56" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>297</v>
-      </c>
-      <c r="B57" s="9" t="str">
+        <v>349</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C57" s="9" t="str">
         <f t="shared" si="83"/>
         <v>Wimberly_etal_2021</v>
       </c>
-      <c r="C57" s="9" t="str">
+      <c r="D57" s="9" t="str">
         <f t="shared" si="84"/>
         <v>Wimberly</v>
       </c>
-      <c r="D57" s="2" t="str">
+      <c r="E57" s="2" t="str">
         <f t="shared" si="85"/>
         <v>etal</v>
       </c>
-      <c r="E57" s="9" t="str">
+      <c r="F57" s="9" t="str">
         <f t="shared" si="86"/>
         <v>2021</v>
       </c>
-      <c r="G57" t="str">
+      <c r="H57" t="str">
         <f t="shared" si="87"/>
-        <v xml:space="preserve">10.1098/rspb.2021.0937 	</v>
-      </c>
-      <c r="I57" t="s">
-        <v>346</v>
-      </c>
-      <c r="J57" s="5" t="str">
+        <v>10.1098/rspb.2021.0937</v>
+      </c>
+      <c r="J57" t="s">
+        <v>338</v>
+      </c>
+      <c r="K57" s="5" t="str">
         <f t="shared" si="90"/>
         <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
-      <c r="K57" s="5" t="str">
+      <c r="L57" s="5" t="str">
         <f t="shared" si="91"/>
-        <v>10.1098%2Frspb.2021.0937	_mammalgait.txt</v>
-      </c>
-      <c r="M57" s="5" t="s">
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+      </c>
+      <c r="N57" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N57" t="str">
-        <f t="array" ref="N57">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O57" t="str">
+        <f t="array" ref="O57">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>345</v>
-      </c>
-      <c r="B58" s="9" t="str">
+        <v>350</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C58" s="9" t="str">
         <f t="shared" si="83"/>
         <v>Granatosky__2018</v>
       </c>
-      <c r="C58" s="9" t="str">
+      <c r="D58" s="9" t="str">
         <f t="shared" si="84"/>
         <v>Granatosky</v>
       </c>
-      <c r="D58" s="2" t="str">
+      <c r="E58" s="2" t="str">
         <f t="shared" si="85"/>
         <v/>
       </c>
-      <c r="E58" s="9" t="str">
+      <c r="F58" s="9" t="str">
         <f t="shared" si="86"/>
         <v>2018</v>
       </c>
-      <c r="G58" t="str">
+      <c r="H58" t="str">
         <f t="shared" si="87"/>
-        <v xml:space="preserve">10.1111/jzo.12608 	</v>
-      </c>
-      <c r="I58" t="s">
+        <v>10.1111/jzo.12608</v>
+      </c>
+      <c r="J58" t="s">
         <v>91</v>
       </c>
-      <c r="J58" s="5" t="str">
+      <c r="K58" s="5" t="str">
         <f t="shared" si="90"/>
         <v>Granatosky__2018_TableS1</v>
       </c>
-      <c r="K58" s="5" t="str">
+      <c r="L58" s="5" t="str">
         <f t="shared" si="91"/>
-        <v>10.1111%2Fjzo.12608	_TableS1</v>
-      </c>
-      <c r="M58" s="5" t="s">
+        <v>10.1111%2Fjzo.12608_TableS1</v>
+      </c>
+      <c r="N58" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N58" t="str">
-        <f t="array" ref="N58">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="O58" t="str">
+        <f t="array" ref="O58">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="W58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="X58" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>347</v>
-      </c>
-      <c r="B59" s="9" t="str">
+        <v>351</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C59" s="9" t="str">
         <f t="shared" si="83"/>
         <v>Wilman_etal_2014</v>
       </c>
-      <c r="C59" s="9" t="str">
+      <c r="D59" s="9" t="str">
         <f t="shared" si="84"/>
         <v>Wilman</v>
       </c>
-      <c r="D59" s="2" t="str">
+      <c r="E59" s="2" t="str">
         <f t="shared" si="85"/>
         <v>etal</v>
       </c>
-      <c r="E59" s="9" t="str">
+      <c r="F59" s="9" t="str">
         <f t="shared" si="86"/>
         <v>2014</v>
       </c>
-      <c r="G59" t="str">
+      <c r="H59" t="str">
         <f t="shared" si="87"/>
-        <v xml:space="preserve">10.1890/13-1917.1 	</v>
-      </c>
-      <c r="I59" t="s">
-        <v>348</v>
-      </c>
-      <c r="J59" s="5" t="str">
+        <v>10.1890/13-1917.1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>339</v>
+      </c>
+      <c r="K59" s="5" t="str">
         <f t="shared" si="90"/>
         <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
-      <c r="K59" s="5" t="str">
+      <c r="L59" s="5" t="str">
         <f t="shared" si="91"/>
-        <v>10.1890%2F13-1917.1	_MamFuncDat.txt</v>
-      </c>
-      <c r="N59" t="str">
-        <f t="array" ref="N59">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+      </c>
+      <c r="O59" t="str">
+        <f t="array" ref="O59">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="V3" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="V6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="V7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="V9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="V28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="V29" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="V13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="V14:V17" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="V27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="V26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="V24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="W3" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="W4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="W6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="W7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="W9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="W28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="W29" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="W13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="W14:W17" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="W27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="W26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="W24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5729,7 +5968,7 @@
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5859,232 +6098,232 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -6398,16 +6637,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1934E1-96D8-B044-ABD9-555549A1755F}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06A6870C-C12F-EC40-BA79-F426324FC52E}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5960" windowWidth="40940" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35120" yWindow="-5120" windowWidth="45340" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="FileList" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="373">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -1139,6 +1138,27 @@
   </si>
   <si>
     <t>https://www.pnas.org/doi/suppl/10.1073/pnas.0905777106/suppl_file/0905777106si.pdf</t>
+  </si>
+  <si>
+    <t>Falcone, C., Wolf-Ochoa, M., Amina, S., Hong, T., Vakilzadeh, G., Hopkins, W. D., Hof, P. R., Sherwood, C. C., Manger, P. R., Noctor, S. C., &amp; Martinez-Cerdeno, V. (2019). Cortical interlaminar astrocytes across the therian mammal radiation. J Comp Neurol, 527(10), 1654-1674. https://doi.org/10.1002/cne.24605</t>
+  </si>
+  <si>
+    <t>TABLE 1 Pial and subpial ILA presence in mammalian species analyzed. Highlighted in red are the species where proper subpial ILA are present</t>
+  </si>
+  <si>
+    <t>TABLE 2 ILA linear density, number of primary processes, number of total processes, total length, and complexity, of mammalian species analyzed</t>
+  </si>
+  <si>
+    <t>Avelino-de-Souza, K., Patzke, N., Karlsson, K. A. E., Manger, P. R., &amp; Herculano-Houzel, S. (2025). Cellular Composition of the Brain of a Northern Minke Whale. J Comp Neurol, 533(9), e70089. https://doi.org/10.1002/cne.70089</t>
+  </si>
+  <si>
+    <t>Baron, G., Frahm, H. D., Bhatnagar, K. P., &amp; Stephan, H. (1983). Comparison of brain structure volumes in Insectivora and Primates. III. Main olfactory bulb (MOB). J Hirnforsch, 24(5), 551-568. https://www.ncbi.nlm.nih.gov/pubmed/6663055</t>
+  </si>
+  <si>
+    <t>10.0000/placeholder.1</t>
+  </si>
+  <si>
+    <t>unpublished</t>
   </si>
 </sst>
 </file>
@@ -1312,8 +1332,10 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1"/>
     <xf numFmtId="49" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1630,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK64"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" style="13" customWidth="1"/>
@@ -1782,421 +1804,348 @@
     </row>
     <row r="2" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C2" t="str">
-        <f>RIGHT(A2,1)</f>
-        <v>0</v>
+        <f t="shared" ref="C2" si="0">RIGHT(A2,1)</f>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <f>E2 &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "_") &amp; IF(G2&lt;&gt;"", "_" &amp; G2, "_") &amp; IF(B2&lt;&gt;"", "_" &amp; B2, "")</f>
-        <v>Brodmann__1913</v>
+        <f t="shared" ref="D2" si="1">E2 &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "_") &amp; IF(G2&lt;&gt;"", "_" &amp; G2, "_") &amp; IF(B2&lt;&gt;"", "_" &amp; B2, "")</f>
+        <v>AvelinodeSouza_etal_2025</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
-        <v>Brodmann</v>
+        <f t="shared" ref="E2" si="2">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
+        <v>AvelinodeSouza</v>
       </c>
       <c r="F2" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A2)),
+        <f t="shared" ref="F2" si="3">IF(ISNUMBER(FIND("&amp;", A2)),
     IF(LEN(A2)-LEN(SUBSTITUTE(A2, ",", ""))&gt;=6, "etal", MID(A2, SEARCH("&amp; ", A2)+2, SEARCH(",", A2, SEARCH("&amp; ", A2)+2) - SEARCH("&amp; ", A2)-2)),
     ""
 )</f>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="G2" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
-        <v>1913</v>
-      </c>
-      <c r="H2" t="e">
-        <f>_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>352</v>
+        <f t="shared" ref="G2" si="4">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
+        <v>2025</v>
+      </c>
+      <c r="H2" t="str">
+        <f t="shared" ref="H2" si="5">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
+        <v>10.1002/cne.70089</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="K2" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D2,(SUBSTITUTE(SUBSTITUTE(J2," ",""), "_", ""))))</f>
-        <v>Brodmann__1913_Tabelle1</v>
+        <f t="shared" ref="K2" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,D2,(SUBSTITUTE(SUBSTITUTE(J2," ",""), "_", ""))))</f>
+        <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L2" s="1" t="str">
-        <f>IF(ISBLANK(I2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.0000%2Fplaceholder_Tabelle1</v>
+        <f t="shared" ref="L2:L38" si="7">IF(ISBLANK(I2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M2" t="str">
         <f t="array" ref="M2">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="C3" t="str">
-        <f>RIGHT(A3,1)</f>
-        <v>3</v>
+        <f t="shared" ref="C3" si="8">RIGHT(A3,1)</f>
+        <v>5</v>
       </c>
       <c r="D3" t="str">
-        <f>E3 &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "_") &amp; IF(G3&lt;&gt;"", "_" &amp; G3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
-        <v>Burger_etal_2019</v>
+        <f t="shared" ref="D3" si="9">E3 &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "_") &amp; IF(G3&lt;&gt;"", "_" &amp; G3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
+        <v>Baron_etal_1983</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
-        <v>Burger</v>
+        <f t="shared" ref="E3" si="10">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
+        <v>Baron</v>
       </c>
       <c r="F3" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A3)),
+        <f t="shared" ref="F3" si="11">IF(ISNUMBER(FIND("&amp;", A3)),
     IF(LEN(A3)-LEN(SUBSTITUTE(A3, ",", ""))&gt;=6, "etal", MID(A3, SEARCH("&amp; ", A3)+2, SEARCH(",", A3, SEARCH("&amp; ", A3)+2) - SEARCH("&amp; ", A3)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="G3" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
-        <v>2019</v>
-      </c>
-      <c r="H3" t="str">
-        <f>_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
-        <v>10.1093/jmammal/gyz043</v>
+        <f t="shared" ref="G3" si="12">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+        <v>1983</v>
+      </c>
+      <c r="H3" t="e">
+        <f t="shared" ref="H3" si="13">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>371</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D3,(SUBSTITUTE(SUBSTITUTE(J3," ",""), "_", ""))))</f>
-        <v>Burger_etal_2019_SupplementaryDataSD1</v>
-      </c>
-      <c r="L3" s="6" t="str">
-        <f>IF(ISBLANK(I3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
+        <f t="shared" ref="K3" si="14">TRIM(_xlfn.TEXTJOIN("_",FALSE,D3,(SUBSTITUTE(SUBSTITUTE(J3," ",""), "_", ""))))</f>
+        <v>Baron_etal_1983_Table1</v>
+      </c>
+      <c r="L3" s="1" t="str">
+        <f t="shared" ref="L3" si="15">IF(ISBLANK(I3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I3, SUBSTITUTE(J3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.0000%2Fplaceholder.1_Table1</v>
       </c>
       <c r="M3" t="str">
         <f t="array" ref="M3">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="13" t="str">
-        <f>IF(S3="N", R3, "write file name")</f>
-        <v>gyz043_suppl_Supplement_Data.csv</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="V3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI3" s="13">
-        <v>17</v>
-      </c>
-      <c r="AK3" s="13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C4" t="str">
-        <f>RIGHT(A4,1)</f>
-        <v>9</v>
+        <f t="shared" ref="C4:C38" si="16">RIGHT(A4,1)</f>
+        <v>0</v>
       </c>
       <c r="D4" t="str">
-        <f>E4 &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "_") &amp; IF(G4&lt;&gt;"", "_" &amp; G4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="E4" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
-        <v>Burish</v>
+        <f t="shared" ref="D4:D38" si="17">E4 &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "_") &amp; IF(G4&lt;&gt;"", "_" &amp; G4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
+        <v>Brodmann__1913</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f t="shared" ref="E4:E38" si="18">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <v>Brodmann</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="F4:F38" si="19">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=6, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
-        <v>etal</v>
-      </c>
-      <c r="G4" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
-        <v>2010</v>
-      </c>
-      <c r="H4" t="str">
-        <f>_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
-        <v>10.1159/000319019</v>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f t="shared" ref="G4:G38" si="20">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <v>1913</v>
+      </c>
+      <c r="H4" t="e">
+        <f t="shared" ref="H4:H38" si="21">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>352</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="K4" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D4,(SUBSTITUTE(SUBSTITUTE(J4," ",""), "_", ""))))</f>
-        <v>Burish_etal_2010_SupplementaryTable1</v>
-      </c>
-      <c r="L4" s="3" t="str">
-        <f>IF(ISBLANK(I4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(J4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I4, SUBSTITUTE(J4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000319019_SupplementaryTable1</v>
+        <v>353</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f t="shared" ref="K4:K38" si="22">TRIM(_xlfn.TEXTJOIN("_",FALSE,D4,(SUBSTITUTE(SUBSTITUTE(J4," ",""), "_", ""))))</f>
+        <v>Brodmann__1913_Tabelle1</v>
+      </c>
+      <c r="L4" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
       <c r="M4" t="str">
         <f t="array" ref="M4">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="Z4" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE4" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>345</v>
+        <v>38</v>
       </c>
       <c r="C5" t="str">
-        <f>RIGHT(A5,1)</f>
-        <v>9</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D5" t="str">
-        <f>E5 &amp; IF(F5&lt;&gt;"", "_" &amp; F5, "_") &amp; IF(G5&lt;&gt;"", "_" &amp; G5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="E5" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
-        <v>Burish</v>
+        <f t="shared" si="17"/>
+        <v>Burger_etal_2019</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="18"/>
+        <v>Burger</v>
       </c>
       <c r="F5" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A5)),
-    IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G5" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
-        <v>2010</v>
+      <c r="G5" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>2019</v>
       </c>
       <c r="H5" t="str">
-        <f>_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
-        <v>10.1159/000319019</v>
+        <f t="shared" si="21"/>
+        <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D5,(SUBSTITUTE(SUBSTITUTE(J5," ",""), "_", ""))))</f>
-        <v>Burish_etal_2010_Table1</v>
-      </c>
-      <c r="L5" s="3" t="str">
-        <f>IF(ISBLANK(I5),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H5, SUBSTITUTE(J5,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I5, SUBSTITUTE(J5,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000319019_Table1</v>
+        <v>39</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>Burger_etal_2019_SupplementaryDataSD1</v>
+      </c>
+      <c r="L5" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="M5" t="str">
         <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_Table1.tsv</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>274</v>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="P5" s="13" t="s">
         <v>41</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>285</v>
+        <v>43</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="13" t="str">
+        <f>IF(S5="N", R5, "write file name")</f>
+        <v>gyz043_suppl_Supplement_Data.csv</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC5" s="13" t="s">
-        <v>281</v>
+        <v>49</v>
+      </c>
+      <c r="AD5" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="AE5" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="AI5" s="13">
+        <v>17</v>
+      </c>
+      <c r="AK5" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="C6" t="str">
-        <f>RIGHT(A6,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>9</v>
       </c>
       <c r="D6" t="str">
-        <f>E6 &amp; IF(F6&lt;&gt;"", "_" &amp; F6, "_") &amp; IF(G6&lt;&gt;"", "_" &amp; G6, "_") &amp; IF(B6&lt;&gt;"", "_" &amp; B6, "")</f>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A6,","), "-", ""), " ", "")</f>
-        <v>Caspar</v>
+        <f t="shared" si="17"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>Burish</v>
       </c>
       <c r="F6" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A6)),
-    IF(LEN(A6)-LEN(SUBSTITUTE(A6, ",", ""))&gt;=6, "etal", MID(A6, SEARCH("&amp; ", A6)+2, SEARCH(",", A6, SEARCH("&amp; ", A6)+2) - SEARCH("&amp; ", A6)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A6, "("), ")")</f>
-        <v>2022</v>
+      <c r="G6" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>2010</v>
       </c>
       <c r="H6" t="str">
-        <f>_xlfn.TEXTAFTER(A6,"https://doi.org/")</f>
-        <v>10.7554/eLife.77875</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000319019</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D6,(SUBSTITUTE(SUBSTITUTE(J6," ",""), "_", ""))))</f>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
-      </c>
-      <c r="L6" s="1" t="str">
-        <f>IF(ISBLANK(I6),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H6, SUBSTITUTE(J6,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I6, SUBSTITUTE(J6,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
+        <v>276</v>
+      </c>
+      <c r="K6" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v>Burish_etal_2010_SupplementaryTable1</v>
+      </c>
+      <c r="L6" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M6" t="str">
         <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>53</v>
+        <v>284</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T6" s="13" t="str">
-        <f>IF(S6="N", R6, "write file name")</f>
-        <v>elife-77875-supp3-v1.xlsx</v>
-      </c>
-      <c r="U6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="V6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W6" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X6" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y6" s="13" t="s">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="Z6" s="13" t="s">
-        <v>49</v>
+        <v>278</v>
+      </c>
+      <c r="AC6" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="AE6" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI6" s="13">
-        <v>5</v>
-      </c>
-      <c r="AK6" s="13">
-        <v>12</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="C7" t="str">
-        <f>RIGHT(A7,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>9</v>
       </c>
       <c r="D7" t="str">
-        <f>E7 &amp; IF(F7&lt;&gt;"", "_" &amp; F7, "_") &amp; IF(G7&lt;&gt;"", "_" &amp; G7, "_") &amp; IF(B7&lt;&gt;"", "_" &amp; B7, "")</f>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A7,","), "-", ""), " ", "")</f>
-        <v>Caspar</v>
+        <f t="shared" si="17"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>Burish</v>
       </c>
       <c r="F7" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A7)),
-    IF(LEN(A7)-LEN(SUBSTITUTE(A7, ",", ""))&gt;=6, "etal", MID(A7, SEARCH("&amp; ", A7)+2, SEARCH(",", A7, SEARCH("&amp; ", A7)+2) - SEARCH("&amp; ", A7)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A7, "("), ")")</f>
-        <v>2022</v>
+      <c r="G7" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>2010</v>
       </c>
       <c r="H7" t="str">
-        <f>_xlfn.TEXTAFTER(A7,"https://doi.org/")</f>
-        <v>10.7554/eLife.77875</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000319019</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D7,(SUBSTITUTE(SUBSTITUTE(J7," ",""), "_", ""))))</f>
-        <v>Caspar_etal_2022_Table1</v>
-      </c>
-      <c r="L7" s="1" t="str">
-        <f>IF(ISBLANK(I7),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H7, SUBSTITUTE(J7,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I7, SUBSTITUTE(J7,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.7554%2FeLife.77875_Table1</v>
+      <c r="K7" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v>Burish_etal_2010_Table1</v>
+      </c>
+      <c r="L7" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M7" t="str">
         <f t="array" ref="M7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>60</v>
+        <v>274</v>
       </c>
       <c r="P7" s="13" t="s">
         <v>41</v>
@@ -2205,173 +2154,153 @@
         <v>53</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T7" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="U7" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W7" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X7" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y7" s="13" t="s">
-        <v>61</v>
+        <v>285</v>
       </c>
       <c r="Z7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD7" s="13" t="s">
-        <v>63</v>
+        <v>277</v>
+      </c>
+      <c r="AC7" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="AE7" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI7" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK7" s="13">
-        <v>8</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C8" t="str">
-        <f>RIGHT(A8,1)</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D8" t="str">
-        <f>E8 &amp; IF(F8&lt;&gt;"", "_" &amp; F8, "_") &amp; IF(G8&lt;&gt;"", "_" &amp; G8, "_") &amp; IF(B8&lt;&gt;"", "_" &amp; B8, "")</f>
-        <v>Changizi__2001</v>
+        <f t="shared" si="17"/>
+        <v>Caspar_etal_2022</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A8,","), "-", ""), " ", "")</f>
-        <v>Changizi</v>
+        <f t="shared" si="18"/>
+        <v>Caspar</v>
       </c>
       <c r="F8" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A8)),
-    IF(LEN(A8)-LEN(SUBSTITUTE(A8, ",", ""))&gt;=6, "etal", MID(A8, SEARCH("&amp; ", A8)+2, SEARCH(",", A8, SEARCH("&amp; ", A8)+2) - SEARCH("&amp; ", A8)-2)),
-    ""
-)</f>
-        <v/>
+        <f t="shared" si="19"/>
+        <v>etal</v>
       </c>
       <c r="G8" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A8, "("), ")")</f>
-        <v>2001</v>
+        <f t="shared" si="20"/>
+        <v>2022</v>
       </c>
       <c r="H8" t="str">
-        <f>_xlfn.TEXTAFTER(A8,"https://doi.org/")</f>
-        <v>10.1007/s004220000205</v>
+        <f t="shared" si="21"/>
+        <v>10.7554/eLife.77875</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K8" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D8,(SUBSTITUTE(SUBSTITUTE(J8," ",""), "_", ""))))</f>
-        <v>Changizi__2001_Figure3</v>
+        <f t="shared" si="22"/>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="L8" s="1" t="str">
-        <f>IF(ISBLANK(I8),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H8, SUBSTITUTE(J8,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I8, SUBSTITUTE(J8,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1007%2Fs004220000205_Figure3</v>
+        <f t="shared" si="7"/>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M8" t="str">
         <f t="array" ref="M8">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="S8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T8" s="13" t="s">
-        <v>76</v>
+        <v>44</v>
+      </c>
+      <c r="T8" s="13" t="str">
+        <f>IF(S8="N", R8, "write file name")</f>
+        <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="U8" s="13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="V8" s="13" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="X8" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="Y8" s="13" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD8" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI8" s="13" t="s">
-        <v>81</v>
+        <v>49</v>
+      </c>
+      <c r="AE8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI8" s="13">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="13">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C9" t="str">
-        <f>RIGHT(A9,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D9" t="str">
-        <f>E9 &amp; IF(F9&lt;&gt;"", "_" &amp; F9, "_") &amp; IF(G9&lt;&gt;"", "_" &amp; G9, "_") &amp; IF(B9&lt;&gt;"", "_" &amp; B9, "")</f>
-        <v>Chen_Wiens_2020</v>
+        <f t="shared" si="17"/>
+        <v>Caspar_etal_2022</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A9,","), "-", ""), " ", "")</f>
-        <v>Chen</v>
+        <f t="shared" si="18"/>
+        <v>Caspar</v>
       </c>
       <c r="F9" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A9)),
-    IF(LEN(A9)-LEN(SUBSTITUTE(A9, ",", ""))&gt;=6, "etal", MID(A9, SEARCH("&amp; ", A9)+2, SEARCH(",", A9, SEARCH("&amp; ", A9)+2) - SEARCH("&amp; ", A9)-2)),
-    ""
-)</f>
-        <v>Wiens</v>
+        <f t="shared" si="19"/>
+        <v>etal</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A9, "("), ")")</f>
-        <v>2020</v>
+        <f t="shared" si="20"/>
+        <v>2022</v>
       </c>
       <c r="H9" t="str">
-        <f>_xlfn.TEXTAFTER(A9,"https://doi.org/")</f>
-        <v>10.1038/s41467-020-14356-3</v>
+        <f t="shared" si="21"/>
+        <v>10.7554/eLife.77875</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="K9" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D9,(SUBSTITUTE(SUBSTITUTE(J9," ",""), "_", ""))))</f>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
+        <f t="shared" si="22"/>
+        <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="L9" s="1" t="str">
-        <f>IF(ISBLANK(I9),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H9, SUBSTITUTE(J9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I9, SUBSTITUTE(J9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
+        <f t="shared" si="7"/>
+        <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M9" t="str">
         <f t="array" ref="M9">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="P9" s="13" t="s">
         <v>41</v>
@@ -2380,150 +2309,167 @@
         <v>53</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T9" s="13" t="str">
-        <f>IF(S9="N", R9, "write file name")</f>
-        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+        <v>55</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="U9" s="13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="V9" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="X9" s="13" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="Z9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC9" s="13" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="AD9" s="13" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="AE9" s="13" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="AI9" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK9" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>356</v>
+        <v>72</v>
       </c>
       <c r="C10" t="str">
-        <f>RIGHT(A10,1)</f>
-        <v>7</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D10" t="str">
-        <f>E10 &amp; IF(F10&lt;&gt;"", "_" &amp; F10, "_") &amp; IF(G10&lt;&gt;"", "_" &amp; G10, "_") &amp; IF(B10&lt;&gt;"", "_" &amp; B10, "")</f>
-        <v>Collins_etal_2010</v>
+        <f t="shared" si="17"/>
+        <v>Changizi__2001</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A10,","), "-", ""), " ", "")</f>
-        <v>Collins</v>
+        <f t="shared" si="18"/>
+        <v>Changizi</v>
       </c>
       <c r="F10" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A10)),
-    IF(LEN(A10)-LEN(SUBSTITUTE(A10, ",", ""))&gt;=6, "etal", MID(A10, SEARCH("&amp; ", A10)+2, SEARCH(",", A10, SEARCH("&amp; ", A10)+2) - SEARCH("&amp; ", A10)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="19"/>
+        <v/>
       </c>
       <c r="G10" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A10, "("), ")")</f>
-        <v>2010</v>
+        <f t="shared" si="20"/>
+        <v>2001</v>
       </c>
       <c r="H10" t="str">
-        <f>_xlfn.TEXTAFTER(A10,"https://doi.org/")</f>
-        <v>10.1073/pnas.1010356107</v>
+        <f t="shared" si="21"/>
+        <v>10.1007/s004220000205</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="K10" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D10,(SUBSTITUTE(SUBSTITUTE(J10," ",""), "_", ""))))</f>
-        <v>Collins_etal_2010_DatasetS1</v>
-      </c>
-      <c r="L10" t="str">
-        <f>IF(ISBLANK(I10),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H10, SUBSTITUTE(J10,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I10, SUBSTITUTE(J10,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
+        <v>73</v>
+      </c>
+      <c r="K10" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>Changizi__2001_Figure3</v>
+      </c>
+      <c r="L10" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M10" t="str">
         <f t="array" ref="M10">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>99</v>
+        <v>36</v>
+      </c>
+      <c r="AD10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI10" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C11" t="str">
-        <f>RIGHT(A11,1)</f>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D11" t="str">
-        <f>E11 &amp; IF(F11&lt;&gt;"", "_" &amp; F11, "_") &amp; IF(G11&lt;&gt;"", "_" &amp; G11, "_") &amp; IF(B11&lt;&gt;"", "_" &amp; B11, "")</f>
-        <v>DosSantos_etal_2017</v>
+        <f t="shared" si="17"/>
+        <v>Chen_Wiens_2020</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A11,","), "-", ""), " ", "")</f>
-        <v>DosSantos</v>
+        <f t="shared" si="18"/>
+        <v>Chen</v>
       </c>
       <c r="F11" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A11)),
-    IF(LEN(A11)-LEN(SUBSTITUTE(A11, ",", ""))&gt;=6, "etal", MID(A11, SEARCH("&amp; ", A11)+2, SEARCH(",", A11, SEARCH("&amp; ", A11)+2) - SEARCH("&amp; ", A11)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="19"/>
+        <v>Wiens</v>
       </c>
       <c r="G11" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A11, "("), ")")</f>
-        <v>2017</v>
+        <f t="shared" si="20"/>
+        <v>2020</v>
       </c>
       <c r="H11" t="str">
-        <f>_xlfn.TEXTAFTER(A11,"https://doi.org/")</f>
-        <v>10.1159/000452856</v>
+        <f t="shared" si="21"/>
+        <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K11" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D11,(SUBSTITUTE(SUBSTITUTE(J11," ",""), "_", ""))))</f>
-        <v>DosSantos_etal_2017_TableS1</v>
+        <f t="shared" si="22"/>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="L11" s="1" t="str">
-        <f>IF(ISBLANK(I11),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H11, SUBSTITUTE(J11,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I11, SUBSTITUTE(J11,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000452856_TableS1</v>
+        <f t="shared" si="7"/>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="M11" t="str">
         <f t="array" ref="M11">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000452856_TableS1.tsv</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>92</v>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
       <c r="P11" s="13" t="s">
         <v>41</v>
@@ -2532,975 +2478,977 @@
         <v>53</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="13" t="s">
-        <v>94</v>
+        <v>44</v>
+      </c>
+      <c r="T11" s="13" t="str">
+        <f>IF(S11="N", R11, "write file name")</f>
+        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
       <c r="U11" s="13" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="V11" s="13" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="W11" s="13" t="s">
         <v>68</v>
       </c>
       <c r="X11" s="13" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="Z11" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB11" s="13" t="s">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="AC11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD11" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="AE11" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF11" s="13" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="AI11" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK11" s="13">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="C12" t="str">
-        <f>RIGHT(A12,1)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>7</v>
       </c>
       <c r="D12" t="str">
-        <f>E12 &amp; IF(F12&lt;&gt;"", "_" &amp; F12, "_") &amp; IF(G12&lt;&gt;"", "_" &amp; G12, "_") &amp; IF(B12&lt;&gt;"", "_" &amp; B12, "")</f>
-        <v>DosSantos_etal_2020</v>
+        <f t="shared" si="17"/>
+        <v>Collins_etal_2010</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A12,","), "-", ""), " ", "")</f>
-        <v>DosSantos</v>
+        <f t="shared" si="18"/>
+        <v>Collins</v>
       </c>
       <c r="F12" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A12)),
-    IF(LEN(A12)-LEN(SUBSTITUTE(A12, ",", ""))&gt;=6, "etal", MID(A12, SEARCH("&amp; ", A12)+2, SEARCH(",", A12, SEARCH("&amp; ", A12)+2) - SEARCH("&amp; ", A12)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G12" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A12, "("), ")")</f>
-        <v>2020</v>
+        <f t="shared" si="20"/>
+        <v>2010</v>
       </c>
       <c r="H12" t="str">
-        <f>_xlfn.TEXTAFTER(A12,"https://doi.org/")</f>
-        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+        <f t="shared" si="21"/>
+        <v>10.1073/pnas.1010356107</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D12,(SUBSTITUTE(SUBSTITUTE(J12," ",""), "_", ""))))</f>
-        <v>DosSantos_etal_2020_Table1</v>
-      </c>
-      <c r="L12" s="1" t="str">
-        <f>IF(ISBLANK(I12),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H12, SUBSTITUTE(J12,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I12, SUBSTITUTE(J12,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+        <v>357</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="22"/>
+        <v>Collins_etal_2010_DatasetS1</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
       <c r="M12" t="str">
         <f t="array" ref="M12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="S12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T12" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="U12" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="V12" s="13" t="s">
-        <v>46</v>
+        <v>notfound</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>98</v>
+        <v>355</v>
       </c>
       <c r="Z12" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA12" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB12" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE12" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI12" s="13">
-        <v>4</v>
-      </c>
-      <c r="AK12" s="13">
-        <v>10</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C13" t="str">
-        <f>RIGHT(A13,1)</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="D13" t="str">
-        <f>E13 &amp; IF(F13&lt;&gt;"", "_" &amp; F13, "_") &amp; IF(G13&lt;&gt;"", "_" &amp; G13, "_") &amp; IF(B13&lt;&gt;"", "_" &amp; B13, "")</f>
-        <v>Finlay_etal_2006</v>
+        <f t="shared" si="17"/>
+        <v>DosSantos_etal_2017</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A13,","), "-", ""), " ", "")</f>
-        <v>Finlay</v>
+        <f t="shared" si="18"/>
+        <v>DosSantos</v>
       </c>
       <c r="F13" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A13)),
-    IF(LEN(A13)-LEN(SUBSTITUTE(A13, ",", ""))&gt;=6, "etal", MID(A13, SEARCH("&amp; ", A13)+2, SEARCH(",", A13, SEARCH("&amp; ", A13)+2) - SEARCH("&amp; ", A13)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G13" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A13, "("), ")")</f>
-        <v>2006</v>
+        <f t="shared" si="20"/>
+        <v>2017</v>
       </c>
       <c r="H13" t="str">
-        <f>_xlfn.TEXTAFTER(A13,"https://doi.org/")</f>
-        <v>10.1093/oso/9780198568742.003.0006</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000452856</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="K13" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D13,(SUBSTITUTE(SUBSTITUTE(J13," ",""), "_", ""))))</f>
-        <v>Finlay_etal_2006_Table6.1</v>
+        <f t="shared" si="22"/>
+        <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L13" s="1" t="str">
-        <f>IF(ISBLANK(I13),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H13, SUBSTITUTE(J13,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I13, SUBSTITUTE(J13,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M13" t="str">
         <f t="array" ref="M13">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+        <v>10.1159%2F000452856_TableS1.tsv</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="S13" s="13" t="s">
         <v>55</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="U13" s="13" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="V13" s="13" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="W13" s="13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="X13" s="13" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD13" s="13" t="s">
-        <v>116</v>
+        <v>99</v>
+      </c>
+      <c r="AA13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB13" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="AE13" s="13" t="s">
-        <v>37</v>
+        <v>101</v>
+      </c>
+      <c r="AF13" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="AI13" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="13">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="C14" t="str">
-        <f>RIGHT(A14,1)</f>
-        <v>x</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="D14" t="str">
-        <f>E14 &amp; IF(F14&lt;&gt;"", "_" &amp; F14, "_") &amp; IF(G14&lt;&gt;"", "_" &amp; G14, "_") &amp; IF(B14&lt;&gt;"", "_" &amp; B14, "")</f>
-        <v>Fu_etal_2013</v>
-      </c>
-      <c r="E14" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A14,","), "-", ""), " ", "")</f>
-        <v>Fu</v>
+        <f t="shared" si="17"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f t="shared" si="18"/>
+        <v>DosSantos</v>
       </c>
       <c r="F14" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A14)),
-    IF(LEN(A14)-LEN(SUBSTITUTE(A14, ",", ""))&gt;=6, "etal", MID(A14, SEARCH("&amp; ", A14)+2, SEARCH(",", A14, SEARCH("&amp; ", A14)+2) - SEARCH("&amp; ", A14)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G14" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A14, "("), ")")</f>
-        <v>2013</v>
+      <c r="G14" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>2020</v>
       </c>
       <c r="H14" t="str">
-        <f>_xlfn.TEXTAFTER(A14,"https://doi.org/")</f>
-        <v>10.1007/s00429-012-0462-x</v>
+        <f t="shared" si="21"/>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D14,(SUBSTITUTE(SUBSTITUTE(J14," ",""), "_", ""))))</f>
-        <v>Fu_etal_2013_Table1</v>
-      </c>
-      <c r="L14" s="3" t="str">
-        <f>IF(ISBLANK(I14),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H14, SUBSTITUTE(J14,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I14, SUBSTITUTE(J14,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
+      <c r="K14" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>DosSantos_etal_2020_Table1</v>
+      </c>
+      <c r="L14" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="M14" t="str">
         <f t="array" ref="M14">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>358</v>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="S14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T14" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="U14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="V14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y14" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="AC14" s="13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="AA14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI14" s="13">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="C15" t="str">
-        <f>RIGHT(A15,1)</f>
-        <v>6</v>
+        <f t="shared" ref="C15" si="23">RIGHT(A15,1)</f>
+        <v>0</v>
       </c>
       <c r="D15" t="str">
-        <f>E15 &amp; IF(F15&lt;&gt;"", "_" &amp; F15, "_") &amp; IF(G15&lt;&gt;"", "_" &amp; G15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" ref="D15" si="24">E15 &amp; IF(F15&lt;&gt;"", "_" &amp; F15, "_") &amp; IF(G15&lt;&gt;"", "_" &amp; G15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
+        <v>DosSantos_etal_2020</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
-        <v>Garwicz</v>
+        <f t="shared" ref="E15" si="25">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
+        <v>DosSantos</v>
       </c>
       <c r="F15" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A15)),
+        <f t="shared" ref="F15" si="26">IF(ISNUMBER(FIND("&amp;", A15)),
     IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="G15" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
-        <v>2009</v>
+        <f t="shared" ref="G15" si="27">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
+        <v>2020</v>
       </c>
       <c r="H15" t="str">
-        <f>_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
-        <v>10.1073/pnas.0905777106</v>
+        <f t="shared" ref="H15" si="28">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" s="16" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D15,(SUBSTITUTE(SUBSTITUTE(J15," ",""), "_", ""))))</f>
-        <v>Garwicz_etal_2009_TableS1</v>
-      </c>
-      <c r="L15" s="16" t="str">
-        <f>IF(ISBLANK(I15),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1073%2Fpnas.0905777106_TableS1</v>
+        <v>372</v>
+      </c>
+      <c r="K15" s="1" t="str">
+        <f t="shared" ref="K15" si="29">TRIM(_xlfn.TEXTJOIN("_",FALSE,D15,(SUBSTITUTE(SUBSTITUTE(J15," ",""), "_", ""))))</f>
+        <v>DosSantos_etal_2020_unpublished</v>
+      </c>
+      <c r="L15" s="1" t="str">
+        <f t="shared" ref="L15" si="30">IF(ISBLANK(I15),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
       <c r="M15" t="str">
         <f t="array" ref="M15">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>361</v>
+      <c r="P15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R15" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="S15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T15" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X15" s="17" t="s">
-        <v>365</v>
+        <v>106</v>
+      </c>
+      <c r="V15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y15" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI15" s="13">
+        <v>4</v>
+      </c>
+      <c r="AK15" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C16" t="str">
-        <f>RIGHT(A16,1)</f>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D16" t="str">
-        <f>E16 &amp; IF(F16&lt;&gt;"", "_" &amp; F16, "_") &amp; IF(G16&lt;&gt;"", "_" &amp; G16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" si="17"/>
+        <v>Falcone_etal_2019</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
-        <v>Garwicz</v>
+        <f t="shared" si="18"/>
+        <v>Falcone</v>
       </c>
       <c r="F16" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A16)),
-    IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G16" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
-        <v>2009</v>
+        <f t="shared" si="20"/>
+        <v>2019</v>
       </c>
       <c r="H16" t="str">
-        <f>_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
-        <v>10.1073/pnas.0905777106</v>
+        <f t="shared" si="21"/>
+        <v>10.1002/cne.24605</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="K16" s="16" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D16,(SUBSTITUTE(SUBSTITUTE(J16," ",""), "_", ""))))</f>
-        <v>Garwicz_etal_2009_TableS2</v>
-      </c>
-      <c r="L16" s="16" t="str">
-        <f>IF(ISBLANK(I16),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H16, SUBSTITUTE(J16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I16, SUBSTITUTE(J16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1073%2Fpnas.0905777106_TableS2</v>
+        <v>152</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="22"/>
+        <v>Falcone_etal_2019_TABLE1</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M16" t="str">
         <f t="array" ref="M16">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>359</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="R16" s="14"/>
       <c r="U16" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W16" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X16" s="17" t="s">
-        <v>365</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C17" t="str">
-        <f>RIGHT(A17,1)</f>
-        <v>0</v>
+        <f t="shared" ref="C17" si="31">RIGHT(A17,1)</f>
+        <v>5</v>
       </c>
       <c r="D17" t="str">
-        <f>E17 &amp; IF(F17&lt;&gt;"", "_" &amp; F17, "_") &amp; IF(G17&lt;&gt;"", "_" &amp; G17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
-        <v>Genoud_etal_2018</v>
-      </c>
-      <c r="E17" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
-        <v>Genoud</v>
+        <f t="shared" ref="D17" si="32">E17 &amp; IF(F17&lt;&gt;"", "_" &amp; F17, "_") &amp; IF(G17&lt;&gt;"", "_" &amp; G17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <v>Falcone_etal_2019</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f t="shared" ref="E17" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <v>Falcone</v>
       </c>
       <c r="F17" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="F17" si="34">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="G17" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
-        <v>2018</v>
+      <c r="G17" s="2" t="str">
+        <f t="shared" ref="G17" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <v>2019</v>
       </c>
       <c r="H17" t="str">
-        <f>_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
-        <v>10.1111/brv.12350</v>
+        <f t="shared" ref="H17" si="36">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
+        <v>10.1002/cne.24605</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="K17" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D17,(SUBSTITUTE(SUBSTITUTE(J17," ",""), "_", ""))))</f>
-        <v>Genoud_etal_2018_TableS2</v>
-      </c>
-      <c r="L17" s="3" t="str">
-        <f>IF(ISBLANK(I17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1111%2Fbrv.12350_TableS2</v>
+        <v>158</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" ref="K17" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,D17,(SUBSTITUTE(SUBSTITUTE(J17," ",""), "_", ""))))</f>
+        <v>Falcone_etal_2019_TABLE2</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" ref="L17" si="38">IF(ISBLANK(I17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2Fcne.24605_TABLE2</v>
       </c>
       <c r="M17" t="str">
         <f t="array" ref="M17">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC17" s="13" t="s">
-        <v>282</v>
+        <v>368</v>
+      </c>
+      <c r="R17" s="14"/>
+      <c r="U17" s="13" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="C18" t="str">
-        <f>RIGHT(A18,1)</f>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>6</v>
       </c>
       <c r="D18" t="str">
-        <f>E18 &amp; IF(F18&lt;&gt;"", "_" &amp; F18, "_") &amp; IF(G18&lt;&gt;"", "_" &amp; G18, "_") &amp; IF(B18&lt;&gt;"", "_" &amp; B18, "")</f>
-        <v>Granatosky__2018</v>
-      </c>
-      <c r="E18" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A18,","), "-", ""), " ", "")</f>
-        <v>Granatosky</v>
+        <f t="shared" si="17"/>
+        <v>Finlay_etal_2006</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f t="shared" si="18"/>
+        <v>Finlay</v>
       </c>
       <c r="F18" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A18)),
-    IF(LEN(A18)-LEN(SUBSTITUTE(A18, ",", ""))&gt;=6, "etal", MID(A18, SEARCH("&amp; ", A18)+2, SEARCH(",", A18, SEARCH("&amp; ", A18)+2) - SEARCH("&amp; ", A18)-2)),
-    ""
-)</f>
-        <v/>
-      </c>
-      <c r="G18" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A18, "("), ")")</f>
-        <v>2018</v>
+        <f t="shared" si="19"/>
+        <v>etal</v>
+      </c>
+      <c r="G18" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>2006</v>
       </c>
       <c r="H18" t="str">
-        <f>_xlfn.TEXTAFTER(A18,"https://doi.org/")</f>
-        <v>10.1111/jzo.12608</v>
+        <f t="shared" si="21"/>
+        <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K18" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D18,(SUBSTITUTE(SUBSTITUTE(J18," ",""), "_", ""))))</f>
-        <v>Granatosky__2018_TableS1</v>
-      </c>
-      <c r="L18" s="3" t="str">
-        <f>IF(ISBLANK(I18),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H18, SUBSTITUTE(J18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I18, SUBSTITUTE(J18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1111%2Fjzo.12608_TableS1</v>
+        <v>110</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>Finlay_etal_2006_Table6.1</v>
+      </c>
+      <c r="L18" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M18" t="str">
         <f t="array" ref="M18">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>336</v>
-      </c>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+      </c>
+      <c r="N18" s="17"/>
       <c r="P18" s="13" t="s">
-        <v>125</v>
+        <v>74</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="S18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="U18" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="V18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X18" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD18" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI18" s="13">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="13">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>117</v>
+        <v>346</v>
       </c>
       <c r="C19" t="str">
-        <f>RIGHT(A19,1)</f>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>x</v>
       </c>
       <c r="D19" t="str">
-        <f>E19 &amp; IF(F19&lt;&gt;"", "_" &amp; F19, "_") &amp; IF(G19&lt;&gt;"", "_" &amp; G19, "_") &amp; IF(B19&lt;&gt;"", "_" &amp; B19, "")</f>
-        <v>Heffner_Masterton_1975</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A19,","), "-", ""), " ", "")</f>
-        <v>Heffner</v>
+        <f t="shared" si="17"/>
+        <v>Fu_etal_2013</v>
+      </c>
+      <c r="E19" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>Fu</v>
       </c>
       <c r="F19" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A19)),
-    IF(LEN(A19)-LEN(SUBSTITUTE(A19, ",", ""))&gt;=6, "etal", MID(A19, SEARCH("&amp; ", A19)+2, SEARCH(",", A19, SEARCH("&amp; ", A19)+2) - SEARCH("&amp; ", A19)-2)),
-    ""
-)</f>
-        <v>Masterton</v>
-      </c>
-      <c r="G19" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A19, "("), ")")</f>
-        <v>1975</v>
+        <f t="shared" si="19"/>
+        <v>etal</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>2013</v>
       </c>
       <c r="H19" t="str">
-        <f>_xlfn.TEXTAFTER(A19,"https://doi.org/")</f>
-        <v>10.1159/000124401</v>
+        <f t="shared" si="21"/>
+        <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K19" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D19,(SUBSTITUTE(SUBSTITUTE(J19," ",""), "_", ""))))</f>
-        <v>Heffner_Masterton_1975_TableI</v>
-      </c>
-      <c r="L19" s="1" t="str">
-        <f>IF(ISBLANK(I19),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H19, SUBSTITUTE(J19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I19, SUBSTITUTE(J19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000124401_TableI</v>
+        <v>52</v>
+      </c>
+      <c r="K19" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v>Fu_etal_2013_Table1</v>
+      </c>
+      <c r="L19" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M19" t="str">
         <f t="array" ref="M19">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000124401_TableI.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>358</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="S19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T19" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="U19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W19" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>122</v>
+        <v>283</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE19" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI19" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK19" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="C20" t="str">
-        <f>RIGHT(A20,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>6</v>
       </c>
       <c r="D20" t="str">
-        <f>E20 &amp; IF(F20&lt;&gt;"", "_" &amp; F20, "_") &amp; IF(G20&lt;&gt;"", "_" &amp; G20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
-        <v>Heffner_Masterton_1983</v>
+        <f t="shared" si="17"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
-        <v>Heffner</v>
+        <f t="shared" si="18"/>
+        <v>Garwicz</v>
       </c>
       <c r="F20" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A20)),
-    IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
-    ""
-)</f>
-        <v>Masterton</v>
+        <f t="shared" si="19"/>
+        <v>etal</v>
       </c>
       <c r="G20" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
-        <v>1983</v>
+        <f t="shared" si="20"/>
+        <v>2009</v>
       </c>
       <c r="H20" t="str">
-        <f>_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
-        <v>10.1159/000121494</v>
+        <f t="shared" si="21"/>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D20,(SUBSTITUTE(SUBSTITUTE(J20," ",""), "_", ""))))</f>
-        <v>Heffner_Masterton_1983_TableI</v>
-      </c>
-      <c r="L20" s="1" t="str">
-        <f>IF(ISBLANK(I20),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H20, SUBSTITUTE(J20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I20, SUBSTITUTE(J20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000121494_TableI</v>
+        <v>91</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="22"/>
+        <v>Garwicz_etal_2009_TableS1</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M20" t="str">
         <f t="array" ref="M20">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P20" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R20" s="14"/>
-      <c r="T20" s="13" t="str">
-        <f>IF(S20="N", R20, "write file name")</f>
-        <v>write file name</v>
+      <c r="N20" s="13" t="s">
+        <v>361</v>
       </c>
       <c r="U20" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V20" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="W20" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y20" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE20" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG20" s="13" t="s">
-        <v>126</v>
+        <v>68</v>
+      </c>
+      <c r="X20" s="16" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>127</v>
+        <v>360</v>
       </c>
       <c r="C21" t="str">
-        <f>RIGHT(A21,1)</f>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>6</v>
       </c>
       <c r="D21" t="str">
-        <f>E21 &amp; IF(F21&lt;&gt;"", "_" &amp; F21, "_") &amp; IF(G21&lt;&gt;"", "_" &amp; G21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
-        <v>Heldstab_etal_2016</v>
+        <f t="shared" si="17"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
-        <v>Heldstab</v>
+        <f t="shared" si="18"/>
+        <v>Garwicz</v>
       </c>
       <c r="F21" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A21)),
-    IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G21" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
-        <v>2016</v>
+        <f t="shared" si="20"/>
+        <v>2009</v>
       </c>
       <c r="H21" t="str">
-        <f>_xlfn.TEXTAFTER(A21,"https://doi.org/")</f>
-        <v>10.1038/srep24528</v>
+        <f t="shared" si="21"/>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K21" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D21,(SUBSTITUTE(SUBSTITUTE(J21," ",""), "_", ""))))</f>
-        <v>Heldstab_etal_2016_TableS1</v>
-      </c>
-      <c r="L21" s="1" t="str">
-        <f>IF(ISBLANK(I21),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H21, SUBSTITUTE(J21,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I21, SUBSTITUTE(J21,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fsrep24528_TableS1</v>
+        <v>220</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="22"/>
+        <v>Garwicz_etal_2009_TableS2</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M21" t="str">
         <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P21" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q21" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R21" s="14"/>
-      <c r="T21" s="13" t="str">
-        <f>IF(S21="N", R21, "write file name")</f>
-        <v>write file name</v>
+      <c r="N21" s="13" t="s">
+        <v>359</v>
       </c>
       <c r="U21" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V21" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y21" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE21" s="13" t="s">
-        <v>64</v>
+      <c r="W21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X21" s="16" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
-        <v>212</v>
+        <v>343</v>
       </c>
       <c r="C22" t="str">
-        <f>RIGHT(A22,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="D22" t="str">
-        <f>E22 &amp; IF(F22&lt;&gt;"", "_" &amp; F22, "_") &amp; IF(G22&lt;&gt;"", "_" &amp; G22, "_") &amp; IF(B22&lt;&gt;"", "_" &amp; B22, "")</f>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A22,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" si="17"/>
+        <v>Genoud_etal_2018</v>
+      </c>
+      <c r="E22" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>Genoud</v>
       </c>
       <c r="F22" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A22)),
-    IF(LEN(A22)-LEN(SUBSTITUTE(A22, ",", ""))&gt;=6, "etal", MID(A22, SEARCH("&amp; ", A22)+2, SEARCH(",", A22, SEARCH("&amp; ", A22)+2) - SEARCH("&amp; ", A22)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G22" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, "("), ")")</f>
-        <v>2013</v>
+      <c r="G22" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>2018</v>
       </c>
       <c r="H22" t="str">
-        <f>_xlfn.TEXTAFTER(A22,"https://doi.org/")</f>
-        <v>10.3389/fnana.2013.00035</v>
+        <f t="shared" si="21"/>
+        <v>10.1111/brv.12350</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="K22" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D22,(SUBSTITUTE(SUBSTITUTE(J22," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
-      </c>
-      <c r="L22" s="1" t="str">
-        <f>IF(ISBLANK(I22),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H22, SUBSTITUTE(J22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I22, SUBSTITUTE(J22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
+        <v>220</v>
+      </c>
+      <c r="K22" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v>Genoud_etal_2018_TableS2</v>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="M22" t="str">
         <f t="array" ref="M22">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI22" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC22" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
-        <v>212</v>
+        <v>349</v>
       </c>
       <c r="C23" t="str">
-        <f>RIGHT(A23,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>8</v>
       </c>
       <c r="D23" t="str">
-        <f>E23 &amp; IF(F23&lt;&gt;"", "_" &amp; F23, "_") &amp; IF(G23&lt;&gt;"", "_" &amp; G23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" si="17"/>
+        <v>Granatosky__2018</v>
+      </c>
+      <c r="E23" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>Granatosky</v>
       </c>
       <c r="F23" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A23)),
-    IF(LEN(A23)-LEN(SUBSTITUTE(A23, ",", ""))&gt;=6, "etal", MID(A23, SEARCH("&amp; ", A23)+2, SEARCH(",", A23, SEARCH("&amp; ", A23)+2) - SEARCH("&amp; ", A23)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="G23" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
-        <v>2013</v>
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="G23" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>2018</v>
       </c>
       <c r="H23" t="str">
-        <f>_xlfn.TEXTAFTER(A23,"https://doi.org/")</f>
-        <v>10.3389/fnana.2013.00035</v>
+        <f t="shared" si="21"/>
+        <v>10.1111/jzo.12608</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="K23" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D23,(SUBSTITUTE(SUBSTITUTE(J23," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
-      </c>
-      <c r="L23" s="1" t="str">
-        <f>IF(ISBLANK(I23),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H23, SUBSTITUTE(J23,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I23, SUBSTITUTE(J23,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+        <v>91</v>
+      </c>
+      <c r="K23" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v>Granatosky__2018_TableS1</v>
+      </c>
+      <c r="L23" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1111%2Fjzo.12608_TableS1</v>
       </c>
       <c r="M23" t="str">
         <f t="array" ref="M23">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI23" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="C24" t="str">
-        <f>RIGHT(A24,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="D24" t="str">
-        <f>E24 &amp; IF(F24&lt;&gt;"", "_" &amp; F24, "_") &amp; IF(G24&lt;&gt;"", "_" &amp; G24, "_") &amp; IF(B24&lt;&gt;"", "_" &amp; B24, "")</f>
-        <v>HerculanoHouzel_etal_2013</v>
+        <f t="shared" si="17"/>
+        <v>Heffner_Masterton_1975</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A24,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" si="18"/>
+        <v>Heffner</v>
       </c>
       <c r="F24" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A24)),
-    IF(LEN(A24)-LEN(SUBSTITUTE(A24, ",", ""))&gt;=6, "etal", MID(A24, SEARCH("&amp; ", A24)+2, SEARCH(",", A24, SEARCH("&amp; ", A24)+2) - SEARCH("&amp; ", A24)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="19"/>
+        <v>Masterton</v>
       </c>
       <c r="G24" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A24, "("), ")")</f>
-        <v>2013</v>
+        <f t="shared" si="20"/>
+        <v>1975</v>
       </c>
       <c r="H24" t="str">
-        <f>_xlfn.TEXTAFTER(A24,"https://doi.org/")</f>
-        <v>10.3389/fnana.2013.00035</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000124401</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="K24" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D24,(SUBSTITUTE(SUBSTITUTE(J24," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+        <f t="shared" si="22"/>
+        <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="L24" s="1" t="str">
-        <f>IF(ISBLANK(I24),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H24, SUBSTITUTE(J24,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I24, SUBSTITUTE(J24,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M24" t="str">
         <f t="array" ref="M24">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+        <v>10.1159%2F000124401_TableI.tsv</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI24" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="S24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T24" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="U24" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V24" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y24" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z24" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC24" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI24" s="13">
+        <v>7</v>
+      </c>
+      <c r="AK24" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C25" t="str">
-        <f>RIGHT(A25,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
-        <f>E25 &amp; IF(F25&lt;&gt;"", "_" &amp; F25, "_") &amp; IF(G25&lt;&gt;"", "_" &amp; G25, "_") &amp; IF(B25&lt;&gt;"", "_" &amp; B25, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="17"/>
+        <v>Heffner_Masterton_1983</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A25,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" si="18"/>
+        <v>Heffner</v>
       </c>
       <c r="F25" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A25)),
-    IF(LEN(A25)-LEN(SUBSTITUTE(A25, ",", ""))&gt;=6, "etal", MID(A25, SEARCH("&amp; ", A25)+2, SEARCH(",", A25, SEARCH("&amp; ", A25)+2) - SEARCH("&amp; ", A25)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="19"/>
+        <v>Masterton</v>
       </c>
       <c r="G25" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="20"/>
+        <v>1983</v>
       </c>
       <c r="H25" t="str">
-        <f>_xlfn.TEXTAFTER(A25,"https://doi.org/")</f>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000121494</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="K25" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D25,(SUBSTITUTE(SUBSTITUTE(J25," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2015_Table1</v>
+        <f t="shared" si="22"/>
+        <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="L25" s="1" t="str">
-        <f>IF(ISBLANK(I25),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H25, SUBSTITUTE(J25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I25, SUBSTITUTE(J25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000437413_Table1</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="M25" t="str">
         <f t="array" ref="M25">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>133</v>
+        <v>notfound</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R25" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="S25" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T25" s="13" t="s">
-        <v>131</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="14"/>
+      <c r="T25" s="13" t="str">
+        <f>IF(S25="N", R25, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U25" s="13" t="s">
         <v>57</v>
@@ -3509,93 +3457,71 @@
         <v>46</v>
       </c>
       <c r="W25" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X25" s="13" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="Y25" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA25" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB25" s="13" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="AE25" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI25" s="13">
-        <v>9</v>
-      </c>
-      <c r="AK25" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="AG25" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C26" t="str">
-        <f>RIGHT(A26,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>8</v>
       </c>
       <c r="D26" t="str">
-        <f>E26 &amp; IF(F26&lt;&gt;"", "_" &amp; F26, "_") &amp; IF(G26&lt;&gt;"", "_" &amp; G26, "_") &amp; IF(B26&lt;&gt;"", "_" &amp; B26, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="17"/>
+        <v>Heldstab_etal_2016</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A26,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" si="18"/>
+        <v>Heldstab</v>
       </c>
       <c r="F26" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A26)),
-    IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=6, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G26" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="20"/>
+        <v>2016</v>
       </c>
       <c r="H26" t="str">
-        <f>_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="21"/>
+        <v>10.1038/srep24528</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="K26" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D26,(SUBSTITUTE(SUBSTITUTE(J26," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2015_Table2</v>
+        <f t="shared" si="22"/>
+        <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="L26" s="1" t="str">
-        <f>IF(ISBLANK(I26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(J26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I26, SUBSTITUTE(J26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000437413_Table2</v>
+        <f t="shared" si="7"/>
+        <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="M26" t="str">
         <f t="array" ref="M26">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table2.tsv</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>138</v>
+        <v>notfound</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T26" s="13" t="s">
-        <v>137</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="14"/>
+      <c r="T26" s="13" t="str">
+        <f>IF(S26="N", R26, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U26" s="13" t="s">
         <v>57</v>
@@ -3603,364 +3529,208 @@
       <c r="V26" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X26" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="Y26" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA26" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB26" s="13" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="AE26" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI26" s="13">
-        <v>9</v>
-      </c>
-      <c r="AK26" s="13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="C27" t="str">
-        <f>RIGHT(A27,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D27" t="str">
-        <f>E27 &amp; IF(F27&lt;&gt;"", "_" &amp; F27, "_") &amp; IF(G27&lt;&gt;"", "_" &amp; G27, "_") &amp; IF(B27&lt;&gt;"", "_" &amp; B27, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A27,","), "-", ""), " ", "")</f>
+        <f t="shared" si="18"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="F27" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A27)),
-    IF(LEN(A27)-LEN(SUBSTITUTE(A27, ",", ""))&gt;=6, "etal", MID(A27, SEARCH("&amp; ", A27)+2, SEARCH(",", A27, SEARCH("&amp; ", A27)+2) - SEARCH("&amp; ", A27)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G27" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A27, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="20"/>
+        <v>2013</v>
       </c>
       <c r="H27" t="str">
-        <f>_xlfn.TEXTAFTER(A27,"https://doi.org/")</f>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="21"/>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
       <c r="K27" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D27,(SUBSTITUTE(SUBSTITUTE(J27," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2015_Table3</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="L27" s="1" t="str">
-        <f>IF(ISBLANK(I27),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H27, SUBSTITUTE(J27,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I27, SUBSTITUTE(J27,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000437413_Table3</v>
+        <f t="shared" si="7"/>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M27" t="str">
         <f t="array" ref="M27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table3.tsv</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>41</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R27" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="S27" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T27" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="U27" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V27" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W27" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X27" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y27" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA27" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB27" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE27" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI27" s="13">
-        <v>9</v>
-      </c>
-      <c r="AK27" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="AI27" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="C28" t="str">
-        <f>RIGHT(A28,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D28" t="str">
-        <f>E28 &amp; IF(F28&lt;&gt;"", "_" &amp; F28, "_") &amp; IF(G28&lt;&gt;"", "_" &amp; G28, "_") &amp; IF(B28&lt;&gt;"", "_" &amp; B28, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A28,","), "-", ""), " ", "")</f>
+        <f t="shared" si="18"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="F28" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A28)),
-    IF(LEN(A28)-LEN(SUBSTITUTE(A28, ",", ""))&gt;=6, "etal", MID(A28, SEARCH("&amp; ", A28)+2, SEARCH(",", A28, SEARCH("&amp; ", A28)+2) - SEARCH("&amp; ", A28)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G28" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A28, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="20"/>
+        <v>2013</v>
       </c>
       <c r="H28" t="str">
-        <f>_xlfn.TEXTAFTER(A28,"https://doi.org/")</f>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="21"/>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="K28" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D28,(SUBSTITUTE(SUBSTITUTE(J28," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2015_Table4</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="L28" s="1" t="str">
-        <f>IF(ISBLANK(I28),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H28, SUBSTITUTE(J28,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I28, SUBSTITUTE(J28,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000437413_Table4</v>
+        <f t="shared" si="7"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="M28" t="str">
         <f t="array" ref="M28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table4.tsv</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>41</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R28" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="S28" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T28" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="U28" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V28" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W28" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X28" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y28" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA28" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB28" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE28" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI28" s="13">
-        <v>8</v>
-      </c>
-      <c r="AK28" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="AI28" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="C29" t="str">
-        <f>RIGHT(A29,1)</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D29" t="str">
-        <f>E29 &amp; IF(F29&lt;&gt;"", "_" &amp; F29, "_") &amp; IF(G29&lt;&gt;"", "_" &amp; G29, "_") &amp; IF(B29&lt;&gt;"", "_" &amp; B29, "")</f>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="E29" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A29,","), "-", ""), " ", "")</f>
+        <f t="shared" si="18"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="F29" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A29)),
-    IF(LEN(A29)-LEN(SUBSTITUTE(A29, ",", ""))&gt;=6, "etal", MID(A29, SEARCH("&amp; ", A29)+2, SEARCH(",", A29, SEARCH("&amp; ", A29)+2) - SEARCH("&amp; ", A29)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G29" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A29, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="20"/>
+        <v>2013</v>
       </c>
       <c r="H29" t="str">
-        <f>_xlfn.TEXTAFTER(A29,"https://doi.org/")</f>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="21"/>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="K29" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D29,(SUBSTITUTE(SUBSTITUTE(J29," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2015_Table5</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="L29" s="1" t="str">
-        <f>IF(ISBLANK(I29),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H29, SUBSTITUTE(J29,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I29, SUBSTITUTE(J29,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000437413_Table5</v>
+        <f t="shared" si="7"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="M29" t="str">
         <f t="array" ref="M29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table5.tsv</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>41</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R29" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="S29" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T29" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="U29" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V29" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W29" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X29" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA29" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB29" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE29" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI29" s="13">
-        <v>9</v>
-      </c>
-      <c r="AK29" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="AI29" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C30" t="str">
-        <f>RIGHT(A30,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D30" t="str">
-        <f>E30 &amp; IF(F30&lt;&gt;"", "_" &amp; F30, "_") &amp; IF(G30&lt;&gt;"", "_" &amp; G30, "_") &amp; IF(B30&lt;&gt;"", "_" &amp; B30, "")</f>
-        <v>HerculanoHouzel_etal_2020</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A30,","), "-", ""), " ", "")</f>
+        <f t="shared" si="18"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="F30" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A30)),
-    IF(LEN(A30)-LEN(SUBSTITUTE(A30, ",", ""))&gt;=6, "etal", MID(A30, SEARCH("&amp; ", A30)+2, SEARCH(",", A30, SEARCH("&amp; ", A30)+2) - SEARCH("&amp; ", A30)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G30" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A30, "("), ")")</f>
-        <v>2020</v>
+        <f t="shared" si="20"/>
+        <v>2015</v>
       </c>
       <c r="H30" t="str">
-        <f>_xlfn.TEXTAFTER(A30,"https://doi.org/")</f>
-        <v>10.1002/cne.24985</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="K30" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D30,(SUBSTITUTE(SUBSTITUTE(J30," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2020_TABLE1</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="L30" s="1" t="str">
-        <f>IF(ISBLANK(I30),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H30, SUBSTITUTE(J30,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I30, SUBSTITUTE(J30,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1002%2Fcne.24985_TABLE1</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="M30" t="str">
         <f t="array" ref="M30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+        <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="P30" s="13" t="s">
         <v>41</v>
@@ -3969,13 +3739,13 @@
         <v>53</v>
       </c>
       <c r="R30" s="14" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>55</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="U30" s="13" t="s">
         <v>57</v>
@@ -3984,10 +3754,13 @@
         <v>46</v>
       </c>
       <c r="W30" s="13" t="s">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="X30" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="Y30" s="13" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="AA30" s="13" t="s">
         <v>100</v>
@@ -3996,66 +3769,60 @@
         <v>100</v>
       </c>
       <c r="AE30" s="13" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="AI30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C31" t="str">
-        <f>RIGHT(A31,1)</f>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D31" t="str">
-        <f>E31 &amp; IF(F31&lt;&gt;"", "_" &amp; F31, "_") &amp; IF(G31&lt;&gt;"", "_" &amp; G31, "_") &amp; IF(B31&lt;&gt;"", "_" &amp; B31, "")</f>
-        <v>HerculanoHouzel_etal_2020</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="E31" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A31,","), "-", ""), " ", "")</f>
+        <f t="shared" si="18"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="F31" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A31)),
-    IF(LEN(A31)-LEN(SUBSTITUTE(A31, ",", ""))&gt;=6, "etal", MID(A31, SEARCH("&amp; ", A31)+2, SEARCH(",", A31, SEARCH("&amp; ", A31)+2) - SEARCH("&amp; ", A31)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G31" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A31, "("), ")")</f>
-        <v>2020</v>
+        <f t="shared" si="20"/>
+        <v>2015</v>
       </c>
       <c r="H31" t="str">
-        <f>_xlfn.TEXTAFTER(A31,"https://doi.org/")</f>
-        <v>10.1002/cne.24985</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="K31" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D31,(SUBSTITUTE(SUBSTITUTE(J31," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="L31" s="1" t="str">
-        <f>IF(ISBLANK(I31),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H31, SUBSTITUTE(J31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I31, SUBSTITUTE(J31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1002%2Fcne.24985_TABLE2</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="M31" t="str">
         <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+        <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="P31" s="13" t="s">
         <v>41</v>
@@ -4064,13 +3831,13 @@
         <v>53</v>
       </c>
       <c r="R31" s="14" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="S31" s="13" t="s">
         <v>55</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="U31" s="13" t="s">
         <v>57</v>
@@ -4079,10 +3846,13 @@
         <v>46</v>
       </c>
       <c r="W31" s="13" t="s">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="X31" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="AA31" s="13" t="s">
         <v>100</v>
@@ -4091,293 +3861,473 @@
         <v>100</v>
       </c>
       <c r="AE31" s="13" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="AI31" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK31" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="C32" t="str">
-        <f>RIGHT(A32,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D32" t="str">
-        <f>E32 &amp; IF(F32&lt;&gt;"", "_" &amp; F32, "_") &amp; IF(G32&lt;&gt;"", "_" &amp; G32, "_") &amp; IF(B32&lt;&gt;"", "_" &amp; B32, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="E32" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A32,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="F32" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A32)),
-    IF(LEN(A32)-LEN(SUBSTITUTE(A32, ",", ""))&gt;=6, "etal", MID(A32, SEARCH("&amp; ", A32)+2, SEARCH(",", A32, SEARCH("&amp; ", A32)+2) - SEARCH("&amp; ", A32)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G32" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A32, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" si="20"/>
+        <v>2015</v>
       </c>
       <c r="H32" t="str">
-        <f>_xlfn.TEXTAFTER(A32,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K32" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D32,(SUBSTITUTE(SUBSTITUTE(J32," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Table2</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="L32" s="1" t="str">
-        <f>IF(ISBLANK(I32),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H32, SUBSTITUTE(J32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I32, SUBSTITUTE(J32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="M32" t="str">
         <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.1159%2F000437413_Table3.tsv</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q32" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T32" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U32" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V32" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W32" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X32" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y32" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA32" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE32" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="AI32" s="13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AK32" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="C33" t="str">
-        <f>RIGHT(A33,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D33" t="str">
-        <f>E33 &amp; IF(F33&lt;&gt;"", "_" &amp; F33, "_") &amp; IF(G33&lt;&gt;"", "_" &amp; G33, "_") &amp; IF(B33&lt;&gt;"", "_" &amp; B33, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="E33" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A33,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="F33" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A33)),
-    IF(LEN(A33)-LEN(SUBSTITUTE(A33, ",", ""))&gt;=6, "etal", MID(A33, SEARCH("&amp; ", A33)+2, SEARCH(",", A33, SEARCH("&amp; ", A33)+2) - SEARCH("&amp; ", A33)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G33" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A33, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" si="20"/>
+        <v>2015</v>
       </c>
       <c r="H33" t="str">
-        <f>_xlfn.TEXTAFTER(A33,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c r="K33" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D33,(SUBSTITUTE(SUBSTITUTE(J33," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Table7</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="L33" s="1" t="str">
-        <f>IF(ISBLANK(I33),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H33, SUBSTITUTE(J33,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I33, SUBSTITUTE(J33,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="M33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+        <v>10.1159%2F000437413_Table4.tsv</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R33" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="S33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T33" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="U33" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V33" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W33" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X33" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA33" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB33" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE33" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="AI33" s="13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AK33" s="13">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="C34" t="str">
-        <f>RIGHT(A34,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="D34" t="str">
-        <f>E34 &amp; IF(F34&lt;&gt;"", "_" &amp; F34, "_") &amp; IF(G34&lt;&gt;"", "_" &amp; G34, "_") &amp; IF(B34&lt;&gt;"", "_" &amp; B34, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="E34" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A34,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="F34" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A34)),
-    IF(LEN(A34)-LEN(SUBSTITUTE(A34, ",", ""))&gt;=6, "etal", MID(A34, SEARCH("&amp; ", A34)+2, SEARCH(",", A34, SEARCH("&amp; ", A34)+2) - SEARCH("&amp; ", A34)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G34" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" si="20"/>
+        <v>2015</v>
       </c>
       <c r="H34" t="str">
-        <f>_xlfn.TEXTAFTER(A34,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="21"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="K34" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D34,(SUBSTITUTE(SUBSTITUTE(J34," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS1</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="L34" s="1" t="str">
-        <f>IF(ISBLANK(I34),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H34, SUBSTITUTE(J34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I34, SUBSTITUTE(J34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="M34" t="str">
         <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
+        <v>10.1159%2F000437413_Table5.tsv</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI34" s="13" t="s">
-        <v>219</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T34" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="U34" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V34" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W34" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X34" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y34" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE34" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI34" s="13">
+        <v>9</v>
+      </c>
+      <c r="AK34" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="C35" t="str">
-        <f>RIGHT(A35,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D35" t="str">
-        <f>E35 &amp; IF(F35&lt;&gt;"", "_" &amp; F35, "_") &amp; IF(G35&lt;&gt;"", "_" &amp; G35, "_") &amp; IF(B35&lt;&gt;"", "_" &amp; B35, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="E35" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A35,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="F35" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A35)),
-    IF(LEN(A35)-LEN(SUBSTITUTE(A35, ",", ""))&gt;=6, "etal", MID(A35, SEARCH("&amp; ", A35)+2, SEARCH(",", A35, SEARCH("&amp; ", A35)+2) - SEARCH("&amp; ", A35)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G35" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A35, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" si="20"/>
+        <v>2020</v>
       </c>
       <c r="H35" t="str">
-        <f>_xlfn.TEXTAFTER(A35,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="21"/>
+        <v>10.1002/cne.24985</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="K35" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D35,(SUBSTITUTE(SUBSTITUTE(J35," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS2</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L35" s="1" t="str">
-        <f>IF(ISBLANK(I35),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H35, SUBSTITUTE(J35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I35, SUBSTITUTE(J35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
+        <f t="shared" si="7"/>
+        <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M35" t="str">
         <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q35" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R35" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="S35" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T35" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="U35" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V35" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y35" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE35" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="AI35" s="13">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="13">
+        <v>0</v>
       </c>
       <c r="AK35" s="13">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="C36" t="str">
-        <f>RIGHT(A36,1)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="D36" t="str">
-        <f>E36 &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "_") &amp; IF(G36&lt;&gt;"", "_" &amp; G36, "_") &amp; IF(B36&lt;&gt;"", "_" &amp; B36, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="17"/>
+        <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="E36" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="F36" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A36)),
-    IF(LEN(A36)-LEN(SUBSTITUTE(A36, ",", ""))&gt;=6, "etal", MID(A36, SEARCH("&amp; ", A36)+2, SEARCH(",", A36, SEARCH("&amp; ", A36)+2) - SEARCH("&amp; ", A36)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
       <c r="G36" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" si="20"/>
+        <v>2020</v>
       </c>
       <c r="H36" t="str">
-        <f>_xlfn.TEXTAFTER(A36,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="21"/>
+        <v>10.1002/cne.24985</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="K36" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D36,(SUBSTITUTE(SUBSTITUTE(J36," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS3</v>
+        <f t="shared" si="22"/>
+        <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="L36" s="1" t="str">
-        <f>IF(ISBLANK(I36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(J36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I36, SUBSTITUTE(J36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+        <f t="shared" si="7"/>
+        <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="M36" t="str">
         <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q36" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R36" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="S36" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T36" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="U36" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V36" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y36" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE36" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="AI36" s="13">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="13">
+        <v>0</v>
       </c>
       <c r="AK36" s="13">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4385,1483 +4335,1336 @@
         <v>217</v>
       </c>
       <c r="C37" t="str">
-        <f>RIGHT(A37,1)</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="D37" t="str">
-        <f>E37 &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "_") &amp; IF(G37&lt;&gt;"", "_" &amp; G37, "_") &amp; IF(B37&lt;&gt;"", "_" &amp; B37, "")</f>
+        <f t="shared" si="17"/>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="E37" s="5" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+      <c r="E37" s="2" t="str">
+        <f t="shared" si="18"/>
         <v>Isler</v>
       </c>
       <c r="F37" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A37)),
-    IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=6, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G37" s="5" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+      <c r="G37" s="2" t="str">
+        <f t="shared" si="20"/>
         <v>2008</v>
       </c>
-      <c r="H37" s="4" t="str">
-        <f>_xlfn.TEXTAFTER(A37,"https://doi.org/")</f>
+      <c r="H37" t="str">
+        <f t="shared" si="21"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="K37" s="4" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D37,(SUBSTITUTE(SUBSTITUTE(J37," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
-      </c>
-      <c r="L37" s="6" t="str">
-        <f>IF(ISBLANK(I37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(J37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I37, SUBSTITUTE(J37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
+        <v>135</v>
+      </c>
+      <c r="K37" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>Isler_etal_2008_Table2</v>
+      </c>
+      <c r="L37" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="M37" t="str">
         <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="Q37" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="AI37" s="13">
+        <v>6</v>
+      </c>
+      <c r="AK37" s="13">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
-        <v>342</v>
+        <v>217</v>
       </c>
       <c r="C38" t="str">
-        <f>RIGHT(A38,1)</f>
-        <v>x</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="D38" t="str">
-        <f>E38 &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "_") &amp; IF(G38&lt;&gt;"", "_" &amp; G38, "_") &amp; IF(B38&lt;&gt;"", "_" &amp; B38, "")</f>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="E38" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
-        <v>Iwaniuk</v>
+        <f t="shared" si="17"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f t="shared" si="18"/>
+        <v>Isler</v>
       </c>
       <c r="F38" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A38)),
-    IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=6, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
-    ""
-)</f>
+        <f t="shared" si="19"/>
         <v>etal</v>
       </c>
-      <c r="G38" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
-        <v>1999</v>
+      <c r="G38" s="2" t="str">
+        <f t="shared" si="20"/>
+        <v>2008</v>
       </c>
       <c r="H38" t="str">
-        <f>_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" si="21"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="K38" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D38,(SUBSTITUTE(SUBSTITUTE(J38," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_1999_References</v>
-      </c>
-      <c r="L38" s="3" t="str">
-        <f>IF(ISBLANK(I38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(J38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I38, SUBSTITUTE(J38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
+        <v>218</v>
+      </c>
+      <c r="K38" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v>Isler_etal_2008_Table7</v>
+      </c>
+      <c r="L38" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
       <c r="M38" t="str">
         <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N38" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="P38" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="V38" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="W38" s="13" t="s">
-        <v>78</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI38" s="13">
+        <v>3</v>
+      </c>
+      <c r="AK38" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="13" t="s">
-        <v>342</v>
+        <v>217</v>
       </c>
       <c r="C39" t="str">
-        <f>RIGHT(A39,1)</f>
-        <v>x</v>
+        <f t="shared" ref="C39:C69" si="39">RIGHT(A39,1)</f>
+        <v>4</v>
       </c>
       <c r="D39" t="str">
-        <f>E39 &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "_") &amp; IF(G39&lt;&gt;"", "_" &amp; G39, "_") &amp; IF(B39&lt;&gt;"", "_" &amp; B39, "")</f>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="E39" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
-        <v>Iwaniuk</v>
+        <f t="shared" ref="D39:D69" si="40">E39 &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "_") &amp; IF(G39&lt;&gt;"", "_" &amp; G39, "_") &amp; IF(B39&lt;&gt;"", "_" &amp; B39, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f t="shared" ref="E39:E69" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
       </c>
       <c r="F39" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A39)),
+        <f t="shared" ref="F39:F69" si="42">IF(ISNUMBER(FIND("&amp;", A39)),
     IF(LEN(A39)-LEN(SUBSTITUTE(A39, ",", ""))&gt;=6, "etal", MID(A39, SEARCH("&amp; ", A39)+2, SEARCH(",", A39, SEARCH("&amp; ", A39)+2) - SEARCH("&amp; ", A39)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="G39" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
-        <v>1999</v>
+      <c r="G39" s="2" t="str">
+        <f t="shared" ref="G39:G69" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
+        <v>2008</v>
       </c>
       <c r="H39" t="str">
-        <f>_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" ref="H39:H69" si="44">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K39" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D39,(SUBSTITUTE(SUBSTITUTE(J39," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_1999_Table1</v>
-      </c>
-      <c r="L39" s="3" t="str">
-        <f>IF(ISBLANK(I39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
+        <v>91</v>
+      </c>
+      <c r="K39" s="1" t="str">
+        <f t="shared" ref="K39:K69" si="45">TRIM(_xlfn.TEXTJOIN("_",FALSE,D39,(SUBSTITUTE(SUBSTITUTE(J39," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_TableS1</v>
+      </c>
+      <c r="L39" s="1" t="str">
+        <f t="shared" ref="L39:L69" si="46">IF(ISBLANK(I39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
       <c r="M39" t="str">
         <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N39" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="P39" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="V39" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W39" s="13" t="s">
-        <v>78</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI39" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C40" t="str">
-        <f>RIGHT(A40,1)</f>
-        <v>9</v>
+        <f t="shared" si="39"/>
+        <v>4</v>
       </c>
       <c r="D40" t="str">
-        <f>E40 &amp; IF(F40&lt;&gt;"", "_" &amp; F40, "_") &amp; IF(G40&lt;&gt;"", "_" &amp; G40, "_") &amp; IF(B40&lt;&gt;"", "_" &amp; B40, "")</f>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="40"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="E40" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A40,","), "-", ""), " ", "")</f>
-        <v>Iwaniuk</v>
+        <f t="shared" si="41"/>
+        <v>Isler</v>
       </c>
       <c r="F40" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A40)),
-    IF(LEN(A40)-LEN(SUBSTITUTE(A40, ",", ""))&gt;=6, "etal", MID(A40, SEARCH("&amp; ", A40)+2, SEARCH(",", A40, SEARCH("&amp; ", A40)+2) - SEARCH("&amp; ", A40)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G40" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A40, "("), ")")</f>
-        <v>2001</v>
+        <f t="shared" si="43"/>
+        <v>2008</v>
       </c>
       <c r="H40" t="str">
-        <f>_xlfn.TEXTAFTER(A40,"https://doi.org/")</f>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="44"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="K40" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D40,(SUBSTITUTE(SUBSTITUTE(J40," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_2001_Table1</v>
+        <f t="shared" si="45"/>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L40" s="1" t="str">
-        <f>IF(ISBLANK(I40),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H40, SUBSTITUTE(J40,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I40, SUBSTITUTE(J40,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+        <f t="shared" si="46"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M40" t="str">
         <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N40" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="P40" s="13" t="s">
-        <v>164</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="Q40" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R40" s="14"/>
-      <c r="T40" s="13" t="str">
-        <f>IF(S40="N", R40, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U40" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V40" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y40" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE40" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
+      </c>
+      <c r="AI40" s="13">
+        <v>8</v>
+      </c>
+      <c r="AK40" s="13">
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C41" t="str">
-        <f>RIGHT(A41,1)</f>
-        <v>9</v>
+        <f t="shared" si="39"/>
+        <v>4</v>
       </c>
       <c r="D41" t="str">
-        <f>E41 &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "_") &amp; IF(G41&lt;&gt;"", "_" &amp; G41, "_") &amp; IF(B41&lt;&gt;"", "_" &amp; B41, "")</f>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="40"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="E41" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
-        <v>Iwaniuk</v>
+        <f t="shared" si="41"/>
+        <v>Isler</v>
       </c>
       <c r="F41" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A41)),
-    IF(LEN(A41)-LEN(SUBSTITUTE(A41, ",", ""))&gt;=6, "etal", MID(A41, SEARCH("&amp; ", A41)+2, SEARCH(",", A41, SEARCH("&amp; ", A41)+2) - SEARCH("&amp; ", A41)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G41" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
-        <v>2001</v>
+        <f t="shared" si="43"/>
+        <v>2008</v>
       </c>
       <c r="H41" t="str">
-        <f>_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="44"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="K41" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D41,(SUBSTITUTE(SUBSTITUTE(J41," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_2001_Table2</v>
+        <f t="shared" si="45"/>
+        <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L41" s="1" t="str">
-        <f>IF(ISBLANK(I41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(J41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I41, SUBSTITUTE(J41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+        <f t="shared" si="46"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M41" t="str">
         <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N41" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="P41" s="13" t="s">
-        <v>164</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="Q41" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R41" s="14"/>
-      <c r="T41" s="13" t="str">
-        <f>IF(S41="N", R41, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U41" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V41" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y41" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE41" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
+      </c>
+      <c r="AI41" s="13">
+        <v>7</v>
+      </c>
+      <c r="AK41" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C42" t="str">
-        <f>RIGHT(A42,1)</f>
-        <v>9</v>
+        <f t="shared" si="39"/>
+        <v>4</v>
       </c>
       <c r="D42" t="str">
-        <f>E42 &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "_") &amp; IF(G42&lt;&gt;"", "_" &amp; G42, "_") &amp; IF(B42&lt;&gt;"", "_" &amp; B42, "")</f>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
-        <v>Iwaniuk</v>
+        <f t="shared" si="40"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="E42" s="5" t="str">
+        <f t="shared" si="41"/>
+        <v>Isler</v>
       </c>
       <c r="F42" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A42)),
-    IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=6, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G42" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
-        <v>2001</v>
-      </c>
-      <c r="H42" t="str">
-        <f>_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
-        <v>10.1037/0735-7036.115.1.29</v>
+      <c r="G42" s="5" t="str">
+        <f t="shared" si="43"/>
+        <v>2008</v>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="K42" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D42,(SUBSTITUTE(SUBSTITUTE(J42," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_2001_Table3</v>
-      </c>
-      <c r="L42" s="1" t="str">
-        <f>IF(ISBLANK(I42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(J42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I42, SUBSTITUTE(J42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+        <v>222</v>
+      </c>
+      <c r="K42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>Isler_etal_2008_Tree.nex</v>
+      </c>
+      <c r="L42" s="6" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M42" t="str">
         <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N42" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="P42" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="Q42" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42" s="14"/>
-      <c r="T42" s="13" t="str">
-        <f>IF(S42="N", R42, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U42" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V42" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y42" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE42" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
-        <v>163</v>
+        <v>342</v>
       </c>
       <c r="C43" t="str">
-        <f>RIGHT(A43,1)</f>
-        <v>9</v>
+        <f t="shared" si="39"/>
+        <v>x</v>
       </c>
       <c r="D43" t="str">
-        <f>E43 &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "_") &amp; IF(G43&lt;&gt;"", "_" &amp; G43, "_") &amp; IF(B43&lt;&gt;"", "_" &amp; B43, "")</f>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="E43" s="7" t="str">
+        <f t="shared" si="41"/>
         <v>Iwaniuk</v>
       </c>
       <c r="F43" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A43)),
-    IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=6, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G43" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
-        <v>2001</v>
+      <c r="G43" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>1999</v>
       </c>
       <c r="H43" t="str">
-        <f>_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="44"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="K43" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D43,(SUBSTITUTE(SUBSTITUTE(J43," ",""), "_", ""))))</f>
-        <v>Iwaniuk_etal_2001_Table4</v>
-      </c>
-      <c r="L43" s="1" t="str">
-        <f>IF(ISBLANK(I43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(J43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I43, SUBSTITUTE(J43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
+        <v>339</v>
+      </c>
+      <c r="K43" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_1999_References</v>
+      </c>
+      <c r="L43" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M43" t="str">
         <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>170</v>
+        <v>339</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q43" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R43" s="14"/>
-      <c r="T43" s="13" t="str">
-        <f>IF(S43="N", R43, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U43" s="13" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="V43" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y43" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE43" s="13" t="s">
-        <v>167</v>
+        <v>341</v>
+      </c>
+      <c r="W43" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="C44" t="str">
-        <f>RIGHT(A44,1)</f>
-        <v>8</v>
+        <f t="shared" si="39"/>
+        <v>x</v>
       </c>
       <c r="D44" t="str">
-        <f>E44 &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "_") &amp; IF(G44&lt;&gt;"", "_" &amp; G44, "_") &amp; IF(B44&lt;&gt;"", "_" &amp; B44, "")</f>
-        <v>JardimMesseder_etal_2017</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
-        <v>JardimMesseder</v>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="E44" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F44" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A44)),
-    IF(LEN(A44)-LEN(SUBSTITUTE(A44, ",", ""))&gt;=6, "etal", MID(A44, SEARCH("&amp; ", A44)+2, SEARCH(",", A44, SEARCH("&amp; ", A44)+2) - SEARCH("&amp; ", A44)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G44" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
-        <v>2017</v>
+      <c r="G44" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>1999</v>
       </c>
       <c r="H44" t="str">
-        <f>_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
-        <v>10.3389/fnana.2017.00118</v>
+        <f t="shared" si="44"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="J44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K44" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D44,(SUBSTITUTE(SUBSTITUTE(J44," ",""), "_", ""))))</f>
-        <v>JardimMesseder_etal_2017_Table1</v>
-      </c>
-      <c r="L44" s="1" t="str">
-        <f>IF(ISBLANK(I44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(J44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I44, SUBSTITUTE(J44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+      <c r="K44" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_1999_Table1</v>
+      </c>
+      <c r="L44" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M44" t="str">
         <f t="array" ref="M44">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q44" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R44" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="S44" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T44" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="U44" s="13" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="V44" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W44" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X44" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y44" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z44" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA44" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB44" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE44" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI44" s="13">
-        <v>2</v>
-      </c>
-      <c r="AK44" s="13">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C45" t="str">
-        <f>RIGHT(A45,1)</f>
-        <v>8</v>
+        <f t="shared" si="39"/>
+        <v>9</v>
       </c>
       <c r="D45" t="str">
-        <f>E45 &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "_") &amp; IF(G45&lt;&gt;"", "_" &amp; G45, "_") &amp; IF(B45&lt;&gt;"", "_" &amp; B45, "")</f>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E45" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
-        <v>Kverkova</v>
+        <f t="shared" si="41"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F45" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A45)),
-    IF(LEN(A45)-LEN(SUBSTITUTE(A45, ",", ""))&gt;=6, "etal", MID(A45, SEARCH("&amp; ", A45)+2, SEARCH(",", A45, SEARCH("&amp; ", A45)+2) - SEARCH("&amp; ", A45)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G45" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
-        <v>2018</v>
+        <f t="shared" si="43"/>
+        <v>2001</v>
       </c>
       <c r="H45" t="str">
-        <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="44"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J45" s="13" t="s">
         <v>52</v>
       </c>
       <c r="K45" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D45,(SUBSTITUTE(SUBSTITUTE(J45," ",""), "_", ""))))</f>
-        <v>Kverkova_etal_2018_Table1</v>
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="L45" s="1" t="str">
-        <f>IF(ISBLANK(I45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+        <f t="shared" si="46"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M45" t="str">
         <f t="array" ref="M45">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N45" s="13" t="s">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R45" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="S45" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T45" s="13" t="s">
-        <v>178</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="14"/>
+      <c r="T45" s="13" t="str">
+        <f>IF(S45="N", R45, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U45" s="13" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="V45" s="13" t="s">
         <v>46</v>
       </c>
       <c r="Y45" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z45" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB45" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE45" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI45" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK45" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C46" t="str">
-        <f>RIGHT(A46,1)</f>
-        <v>8</v>
+        <f t="shared" si="39"/>
+        <v>9</v>
       </c>
       <c r="D46" t="str">
-        <f>E46 &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "_") &amp; IF(G46&lt;&gt;"", "_" &amp; G46, "_") &amp; IF(B46&lt;&gt;"", "_" &amp; B46, "")</f>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E46" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
-        <v>Kverkova</v>
+        <f t="shared" si="41"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F46" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A46)),
-    IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=6, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G46" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
-        <v>2018</v>
+        <f t="shared" si="43"/>
+        <v>2001</v>
       </c>
       <c r="H46" t="str">
-        <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="44"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="K46" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D46,(SUBSTITUTE(SUBSTITUTE(J46," ",""), "_", ""))))</f>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="L46" s="1" t="str">
-        <f>IF(ISBLANK(I46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(J46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I46, SUBSTITUTE(J46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <f t="shared" si="46"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M46" t="str">
         <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N46" s="13" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R46" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="S46" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T46" s="13" t="s">
-        <v>178</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="14"/>
+      <c r="T46" s="13" t="str">
+        <f>IF(S46="N", R46, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U46" s="13" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="V46" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W46" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X46" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="Y46" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z46" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB46" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE46" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI46" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK46" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C47" t="str">
-        <f>RIGHT(A47,1)</f>
-        <v>8</v>
+        <f t="shared" si="39"/>
+        <v>9</v>
       </c>
       <c r="D47" t="str">
-        <f>E47 &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "_") &amp; IF(G47&lt;&gt;"", "_" &amp; G47, "_") &amp; IF(B47&lt;&gt;"", "_" &amp; B47, "")</f>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E47" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
-        <v>Kverkova</v>
+        <f t="shared" si="41"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F47" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A47)),
-    IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=6, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G47" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
-        <v>2018</v>
+        <f t="shared" si="43"/>
+        <v>2001</v>
       </c>
       <c r="H47" t="str">
-        <f>_xlfn.TEXTAFTER(A47,"https://doi.org/")</f>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="44"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="K47" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D47,(SUBSTITUTE(SUBSTITUTE(J47," ",""), "_", ""))))</f>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="L47" s="1" t="str">
-        <f>IF(ISBLANK(I47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(J47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I47, SUBSTITUTE(J47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <f t="shared" si="46"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M47" t="str">
         <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N47" s="13" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q47" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R47" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S47" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T47" s="13" t="s">
-        <v>185</v>
+        <v>35</v>
+      </c>
+      <c r="R47" s="14"/>
+      <c r="T47" s="13" t="str">
+        <f>IF(S47="N", R47, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U47" s="13" t="s">
-        <v>186</v>
+        <v>57</v>
       </c>
       <c r="V47" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W47" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X47" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="Y47" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z47" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB47" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE47" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI47" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK47" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="C48" t="str">
-        <f>RIGHT(A48,1)</f>
-        <v>4</v>
+        <f t="shared" si="39"/>
+        <v>9</v>
       </c>
       <c r="D48" t="str">
-        <f>E48 &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "_") &amp; IF(G48&lt;&gt;"", "_" &amp; G48, "_") &amp; IF(B48&lt;&gt;"", "_" &amp; B48, "")</f>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="E48" s="5" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
-        <v>Lewitus</v>
+        <f t="shared" si="40"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F48" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A48)),
-    IF(LEN(A48)-LEN(SUBSTITUTE(A48, ",", ""))&gt;=6, "etal", MID(A48, SEARCH("&amp; ", A48)+2, SEARCH(",", A48, SEARCH("&amp; ", A48)+2) - SEARCH("&amp; ", A48)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G48" s="5" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
-        <v>2013</v>
-      </c>
-      <c r="H48" s="4" t="str">
-        <f>_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
-        <v>10.3389/fnhum.2013.00424</v>
+      <c r="G48" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2001</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K48" s="4" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D48,(SUBSTITUTE(SUBSTITUTE(J48," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2013_TableS2partial</v>
-      </c>
-      <c r="L48" s="6" t="str">
-        <f>IF(ISBLANK(I48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(J48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I48, SUBSTITUTE(J48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+        <v>143</v>
+      </c>
+      <c r="K48" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Iwaniuk_etal_2001_Table4</v>
+      </c>
+      <c r="L48" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M48" t="str">
         <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N48" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="P48" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="Q48" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA48" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="AI48" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK48" s="13">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="14"/>
+      <c r="T48" s="13" t="str">
+        <f>IF(S48="N", R48, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U48" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V48" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y48" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE48" s="13" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="13" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="C49" t="str">
-        <f>RIGHT(A49,1)</f>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>8</v>
       </c>
       <c r="D49" t="str">
-        <f>E49 &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "_") &amp; IF(G49&lt;&gt;"", "_" &amp; G49, "_") &amp; IF(B49&lt;&gt;"", "_" &amp; B49, "")</f>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="40"/>
+        <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="E49" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
-        <v>Lewitus</v>
+        <f t="shared" si="41"/>
+        <v>JardimMesseder</v>
       </c>
       <c r="F49" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A49)),
-    IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=6, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G49" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
-        <v>2014</v>
+        <f t="shared" si="43"/>
+        <v>2017</v>
       </c>
       <c r="H49" t="str">
-        <f>_xlfn.TEXTAFTER(A49,"https://doi.org/")</f>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="44"/>
+        <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="K49" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D49,(SUBSTITUTE(SUBSTITUTE(J49," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2014_TableS1</v>
+        <f t="shared" si="45"/>
+        <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="L49" s="1" t="str">
-        <f>IF(ISBLANK(I49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(J49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I49, SUBSTITUTE(J49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <f t="shared" si="46"/>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="M49" t="str">
         <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>269</v>
+        <v>175</v>
+      </c>
+      <c r="P49" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q49" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="S49" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T49" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="U49" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V49" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W49" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X49" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y49" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z49" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="AA49" s="13" t="s">
-        <v>270</v>
+        <v>100</v>
+      </c>
+      <c r="AB49" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE49" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="AI49" s="13">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AK49" s="13">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C50" t="str">
-        <f>RIGHT(A50,1)</f>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>8</v>
       </c>
       <c r="D50" t="str">
-        <f>E50 &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "_") &amp; IF(G50&lt;&gt;"", "_" &amp; G50, "_") &amp; IF(B50&lt;&gt;"", "_" &amp; B50, "")</f>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="40"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="E50" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
-        <v>Lewitus</v>
+        <f t="shared" si="41"/>
+        <v>Kverkova</v>
       </c>
       <c r="F50" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A50)),
-    IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G50" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
-        <v>2014</v>
+        <f t="shared" si="43"/>
+        <v>2018</v>
       </c>
       <c r="H50" t="str">
-        <f>_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="44"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="K50" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D50,(SUBSTITUTE(SUBSTITUTE(J50," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <f t="shared" si="45"/>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L50" s="1" t="str">
-        <f>IF(ISBLANK(I50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(J50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I50, SUBSTITUTE(J50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <f t="shared" si="46"/>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M50" t="str">
         <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>225</v>
+        <v>264</v>
+      </c>
+      <c r="P50" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q50" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA50" s="13" t="s">
-        <v>270</v>
+        <v>53</v>
+      </c>
+      <c r="R50" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="S50" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T50" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="U50" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="V50" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y50" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z50" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB50" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE50" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="AI50" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK50" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C51" t="str">
-        <f>RIGHT(A51,1)</f>
-        <v>5</v>
+        <f t="shared" si="39"/>
+        <v>8</v>
       </c>
       <c r="D51" t="str">
-        <f>E51 &amp; IF(F51&lt;&gt;"", "_" &amp; F51, "_") &amp; IF(G51&lt;&gt;"", "_" &amp; G51, "_") &amp; IF(B51&lt;&gt;"", "_" &amp; B51, "")</f>
-        <v>MacLarnon__1996</v>
-      </c>
-      <c r="E51" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A51,","), "-", ""), " ", "")</f>
-        <v>MacLarnon</v>
+        <f t="shared" si="40"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Kverkova</v>
       </c>
       <c r="F51" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A51)),
-    IF(LEN(A51)-LEN(SUBSTITUTE(A51, ",", ""))&gt;=6, "etal", MID(A51, SEARCH("&amp; ", A51)+2, SEARCH(",", A51, SEARCH("&amp; ", A51)+2) - SEARCH("&amp; ", A51)-2)),
-    ""
-)</f>
-        <v/>
-      </c>
-      <c r="G51" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A51, "("), ")")</f>
-        <v>1996</v>
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G51" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2018</v>
       </c>
       <c r="H51" t="str">
-        <f>_xlfn.TEXTAFTER(A51,"https://doi.org/")</f>
-        <v>10.1006/jhev.1996.0005</v>
+        <f t="shared" si="44"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K51" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D51,(SUBSTITUTE(SUBSTITUTE(J51," ",""), "_", ""))))</f>
-        <v>MacLarnon__1996_Table1</v>
-      </c>
-      <c r="L51" s="3" t="str">
-        <f>IF(ISBLANK(I51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <v>91</v>
+      </c>
+      <c r="K51" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Kverkova_etal_2018_TableS1</v>
+      </c>
+      <c r="L51" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M51" t="str">
         <f t="array" ref="M51">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N51" s="13" t="s">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="Q51" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R51" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="S51" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T51" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="U51" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="V51" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W51" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X51" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y51" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z51" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB51" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE51" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI51" s="13">
+        <v>1</v>
+      </c>
+      <c r="AK51" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C52" t="str">
-        <f>RIGHT(A52,1)</f>
-        <v>2</v>
+        <f t="shared" si="39"/>
+        <v>8</v>
       </c>
       <c r="D52" t="str">
-        <f>E52 &amp; IF(F52&lt;&gt;"", "_" &amp; F52, "_") &amp; IF(G52&lt;&gt;"", "_" &amp; G52, "_") &amp; IF(B52&lt;&gt;"", "_" &amp; B52, "")</f>
-        <v>ManyPrimates__2022</v>
+        <f t="shared" si="40"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="E52" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A52,","), "-", ""), " ", "")</f>
-        <v>ManyPrimates</v>
+        <f t="shared" si="41"/>
+        <v>Kverkova</v>
       </c>
       <c r="F52" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A52)),
-    IF(LEN(A52)-LEN(SUBSTITUTE(A52, ",", ""))&gt;=6, "etal", MID(A52, SEARCH("&amp; ", A52)+2, SEARCH(",", A52, SEARCH("&amp; ", A52)+2) - SEARCH("&amp; ", A52)-2)),
-    ""
-)</f>
-        <v/>
+        <f t="shared" si="42"/>
+        <v>etal</v>
       </c>
       <c r="G52" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A52, "("), ")")</f>
-        <v>2022</v>
+        <f t="shared" si="43"/>
+        <v>2018</v>
       </c>
       <c r="H52" t="str">
-        <f>_xlfn.TEXTAFTER(A52,"https://doi.org/")</f>
-        <v>10.26451/abc.09.04.06.2022</v>
+        <f t="shared" si="44"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K52" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D52,(SUBSTITUTE(SUBSTITUTE(J52," ",""), "_", ""))))</f>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+        <f t="shared" si="45"/>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L52" s="1" t="str">
-        <f>IF(ISBLANK(I52),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H52, SUBSTITUTE(J52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I52, SUBSTITUTE(J52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <f t="shared" si="46"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M52" t="str">
         <f t="array" ref="M52">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="P52" s="13" t="s">
-        <v>190</v>
+        <v>41</v>
       </c>
       <c r="Q52" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R52" s="14"/>
-      <c r="T52" s="13" t="str">
-        <f>IF(S52="N", R52, "write file name")</f>
-        <v>write file name</v>
+        <v>53</v>
+      </c>
+      <c r="R52" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S52" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T52" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="U52" s="13" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="V52" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W52" s="13" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="X52" s="13" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="Y52" s="13" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="Z52" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC52" s="13" t="s">
-        <v>193</v>
+        <v>99</v>
+      </c>
+      <c r="AB52" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="AE52" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+      <c r="AI52" s="13">
+        <v>1</v>
+      </c>
+      <c r="AK52" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="13" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C53" t="str">
-        <f>RIGHT(A53,1)</f>
-        <v>1</v>
+        <f t="shared" si="39"/>
+        <v>4</v>
       </c>
       <c r="D53" t="str">
-        <f>E53 &amp; IF(F53&lt;&gt;"", "_" &amp; F53, "_") &amp; IF(G53&lt;&gt;"", "_" &amp; G53, "_") &amp; IF(B53&lt;&gt;"", "_" &amp; B53, "")</f>
-        <v>Mota_etal_2015</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A53,","), "-", ""), " ", "")</f>
-        <v>Mota</v>
+        <f t="shared" si="40"/>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="E53" s="5" t="str">
+        <f t="shared" si="41"/>
+        <v>Lewitus</v>
       </c>
       <c r="F53" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A53)),
-    IF(LEN(A53)-LEN(SUBSTITUTE(A53, ",", ""))&gt;=6, "etal", MID(A53, SEARCH("&amp; ", A53)+2, SEARCH(",", A53, SEARCH("&amp; ", A53)+2) - SEARCH("&amp; ", A53)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G53" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
-        <v>2015</v>
-      </c>
-      <c r="H53" t="str">
-        <f>_xlfn.TEXTAFTER(A53,"https://doi.org/")</f>
-        <v>10.1126/science.aaa9101</v>
+      <c r="G53" s="5" t="str">
+        <f t="shared" si="43"/>
+        <v>2013</v>
+      </c>
+      <c r="H53" s="4" t="str">
+        <f t="shared" si="44"/>
+        <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K53" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D53,(SUBSTITUTE(SUBSTITUTE(J53," ",""), "_", ""))))</f>
-        <v>Mota_etal_2015_TableS1</v>
-      </c>
-      <c r="L53" s="1" t="str">
-        <f>IF(ISBLANK(I53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <v>227</v>
+      </c>
+      <c r="K53" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>Lewitus_etal_2013_TableS2partial</v>
+      </c>
+      <c r="L53" s="6" t="str">
+        <f t="shared" si="46"/>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M53" t="str">
         <f t="array" ref="M53">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="Q53" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="AA53" s="13" t="s">
+        <v>270</v>
+      </c>
       <c r="AI53" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK53" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
-        <v>344</v>
+        <v>223</v>
       </c>
       <c r="C54" t="str">
-        <f>RIGHT(A54,1)</f>
-        <v>6</v>
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
       <c r="D54" t="str">
-        <f>E54 &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "_") &amp; IF(G54&lt;&gt;"", "_" &amp; G54, "_") &amp; IF(B54&lt;&gt;"", "_" &amp; B54, "")</f>
-        <v>Mota_etal_2019</v>
-      </c>
-      <c r="E54" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
-        <v>Mota</v>
+        <f t="shared" si="40"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Lewitus</v>
       </c>
       <c r="F54" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A54)),
-    IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G54" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
-        <v>2019</v>
+      <c r="G54" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2014</v>
       </c>
       <c r="H54" t="str">
-        <f>_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
-        <v>10.1073/pnas.1716956116</v>
+        <f t="shared" si="44"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="K54" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D54,(SUBSTITUTE(SUBSTITUTE(J54," ",""), "_", ""))))</f>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
-      </c>
-      <c r="L54" s="3" t="str">
-        <f>IF(ISBLANK(I54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>91</v>
+      </c>
+      <c r="K54" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Lewitus_etal_2014_TableS1</v>
+      </c>
+      <c r="L54" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M54" t="str">
         <f t="array" ref="M54">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="P54" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC54" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="55" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+      <c r="Q54" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA54" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI54" s="13">
+        <v>9</v>
+      </c>
+      <c r="AK54" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="13" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C55" t="str">
-        <f>RIGHT(A55,1)</f>
-        <v>5</v>
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
       <c r="D55" t="str">
-        <f>E55 &amp; IF(F55&lt;&gt;"", "_" &amp; F55, "_") &amp; IF(G55&lt;&gt;"", "_" &amp; G55, "_") &amp; IF(B55&lt;&gt;"", "_" &amp; B55, "")</f>
-        <v>Powell_etal_2017</v>
+        <f t="shared" si="40"/>
+        <v>Lewitus_etal_2014</v>
       </c>
       <c r="E55" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A55,","), "-", ""), " ", "")</f>
-        <v>Powell</v>
+        <f t="shared" si="41"/>
+        <v>Lewitus</v>
       </c>
       <c r="F55" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A55)),
-    IF(LEN(A55)-LEN(SUBSTITUTE(A55, ",", ""))&gt;=6, "etal", MID(A55, SEARCH("&amp; ", A55)+2, SEARCH(",", A55, SEARCH("&amp; ", A55)+2) - SEARCH("&amp; ", A55)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G55" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A55, "("), ")")</f>
-        <v>2017</v>
+        <f t="shared" si="43"/>
+        <v>2014</v>
       </c>
       <c r="H55" t="str">
-        <f>_xlfn.TEXTAFTER(A55,"https://doi.org/")</f>
-        <v>10.1098/rspb.2017.1765</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>195</v>
+        <f t="shared" si="44"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="K55" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D55,(SUBSTITUTE(SUBSTITUTE(J55," ",""), "_", ""))))</f>
-        <v>Powell_etal_2017_Dataset1</v>
+        <f t="shared" si="45"/>
+        <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L55" s="1" t="str">
-        <f>IF(ISBLANK(I55),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H55, SUBSTITUTE(J55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I55, SUBSTITUTE(J55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <f t="shared" si="46"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M55" t="str">
         <f t="array" ref="M55">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P55" s="13" t="s">
-        <v>125</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+      </c>
+      <c r="N55" s="13" t="s">
+        <v>225</v>
       </c>
       <c r="Q55" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R55" s="14"/>
-      <c r="T55" s="13" t="str">
-        <f>IF(S55="N", R55, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U55" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="V55" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W55" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X55" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y55" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z55" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC55" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE55" s="13" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="AA55" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI55" s="13">
+        <v>6</v>
+      </c>
+      <c r="AK55" s="13">
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="C56" t="str">
-        <f>RIGHT(A56,1)</f>
-        <v>2</v>
+        <f t="shared" si="39"/>
+        <v>5</v>
       </c>
       <c r="D56" t="str">
-        <f>E56 &amp; IF(F56&lt;&gt;"", "_" &amp; F56, "_") &amp; IF(G56&lt;&gt;"", "_" &amp; G56, "_") &amp; IF(B56&lt;&gt;"", "_" &amp; B56, "")</f>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A56,","), "-", ""), " ", "")</f>
-        <v>Sherwood</v>
+        <f t="shared" si="40"/>
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="E56" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>MacLarnon</v>
       </c>
       <c r="F56" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A56)),
-    IF(LEN(A56)-LEN(SUBSTITUTE(A56, ",", ""))&gt;=6, "etal", MID(A56, SEARCH("&amp; ", A56)+2, SEARCH(",", A56, SEARCH("&amp; ", A56)+2) - SEARCH("&amp; ", A56)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="G56" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A56, "("), ")")</f>
-        <v>2004</v>
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="G56" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>1996</v>
       </c>
       <c r="H56" t="str">
-        <f>_xlfn.TEXTAFTER(A56,"https://doi.org/")</f>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="44"/>
+        <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="K56" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D56,(SUBSTITUTE(SUBSTITUTE(J56," ",""), "_", ""))))</f>
-        <v>Sherwood_etal_2004_I_Table4</v>
-      </c>
-      <c r="L56" s="1" t="str">
-        <f>IF(ISBLANK(I56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>52</v>
+      </c>
+      <c r="K56" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="L56" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M56" t="str">
         <f t="array" ref="M56">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q56" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R56" s="14"/>
-      <c r="T56" s="13" t="str">
-        <f>IF(S56="N", R56, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U56" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V56" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y56" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z56" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE56" s="13" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C57" t="str">
-        <f>RIGHT(A57,1)</f>
+        <f t="shared" si="39"/>
         <v>2</v>
       </c>
       <c r="D57" t="str">
-        <f>E57 &amp; IF(F57&lt;&gt;"", "_" &amp; F57, "_") &amp; IF(G57&lt;&gt;"", "_" &amp; G57, "_") &amp; IF(B57&lt;&gt;"", "_" &amp; B57, "")</f>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="40"/>
+        <v>ManyPrimates__2022</v>
       </c>
       <c r="E57" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A57,","), "-", ""), " ", "")</f>
-        <v>Sherwood</v>
+        <f t="shared" si="41"/>
+        <v>ManyPrimates</v>
       </c>
       <c r="F57" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A57)),
-    IF(LEN(A57)-LEN(SUBSTITUTE(A57, ",", ""))&gt;=6, "etal", MID(A57, SEARCH("&amp; ", A57)+2, SEARCH(",", A57, SEARCH("&amp; ", A57)+2) - SEARCH("&amp; ", A57)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="42"/>
+        <v/>
       </c>
       <c r="G57" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A57, "("), ")")</f>
-        <v>2004</v>
+        <f t="shared" si="43"/>
+        <v>2022</v>
       </c>
       <c r="H57" t="str">
-        <f>_xlfn.TEXTAFTER(A57,"https://doi.org/")</f>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="44"/>
+        <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K57" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D57,(SUBSTITUTE(SUBSTITUTE(J57," ",""), "_", ""))))</f>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f t="shared" si="45"/>
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="L57" s="1" t="str">
-        <f>IF(ISBLANK(I57),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H57, SUBSTITUTE(J57,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I57, SUBSTITUTE(J57,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000075672_Table5</v>
+        <f t="shared" si="46"/>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M57" t="str">
         <f t="array" ref="M57">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
-      </c>
-      <c r="N57" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="P57" s="13" t="s">
         <v>190</v>
@@ -5875,16 +5678,25 @@
         <v>write file name</v>
       </c>
       <c r="U57" s="13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="V57" s="13" t="s">
-        <v>201</v>
+        <v>46</v>
+      </c>
+      <c r="W57" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X57" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="Y57" s="13" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="Z57" s="13" t="s">
-        <v>99</v>
+        <v>49</v>
+      </c>
+      <c r="AC57" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="AE57" s="13" t="s">
         <v>64</v>
@@ -5892,419 +5704,738 @@
     </row>
     <row r="58" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="13" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C58" t="str">
-        <f>RIGHT(A58,1)</f>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="D58" t="str">
-        <f>E58 &amp; IF(F58&lt;&gt;"", "_" &amp; F58, "_") &amp; IF(G58&lt;&gt;"", "_" &amp; G58, "_") &amp; IF(B58&lt;&gt;"", "_" &amp; B58, "")</f>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="E58" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A58,","), "-", ""), " ", "")</f>
-        <v>Smaers</v>
+        <f t="shared" si="40"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="E58" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Mota</v>
       </c>
       <c r="F58" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A58)),
-    IF(LEN(A58)-LEN(SUBSTITUTE(A58, ",", ""))&gt;=6, "etal", MID(A58, SEARCH("&amp; ", A58)+2, SEARCH(",", A58, SEARCH("&amp; ", A58)+2) - SEARCH("&amp; ", A58)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G58" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A58, "("), ")")</f>
-        <v>2011</v>
+      <c r="G58" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2015</v>
       </c>
       <c r="H58" t="str">
-        <f>_xlfn.TEXTAFTER(A58,"https://doi.org/")</f>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="44"/>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="K58" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D58,(SUBSTITUTE(SUBSTITUTE(J58," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="L58" s="3" t="str">
-        <f>IF(ISBLANK(I58),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H58, SUBSTITUTE(J58,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I58, SUBSTITUTE(J58,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <v>91</v>
+      </c>
+      <c r="K58" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Mota_etal_2015_TableS1</v>
+      </c>
+      <c r="L58" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M58" t="str">
         <f t="array" ref="M58">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="Q58" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI58" s="13" t="s">
-        <v>230</v>
+      <c r="AI58" s="13">
+        <v>10</v>
+      </c>
+      <c r="AK58" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="13" t="s">
-        <v>228</v>
+        <v>344</v>
       </c>
       <c r="C59" t="str">
-        <f>RIGHT(A59,1)</f>
-        <v>1</v>
+        <f t="shared" si="39"/>
+        <v>6</v>
       </c>
       <c r="D59" t="str">
-        <f>E59 &amp; IF(F59&lt;&gt;"", "_" &amp; F59, "_") &amp; IF(G59&lt;&gt;"", "_" &amp; G59, "_") &amp; IF(B59&lt;&gt;"", "_" &amp; B59, "")</f>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="40"/>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="E59" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A59,","), "-", ""), " ", "")</f>
-        <v>Smaers</v>
+        <f t="shared" si="41"/>
+        <v>Mota</v>
       </c>
       <c r="F59" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A59)),
-    IF(LEN(A59)-LEN(SUBSTITUTE(A59, ",", ""))&gt;=6, "etal", MID(A59, SEARCH("&amp; ", A59)+2, SEARCH(",", A59, SEARCH("&amp; ", A59)+2) - SEARCH("&amp; ", A59)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
       <c r="G59" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A59, "("), ")")</f>
-        <v>2011</v>
+        <f t="shared" si="43"/>
+        <v>2019</v>
       </c>
       <c r="H59" t="str">
-        <f>_xlfn.TEXTAFTER(A59,"https://doi.org/")</f>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="44"/>
+        <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="K59" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D59,(SUBSTITUTE(SUBSTITUTE(J59," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" si="45"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L59" s="3" t="str">
-        <f>IF(ISBLANK(I59),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H59, SUBSTITUTE(J59,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I59, SUBSTITUTE(J59,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <f t="shared" si="46"/>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M59" t="str">
         <f t="array" ref="M59">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
-      </c>
-      <c r="Q59" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI59" s="13" t="s">
-        <v>230</v>
+        <v>notfound</v>
+      </c>
+      <c r="N59" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="P59" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC59" s="13" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="60" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="13" t="s">
-        <v>364</v>
+        <v>194</v>
       </c>
       <c r="C60" t="str">
-        <f>RIGHT(A60,1)</f>
-        <v>2</v>
+        <f t="shared" si="39"/>
+        <v>5</v>
       </c>
       <c r="D60" t="str">
-        <f>E60 &amp; IF(F60&lt;&gt;"", "_" &amp; F60, "_") &amp; IF(G60&lt;&gt;"", "_" &amp; G60, "_") &amp; IF(B60&lt;&gt;"", "_" &amp; B60, "")</f>
-        <v>Turner_etal_2016</v>
-      </c>
-      <c r="E60" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A60,","), "-", ""), " ", "")</f>
-        <v>Turner</v>
+        <f t="shared" si="40"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="E60" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Powell</v>
       </c>
       <c r="F60" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A60)),
-    IF(LEN(A60)-LEN(SUBSTITUTE(A60, ",", ""))&gt;=6, "etal", MID(A60, SEARCH("&amp; ", A60)+2, SEARCH(",", A60, SEARCH("&amp; ", A60)+2) - SEARCH("&amp; ", A60)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G60" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A60, "("), ")")</f>
-        <v>2016</v>
+      <c r="G60" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2017</v>
       </c>
       <c r="H60" t="str">
-        <f>_xlfn.TEXTAFTER(A60,"https://doi.org/")</f>
-        <v>10.1159/000446762</v>
+        <f t="shared" si="44"/>
+        <v>10.1098/rspb.2017.1765</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>195</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K60" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D60,(SUBSTITUTE(SUBSTITUTE(J60," ",""), "_", ""))))</f>
-        <v>Turner_etal_2016_Table1</v>
-      </c>
-      <c r="L60" s="3" t="str">
-        <f>IF(ISBLANK(I60),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H60, SUBSTITUTE(J60,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I60, SUBSTITUTE(J60,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000446762_Table1</v>
+        <v>196</v>
+      </c>
+      <c r="K60" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Powell_etal_2017_Dataset1</v>
+      </c>
+      <c r="L60" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M60" t="str">
         <f t="array" ref="M60">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L60, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N60" s="13" t="s">
-        <v>362</v>
+      <c r="P60" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q60" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" s="14"/>
+      <c r="T60" s="13" t="str">
+        <f>IF(S60="N", R60, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U60" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="V60" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W60" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X60" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="Y60" s="13" t="s">
-        <v>363</v>
+        <v>198</v>
+      </c>
+      <c r="Z60" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC60" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE60" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="13" t="s">
-        <v>350</v>
+        <v>199</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="C61" t="str">
-        <f>RIGHT(A61,1)</f>
-        <v>1</v>
+        <f t="shared" si="39"/>
+        <v>2</v>
       </c>
       <c r="D61" t="str">
-        <f>E61 &amp; IF(F61&lt;&gt;"", "_" &amp; F61, "_") &amp; IF(G61&lt;&gt;"", "_" &amp; G61, "_") &amp; IF(B61&lt;&gt;"", "_" &amp; B61, "")</f>
-        <v>Wilman_etal_2014</v>
-      </c>
-      <c r="E61" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A61,","), "-", ""), " ", "")</f>
-        <v>Wilman</v>
+        <f t="shared" si="40"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="E61" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Sherwood</v>
       </c>
       <c r="F61" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A61)),
-    IF(LEN(A61)-LEN(SUBSTITUTE(A61, ",", ""))&gt;=6, "etal", MID(A61, SEARCH("&amp; ", A61)+2, SEARCH(",", A61, SEARCH("&amp; ", A61)+2) - SEARCH("&amp; ", A61)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G61" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A61, "("), ")")</f>
-        <v>2014</v>
+      <c r="G61" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2004</v>
       </c>
       <c r="H61" t="str">
-        <f>_xlfn.TEXTAFTER(A61,"https://doi.org/")</f>
-        <v>10.1890/13-1917.1</v>
+        <f t="shared" si="44"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="K61" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D61,(SUBSTITUTE(SUBSTITUTE(J61," ",""), "_", ""))))</f>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
-      </c>
-      <c r="L61" s="3" t="str">
-        <f>IF(ISBLANK(I61),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H61, SUBSTITUTE(J61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I61, SUBSTITUTE(J61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <v>143</v>
+      </c>
+      <c r="K61" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Sherwood_etal_2004_I_Table4</v>
+      </c>
+      <c r="L61" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M61" t="str">
         <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
+      <c r="N61" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="P61" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q61" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" s="14"/>
+      <c r="T61" s="13" t="str">
+        <f>IF(S61="N", R61, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U61" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V61" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y61" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z61" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE61" s="13" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="62" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="13" t="s">
-        <v>348</v>
+        <v>199</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="C62" t="str">
-        <f>RIGHT(A62,1)</f>
-        <v>7</v>
+        <f t="shared" si="39"/>
+        <v>2</v>
       </c>
       <c r="D62" t="str">
-        <f>E62 &amp; IF(F62&lt;&gt;"", "_" &amp; F62, "_") &amp; IF(G62&lt;&gt;"", "_" &amp; G62, "_") &amp; IF(B62&lt;&gt;"", "_" &amp; B62, "")</f>
-        <v>Wimberly_etal_2021</v>
-      </c>
-      <c r="E62" s="7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A62,","), "-", ""), " ", "")</f>
-        <v>Wimberly</v>
+        <f t="shared" si="40"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="E62" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Sherwood</v>
       </c>
       <c r="F62" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A62)),
-    IF(LEN(A62)-LEN(SUBSTITUTE(A62, ",", ""))&gt;=6, "etal", MID(A62, SEARCH("&amp; ", A62)+2, SEARCH(",", A62, SEARCH("&amp; ", A62)+2) - SEARCH("&amp; ", A62)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G62" s="7" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A62, "("), ")")</f>
-        <v>2021</v>
+      <c r="G62" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2004</v>
       </c>
       <c r="H62" t="str">
-        <f>_xlfn.TEXTAFTER(A62,"https://doi.org/")</f>
-        <v>10.1098/rspb.2021.0937</v>
+        <f t="shared" si="44"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="K62" s="3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D62,(SUBSTITUTE(SUBSTITUTE(J62," ",""), "_", ""))))</f>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
-      </c>
-      <c r="L62" s="3" t="str">
-        <f>IF(ISBLANK(I62),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H62, SUBSTITUTE(J62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I62, SUBSTITUTE(J62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <v>147</v>
+      </c>
+      <c r="K62" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
+      </c>
+      <c r="L62" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M62" t="str">
         <f t="array" ref="M62">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L62, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
+      <c r="N62" s="13" t="s">
+        <v>204</v>
+      </c>
       <c r="P62" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+      <c r="Q62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" s="14"/>
+      <c r="T62" s="13" t="str">
+        <f>IF(S62="N", R62, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U62" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V62" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y62" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z62" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE62" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="13" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C63" t="str">
-        <f>RIGHT(A63,1)</f>
-        <v>5</v>
+        <f t="shared" si="39"/>
+        <v>1</v>
       </c>
       <c r="D63" t="str">
-        <f>E63 &amp; IF(F63&lt;&gt;"", "_" &amp; F63, "_") &amp; IF(G63&lt;&gt;"", "_" &amp; G63, "_") &amp; IF(B63&lt;&gt;"", "_" &amp; B63, "")</f>
-        <v>Winkler_Bryant_2021</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A63,","), "-", ""), " ", "")</f>
-        <v>Winkler</v>
+        <f t="shared" si="40"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="E63" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Smaers</v>
       </c>
       <c r="F63" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A63)),
-    IF(LEN(A63)-LEN(SUBSTITUTE(A63, ",", ""))&gt;=6, "etal", MID(A63, SEARCH("&amp; ", A63)+2, SEARCH(",", A63, SEARCH("&amp; ", A63)+2) - SEARCH("&amp; ", A63)-2)),
-    ""
-)</f>
-        <v>Bryant</v>
-      </c>
-      <c r="G63" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A63, "("), ")")</f>
-        <v>2021</v>
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G63" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>2011</v>
       </c>
       <c r="H63" t="str">
-        <f>_xlfn.TEXTAFTER(A63,"https://doi.org/")</f>
-        <v>10.1080/09524622.2021.1905065</v>
+        <f t="shared" si="44"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="K63" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D63,(SUBSTITUTE(SUBSTITUTE(J63," ",""), "_", ""))))</f>
-        <v>Winkler_Bryant_2021_Figure1</v>
-      </c>
-      <c r="L63" s="1" t="str">
-        <f>IF(ISBLANK(I63),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H63, SUBSTITUTE(J63,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I63, SUBSTITUTE(J63,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <v>229</v>
+      </c>
+      <c r="K63" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
+      </c>
+      <c r="L63" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M63" t="str">
         <f t="array" ref="M63">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L63, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P63" s="13" t="s">
-        <v>125</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q63" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R63" s="14"/>
-      <c r="T63" s="13" t="str">
-        <f>IF(S63="N", R63, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U63" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V63" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y63" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE63" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="AI63" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C64" t="str">
-        <f>RIGHT(A64,1)</f>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>1</v>
       </c>
       <c r="D64" t="str">
-        <f>E64 &amp; IF(F64&lt;&gt;"", "_" &amp; F64, "_") &amp; IF(G64&lt;&gt;"", "_" &amp; G64, "_") &amp; IF(B64&lt;&gt;"", "_" &amp; B64, "")</f>
-        <v>Young_etal_2013</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A64,","), "-", ""), " ", "")</f>
-        <v>Young</v>
+        <f t="shared" si="40"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="E64" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Smaers</v>
       </c>
       <c r="F64" s="2" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A64)),
-    IF(LEN(A64)-LEN(SUBSTITUTE(A64, ",", ""))&gt;=6, "etal", MID(A64, SEARCH("&amp; ", A64)+2, SEARCH(",", A64, SEARCH("&amp; ", A64)+2) - SEARCH("&amp; ", A64)-2)),
-    ""
-)</f>
+        <f t="shared" si="42"/>
         <v>etal</v>
       </c>
-      <c r="G64" s="2" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A64, "("), ")")</f>
-        <v>2013</v>
+      <c r="G64" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>2011</v>
       </c>
       <c r="H64" t="str">
-        <f>_xlfn.TEXTAFTER(A64,"https://doi.org/")</f>
-        <v>10.3389/fncir.2013.00030</v>
+        <f t="shared" si="44"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K64" s="1" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D64,(SUBSTITUTE(SUBSTITUTE(J64," ",""), "_", ""))))</f>
-        <v>Young_etal_2013_Table1</v>
-      </c>
-      <c r="L64" s="1" t="str">
-        <f>IF(ISBLANK(I64),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H64, SUBSTITUTE(J64,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I64, SUBSTITUTE(J64,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <v>231</v>
+      </c>
+      <c r="K64" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="L64" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M64" t="str">
         <f t="array" ref="M64">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L64, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="Q64" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI64" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="39"/>
+        <v>2</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="40"/>
+        <v>Turner_etal_2016</v>
+      </c>
+      <c r="E65" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Turner</v>
+      </c>
+      <c r="F65" s="2" t="str">
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G65" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>2016</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1159/000446762</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Turner_etal_2016_Table1</v>
+      </c>
+      <c r="L65" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000446762_Table1</v>
+      </c>
+      <c r="M65" t="str">
+        <f t="array" ref="M65">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L65, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P64" s="13" t="s">
+      <c r="N65" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y65" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="39"/>
+        <v>1</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="40"/>
+        <v>Wilman_etal_2014</v>
+      </c>
+      <c r="E66" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Wilman</v>
+      </c>
+      <c r="F66" s="2" t="str">
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G66" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>2014</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1890/13-1917.1</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="K66" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+      </c>
+      <c r="L66" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+      </c>
+      <c r="M66" t="str">
+        <f t="array" ref="M66">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L66, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="39"/>
+        <v>7</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="40"/>
+        <v>Wimberly_etal_2021</v>
+      </c>
+      <c r="E67" s="7" t="str">
+        <f t="shared" si="41"/>
+        <v>Wimberly</v>
+      </c>
+      <c r="F67" s="2" t="str">
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G67" s="7" t="str">
+        <f t="shared" si="43"/>
+        <v>2021</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1098/rspb.2021.0937</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="K67" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
+      </c>
+      <c r="L67" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+      </c>
+      <c r="M67" t="str">
+        <f t="array" ref="M67">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L67, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P67" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A68" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="40"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="E68" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Winkler</v>
+      </c>
+      <c r="F68" s="2" t="str">
+        <f t="shared" si="42"/>
+        <v>Bryant</v>
+      </c>
+      <c r="G68" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2021</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1080/09524622.2021.1905065</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K68" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
+      </c>
+      <c r="L68" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="array" ref="M68">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L68, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P68" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q68" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" s="14"/>
+      <c r="T68" s="13" t="str">
+        <f>IF(S68="N", R68, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U68" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V68" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y68" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE68" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A69" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="40"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="E69" s="2" t="str">
+        <f t="shared" si="41"/>
+        <v>Young</v>
+      </c>
+      <c r="F69" s="2" t="str">
+        <f t="shared" si="42"/>
+        <v>etal</v>
+      </c>
+      <c r="G69" s="2" t="str">
+        <f t="shared" si="43"/>
+        <v>2013</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="44"/>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K69" s="1" t="str">
+        <f t="shared" si="45"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L69" s="1" t="str">
+        <f t="shared" si="46"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="array" ref="M69">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L69, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P69" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="Q64" s="13" t="s">
+      <c r="Q69" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="R64" s="14"/>
-      <c r="T64" s="13" t="str">
-        <f>IF(S64="N", R64, "write file name")</f>
+      <c r="R69" s="14"/>
+      <c r="T69" s="13" t="str">
+        <f>IF(S69="N", R69, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U64" s="13" t="s">
+      <c r="U69" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="V64" s="13" t="s">
+      <c r="V69" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Y64" s="13" t="s">
+      <c r="Y69" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="AE64" s="13" t="s">
+      <c r="AE69" s="13" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK64">
-    <sortCondition ref="K2:K64"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AK69">
+    <sortCondition ref="K4:K69"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="X7" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="X6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="X9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X11" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="X13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X52" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X55" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X25" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X18:X21" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X47" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X46" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X44" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X15" r:id="rId13" xr:uid="{C1F957F4-0EDC-0E49-A387-57F382261715}"/>
-    <hyperlink ref="X16" r:id="rId14" xr:uid="{9C2C9343-3842-7E45-A05C-5DD83A0C30F9}"/>
+    <hyperlink ref="X9" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="X8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="X11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="X13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="X18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="X57" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X60" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="X30" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="X23:X26" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X52" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="X51" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X49" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="X20" r:id="rId13" xr:uid="{C1F957F4-0EDC-0E49-A387-57F382261715}"/>
+    <hyperlink ref="X21" r:id="rId14" xr:uid="{9C2C9343-3842-7E45-A05C-5DD83A0C30F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6731,17 +6862,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6750,9 +6870,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca9bcfe5a103c514723d0bd46d8b738f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b0efe988aa2f142173325409561b0e5" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -7005,24 +7125,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E6C6718-1083-4BA4-895F-4D544A70F5E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -7030,8 +7144,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{626A4699-A325-43EA-975B-831A3E6EEB9F}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196EEE13-1E58-4887-9EDC-D5AC20223AD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7047,4 +7161,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F26DD8C4A4E48D1A3D61CC6E603E869C6E2D4135" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Species/Evo-M1-Trait-Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC53FC2-4916-F04E-AD16-87ADF0B3D25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36260" yWindow="-5960" windowWidth="39560" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36240" yWindow="-5840" windowWidth="47980" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,17 +18,28 @@
     <sheet name="Conflicts" sheetId="4" r:id="rId3"/>
     <sheet name="FileList" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="405">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -578,9 +594,6 @@
     <t>Herculano-Houzel, S. (2015). Decreasing sleep requirement with increasing numbers of neurons as a driver for bigger brains and bodies in mammalian evolution. Proc Biol Sci, 282(1816), 20151853. https://doi.org/10.1098/rspb.2015.1853</t>
   </si>
   <si>
-    <t>Table 1. Dataset used in this study.</t>
-  </si>
-  <si>
     <t>Herculano-Houzel, S., Watson, C., &amp; Paxinos, G. (2013). Distribution of neurons in functional areas of the mouse cerebral cortex reveals quantitatively different cortical zones. Front Neuroanat, 7, 35. https://doi.org/10.3389/fnana.2013.00035</t>
   </si>
   <si>
@@ -1233,13 +1246,22 @@
   </si>
   <si>
     <t>README.md</t>
+  </si>
+  <si>
+    <t>Per cent of hours asleep and brain size and composition</t>
+  </si>
+  <si>
+    <t>Table 2. Dataset on the ontogeny of sleep and cellular composition of the rat brain used in this study.</t>
+  </si>
+  <si>
+    <t>proportion REM and developmental milestones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1251,6 +1273,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1266,6 +1289,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1296,7 +1320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1319,11 +1343,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1340,6 +1375,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,9 +1395,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1398,7 +1435,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1504,7 +1541,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1646,7 +1683,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1655,40 +1692,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH77"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.125" customWidth="1"/>
-    <col min="2" max="2" width="5.125" customWidth="1"/>
-    <col min="3" max="3" width="22.875" customWidth="1"/>
-    <col min="4" max="4" width="34.875" customWidth="1"/>
+    <col min="1" max="1" width="42.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="23.625" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="5.125" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="31.125" customWidth="1"/>
+    <col min="11" max="11" width="31.1640625" customWidth="1"/>
     <col min="12" max="12" width="46.5" customWidth="1"/>
     <col min="13" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="15.375" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="20" width="14.125" customWidth="1"/>
-    <col min="21" max="21" width="13.875" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="22.125" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
+    <col min="17" max="20" width="14.1640625" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="22.1640625" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" customWidth="1"/>
     <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.125" customWidth="1"/>
+    <col min="26" max="26" width="11.1640625" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.625" customWidth="1"/>
-    <col min="30" max="30" width="10.875" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" customWidth="1"/>
     <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.875" customWidth="1"/>
+    <col min="32" max="34" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.95" customHeight="1">
+    <row r="1" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1792,7 +1829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15.95" customHeight="1">
+    <row r="2" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1827,16 +1864,16 @@
         <v>10.1002/cne.70089</v>
       </c>
       <c r="K2" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
+        <f t="shared" ref="K2:K14" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
         <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L2" t="str">
-        <f>IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L2:L14" si="7">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M2" t="str">
         <f t="array" ref="M2">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1002%2Fcne.70089_TABLE1.tsv</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>36</v>
@@ -1848,7 +1885,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="15.95" customHeight="1">
+    <row r="3" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -1859,38 +1896,38 @@
         <v>41</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E4" si="6">RIGHT(A3,1)</f>
+        <f t="shared" ref="E3:E4" si="8">RIGHT(A3,1)</f>
         <v>5</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3" si="7">G3 &amp; IF(H3&lt;&gt;"", "_" &amp; H3, "_") &amp; IF(I3&lt;&gt;"", "_" &amp; I3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
+        <f t="shared" ref="F3" si="9">G3 &amp; IF(H3&lt;&gt;"", "_" &amp; H3, "_") &amp; IF(I3&lt;&gt;"", "_" &amp; I3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
         <v>Baron_etal_1983</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G3" si="10">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3" si="9">IF(ISNUMBER(FIND("&amp;", A3)),
+        <f t="shared" ref="H3" si="11">IF(ISNUMBER(FIND("&amp;", A3)),
     IF(LEN(A3)-LEN(SUBSTITUTE(A3, ",", ""))&gt;=6, "etal", MID(A3, SEARCH("&amp; ", A3)+2, SEARCH(",", A3, SEARCH("&amp; ", A3)+2) - SEARCH("&amp; ", A3)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3" si="10">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+        <f t="shared" ref="I3" si="12">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>1983</v>
       </c>
       <c r="J3" t="e">
-        <f t="shared" ref="J3" si="11">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <f t="shared" ref="J3" si="13">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
         <v>#N/A</v>
       </c>
       <c r="K3" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F3,(SUBSTITUTE(SUBSTITUTE(D3," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Baron_etal_1983_Table1</v>
       </c>
       <c r="L3" t="str">
-        <f>IF(ISBLANK(C3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder.1_Table1</v>
       </c>
       <c r="M3" t="str">
@@ -1907,7 +1944,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="15.95" customHeight="1">
+    <row r="4" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1918,38 +1955,38 @@
         <v>41</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4" si="12">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
+        <f t="shared" ref="F4" si="14">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
         <v>Baron_etal_1987</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4" si="13">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G4" si="15">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4" si="14">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="H4" si="16">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=6, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4" si="15">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <f t="shared" ref="I4" si="17">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
         <v>1987</v>
       </c>
       <c r="J4" t="e">
-        <f t="shared" ref="J4" si="16">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
+        <f t="shared" ref="J4" si="18">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
         <v>#N/A</v>
       </c>
       <c r="K4" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F4,(SUBSTITUTE(SUBSTITUTE(D4," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Baron_etal_1987_Table1</v>
       </c>
       <c r="L4" t="str">
-        <f>IF(ISBLANK(C4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J4, SUBSTITUTE(D4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C4, SUBSTITUTE(D4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder.2_Table1</v>
       </c>
       <c r="M4" t="str">
@@ -1966,7 +2003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15.95" customHeight="1">
+    <row r="5" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -1977,38 +2014,38 @@
         <v>47</v>
       </c>
       <c r="E5" t="str">
-        <f t="shared" ref="E5:E45" si="17">RIGHT(A5,1)</f>
+        <f t="shared" ref="E5:E45" si="19">RIGHT(A5,1)</f>
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" ref="F5:F45" si="18">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
+        <f t="shared" ref="F5:F45" si="20">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
         <v>Brodmann__1913</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" ref="G5:G45" si="19">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G5:G45" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
         <v>Brodmann</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H45" ca="1" si="20">IF(ISNUMBER(FIND("&amp;", A5)),
+        <f t="shared" ref="H5:H45" si="22">IF(ISNUMBER(FIND("&amp;", A5)),
     IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
     ""
 )</f>
         <v/>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I45" si="21">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
+        <f t="shared" ref="I5:I45" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
         <v>1913</v>
       </c>
       <c r="J5" t="e">
-        <f t="shared" ref="J5:J45" si="22">_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
+        <f t="shared" ref="J5:J45" si="24">_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
         <v>#N/A</v>
       </c>
       <c r="K5" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F5,(SUBSTITUTE(SUBSTITUTE(D5," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Brodmann__1913_Tabelle1</v>
       </c>
       <c r="L5" t="str">
-        <f>IF(ISBLANK(C5),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J5, SUBSTITUTE(D5,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C5, SUBSTITUTE(D5,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
       <c r="M5" t="str">
@@ -2016,7 +2053,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="6" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>48</v>
       </c>
@@ -2024,35 +2061,35 @@
         <v>49</v>
       </c>
       <c r="E6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Burger_etal_2019</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Burger</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="K6" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F6,(SUBSTITUTE(SUBSTITUTE(D6," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="L6" t="str">
-        <f>IF(ISBLANK(C6),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J6, SUBSTITUTE(D6,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C6, SUBSTITUTE(D6,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="M6" t="str">
@@ -2100,7 +2137,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>61</v>
       </c>
@@ -2108,35 +2145,35 @@
         <v>62</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Burish</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000319019</v>
       </c>
       <c r="K7" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F7,(SUBSTITUTE(SUBSTITUTE(D7," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
       <c r="L7" t="str">
-        <f>IF(ISBLANK(C7),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J7, SUBSTITUTE(D7,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C7, SUBSTITUTE(D7,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M7" t="str">
@@ -2162,7 +2199,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="15.95" customHeight="1">
+    <row r="8" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -2170,35 +2207,35 @@
         <v>41</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Burish</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000319019</v>
       </c>
       <c r="K8" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F8,(SUBSTITUTE(SUBSTITUTE(D8," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Burish_etal_2010_Table1</v>
       </c>
       <c r="L8" t="str">
-        <f>IF(ISBLANK(C8),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J8, SUBSTITUTE(D8,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C8, SUBSTITUTE(D8,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M8" t="str">
@@ -2227,7 +2264,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15.95" customHeight="1">
+    <row r="9" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>73</v>
       </c>
@@ -2235,35 +2272,35 @@
         <v>74</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Caspar</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2022</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="K9" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F9,(SUBSTITUTE(SUBSTITUTE(D9," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="L9" t="str">
-        <f>IF(ISBLANK(C9),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J9, SUBSTITUTE(D9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C9, SUBSTITUTE(D9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M9" t="str">
@@ -2311,7 +2348,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15.95" customHeight="1">
+    <row r="10" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
@@ -2319,35 +2356,35 @@
         <v>41</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Caspar</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2022</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="K10" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F10,(SUBSTITUTE(SUBSTITUTE(D10," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="L10" t="str">
-        <f>IF(ISBLANK(C10),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J10, SUBSTITUTE(D10,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C10, SUBSTITUTE(D10,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M10" t="str">
@@ -2397,7 +2434,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15.95" customHeight="1">
+    <row r="11" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>92</v>
       </c>
@@ -2405,35 +2442,35 @@
         <v>93</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Changizi__2001</v>
       </c>
       <c r="G11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Changizi</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2001</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1007/s004220000205</v>
       </c>
       <c r="K11" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F11,(SUBSTITUTE(SUBSTITUTE(D11," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Changizi__2001_Figure3</v>
       </c>
       <c r="L11" t="str">
-        <f>IF(ISBLANK(C11),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J11, SUBSTITUTE(D11,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C11, SUBSTITUTE(D11,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M11" t="str">
@@ -2474,7 +2511,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15.95" customHeight="1">
+    <row r="12" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>103</v>
       </c>
@@ -2482,35 +2519,35 @@
         <v>104</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Chen_Wiens_2020</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Chen</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>Wiens</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="K12" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F12,(SUBSTITUTE(SUBSTITUTE(D12," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="L12" t="str">
-        <f>IF(ISBLANK(C12),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J12, SUBSTITUTE(D12,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C12, SUBSTITUTE(D12,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="M12" t="str">
@@ -2561,7 +2598,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15.95" customHeight="1">
+    <row r="13" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>111</v>
       </c>
@@ -2569,35 +2606,35 @@
         <v>112</v>
       </c>
       <c r="E13" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Collins_etal_2010</v>
       </c>
       <c r="G13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Collins</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J13" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1073/pnas.1010356107</v>
       </c>
       <c r="K13" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F13,(SUBSTITUTE(SUBSTITUTE(D13," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>Collins_etal_2010_DatasetS1</v>
       </c>
       <c r="L13" t="str">
-        <f>IF(ISBLANK(C13),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J13, SUBSTITUTE(D13,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C13, SUBSTITUTE(D13,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
       <c r="M13" t="str">
@@ -2611,7 +2648,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+    <row r="14" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>114</v>
       </c>
@@ -2619,35 +2656,35 @@
         <v>115</v>
       </c>
       <c r="E14" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>DeCasien</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>Higham</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J14" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K14" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F14,(SUBSTITUTE(SUBSTITUTE(D14," ",""), "_", ""))))</f>
+        <f t="shared" si="6"/>
         <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="L14" t="str">
-        <f>IF(ISBLANK(C14),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J14, SUBSTITUTE(D14,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C14, SUBSTITUTE(D14,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="7"/>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="M14" t="str">
@@ -2682,7 +2719,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15.95" customHeight="1">
+    <row r="15" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>114</v>
       </c>
@@ -2690,30 +2727,30 @@
         <v>121</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" ref="E15" si="23">RIGHT(A15,1)</f>
+        <f t="shared" ref="E15" si="25">RIGHT(A15,1)</f>
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" ref="F15" si="24">G15 &amp; IF(H15&lt;&gt;"", "_" &amp; H15, "_") &amp; IF(I15&lt;&gt;"", "_" &amp; I15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
+        <f t="shared" ref="F15" si="26">G15 &amp; IF(H15&lt;&gt;"", "_" &amp; H15, "_") &amp; IF(I15&lt;&gt;"", "_" &amp; I15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" ref="G15" si="25">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G15" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" ref="H15" si="26">IF(ISNUMBER(FIND("&amp;", A15)),
+        <f t="shared" ref="H15" si="28">IF(ISNUMBER(FIND("&amp;", A15)),
     IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" ref="I15" si="27">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
+        <f t="shared" ref="I15" si="29">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J15" t="str">
-        <f t="shared" ref="J15" si="28">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
+        <f t="shared" ref="J15" si="30">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K15" t="str">
@@ -2753,7 +2790,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+    <row r="16" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>114</v>
       </c>
@@ -2761,30 +2798,30 @@
         <v>123</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" ref="E16" si="29">RIGHT(A16,1)</f>
+        <f t="shared" ref="E16" si="31">RIGHT(A16,1)</f>
         <v>0</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" ref="F16" si="30">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
+        <f t="shared" ref="F16" si="32">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" ref="G16" si="31">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G16" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" ref="H16" si="32">IF(ISNUMBER(FIND("&amp;", A16)),
+        <f t="shared" ref="H16" si="34">IF(ISNUMBER(FIND("&amp;", A16)),
     IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" ref="I16" si="33">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
+        <f t="shared" ref="I16" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J16" t="str">
-        <f t="shared" ref="J16" si="34">_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
+        <f t="shared" ref="J16" si="36">_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K16" t="str">
@@ -2824,7 +2861,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="15.95" customHeight="1">
+    <row r="17" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>114</v>
       </c>
@@ -2832,38 +2869,38 @@
         <v>125</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17" si="35">RIGHT(A17,1)</f>
+        <f t="shared" ref="E17" si="37">RIGHT(A17,1)</f>
         <v>0</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" ref="F17" si="36">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <f t="shared" ref="F17" si="38">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" ref="G17" si="37">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G17" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" ref="H17" si="38">IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="H17" si="40">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" ref="I17" si="39">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <f t="shared" ref="I17" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" ref="J17" si="40">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
+        <f t="shared" ref="J17" si="42">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K17" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
+        <f t="shared" ref="K17:K48" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L17" t="str">
-        <f>IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L17:L48" si="44">IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M17" t="str">
@@ -2895,7 +2932,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="15.95" customHeight="1">
+    <row r="18" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>127</v>
       </c>
@@ -2903,35 +2940,35 @@
         <v>128</v>
       </c>
       <c r="E18" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="F18" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>DosSantos_etal_2017</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>DosSantos</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2017</v>
       </c>
       <c r="J18" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000452856</v>
       </c>
       <c r="K18" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F18,(SUBSTITUTE(SUBSTITUTE(D18," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L18" t="str">
-        <f>IF(ISBLANK(C18),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M18" t="str">
@@ -2987,7 +3024,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="15.95" customHeight="1">
+    <row r="19" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>139</v>
       </c>
@@ -2995,35 +3032,35 @@
         <v>41</v>
       </c>
       <c r="E19" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>DosSantos</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J19" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="K19" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F19,(SUBSTITUTE(SUBSTITUTE(D19," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="L19" t="str">
-        <f>IF(ISBLANK(C19),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J19, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C19, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="M19" t="str">
@@ -3067,7 +3104,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="15.95" customHeight="1">
+    <row r="20" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>139</v>
       </c>
@@ -3075,38 +3112,38 @@
         <v>145</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" ref="E20" si="41">RIGHT(A20,1)</f>
+        <f t="shared" ref="E20" si="45">RIGHT(A20,1)</f>
         <v>0</v>
       </c>
       <c r="F20" t="str">
-        <f t="shared" ref="F20" si="42">G20 &amp; IF(H20&lt;&gt;"", "_" &amp; H20, "_") &amp; IF(I20&lt;&gt;"", "_" &amp; I20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
+        <f t="shared" ref="F20" si="46">G20 &amp; IF(H20&lt;&gt;"", "_" &amp; H20, "_") &amp; IF(I20&lt;&gt;"", "_" &amp; I20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" ref="G20" si="43">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G20" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
         <v>DosSantos</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" ref="H20" si="44">IF(ISNUMBER(FIND("&amp;", A20)),
+        <f t="shared" ref="H20" si="48">IF(ISNUMBER(FIND("&amp;", A20)),
     IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" ref="I20" si="45">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
+        <f t="shared" ref="I20" si="49">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
         <v>2020</v>
       </c>
       <c r="J20" t="str">
-        <f t="shared" ref="J20" si="46">_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
+        <f t="shared" ref="J20" si="50">_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="K20" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F20,(SUBSTITUTE(SUBSTITUTE(D20," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>DosSantos_etal_2020_unpublished</v>
       </c>
       <c r="L20" t="str">
-        <f>IF(ISBLANK(C20),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J20, SUBSTITUTE(D20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C20, SUBSTITUTE(D20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
       <c r="M20" t="str">
@@ -3150,7 +3187,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="15.95" customHeight="1">
+    <row r="21" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>146</v>
       </c>
@@ -3158,38 +3195,38 @@
         <v>35</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" ref="E21" si="47">RIGHT(A21,1)</f>
+        <f t="shared" ref="E21" si="51">RIGHT(A21,1)</f>
         <v>3</v>
       </c>
       <c r="F21" t="str">
-        <f t="shared" ref="F21" si="48">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
+        <f t="shared" ref="F21" si="52">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
         <v>Eagleman_Vaughn_2021</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" ref="G21" si="49">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G21" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
         <v>Eagleman</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" ref="H21" si="50">IF(ISNUMBER(FIND("&amp;", A21)),
+        <f t="shared" ref="H21" si="54">IF(ISNUMBER(FIND("&amp;", A21)),
     IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
     ""
 )</f>
         <v>Vaughn</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" ref="I21" si="51">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
+        <f t="shared" ref="I21" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
         <v>2021</v>
       </c>
       <c r="J21" t="str">
-        <f t="shared" ref="J21" si="52">_xlfn.TEXTAFTER(A21,"https://doi.org/")</f>
+        <f t="shared" ref="J21" si="56">_xlfn.TEXTAFTER(A21,"https://doi.org/")</f>
         <v>10.3389/fnins.2021.632853</v>
       </c>
       <c r="K21" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F21,(SUBSTITUTE(SUBSTITUTE(D21," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Eagleman_Vaughn_2021_TABLE1</v>
       </c>
       <c r="L21" t="str">
-        <f>IF(ISBLANK(C21),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J21, SUBSTITUTE(D21,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C21, SUBSTITUTE(D21,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.3389%2Ffnins.2021.632853_TABLE1</v>
       </c>
       <c r="M21" t="str">
@@ -3203,11 +3240,14 @@
       <c r="U21" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="Y21" s="11" t="s">
+        <v>404</v>
+      </c>
       <c r="Z21" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="15.95" customHeight="1">
+    <row r="22" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>148</v>
       </c>
@@ -3215,35 +3255,35 @@
         <v>35</v>
       </c>
       <c r="E22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Falcone_etal_2019</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Falcone</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J22" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1002/cne.24605</v>
       </c>
       <c r="K22" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F22,(SUBSTITUTE(SUBSTITUTE(D22," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Falcone_etal_2019_TABLE1</v>
       </c>
       <c r="L22" t="str">
-        <f>IF(ISBLANK(C22),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J22, SUBSTITUTE(D22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C22, SUBSTITUTE(D22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M22" t="str">
@@ -3261,7 +3301,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="15.95" customHeight="1">
+    <row r="23" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -3269,38 +3309,38 @@
         <v>150</v>
       </c>
       <c r="E23" t="str">
-        <f t="shared" ref="E23" si="53">RIGHT(A23,1)</f>
+        <f t="shared" ref="E23" si="57">RIGHT(A23,1)</f>
         <v>5</v>
       </c>
       <c r="F23" t="str">
-        <f t="shared" ref="F23" si="54">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
+        <f t="shared" ref="F23" si="58">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
         <v>Falcone_etal_2019</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" ref="G23" si="55">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G23" si="59">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
         <v>Falcone</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" ref="H23" si="56">IF(ISNUMBER(FIND("&amp;", A23)),
+        <f t="shared" ref="H23" si="60">IF(ISNUMBER(FIND("&amp;", A23)),
     IF(LEN(A23)-LEN(SUBSTITUTE(A23, ",", ""))&gt;=6, "etal", MID(A23, SEARCH("&amp; ", A23)+2, SEARCH(",", A23, SEARCH("&amp; ", A23)+2) - SEARCH("&amp; ", A23)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" ref="I23" si="57">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
+        <f t="shared" ref="I23" si="61">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J23" t="str">
-        <f t="shared" ref="J23" si="58">_xlfn.TEXTAFTER(A23,"https://doi.org/")</f>
+        <f t="shared" ref="J23" si="62">_xlfn.TEXTAFTER(A23,"https://doi.org/")</f>
         <v>10.1002/cne.24605</v>
       </c>
       <c r="K23" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F23,(SUBSTITUTE(SUBSTITUTE(D23," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Falcone_etal_2019_TABLE2</v>
       </c>
       <c r="L23" t="str">
-        <f>IF(ISBLANK(C23),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J23, SUBSTITUTE(D23,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C23, SUBSTITUTE(D23,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1002%2Fcne.24605_TABLE2</v>
       </c>
       <c r="M23" t="str">
@@ -3318,7 +3358,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="15.95" customHeight="1">
+    <row r="24" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>152</v>
       </c>
@@ -3326,35 +3366,35 @@
         <v>153</v>
       </c>
       <c r="E24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="F24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Finlay_etal_2006</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Finlay</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2006</v>
       </c>
       <c r="J24" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="K24" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F24,(SUBSTITUTE(SUBSTITUTE(D24," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="L24" t="str">
-        <f>IF(ISBLANK(C24),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J24, SUBSTITUTE(D24,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C24, SUBSTITUTE(D24,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M24" t="str">
@@ -3402,7 +3442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="15.95" customHeight="1">
+    <row r="25" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>158</v>
       </c>
@@ -3410,35 +3450,35 @@
         <v>41</v>
       </c>
       <c r="E25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>x</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Fu_etal_2013</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Fu</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J25" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="K25" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F25,(SUBSTITUTE(SUBSTITUTE(D25," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Fu_etal_2013_Table1</v>
       </c>
       <c r="L25" t="str">
-        <f>IF(ISBLANK(C25),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J25, SUBSTITUTE(D25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C25, SUBSTITUTE(D25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M25" t="str">
@@ -3458,7 +3498,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="15" customHeight="1">
+    <row r="26" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>162</v>
       </c>
@@ -3466,35 +3506,35 @@
         <v>128</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Garwicz_etal_2009</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Garwicz</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2009</v>
       </c>
       <c r="J26" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K26" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F26,(SUBSTITUTE(SUBSTITUTE(D26," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Garwicz_etal_2009_TableS1</v>
       </c>
       <c r="L26" t="str">
-        <f>IF(ISBLANK(C26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J26, SUBSTITUTE(D26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C26, SUBSTITUTE(D26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M26" t="str">
@@ -3514,7 +3554,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="15.95" customHeight="1">
+    <row r="27" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>162</v>
       </c>
@@ -3522,35 +3562,35 @@
         <v>165</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Garwicz_etal_2009</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Garwicz</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2009</v>
       </c>
       <c r="J27" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K27" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F27,(SUBSTITUTE(SUBSTITUTE(D27," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Garwicz_etal_2009_TableS2</v>
       </c>
       <c r="L27" t="str">
-        <f>IF(ISBLANK(C27),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J27, SUBSTITUTE(D27,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C27, SUBSTITUTE(D27,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M27" t="str">
@@ -3570,7 +3610,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="15.95" customHeight="1">
+    <row r="28" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>167</v>
       </c>
@@ -3578,35 +3618,35 @@
         <v>165</v>
       </c>
       <c r="E28" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Genoud_etal_2018</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Genoud</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2018</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1111/brv.12350</v>
       </c>
       <c r="K28" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F28,(SUBSTITUTE(SUBSTITUTE(D28," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="L28" t="str">
-        <f>IF(ISBLANK(C28),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J28, SUBSTITUTE(D28,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C28, SUBSTITUTE(D28,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="M28" t="str">
@@ -3623,7 +3663,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="15.95" customHeight="1">
+    <row r="29" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>170</v>
       </c>
@@ -3631,35 +3671,35 @@
         <v>128</v>
       </c>
       <c r="E29" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Granatosky__2018</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Granatosky</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2018</v>
       </c>
       <c r="J29" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1111/jzo.12608</v>
       </c>
       <c r="K29" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F29,(SUBSTITUTE(SUBSTITUTE(D29," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Granatosky__2018_TableS1</v>
       </c>
       <c r="L29" t="str">
-        <f>IF(ISBLANK(C29),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J29, SUBSTITUTE(D29,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C29, SUBSTITUTE(D29,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1111%2Fjzo.12608_TableS1</v>
       </c>
       <c r="M29" t="str">
@@ -3673,7 +3713,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="15.95" customHeight="1">
+    <row r="30" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
@@ -3681,35 +3721,35 @@
         <v>173</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Heffner_Masterton_1975</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Heffner</v>
       </c>
       <c r="H30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>Masterton</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1975</v>
       </c>
       <c r="J30" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000124401</v>
       </c>
       <c r="K30" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F30,(SUBSTITUTE(SUBSTITUTE(D30," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="L30" t="str">
-        <f>IF(ISBLANK(C30),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J30, SUBSTITUTE(D30,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C30, SUBSTITUTE(D30,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M30" t="str">
@@ -3753,7 +3793,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="15.95" customHeight="1">
+    <row r="31" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>179</v>
       </c>
@@ -3761,35 +3801,35 @@
         <v>173</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Heffner_Masterton_1983</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Heffner</v>
       </c>
       <c r="H31" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>Masterton</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1983</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000121494</v>
       </c>
       <c r="K31" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F31,(SUBSTITUTE(SUBSTITUTE(D31," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="L31" t="str">
-        <f>IF(ISBLANK(C31),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="M31" t="str">
@@ -3826,7 +3866,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="15.95" customHeight="1">
+    <row r="32" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>181</v>
       </c>
@@ -3834,35 +3874,35 @@
         <v>128</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Heldstab_etal_2016</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Heldstab</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2016</v>
       </c>
       <c r="J32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1038/srep24528</v>
       </c>
       <c r="K32" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F32,(SUBSTITUTE(SUBSTITUTE(D32," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="L32" t="str">
-        <f>IF(ISBLANK(C32),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="M32" t="str">
@@ -3893,94 +3933,106 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="15.95" customHeight="1">
+    <row r="33" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>183</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" ref="E33" si="59">RIGHT(A33,1)</f>
+        <f t="shared" ref="E33" si="63">RIGHT(A33,1)</f>
         <v>3</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" ref="F33" si="60">G33 &amp; IF(H33&lt;&gt;"", "_" &amp; H33, "_") &amp; IF(I33&lt;&gt;"", "_" &amp; I33, "_") &amp; IF(B33&lt;&gt;"", "_" &amp; B33, "")</f>
+        <f t="shared" ref="F33" si="64">G33 &amp; IF(H33&lt;&gt;"", "_" &amp; H33, "_") &amp; IF(I33&lt;&gt;"", "_" &amp; I33, "_") &amp; IF(B33&lt;&gt;"", "_" &amp; B33, "")</f>
         <v>HerculanoHouzel__2015</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" ref="G33" si="61">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A33,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G33" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A33,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H33" t="str">
-        <f t="shared" ref="H33" ca="1" si="62">IF(ISNUMBER(FIND("&amp;", A33)),
+        <f t="shared" ref="H33" si="66">IF(ISNUMBER(FIND("&amp;", A33)),
     IF(LEN(A33)-LEN(SUBSTITUTE(A33, ",", ""))&gt;=6, "etal", MID(A33, SEARCH("&amp; ", A33)+2, SEARCH(",", A33, SEARCH("&amp; ", A33)+2) - SEARCH("&amp; ", A33)-2)),
     ""
 )</f>
         <v/>
       </c>
       <c r="I33" t="str">
-        <f t="shared" ref="I33" si="63">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A33, "("), ")")</f>
+        <f t="shared" ref="I33" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A33, "("), ")")</f>
         <v>2015</v>
       </c>
       <c r="J33" t="str">
-        <f t="shared" ref="J33" si="64">_xlfn.TEXTAFTER(A33,"https://doi.org/")</f>
+        <f t="shared" ref="J33" si="68">_xlfn.TEXTAFTER(A33,"https://doi.org/")</f>
         <v>10.1098/rspb.2015.1853</v>
       </c>
       <c r="K33" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F33,(SUBSTITUTE(SUBSTITUTE(D33," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel__2015_Table1</v>
+        <f t="shared" si="43"/>
+        <v>HerculanoHouzel__2015_Table2</v>
       </c>
       <c r="L33" t="str">
-        <f>IF(ISBLANK(C33),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J33, SUBSTITUTE(D33,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C33, SUBSTITUTE(D33,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1098%2Frspb.2015.1853_Table1</v>
+        <f t="shared" si="44"/>
+        <v>10.1098%2Frspb.2015.1853_Table2</v>
       </c>
       <c r="M33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N33" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R33" s="4"/>
+      <c r="U33" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="V33" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="Z33" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="R33" s="4"/>
-    </row>
-    <row r="34" spans="1:31" ht="15.95" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="E34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K34" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F34,(SUBSTITUTE(SUBSTITUTE(D34," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="L34" t="str">
-        <f>IF(ISBLANK(C34),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M34" t="str">
@@ -3991,43 +4043,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="18.95" customHeight="1">
+    <row r="35" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K35" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F35,(SUBSTITUTE(SUBSTITUTE(D35," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="L35" t="str">
-        <f>IF(ISBLANK(C35),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J35, SUBSTITUTE(D35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C35, SUBSTITUTE(D35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="M35" t="str">
@@ -4038,43 +4090,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="17.100000000000001" customHeight="1">
+    <row r="36" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J36" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K36" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F36,(SUBSTITUTE(SUBSTITUTE(D36," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="L36" t="str">
-        <f>IF(ISBLANK(C36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="M36" t="str">
@@ -4085,43 +4137,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="17.100000000000001" customHeight="1">
+    <row r="37" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H37" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J37" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K37" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F37,(SUBSTITUTE(SUBSTITUTE(D37," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="L37" t="str">
-        <f>IF(ISBLANK(C37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J37, SUBSTITUTE(D37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C37, SUBSTITUTE(D37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="M37" t="str">
@@ -4129,7 +4181,7 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>51</v>
@@ -4138,13 +4190,13 @@
         <v>70</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U37" s="1" t="s">
         <v>86</v>
@@ -4156,7 +4208,7 @@
         <v>87</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y37" s="1" t="s">
         <v>135</v>
@@ -4168,46 +4220,46 @@
         <v>136</v>
       </c>
       <c r="AE37" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="38" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="E38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J38" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K38" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F38,(SUBSTITUTE(SUBSTITUTE(D38," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="L38" t="str">
-        <f>IF(ISBLANK(C38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J38, SUBSTITUTE(D38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C38, SUBSTITUTE(D38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="M38" t="str">
@@ -4215,7 +4267,7 @@
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>51</v>
@@ -4224,13 +4276,13 @@
         <v>70</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U38" s="1" t="s">
         <v>86</v>
@@ -4242,7 +4294,7 @@
         <v>87</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y38" s="1" t="s">
         <v>135</v>
@@ -4254,46 +4306,46 @@
         <v>136</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" ht="17.100000000000001" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H39" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K39" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F39,(SUBSTITUTE(SUBSTITUTE(D39," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="L39" t="str">
-        <f>IF(ISBLANK(C39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J39, SUBSTITUTE(D39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C39, SUBSTITUTE(D39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="M39" t="str">
@@ -4301,7 +4353,7 @@
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>51</v>
@@ -4310,13 +4362,13 @@
         <v>70</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="U39" s="1" t="s">
         <v>86</v>
@@ -4328,7 +4380,7 @@
         <v>87</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>135</v>
@@ -4340,46 +4392,46 @@
         <v>136</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" ht="15.95" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K40" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F40,(SUBSTITUTE(SUBSTITUTE(D40," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="L40" t="str">
-        <f>IF(ISBLANK(C40),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J40, SUBSTITUTE(D40,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C40, SUBSTITUTE(D40,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="M40" t="str">
@@ -4387,7 +4439,7 @@
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>51</v>
@@ -4396,13 +4448,13 @@
         <v>70</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U40" s="1" t="s">
         <v>86</v>
@@ -4414,7 +4466,7 @@
         <v>87</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y40" s="1" t="s">
         <v>135</v>
@@ -4426,46 +4478,46 @@
         <v>136</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" ht="15.95" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H41" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J41" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K41" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F41,(SUBSTITUTE(SUBSTITUTE(D41," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="L41" t="str">
-        <f>IF(ISBLANK(C41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J41, SUBSTITUTE(D41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C41, SUBSTITUTE(D41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="M41" t="str">
@@ -4473,7 +4525,7 @@
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>51</v>
@@ -4482,13 +4534,13 @@
         <v>70</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="U41" s="1" t="s">
         <v>86</v>
@@ -4500,7 +4552,7 @@
         <v>87</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y41" s="1" t="s">
         <v>135</v>
@@ -4512,46 +4564,46 @@
         <v>136</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" ht="15.95" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H42" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J42" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="K42" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F42,(SUBSTITUTE(SUBSTITUTE(D42," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L42" t="str">
-        <f>IF(ISBLANK(C42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J42, SUBSTITUTE(D42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C42, SUBSTITUTE(D42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M42" t="str">
@@ -4559,7 +4611,7 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>51</v>
@@ -4568,13 +4620,13 @@
         <v>70</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U42" s="1" t="s">
         <v>86</v>
@@ -4586,7 +4638,7 @@
         <v>99</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>136</v>
@@ -4595,46 +4647,46 @@
         <v>136</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" ht="15.95" customHeight="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E43" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="K43" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F43,(SUBSTITUTE(SUBSTITUTE(D43," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="L43" t="str">
-        <f>IF(ISBLANK(C43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J43, SUBSTITUTE(D43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C43, SUBSTITUTE(D43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="M43" t="str">
@@ -4642,7 +4694,7 @@
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>51</v>
@@ -4651,13 +4703,13 @@
         <v>70</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U43" s="1" t="s">
         <v>86</v>
@@ -4669,7 +4721,7 @@
         <v>99</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AA43" s="1" t="s">
         <v>136</v>
@@ -4678,46 +4730,46 @@
         <v>136</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" ht="15.95" customHeight="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Isler</v>
       </c>
       <c r="H44" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2008</v>
       </c>
       <c r="J44" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K44" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F44,(SUBSTITUTE(SUBSTITUTE(D44," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="L44" t="str">
-        <f>IF(ISBLANK(C44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J44, SUBSTITUTE(D44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C44, SUBSTITUTE(D44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="M44" t="str">
@@ -4728,43 +4780,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="15.95" customHeight="1">
+    <row r="45" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E45" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Isler</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>etal</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2008</v>
       </c>
       <c r="J45" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K45" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F45,(SUBSTITUTE(SUBSTITUTE(D45," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
       <c r="L45" t="str">
-        <f>IF(ISBLANK(C45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J45, SUBSTITUTE(D45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C45, SUBSTITUTE(D45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
       <c r="M45" t="str">
@@ -4775,46 +4827,46 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="15.95" customHeight="1">
+    <row r="46" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E46" t="str">
-        <f t="shared" ref="E46:E77" si="65">RIGHT(A46,1)</f>
+        <f t="shared" ref="E46:E77" si="69">RIGHT(A46,1)</f>
         <v>4</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" ref="F46:F77" si="66">G46 &amp; IF(H46&lt;&gt;"", "_" &amp; H46, "_") &amp; IF(I46&lt;&gt;"", "_" &amp; I46, "_") &amp; IF(B46&lt;&gt;"", "_" &amp; B46, "")</f>
+        <f t="shared" ref="F46:F77" si="70">G46 &amp; IF(H46&lt;&gt;"", "_" &amp; H46, "_") &amp; IF(I46&lt;&gt;"", "_" &amp; I46, "_") &amp; IF(B46&lt;&gt;"", "_" &amp; B46, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" ref="G46:G77" si="67">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G46:G77" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="H46" t="str">
-        <f t="shared" ref="H46:H77" si="68">IF(ISNUMBER(FIND("&amp;", A46)),
+        <f t="shared" ref="H46:H77" si="72">IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=6, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" ref="I46:I77" si="69">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <f t="shared" ref="I46:I77" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="J46" t="str">
-        <f t="shared" ref="J46:J77" si="70">_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
+        <f t="shared" ref="J46:J77" si="74">_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K46" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F46,(SUBSTITUTE(SUBSTITUTE(D46," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
       <c r="L46" t="str">
-        <f>IF(ISBLANK(C46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J46, SUBSTITUTE(D46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C46, SUBSTITUTE(D46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
       <c r="M46" t="str">
@@ -4825,43 +4877,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="15.95" customHeight="1">
+    <row r="47" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>165</v>
       </c>
       <c r="E47" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>4</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G47" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Isler</v>
       </c>
       <c r="H47" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2008</v>
       </c>
       <c r="J47" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K47" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F47,(SUBSTITUTE(SUBSTITUTE(D47," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L47" t="str">
-        <f>IF(ISBLANK(C47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J47, SUBSTITUTE(D47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C47, SUBSTITUTE(D47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M47" t="str">
@@ -4872,43 +4924,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="15.95" customHeight="1">
+    <row r="48" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E48" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>4</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Isler</v>
       </c>
       <c r="H48" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2008</v>
       </c>
       <c r="J48" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K48" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F48,(SUBSTITUTE(SUBSTITUTE(D48," ",""), "_", ""))))</f>
+        <f t="shared" si="43"/>
         <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L48" t="str">
-        <f>IF(ISBLANK(C48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J48, SUBSTITUTE(D48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C48, SUBSTITUTE(D48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="44"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M48" t="str">
@@ -4919,43 +4971,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15.95" customHeight="1">
+    <row r="49" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E49" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>4</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Isler</v>
       </c>
       <c r="H49" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2008</v>
       </c>
       <c r="J49" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K49" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F49,(SUBSTITUTE(SUBSTITUTE(D49," ",""), "_", ""))))</f>
+        <f t="shared" ref="K49:K77" si="75">TRIM(_xlfn.TEXTJOIN("_",FALSE,F49,(SUBSTITUTE(SUBSTITUTE(D49," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L49" t="str">
-        <f>IF(ISBLANK(C49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L49:L77" si="76">IF(ISBLANK(C49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M49" t="str">
@@ -4966,43 +5018,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15.95" customHeight="1">
+    <row r="50" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E50" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>x</v>
       </c>
       <c r="F50" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H50" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>1999</v>
       </c>
       <c r="J50" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K50" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F50,(SUBSTITUTE(SUBSTITUTE(D50," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_1999_References</v>
       </c>
       <c r="L50" t="str">
-        <f>IF(ISBLANK(C50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M50" t="str">
@@ -5010,55 +5062,55 @@
         <v>notfound</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>160</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15.95" customHeight="1">
+    <row r="51" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>x</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>1999</v>
       </c>
       <c r="J51" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K51" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F51,(SUBSTITUTE(SUBSTITUTE(D51," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_1999_Table1</v>
       </c>
       <c r="L51" t="str">
-        <f>IF(ISBLANK(C51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J51, SUBSTITUTE(D51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C51, SUBSTITUTE(D51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M51" t="str">
@@ -5066,7 +5118,7 @@
         <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>160</v>
@@ -5078,43 +5130,43 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15.95" customHeight="1">
+    <row r="52" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>9</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2001</v>
       </c>
       <c r="J52" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K52" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F52,(SUBSTITUTE(SUBSTITUTE(D52," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="L52" t="str">
-        <f>IF(ISBLANK(C52),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J52, SUBSTITUTE(D52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C52, SUBSTITUTE(D52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M52" t="str">
@@ -5122,10 +5174,10 @@
         <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
       </c>
       <c r="N52" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="Q52" s="1" t="s">
         <v>95</v>
@@ -5142,49 +5194,49 @@
         <v>36</v>
       </c>
       <c r="Y52" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE52" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AE52" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" ht="15.95" customHeight="1">
+    </row>
+    <row r="53" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E53" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>9</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2001</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K53" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F53,(SUBSTITUTE(SUBSTITUTE(D53," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="L53" t="str">
-        <f>IF(ISBLANK(C53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M53" t="str">
@@ -5192,10 +5244,10 @@
         <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q53" s="1" t="s">
         <v>95</v>
@@ -5212,49 +5264,49 @@
         <v>36</v>
       </c>
       <c r="Y53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE53" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AE53" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" ht="15.95" customHeight="1">
+    </row>
+    <row r="54" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E54" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>9</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2001</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K54" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F54,(SUBSTITUTE(SUBSTITUTE(D54," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="L54" t="str">
-        <f>IF(ISBLANK(C54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J54, SUBSTITUTE(D54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C54, SUBSTITUTE(D54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M54" t="str">
@@ -5262,10 +5314,10 @@
         <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>95</v>
@@ -5282,49 +5334,49 @@
         <v>36</v>
       </c>
       <c r="Y54" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE54" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AE54" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="15.95" customHeight="1">
+    </row>
+    <row r="55" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E55" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>9</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2001</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K55" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F55,(SUBSTITUTE(SUBSTITUTE(D55," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="L55" t="str">
-        <f>IF(ISBLANK(C55),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J55, SUBSTITUTE(D55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C55, SUBSTITUTE(D55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M55" t="str">
@@ -5332,10 +5384,10 @@
         <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q55" s="1" t="s">
         <v>95</v>
@@ -5352,49 +5404,49 @@
         <v>36</v>
       </c>
       <c r="Y55" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE55" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AE55" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="15.95" customHeight="1">
+    </row>
+    <row r="56" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E56" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>8</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>JardimMesseder</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2017</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="K56" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F56,(SUBSTITUTE(SUBSTITUTE(D56," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="L56" t="str">
-        <f>IF(ISBLANK(C56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J56, SUBSTITUTE(D56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C56, SUBSTITUTE(D56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="M56" t="str">
@@ -5402,7 +5454,7 @@
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>51</v>
@@ -5411,13 +5463,13 @@
         <v>70</v>
       </c>
       <c r="R56" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U56" s="1" t="s">
         <v>86</v>
@@ -5429,7 +5481,7 @@
         <v>87</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Y56" s="1" t="s">
         <v>135</v>
@@ -5444,46 +5496,46 @@
         <v>136</v>
       </c>
       <c r="AE56" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" ht="15.95" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>9</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Karl_etal_2024</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Karl</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2024</v>
       </c>
       <c r="J57" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1002/cne.25669</v>
       </c>
       <c r="K57" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F57,(SUBSTITUTE(SUBSTITUTE(D57," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Karl_etal_2024_TABLE1</v>
       </c>
       <c r="L57" t="str">
-        <f>IF(ISBLANK(C57),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J57, SUBSTITUTE(D57,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C57, SUBSTITUTE(D57,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1002%2Fcne.25669_TABLE1</v>
       </c>
       <c r="M57" t="str">
@@ -5491,7 +5543,7 @@
         <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R57" s="4"/>
       <c r="U57" s="1" t="s">
@@ -5504,49 +5556,49 @@
         <v>99</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15.95" customHeight="1">
+    <row r="58" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>8</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Kverkova</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2018</v>
       </c>
       <c r="J58" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K58" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F58,(SUBSTITUTE(SUBSTITUTE(D58," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L58" t="str">
-        <f>IF(ISBLANK(C58),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J58, SUBSTITUTE(D58,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C58, SUBSTITUTE(D58,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M58" t="str">
@@ -5554,7 +5606,7 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>51</v>
@@ -5563,22 +5615,22 @@
         <v>70</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T58" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U58" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>38</v>
@@ -5587,46 +5639,46 @@
         <v>136</v>
       </c>
       <c r="AE58" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" ht="15.95" customHeight="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>8</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Kverkova</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2018</v>
       </c>
       <c r="J59" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K59" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F59,(SUBSTITUTE(SUBSTITUTE(D59," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="L59" t="str">
-        <f>IF(ISBLANK(C59),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J59, SUBSTITUTE(D59,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C59, SUBSTITUTE(D59,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M59" t="str">
@@ -5634,7 +5686,7 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>51</v>
@@ -5643,16 +5695,16 @@
         <v>70</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T59" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U59" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>36</v>
@@ -5661,58 +5713,58 @@
         <v>87</v>
       </c>
       <c r="X59" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z59" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="Y59" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z59" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="AB59" s="1" t="s">
         <v>136</v>
       </c>
       <c r="AE59" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" ht="15.95" customHeight="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E60" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>8</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Kverkova</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2018</v>
       </c>
       <c r="J60" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K60" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F60,(SUBSTITUTE(SUBSTITUTE(D60," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L60" t="str">
-        <f>IF(ISBLANK(C60),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J60, SUBSTITUTE(D60,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C60, SUBSTITUTE(D60,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M60" t="str">
@@ -5720,7 +5772,7 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>51</v>
@@ -5729,16 +5781,16 @@
         <v>70</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T60" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="U60" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>36</v>
@@ -5747,10 +5799,10 @@
         <v>87</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Z60" s="1" t="s">
         <v>38</v>
@@ -5759,46 +5811,46 @@
         <v>136</v>
       </c>
       <c r="AE60" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31" ht="15.95" customHeight="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E61" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>4</v>
       </c>
       <c r="F61" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Lewitus_etal_2013</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Lewitus</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2013</v>
       </c>
       <c r="J61" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="K61" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F61,(SUBSTITUTE(SUBSTITUTE(D61," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="L61" t="str">
-        <f>IF(ISBLANK(C61),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M61" t="str">
@@ -5809,46 +5861,46 @@
         <v>52</v>
       </c>
       <c r="AA61" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31" ht="15.95" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Lewitus</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2014</v>
       </c>
       <c r="J62" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K62" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F62,(SUBSTITUTE(SUBSTITUTE(D62," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="L62" t="str">
-        <f>IF(ISBLANK(C62),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J62, SUBSTITUTE(D62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C62, SUBSTITUTE(D62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M62" t="str">
@@ -5856,52 +5908,52 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q62" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AA62" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="63" spans="1:31" ht="15.95" customHeight="1">
-      <c r="A63" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Lewitus</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2014</v>
       </c>
       <c r="J63" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K63" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F63,(SUBSTITUTE(SUBSTITUTE(D63," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L63" t="str">
-        <f>IF(ISBLANK(C63),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J63, SUBSTITUTE(D63,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C63, SUBSTITUTE(D63,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M63" t="str">
@@ -5909,52 +5961,52 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AA63" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31" ht="15.75" customHeight="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E64" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>5</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>MacLarnon__1996</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>MacLarnon</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" ca="1" si="68"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>1996</v>
       </c>
       <c r="J64" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="K64" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F64,(SUBSTITUTE(SUBSTITUTE(D64," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>MacLarnon__1996_Table1</v>
       </c>
       <c r="L64" t="str">
-        <f>IF(ISBLANK(C64),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J64, SUBSTITUTE(D64,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C64, SUBSTITUTE(D64,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M64" t="str">
@@ -5962,49 +6014,49 @@
         <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15.75" customHeight="1">
+    <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E65" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>ManyPrimates__2022</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>ManyPrimates</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" ca="1" si="68"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2022</v>
       </c>
       <c r="J65" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="K65" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F65,(SUBSTITUTE(SUBSTITUTE(D65," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="L65" t="str">
-        <f>IF(ISBLANK(C65),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J65, SUBSTITUTE(D65,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C65, SUBSTITUTE(D65,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M65" t="str">
@@ -6012,7 +6064,7 @@
         <v>notfound</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q65" s="1" t="s">
         <v>95</v>
@@ -6032,58 +6084,58 @@
         <v>78</v>
       </c>
       <c r="X65" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y65" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="Y65" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="Z65" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AC65" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AE65" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15.75" customHeight="1">
+    <row r="66" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E66" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Mota_etal_2015</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Mota</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2015</v>
       </c>
       <c r="J66" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1126/science.aaa9101</v>
       </c>
       <c r="K66" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F66,(SUBSTITUTE(SUBSTITUTE(D66," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="L66" t="str">
-        <f>IF(ISBLANK(C66),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J66, SUBSTITUTE(D66,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C66, SUBSTITUTE(D66,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M66" t="str">
@@ -6094,43 +6146,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15.75" customHeight="1">
+    <row r="67" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E67" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>6</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Mota_etal_2019</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Mota</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2019</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="K67" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F67,(SUBSTITUTE(SUBSTITUTE(D67," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L67" t="str">
-        <f>IF(ISBLANK(C67),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J67, SUBSTITUTE(D67,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C67, SUBSTITUTE(D67,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M67" t="str">
@@ -6138,55 +6190,55 @@
         <v>notfound</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>160</v>
       </c>
       <c r="AC67" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="68" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A68" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E68" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>5</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Powell_etal_2017</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Powell</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2017</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
       <c r="K68" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F68,(SUBSTITUTE(SUBSTITUTE(D68," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="L68" t="str">
-        <f>IF(ISBLANK(C68),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J68, SUBSTITUTE(D68,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C68, SUBSTITUTE(D68,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M68" t="str">
@@ -6214,10 +6266,10 @@
         <v>78</v>
       </c>
       <c r="X68" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y68" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="Y68" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>58</v>
@@ -6229,46 +6281,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15.75" customHeight="1">
+    <row r="69" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="D69" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E69" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Sherwood</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2004</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="K69" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F69,(SUBSTITUTE(SUBSTITUTE(D69," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="L69" t="str">
-        <f>IF(ISBLANK(C69),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J69, SUBSTITUTE(D69,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C69, SUBSTITUTE(D69,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M69" t="str">
@@ -6276,10 +6328,10 @@
         <v>notfound</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q69" s="1" t="s">
         <v>95</v>
@@ -6293,10 +6345,10 @@
         <v>86</v>
       </c>
       <c r="V69" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y69" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="Y69" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="Z69" s="1" t="s">
         <v>38</v>
@@ -6305,46 +6357,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15.75" customHeight="1">
+    <row r="70" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="D70" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Sherwood</v>
       </c>
       <c r="H70" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2004</v>
       </c>
       <c r="J70" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="K70" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F70,(SUBSTITUTE(SUBSTITUTE(D70," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="L70" t="str">
-        <f>IF(ISBLANK(C70),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J70, SUBSTITUTE(D70,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C70, SUBSTITUTE(D70,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M70" t="str">
@@ -6352,10 +6404,10 @@
         <v>notfound</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q70" s="1" t="s">
         <v>95</v>
@@ -6369,10 +6421,10 @@
         <v>86</v>
       </c>
       <c r="V70" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y70" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="Y70" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="Z70" s="1" t="s">
         <v>38</v>
@@ -6381,43 +6433,43 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15.75" customHeight="1">
+    <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="E71" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Smaers</v>
       </c>
       <c r="H71" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2011</v>
       </c>
       <c r="J71" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="K71" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F71,(SUBSTITUTE(SUBSTITUTE(D71," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L71" t="str">
-        <f>IF(ISBLANK(C71),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J71, SUBSTITUTE(D71,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C71, SUBSTITUTE(D71,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M71" t="str">
@@ -6428,43 +6480,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15.75" customHeight="1">
+    <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Smaers</v>
       </c>
       <c r="H72" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2011</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="K72" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F72,(SUBSTITUTE(SUBSTITUTE(D72," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L72" t="str">
-        <f>IF(ISBLANK(C72),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J72, SUBSTITUTE(D72,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C72, SUBSTITUTE(D72,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M72" t="str">
@@ -6475,43 +6527,43 @@
         <v>52</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15.75" customHeight="1">
+    <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>2</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Turner_etal_2016</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Turner</v>
       </c>
       <c r="H73" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2016</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1159/000446762</v>
       </c>
       <c r="K73" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F73,(SUBSTITUTE(SUBSTITUTE(D73," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L73" t="str">
-        <f>IF(ISBLANK(C73),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J73, SUBSTITUTE(D73,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C73, SUBSTITUTE(D73,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M73" t="str">
@@ -6519,49 +6571,49 @@
         <v>notfound</v>
       </c>
       <c r="N73" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y73" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="Y73" s="1" t="s">
+    </row>
+    <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="74" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E74" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Wilman_etal_2014</v>
       </c>
       <c r="G74" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Wilman</v>
       </c>
       <c r="H74" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2014</v>
       </c>
       <c r="J74" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1890/13-1917.1</v>
       </c>
       <c r="K74" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F74,(SUBSTITUTE(SUBSTITUTE(D74," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L74" t="str">
-        <f>IF(ISBLANK(C74),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J74, SUBSTITUTE(D74,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C74, SUBSTITUTE(D74,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M74" t="str">
@@ -6569,43 +6621,43 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15.75" customHeight="1">
+    <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E75" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>7</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Wimberly_etal_2021</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Wimberly</v>
       </c>
       <c r="H75" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2021</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1098/rspb.2021.0937</v>
       </c>
       <c r="K75" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F75,(SUBSTITUTE(SUBSTITUTE(D75," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L75" t="str">
-        <f>IF(ISBLANK(C75),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J75, SUBSTITUTE(D75,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C75, SUBSTITUTE(D75,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M75" t="str">
@@ -6616,43 +6668,43 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E76" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>5</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Winkler_Bryant_2021</v>
       </c>
       <c r="G76" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Winkler</v>
       </c>
       <c r="H76" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>Bryant</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2021</v>
       </c>
       <c r="J76" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="K76" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F76,(SUBSTITUTE(SUBSTITUTE(D76," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="L76" t="str">
-        <f>IF(ISBLANK(C76),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J76, SUBSTITUTE(D76,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C76, SUBSTITUTE(D76,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="M76" t="str">
@@ -6674,52 +6726,52 @@
         <v>86</v>
       </c>
       <c r="V76" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y76" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="Y76" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="AE76" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E77" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>Young_etal_2013</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>Young</v>
       </c>
       <c r="H77" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2013</v>
       </c>
       <c r="J77" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
       <c r="K77" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F77,(SUBSTITUTE(SUBSTITUTE(D77," ",""), "_", ""))))</f>
+        <f t="shared" si="75"/>
         <v>Young_etal_2013_Table1</v>
       </c>
       <c r="L77" t="str">
-        <f>IF(ISBLANK(C77),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J77, SUBSTITUTE(D77,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C77, SUBSTITUTE(D77,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" si="76"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="M77" t="str">
@@ -6727,7 +6779,7 @@
         <v>notfound</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q77" s="1" t="s">
         <v>95</v>
@@ -6744,7 +6796,7 @@
         <v>36</v>
       </c>
       <c r="Y77" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Z77" s="1" t="s">
         <v>38</v>
@@ -6778,104 +6830,104 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7" t="s">
+      <c r="B3" t="s">
         <v>311</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="7" t="s">
+      <c r="B4" t="s">
         <v>313</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="7" t="s">
+      <c r="B5" t="s">
         <v>315</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="B6" t="s">
         <v>317</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="7" t="s">
+      <c r="B7" t="s">
         <v>319</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="7" t="s">
+      <c r="B8" t="s">
         <v>321</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="7" t="s">
+      <c r="B9" t="s">
         <v>323</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
+      <c r="B10" t="s">
         <v>325</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="7" t="s">
+      <c r="B11" t="s">
         <v>327</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="B12" t="s">
         <v>329</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>330</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="8" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -6887,64 +6939,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="C2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" t="s">
         <v>334</v>
       </c>
-      <c r="C3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" t="s">
         <v>336</v>
       </c>
-      <c r="C4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" t="s">
         <v>338</v>
       </c>
-      <c r="C5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" t="s">
         <v>340</v>
-      </c>
-      <c r="C6" t="s">
-        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6956,311 +7008,311 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -7270,26 +7322,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -7544,14 +7576,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC53FC2-4916-F04E-AD16-87ADF0B3D25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36240" yWindow="-5840" windowWidth="47980" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36240" yWindow="-5840" windowWidth="42680" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="409">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -1255,13 +1255,25 @@
   </si>
   <si>
     <t>proportion REM and developmental milestones</t>
+  </si>
+  <si>
+    <t>Heiss, W. D., Habedank, B., Klein, J. C., Herholz, K., Wienhard, K., Lenox, M., &amp; Nutt, R. (2004). Metabolic rates in small brain nuclei determined by high-resolution PET. J Nucl Med, 45(11), 1811-1815. https://www.ncbi.nlm.nih.gov/pubmed/15534048</t>
+  </si>
+  <si>
+    <t>WOS:000225086000011</t>
+  </si>
+  <si>
+    <t>TABLE 1 rCMRGlc Values</t>
+  </si>
+  <si>
+    <t>regional cerebral metabolic rates for glucose</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1302,6 +1314,13 @@
       <i/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1355,10 +1374,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1375,10 +1395,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1691,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH77"/>
+  <dimension ref="A1:AH78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.1640625" customWidth="1"/>
@@ -1860,15 +1883,15 @@
         <v>2025</v>
       </c>
       <c r="J2" t="str">
-        <f t="shared" ref="J2" si="5">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
+        <f>IF(C2&lt;&gt;"", C2, IF(C2="", _xlfn.TEXTAFTER(A2,"https://doi.org/"), C2))</f>
         <v>10.1002/cne.70089</v>
       </c>
       <c r="K2" t="str">
-        <f t="shared" ref="K2:K14" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
+        <f t="shared" ref="K2:K14" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
         <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L2" t="str">
-        <f t="shared" ref="L2:L14" si="7">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L2:L14" si="6">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M2" t="str">
@@ -1896,38 +1919,38 @@
         <v>41</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E4" si="8">RIGHT(A3,1)</f>
+        <f t="shared" ref="E3:E4" si="7">RIGHT(A3,1)</f>
         <v>5</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3" si="9">G3 &amp; IF(H3&lt;&gt;"", "_" &amp; H3, "_") &amp; IF(I3&lt;&gt;"", "_" &amp; I3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
+        <f t="shared" ref="F3" si="8">G3 &amp; IF(H3&lt;&gt;"", "_" &amp; H3, "_") &amp; IF(I3&lt;&gt;"", "_" &amp; I3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
         <v>Baron_etal_1983</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3" si="10">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G3" si="9">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3" si="11">IF(ISNUMBER(FIND("&amp;", A3)),
+        <f t="shared" ref="H3" si="10">IF(ISNUMBER(FIND("&amp;", A3)),
     IF(LEN(A3)-LEN(SUBSTITUTE(A3, ",", ""))&gt;=6, "etal", MID(A3, SEARCH("&amp; ", A3)+2, SEARCH(",", A3, SEARCH("&amp; ", A3)+2) - SEARCH("&amp; ", A3)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3" si="12">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+        <f t="shared" ref="I3" si="11">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>1983</v>
       </c>
-      <c r="J3" t="e">
-        <f t="shared" ref="J3" si="13">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
-        <v>#N/A</v>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J66" si="12">IF(C3&lt;&gt;"", C3, IF(C3="", _xlfn.TEXTAFTER(A3,"https://doi.org/"), C3))</f>
+        <v>10.0000/placeholder.1</v>
       </c>
       <c r="K3" t="str">
+        <f t="shared" si="5"/>
+        <v>Baron_etal_1983_Table1</v>
+      </c>
+      <c r="L3" t="str">
         <f t="shared" si="6"/>
-        <v>Baron_etal_1983_Table1</v>
-      </c>
-      <c r="L3" t="str">
-        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder.1_Table1</v>
       </c>
       <c r="M3" t="str">
@@ -1955,38 +1978,38 @@
         <v>41</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4" si="14">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
+        <f t="shared" ref="F4" si="13">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
         <v>Baron_etal_1987</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4" si="15">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G4" si="14">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4" si="16">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="H4" si="15">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=6, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4" si="17">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <f t="shared" ref="I4" si="16">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
         <v>1987</v>
       </c>
-      <c r="J4" t="e">
-        <f t="shared" ref="J4" si="18">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
-        <v>#N/A</v>
+      <c r="J4" t="str">
+        <f t="shared" si="12"/>
+        <v>10.0000/placeholder.2</v>
       </c>
       <c r="K4" t="str">
+        <f t="shared" si="5"/>
+        <v>Baron_etal_1987_Table1</v>
+      </c>
+      <c r="L4" t="str">
         <f t="shared" si="6"/>
-        <v>Baron_etal_1987_Table1</v>
-      </c>
-      <c r="L4" t="str">
-        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder.2_Table1</v>
       </c>
       <c r="M4" t="str">
@@ -2014,38 +2037,38 @@
         <v>47</v>
       </c>
       <c r="E5" t="str">
-        <f t="shared" ref="E5:E45" si="19">RIGHT(A5,1)</f>
+        <f t="shared" ref="E5:E46" si="17">RIGHT(A5,1)</f>
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" ref="F5:F45" si="20">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
+        <f t="shared" ref="F5:F46" si="18">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
         <v>Brodmann__1913</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" ref="G5:G45" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G5:G46" si="19">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
         <v>Brodmann</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H45" si="22">IF(ISNUMBER(FIND("&amp;", A5)),
+        <f t="shared" ref="H5:H46" si="20">IF(ISNUMBER(FIND("&amp;", A5)),
     IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
     ""
 )</f>
         <v/>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I45" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
+        <f t="shared" ref="I5:I46" si="21">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
         <v>1913</v>
       </c>
-      <c r="J5" t="e">
-        <f t="shared" ref="J5:J45" si="24">_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
-        <v>#N/A</v>
+      <c r="J5" t="str">
+        <f t="shared" si="12"/>
+        <v>10.0000/placeholder</v>
       </c>
       <c r="K5" t="str">
+        <f t="shared" si="5"/>
+        <v>Brodmann__1913_Tabelle1</v>
+      </c>
+      <c r="L5" t="str">
         <f t="shared" si="6"/>
-        <v>Brodmann__1913_Tabelle1</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
       <c r="M5" t="str">
@@ -2061,35 +2084,35 @@
         <v>49</v>
       </c>
       <c r="E6" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="18"/>
+        <v>Burger_etal_2019</v>
+      </c>
+      <c r="G6" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F6" t="str">
+        <v>Burger</v>
+      </c>
+      <c r="H6" t="str">
         <f t="shared" si="20"/>
-        <v>Burger_etal_2019</v>
-      </c>
-      <c r="G6" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I6" t="str">
         <f t="shared" si="21"/>
-        <v>Burger</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I6" t="str">
-        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="K6" t="str">
+        <f t="shared" si="5"/>
+        <v>Burger_etal_2019_SupplementaryDataSD1</v>
+      </c>
+      <c r="L6" t="str">
         <f t="shared" si="6"/>
-        <v>Burger_etal_2019_SupplementaryDataSD1</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="7"/>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="M6" t="str">
@@ -2145,35 +2168,35 @@
         <v>62</v>
       </c>
       <c r="E7" t="str">
+        <f t="shared" si="17"/>
+        <v>9</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="18"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="G7" t="str">
         <f t="shared" si="19"/>
-        <v>9</v>
-      </c>
-      <c r="F7" t="str">
+        <v>Burish</v>
+      </c>
+      <c r="H7" t="str">
         <f t="shared" si="20"/>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="G7" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I7" t="str">
         <f t="shared" si="21"/>
-        <v>Burish</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000319019</v>
       </c>
       <c r="K7" t="str">
+        <f t="shared" si="5"/>
+        <v>Burish_etal_2010_SupplementaryTable1</v>
+      </c>
+      <c r="L7" t="str">
         <f t="shared" si="6"/>
-        <v>Burish_etal_2010_SupplementaryTable1</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="7"/>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M7" t="str">
@@ -2207,35 +2230,35 @@
         <v>41</v>
       </c>
       <c r="E8" t="str">
+        <f t="shared" si="17"/>
+        <v>9</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="18"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="G8" t="str">
         <f t="shared" si="19"/>
-        <v>9</v>
-      </c>
-      <c r="F8" t="str">
+        <v>Burish</v>
+      </c>
+      <c r="H8" t="str">
         <f t="shared" si="20"/>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="G8" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I8" t="str">
         <f t="shared" si="21"/>
-        <v>Burish</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000319019</v>
       </c>
       <c r="K8" t="str">
+        <f t="shared" si="5"/>
+        <v>Burish_etal_2010_Table1</v>
+      </c>
+      <c r="L8" t="str">
         <f t="shared" si="6"/>
-        <v>Burish_etal_2010_Table1</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="7"/>
         <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M8" t="str">
@@ -2272,35 +2295,35 @@
         <v>74</v>
       </c>
       <c r="E9" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="18"/>
+        <v>Caspar_etal_2022</v>
+      </c>
+      <c r="G9" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F9" t="str">
+        <v>Caspar</v>
+      </c>
+      <c r="H9" t="str">
         <f t="shared" si="20"/>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="G9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I9" t="str">
         <f t="shared" si="21"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="23"/>
         <v>2022</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="K9" t="str">
+        <f t="shared" si="5"/>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
+      </c>
+      <c r="L9" t="str">
         <f t="shared" si="6"/>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="7"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M9" t="str">
@@ -2356,35 +2379,35 @@
         <v>41</v>
       </c>
       <c r="E10" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="18"/>
+        <v>Caspar_etal_2022</v>
+      </c>
+      <c r="G10" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F10" t="str">
+        <v>Caspar</v>
+      </c>
+      <c r="H10" t="str">
         <f t="shared" si="20"/>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="G10" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I10" t="str">
         <f t="shared" si="21"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="23"/>
         <v>2022</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="K10" t="str">
+        <f t="shared" si="5"/>
+        <v>Caspar_etal_2022_Table1</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="6"/>
-        <v>Caspar_etal_2022_Table1</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="7"/>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M10" t="str">
@@ -2442,35 +2465,35 @@
         <v>93</v>
       </c>
       <c r="E11" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="18"/>
+        <v>Changizi__2001</v>
+      </c>
+      <c r="G11" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F11" t="str">
+        <v>Changizi</v>
+      </c>
+      <c r="H11" t="str">
         <f t="shared" si="20"/>
-        <v>Changizi__2001</v>
-      </c>
-      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <f t="shared" si="21"/>
-        <v>Changizi</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="23"/>
         <v>2001</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1007/s004220000205</v>
       </c>
       <c r="K11" t="str">
+        <f t="shared" si="5"/>
+        <v>Changizi__2001_Figure3</v>
+      </c>
+      <c r="L11" t="str">
         <f t="shared" si="6"/>
-        <v>Changizi__2001_Figure3</v>
-      </c>
-      <c r="L11" t="str">
-        <f t="shared" si="7"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M11" t="str">
@@ -2519,35 +2542,35 @@
         <v>104</v>
       </c>
       <c r="E12" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="18"/>
+        <v>Chen_Wiens_2020</v>
+      </c>
+      <c r="G12" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F12" t="str">
+        <v>Chen</v>
+      </c>
+      <c r="H12" t="str">
         <f t="shared" si="20"/>
-        <v>Chen_Wiens_2020</v>
-      </c>
-      <c r="G12" t="str">
+        <v>Wiens</v>
+      </c>
+      <c r="I12" t="str">
         <f t="shared" si="21"/>
-        <v>Chen</v>
-      </c>
-      <c r="H12" t="str">
-        <f t="shared" si="22"/>
-        <v>Wiens</v>
-      </c>
-      <c r="I12" t="str">
-        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="K12" t="str">
+        <f t="shared" si="5"/>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
+      </c>
+      <c r="L12" t="str">
         <f t="shared" si="6"/>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
-      </c>
-      <c r="L12" t="str">
-        <f t="shared" si="7"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="M12" t="str">
@@ -2606,35 +2629,35 @@
         <v>112</v>
       </c>
       <c r="E13" t="str">
+        <f t="shared" si="17"/>
+        <v>7</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="18"/>
+        <v>Collins_etal_2010</v>
+      </c>
+      <c r="G13" t="str">
         <f t="shared" si="19"/>
-        <v>7</v>
-      </c>
-      <c r="F13" t="str">
+        <v>Collins</v>
+      </c>
+      <c r="H13" t="str">
         <f t="shared" si="20"/>
-        <v>Collins_etal_2010</v>
-      </c>
-      <c r="G13" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I13" t="str">
         <f t="shared" si="21"/>
-        <v>Collins</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I13" t="str">
-        <f t="shared" si="23"/>
         <v>2010</v>
       </c>
       <c r="J13" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1073/pnas.1010356107</v>
       </c>
       <c r="K13" t="str">
+        <f t="shared" si="5"/>
+        <v>Collins_etal_2010_DatasetS1</v>
+      </c>
+      <c r="L13" t="str">
         <f t="shared" si="6"/>
-        <v>Collins_etal_2010_DatasetS1</v>
-      </c>
-      <c r="L13" t="str">
-        <f t="shared" si="7"/>
         <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
       <c r="M13" t="str">
@@ -2656,35 +2679,35 @@
         <v>115</v>
       </c>
       <c r="E14" t="str">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="18"/>
+        <v>DeCasien_Higham_2019</v>
+      </c>
+      <c r="G14" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F14" t="str">
+        <v>DeCasien</v>
+      </c>
+      <c r="H14" t="str">
         <f t="shared" si="20"/>
-        <v>DeCasien_Higham_2019</v>
-      </c>
-      <c r="G14" t="str">
+        <v>Higham</v>
+      </c>
+      <c r="I14" t="str">
         <f t="shared" si="21"/>
-        <v>DeCasien</v>
-      </c>
-      <c r="H14" t="str">
-        <f t="shared" si="22"/>
-        <v>Higham</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J14" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K14" t="str">
+        <f t="shared" si="5"/>
+        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
+      </c>
+      <c r="L14" t="str">
         <f t="shared" si="6"/>
-        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
-      </c>
-      <c r="L14" t="str">
-        <f t="shared" si="7"/>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="M14" t="str">
@@ -2727,30 +2750,30 @@
         <v>121</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" ref="E15" si="25">RIGHT(A15,1)</f>
+        <f t="shared" ref="E15" si="22">RIGHT(A15,1)</f>
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" ref="F15" si="26">G15 &amp; IF(H15&lt;&gt;"", "_" &amp; H15, "_") &amp; IF(I15&lt;&gt;"", "_" &amp; I15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
+        <f t="shared" ref="F15" si="23">G15 &amp; IF(H15&lt;&gt;"", "_" &amp; H15, "_") &amp; IF(I15&lt;&gt;"", "_" &amp; I15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" ref="G15" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G15" si="24">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" ref="H15" si="28">IF(ISNUMBER(FIND("&amp;", A15)),
+        <f t="shared" ref="H15" si="25">IF(ISNUMBER(FIND("&amp;", A15)),
     IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" ref="I15" si="29">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
+        <f t="shared" ref="I15" si="26">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J15" t="str">
-        <f t="shared" ref="J15" si="30">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K15" t="str">
@@ -2798,30 +2821,30 @@
         <v>123</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" ref="E16" si="31">RIGHT(A16,1)</f>
+        <f t="shared" ref="E16" si="27">RIGHT(A16,1)</f>
         <v>0</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" ref="F16" si="32">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
+        <f t="shared" ref="F16" si="28">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" ref="G16" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G16" si="29">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" ref="H16" si="34">IF(ISNUMBER(FIND("&amp;", A16)),
+        <f t="shared" ref="H16" si="30">IF(ISNUMBER(FIND("&amp;", A16)),
     IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" ref="I16" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
+        <f t="shared" ref="I16" si="31">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J16" t="str">
-        <f t="shared" ref="J16" si="36">_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K16" t="str">
@@ -2869,38 +2892,38 @@
         <v>125</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17" si="37">RIGHT(A17,1)</f>
+        <f t="shared" ref="E17" si="32">RIGHT(A17,1)</f>
         <v>0</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" ref="F17" si="38">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <f t="shared" ref="F17" si="33">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" ref="G17" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G17" si="34">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" ref="H17" si="40">IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="H17" si="35">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" ref="I17" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <f t="shared" ref="I17" si="36">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" ref="J17" si="42">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" ref="K17:K48" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
+        <f t="shared" ref="K17:K49" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" ref="L17:L48" si="44">IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L17:L49" si="38">IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M17" t="str">
@@ -2940,35 +2963,35 @@
         <v>128</v>
       </c>
       <c r="E18" t="str">
+        <f t="shared" si="17"/>
+        <v>6</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="18"/>
+        <v>DosSantos_etal_2017</v>
+      </c>
+      <c r="G18" t="str">
         <f t="shared" si="19"/>
-        <v>6</v>
-      </c>
-      <c r="F18" t="str">
+        <v>DosSantos</v>
+      </c>
+      <c r="H18" t="str">
         <f t="shared" si="20"/>
-        <v>DosSantos_etal_2017</v>
-      </c>
-      <c r="G18" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I18" t="str">
         <f t="shared" si="21"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I18" t="str">
-        <f t="shared" si="23"/>
         <v>2017</v>
       </c>
       <c r="J18" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000452856</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M18" t="str">
@@ -3032,35 +3055,35 @@
         <v>41</v>
       </c>
       <c r="E19" t="str">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="18"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="G19" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F19" t="str">
+        <v>DosSantos</v>
+      </c>
+      <c r="H19" t="str">
         <f t="shared" si="20"/>
-        <v>DosSantos_etal_2020</v>
-      </c>
-      <c r="G19" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I19" t="str">
         <f t="shared" si="21"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J19" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="M19" t="str">
@@ -3112,38 +3135,38 @@
         <v>145</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" ref="E20" si="45">RIGHT(A20,1)</f>
+        <f t="shared" ref="E20" si="39">RIGHT(A20,1)</f>
         <v>0</v>
       </c>
       <c r="F20" t="str">
-        <f t="shared" ref="F20" si="46">G20 &amp; IF(H20&lt;&gt;"", "_" &amp; H20, "_") &amp; IF(I20&lt;&gt;"", "_" &amp; I20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
+        <f t="shared" ref="F20" si="40">G20 &amp; IF(H20&lt;&gt;"", "_" &amp; H20, "_") &amp; IF(I20&lt;&gt;"", "_" &amp; I20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" ref="G20" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G20" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
         <v>DosSantos</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" ref="H20" si="48">IF(ISNUMBER(FIND("&amp;", A20)),
+        <f t="shared" ref="H20" si="42">IF(ISNUMBER(FIND("&amp;", A20)),
     IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" ref="I20" si="49">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
+        <f t="shared" ref="I20" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
         <v>2020</v>
       </c>
       <c r="J20" t="str">
-        <f t="shared" ref="J20" si="50">_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>DosSantos_etal_2020_unpublished</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
       <c r="M20" t="str">
@@ -3195,38 +3218,38 @@
         <v>35</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" ref="E21" si="51">RIGHT(A21,1)</f>
+        <f t="shared" ref="E21" si="44">RIGHT(A21,1)</f>
         <v>3</v>
       </c>
       <c r="F21" t="str">
-        <f t="shared" ref="F21" si="52">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
+        <f t="shared" ref="F21" si="45">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
         <v>Eagleman_Vaughn_2021</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" ref="G21" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G21" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
         <v>Eagleman</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" ref="H21" si="54">IF(ISNUMBER(FIND("&amp;", A21)),
+        <f t="shared" ref="H21" si="47">IF(ISNUMBER(FIND("&amp;", A21)),
     IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
     ""
 )</f>
         <v>Vaughn</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" ref="I21" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
+        <f t="shared" ref="I21" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
         <v>2021</v>
       </c>
       <c r="J21" t="str">
-        <f t="shared" ref="J21" si="56">_xlfn.TEXTAFTER(A21,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.3389/fnins.2021.632853</v>
       </c>
       <c r="K21" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Eagleman_Vaughn_2021_TABLE1</v>
       </c>
       <c r="L21" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.3389%2Ffnins.2021.632853_TABLE1</v>
       </c>
       <c r="M21" t="str">
@@ -3255,35 +3278,35 @@
         <v>35</v>
       </c>
       <c r="E22" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="18"/>
+        <v>Falcone_etal_2019</v>
+      </c>
+      <c r="G22" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F22" t="str">
+        <v>Falcone</v>
+      </c>
+      <c r="H22" t="str">
         <f t="shared" si="20"/>
-        <v>Falcone_etal_2019</v>
-      </c>
-      <c r="G22" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I22" t="str">
         <f t="shared" si="21"/>
-        <v>Falcone</v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I22" t="str">
-        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="J22" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1002/cne.24605</v>
       </c>
       <c r="K22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Falcone_etal_2019_TABLE1</v>
       </c>
       <c r="L22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M22" t="str">
@@ -3309,38 +3332,38 @@
         <v>150</v>
       </c>
       <c r="E23" t="str">
-        <f t="shared" ref="E23" si="57">RIGHT(A23,1)</f>
+        <f t="shared" ref="E23" si="49">RIGHT(A23,1)</f>
         <v>5</v>
       </c>
       <c r="F23" t="str">
-        <f t="shared" ref="F23" si="58">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
+        <f t="shared" ref="F23" si="50">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
         <v>Falcone_etal_2019</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" ref="G23" si="59">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G23" si="51">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
         <v>Falcone</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" ref="H23" si="60">IF(ISNUMBER(FIND("&amp;", A23)),
+        <f t="shared" ref="H23" si="52">IF(ISNUMBER(FIND("&amp;", A23)),
     IF(LEN(A23)-LEN(SUBSTITUTE(A23, ",", ""))&gt;=6, "etal", MID(A23, SEARCH("&amp; ", A23)+2, SEARCH(",", A23, SEARCH("&amp; ", A23)+2) - SEARCH("&amp; ", A23)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" ref="I23" si="61">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
+        <f t="shared" ref="I23" si="53">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J23" t="str">
-        <f t="shared" ref="J23" si="62">_xlfn.TEXTAFTER(A23,"https://doi.org/")</f>
+        <f t="shared" si="12"/>
         <v>10.1002/cne.24605</v>
       </c>
       <c r="K23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Falcone_etal_2019_TABLE2</v>
       </c>
       <c r="L23" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1002%2Fcne.24605_TABLE2</v>
       </c>
       <c r="M23" t="str">
@@ -3366,35 +3389,35 @@
         <v>153</v>
       </c>
       <c r="E24" t="str">
+        <f t="shared" si="17"/>
+        <v>6</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="18"/>
+        <v>Finlay_etal_2006</v>
+      </c>
+      <c r="G24" t="str">
         <f t="shared" si="19"/>
-        <v>6</v>
-      </c>
-      <c r="F24" t="str">
+        <v>Finlay</v>
+      </c>
+      <c r="H24" t="str">
         <f t="shared" si="20"/>
-        <v>Finlay_etal_2006</v>
-      </c>
-      <c r="G24" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I24" t="str">
         <f t="shared" si="21"/>
-        <v>Finlay</v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="23"/>
         <v>2006</v>
       </c>
       <c r="J24" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="K24" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="L24" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M24" t="str">
@@ -3450,35 +3473,35 @@
         <v>41</v>
       </c>
       <c r="E25" t="str">
+        <f t="shared" si="17"/>
+        <v>x</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="18"/>
+        <v>Fu_etal_2013</v>
+      </c>
+      <c r="G25" t="str">
         <f t="shared" si="19"/>
-        <v>x</v>
-      </c>
-      <c r="F25" t="str">
+        <v>Fu</v>
+      </c>
+      <c r="H25" t="str">
         <f t="shared" si="20"/>
-        <v>Fu_etal_2013</v>
-      </c>
-      <c r="G25" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I25" t="str">
         <f t="shared" si="21"/>
-        <v>Fu</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I25" t="str">
-        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J25" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="K25" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Fu_etal_2013_Table1</v>
       </c>
       <c r="L25" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M25" t="str">
@@ -3506,35 +3529,35 @@
         <v>128</v>
       </c>
       <c r="E26" t="str">
+        <f t="shared" si="17"/>
+        <v>6</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="18"/>
+        <v>Garwicz_etal_2009</v>
+      </c>
+      <c r="G26" t="str">
         <f t="shared" si="19"/>
-        <v>6</v>
-      </c>
-      <c r="F26" t="str">
+        <v>Garwicz</v>
+      </c>
+      <c r="H26" t="str">
         <f t="shared" si="20"/>
-        <v>Garwicz_etal_2009</v>
-      </c>
-      <c r="G26" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I26" t="str">
         <f t="shared" si="21"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I26" t="str">
-        <f t="shared" si="23"/>
         <v>2009</v>
       </c>
       <c r="J26" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K26" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Garwicz_etal_2009_TableS1</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M26" t="str">
@@ -3562,35 +3585,35 @@
         <v>165</v>
       </c>
       <c r="E27" t="str">
+        <f t="shared" si="17"/>
+        <v>6</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="18"/>
+        <v>Garwicz_etal_2009</v>
+      </c>
+      <c r="G27" t="str">
         <f t="shared" si="19"/>
-        <v>6</v>
-      </c>
-      <c r="F27" t="str">
+        <v>Garwicz</v>
+      </c>
+      <c r="H27" t="str">
         <f t="shared" si="20"/>
-        <v>Garwicz_etal_2009</v>
-      </c>
-      <c r="G27" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I27" t="str">
         <f t="shared" si="21"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="23"/>
         <v>2009</v>
       </c>
       <c r="J27" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Garwicz_etal_2009_TableS2</v>
       </c>
       <c r="L27" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M27" t="str">
@@ -3618,35 +3641,35 @@
         <v>165</v>
       </c>
       <c r="E28" t="str">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="18"/>
+        <v>Genoud_etal_2018</v>
+      </c>
+      <c r="G28" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F28" t="str">
+        <v>Genoud</v>
+      </c>
+      <c r="H28" t="str">
         <f t="shared" si="20"/>
-        <v>Genoud_etal_2018</v>
-      </c>
-      <c r="G28" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I28" t="str">
         <f t="shared" si="21"/>
-        <v>Genoud</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="23"/>
         <v>2018</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1111/brv.12350</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="M28" t="str">
@@ -3671,35 +3694,35 @@
         <v>128</v>
       </c>
       <c r="E29" t="str">
+        <f t="shared" si="17"/>
+        <v>8</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="18"/>
+        <v>Granatosky__2018</v>
+      </c>
+      <c r="G29" t="str">
         <f t="shared" si="19"/>
-        <v>8</v>
-      </c>
-      <c r="F29" t="str">
+        <v>Granatosky</v>
+      </c>
+      <c r="H29" t="str">
         <f t="shared" si="20"/>
-        <v>Granatosky__2018</v>
-      </c>
-      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <f t="shared" si="21"/>
-        <v>Granatosky</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="23"/>
         <v>2018</v>
       </c>
       <c r="J29" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1111/jzo.12608</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Granatosky__2018_TableS1</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1111%2Fjzo.12608_TableS1</v>
       </c>
       <c r="M29" t="str">
@@ -3721,35 +3744,35 @@
         <v>173</v>
       </c>
       <c r="E30" t="str">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="18"/>
+        <v>Heffner_Masterton_1975</v>
+      </c>
+      <c r="G30" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="F30" t="str">
+        <v>Heffner</v>
+      </c>
+      <c r="H30" t="str">
         <f t="shared" si="20"/>
-        <v>Heffner_Masterton_1975</v>
-      </c>
-      <c r="G30" t="str">
+        <v>Masterton</v>
+      </c>
+      <c r="I30" t="str">
         <f t="shared" si="21"/>
-        <v>Heffner</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="22"/>
-        <v>Masterton</v>
-      </c>
-      <c r="I30" t="str">
-        <f t="shared" si="23"/>
         <v>1975</v>
       </c>
       <c r="J30" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000124401</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="L30" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M30" t="str">
@@ -3801,35 +3824,35 @@
         <v>173</v>
       </c>
       <c r="E31" t="str">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="18"/>
+        <v>Heffner_Masterton_1983</v>
+      </c>
+      <c r="G31" t="str">
         <f t="shared" si="19"/>
-        <v>4</v>
-      </c>
-      <c r="F31" t="str">
+        <v>Heffner</v>
+      </c>
+      <c r="H31" t="str">
         <f t="shared" si="20"/>
-        <v>Heffner_Masterton_1983</v>
-      </c>
-      <c r="G31" t="str">
+        <v>Masterton</v>
+      </c>
+      <c r="I31" t="str">
         <f t="shared" si="21"/>
-        <v>Heffner</v>
-      </c>
-      <c r="H31" t="str">
-        <f t="shared" si="22"/>
-        <v>Masterton</v>
-      </c>
-      <c r="I31" t="str">
-        <f t="shared" si="23"/>
         <v>1983</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000121494</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="L31" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="M31" t="str">
@@ -3868,270 +3891,288 @@
     </row>
     <row r="32" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>181</v>
+        <v>405</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>406</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="E32" si="54">RIGHT(A32,1)</f>
         <v>8</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="20"/>
-        <v>Heldstab_etal_2016</v>
+        <f t="shared" ref="F32" si="55">G32 &amp; IF(H32&lt;&gt;"", "_" &amp; H32, "_") &amp; IF(I32&lt;&gt;"", "_" &amp; I32, "_") &amp; IF(B32&lt;&gt;"", "_" &amp; B32, "")</f>
+        <v>Heiss_etal_2004</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="21"/>
-        <v>Heldstab</v>
+        <f t="shared" ref="G32" si="56">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A32,","), "-", ""), " ", "")</f>
+        <v>Heiss</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="H32" si="57">IF(ISNUMBER(FIND("&amp;", A32)),
+    IF(LEN(A32)-LEN(SUBSTITUTE(A32, ",", ""))&gt;=6, "etal", MID(A32, SEARCH("&amp; ", A32)+2, SEARCH(",", A32, SEARCH("&amp; ", A32)+2) - SEARCH("&amp; ", A32)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="23"/>
-        <v>2016</v>
+        <f t="shared" ref="I32" si="58">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A32, "("), ")")</f>
+        <v>2004</v>
       </c>
       <c r="J32" t="str">
-        <f t="shared" si="24"/>
-        <v>10.1038/srep24528</v>
+        <f t="shared" si="12"/>
+        <v>WOS:000225086000011</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" si="43"/>
-        <v>Heldstab_etal_2016_TableS1</v>
+        <f t="shared" ref="K32" si="59">TRIM(_xlfn.TEXTJOIN("_",FALSE,F32,(SUBSTITUTE(SUBSTITUTE(D32," ",""), "_", ""))))</f>
+        <v>Heiss_etal_2004_TABLE1</v>
       </c>
       <c r="L32" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1038%2Fsrep24528_TableS1</v>
+        <f t="shared" ref="L32" si="60">IF(ISBLANK(C32),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>WOS%3A000225086000011_TABLE1</v>
       </c>
       <c r="M32" t="str">
         <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="N32" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
       <c r="R32" s="4"/>
-      <c r="T32" s="1" t="str">
-        <f>IF(S32="N", R32, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="12"/>
       <c r="Y32" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE32" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="AE32" s="1"/>
+      <c r="AG32" s="12"/>
     </row>
     <row r="33" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="17"/>
+        <v>8</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="18"/>
+        <v>Heldstab_etal_2016</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="19"/>
+        <v>Heldstab</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="20"/>
+        <v>etal</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="21"/>
+        <v>2016</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1038/srep24528</v>
+      </c>
+      <c r="K33" t="str">
+        <f t="shared" si="37"/>
+        <v>Heldstab_etal_2016_TableS1</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="38"/>
+        <v>10.1038%2Fsrep24528_TableS1</v>
+      </c>
+      <c r="M33" t="str">
+        <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R33" s="4"/>
+      <c r="T33" s="1" t="str">
+        <f>IF(S33="N", R33, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E33" t="str">
-        <f t="shared" ref="E33" si="63">RIGHT(A33,1)</f>
+      <c r="E34" t="str">
+        <f t="shared" ref="E34" si="61">RIGHT(A34,1)</f>
         <v>3</v>
       </c>
-      <c r="F33" t="str">
-        <f t="shared" ref="F33" si="64">G33 &amp; IF(H33&lt;&gt;"", "_" &amp; H33, "_") &amp; IF(I33&lt;&gt;"", "_" &amp; I33, "_") &amp; IF(B33&lt;&gt;"", "_" &amp; B33, "")</f>
+      <c r="F34" t="str">
+        <f t="shared" ref="F34" si="62">G34 &amp; IF(H34&lt;&gt;"", "_" &amp; H34, "_") &amp; IF(I34&lt;&gt;"", "_" &amp; I34, "_") &amp; IF(B34&lt;&gt;"", "_" &amp; B34, "")</f>
         <v>HerculanoHouzel__2015</v>
       </c>
-      <c r="G33" t="str">
-        <f t="shared" ref="G33" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A33,","), "-", ""), " ", "")</f>
+      <c r="G34" t="str">
+        <f t="shared" ref="G34" si="63">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A34,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="H33" t="str">
-        <f t="shared" ref="H33" si="66">IF(ISNUMBER(FIND("&amp;", A33)),
-    IF(LEN(A33)-LEN(SUBSTITUTE(A33, ",", ""))&gt;=6, "etal", MID(A33, SEARCH("&amp; ", A33)+2, SEARCH(",", A33, SEARCH("&amp; ", A33)+2) - SEARCH("&amp; ", A33)-2)),
+      <c r="H34" t="str">
+        <f t="shared" ref="H34" si="64">IF(ISNUMBER(FIND("&amp;", A34)),
+    IF(LEN(A34)-LEN(SUBSTITUTE(A34, ",", ""))&gt;=6, "etal", MID(A34, SEARCH("&amp; ", A34)+2, SEARCH(",", A34, SEARCH("&amp; ", A34)+2) - SEARCH("&amp; ", A34)-2)),
     ""
 )</f>
         <v/>
       </c>
-      <c r="I33" t="str">
-        <f t="shared" ref="I33" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A33, "("), ")")</f>
+      <c r="I34" t="str">
+        <f t="shared" ref="I34" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, "("), ")")</f>
         <v>2015</v>
       </c>
-      <c r="J33" t="str">
-        <f t="shared" ref="J33" si="68">_xlfn.TEXTAFTER(A33,"https://doi.org/")</f>
+      <c r="J34" t="str">
+        <f t="shared" si="12"/>
         <v>10.1098/rspb.2015.1853</v>
       </c>
-      <c r="K33" t="str">
-        <f t="shared" si="43"/>
+      <c r="K34" t="str">
+        <f t="shared" si="37"/>
         <v>HerculanoHouzel__2015_Table2</v>
       </c>
-      <c r="L33" t="str">
-        <f t="shared" si="44"/>
+      <c r="L34" t="str">
+        <f t="shared" si="38"/>
         <v>10.1098%2Frspb.2015.1853_Table2</v>
-      </c>
-      <c r="M33" t="str">
-        <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="R33" s="4"/>
-      <c r="U33" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="V33" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y33" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="Z33" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" t="str">
-        <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F34" t="str">
-        <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="G34" t="str">
-        <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H34" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I34" t="str">
-        <f t="shared" si="23"/>
-        <v>2013</v>
-      </c>
-      <c r="J34" t="str">
-        <f t="shared" si="24"/>
-        <v>10.3389/fnana.2013.00035</v>
-      </c>
-      <c r="K34" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
-      </c>
-      <c r="L34" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M34" t="str">
         <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R34" s="4"/>
+      <c r="U34" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="V34" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y34" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="Z34" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="G35" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F35" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H35" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="G35" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I35" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I35" t="str">
-        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="L35" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+        <f t="shared" si="38"/>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M35" t="str">
         <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E36" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="G36" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F36" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H36" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="G36" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I36" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H36" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I36" t="str">
-        <f t="shared" si="23"/>
         <v>2013</v>
       </c>
       <c r="J36" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="L36" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+        <f t="shared" si="38"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="M36" t="str">
         <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>52</v>
@@ -4139,88 +4180,49 @@
     </row>
     <row r="37" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
       <c r="E37" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="G37" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F37" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H37" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="G37" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I37" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H37" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I37" t="str">
-        <f t="shared" si="23"/>
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="J37" t="str">
-        <f t="shared" si="24"/>
-        <v>10.1159/000437413</v>
+        <f t="shared" si="12"/>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2015_Table1</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="L37" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159%2F000437413_Table1</v>
+        <f t="shared" si="38"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="M37" t="str">
         <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>51</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R37" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA37" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB37" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE37" s="1" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4228,46 +4230,46 @@
         <v>188</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>194</v>
+        <v>41</v>
       </c>
       <c r="E38" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="G38" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F38" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H38" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="G38" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I38" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H38" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I38" t="str">
-        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K38" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2015_Table2</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="L38" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159%2F000437413_Table2</v>
+        <f t="shared" si="38"/>
+        <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="M38" t="str">
         <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table2.tsv</v>
+        <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>51</v>
@@ -4276,13 +4278,13 @@
         <v>70</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="U38" s="1" t="s">
         <v>86</v>
@@ -4314,46 +4316,46 @@
         <v>188</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E39" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="G39" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F39" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H39" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="G39" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I39" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I39" t="str">
-        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2015_Table3</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="L39" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159%2F000437413_Table3</v>
+        <f t="shared" si="38"/>
+        <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="M39" t="str">
         <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table3.tsv</v>
+        <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>51</v>
@@ -4362,13 +4364,13 @@
         <v>70</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="U39" s="1" t="s">
         <v>86</v>
@@ -4395,51 +4397,51 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E40" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="G40" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F40" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H40" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="G40" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I40" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J40" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K40" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2015_Table4</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="L40" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159%2F000437413_Table4</v>
+        <f t="shared" si="38"/>
+        <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="M40" t="str">
         <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table4.tsv</v>
+        <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>51</v>
@@ -4448,13 +4450,13 @@
         <v>70</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="U40" s="1" t="s">
         <v>86</v>
@@ -4486,46 +4488,46 @@
         <v>188</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E41" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="G41" t="str">
         <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="F41" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H41" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="G41" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I41" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I41" t="str">
-        <f t="shared" si="23"/>
         <v>2015</v>
       </c>
       <c r="J41" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2015_Table5</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="L41" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159%2F000437413_Table5</v>
+        <f t="shared" si="38"/>
+        <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="M41" t="str">
         <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table5.tsv</v>
+        <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>51</v>
@@ -4534,13 +4536,13 @@
         <v>70</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="U41" s="1" t="s">
         <v>86</v>
@@ -4569,49 +4571,49 @@
     </row>
     <row r="42" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="E42" t="str">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="G42" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F42" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H42" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="G42" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I42" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H42" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I42" t="str">
-        <f t="shared" si="23"/>
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="J42" t="str">
-        <f t="shared" si="24"/>
-        <v>10.1002/cne.24985</v>
+        <f t="shared" si="12"/>
+        <v>10.1159/000437413</v>
       </c>
       <c r="K42" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2020_TABLE1</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="L42" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1002%2Fcne.24985_TABLE1</v>
+        <f t="shared" si="38"/>
+        <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="M42" t="str">
         <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+        <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>51</v>
@@ -4620,13 +4622,13 @@
         <v>70</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="U42" s="1" t="s">
         <v>86</v>
@@ -4635,10 +4637,13 @@
         <v>36</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>136</v>
@@ -4647,7 +4652,7 @@
         <v>136</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4655,46 +4660,46 @@
         <v>210</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="E43" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="G43" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="F43" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H43" t="str">
         <f t="shared" si="20"/>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="G43" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I43" t="str">
         <f t="shared" si="21"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I43" t="str">
-        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="J43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="K43" t="str">
-        <f t="shared" si="43"/>
-        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L43" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1002%2Fcne.24985_TABLE2</v>
+        <f t="shared" si="38"/>
+        <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M43" t="str">
         <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>51</v>
@@ -4703,13 +4708,13 @@
         <v>70</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="U43" s="1" t="s">
         <v>86</v>
@@ -4721,7 +4726,7 @@
         <v>99</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AA43" s="1" t="s">
         <v>136</v>
@@ -4735,49 +4740,85 @@
     </row>
     <row r="44" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
       <c r="E44" t="str">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="18"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="G44" t="str">
         <f t="shared" si="19"/>
-        <v>4</v>
-      </c>
-      <c r="F44" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H44" t="str">
         <f t="shared" si="20"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G44" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I44" t="str">
         <f t="shared" si="21"/>
-        <v>Isler</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I44" t="str">
-        <f t="shared" si="23"/>
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="J44" t="str">
-        <f t="shared" si="24"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="12"/>
+        <v>10.1002/cne.24985</v>
       </c>
       <c r="K44" t="str">
-        <f t="shared" si="43"/>
-        <v>Isler_etal_2008_Table2</v>
+        <f t="shared" si="37"/>
+        <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="L44" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+        <f t="shared" si="38"/>
+        <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="M44" t="str">
         <f t="array" ref="M44">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE44" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4785,43 +4826,43 @@
         <v>220</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="E45" t="str">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="18"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G45" t="str">
         <f t="shared" si="19"/>
-        <v>4</v>
-      </c>
-      <c r="F45" t="str">
+        <v>Isler</v>
+      </c>
+      <c r="H45" t="str">
         <f t="shared" si="20"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G45" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I45" t="str">
         <f t="shared" si="21"/>
-        <v>Isler</v>
-      </c>
-      <c r="H45" t="str">
-        <f t="shared" si="22"/>
-        <v>etal</v>
-      </c>
-      <c r="I45" t="str">
-        <f t="shared" si="23"/>
         <v>2008</v>
       </c>
       <c r="J45" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="43"/>
-        <v>Isler_etal_2008_Table7</v>
+        <f t="shared" si="37"/>
+        <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="L45" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+        <f t="shared" si="38"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="M45" t="str">
         <f t="array" ref="M45">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>52</v>
@@ -4832,93 +4873,93 @@
         <v>220</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="18"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="19"/>
+        <v>Isler</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="20"/>
+        <v>etal</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="21"/>
+        <v>2008</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="37"/>
+        <v>Isler_etal_2008_Table7</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="38"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E46" t="str">
-        <f t="shared" ref="E46:E77" si="69">RIGHT(A46,1)</f>
+      <c r="E47" t="str">
+        <f t="shared" ref="E47:E78" si="66">RIGHT(A47,1)</f>
         <v>4</v>
       </c>
-      <c r="F46" t="str">
-        <f t="shared" ref="F46:F77" si="70">G46 &amp; IF(H46&lt;&gt;"", "_" &amp; H46, "_") &amp; IF(I46&lt;&gt;"", "_" &amp; I46, "_") &amp; IF(B46&lt;&gt;"", "_" &amp; B46, "")</f>
+      <c r="F47" t="str">
+        <f t="shared" ref="F47:F78" si="67">G47 &amp; IF(H47&lt;&gt;"", "_" &amp; H47, "_") &amp; IF(I47&lt;&gt;"", "_" &amp; I47, "_") &amp; IF(B47&lt;&gt;"", "_" &amp; B47, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="G46" t="str">
-        <f t="shared" ref="G46:G77" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+      <c r="G47" t="str">
+        <f t="shared" ref="G47:G78" si="68">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="H46" t="str">
-        <f t="shared" ref="H46:H77" si="72">IF(ISNUMBER(FIND("&amp;", A46)),
-    IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=6, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
+      <c r="H47" t="str">
+        <f t="shared" ref="H47:H78" si="69">IF(ISNUMBER(FIND("&amp;", A47)),
+    IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=6, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I46" t="str">
-        <f t="shared" ref="I46:I77" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+      <c r="I47" t="str">
+        <f t="shared" ref="I47:I78" si="70">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="J46" t="str">
-        <f t="shared" ref="J46:J77" si="74">_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
+      <c r="J47" t="str">
+        <f t="shared" si="12"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="K46" t="str">
-        <f t="shared" si="43"/>
+      <c r="K47" t="str">
+        <f t="shared" si="37"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="L46" t="str">
-        <f t="shared" si="44"/>
+      <c r="L47" t="str">
+        <f t="shared" si="38"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
-      </c>
-      <c r="M46" t="str">
-        <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E47" t="str">
-        <f t="shared" si="69"/>
-        <v>4</v>
-      </c>
-      <c r="F47" t="str">
-        <f t="shared" si="70"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G47" t="str">
-        <f t="shared" si="71"/>
-        <v>Isler</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I47" t="str">
-        <f t="shared" si="73"/>
-        <v>2008</v>
-      </c>
-      <c r="J47" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="K47" t="str">
-        <f t="shared" si="43"/>
-        <v>Isler_etal_2008_TableS2</v>
-      </c>
-      <c r="L47" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M47" t="str">
         <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="Q47" s="1" t="s">
         <v>52</v>
@@ -4929,43 +4970,43 @@
         <v>220</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="E48" t="str">
+        <f t="shared" si="66"/>
+        <v>4</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="67"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="68"/>
+        <v>Isler</v>
+      </c>
+      <c r="H48" t="str">
         <f t="shared" si="69"/>
-        <v>4</v>
-      </c>
-      <c r="F48" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I48" t="str">
         <f t="shared" si="70"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G48" t="str">
-        <f t="shared" si="71"/>
-        <v>Isler</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I48" t="str">
-        <f t="shared" si="73"/>
         <v>2008</v>
       </c>
       <c r="J48" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="12"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="43"/>
-        <v>Isler_etal_2008_TableS3</v>
+        <f t="shared" si="37"/>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L48" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+        <f t="shared" si="38"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M48" t="str">
         <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="Q48" s="1" t="s">
         <v>52</v>
@@ -4976,43 +5017,43 @@
         <v>220</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E49" t="str">
+        <f t="shared" si="66"/>
+        <v>4</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="67"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="68"/>
+        <v>Isler</v>
+      </c>
+      <c r="H49" t="str">
         <f t="shared" si="69"/>
-        <v>4</v>
-      </c>
-      <c r="F49" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I49" t="str">
         <f t="shared" si="70"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G49" t="str">
-        <f t="shared" si="71"/>
-        <v>Isler</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I49" t="str">
-        <f t="shared" si="73"/>
         <v>2008</v>
       </c>
       <c r="J49" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="12"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K49" t="str">
-        <f t="shared" ref="K49:K77" si="75">TRIM(_xlfn.TEXTJOIN("_",FALSE,F49,(SUBSTITUTE(SUBSTITUTE(D49," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
+        <f t="shared" si="37"/>
+        <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L49" t="str">
-        <f t="shared" ref="L49:L77" si="76">IF(ISBLANK(C49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C49, SUBSTITUTE(D49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
+        <f t="shared" si="38"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M49" t="str">
         <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="Q49" s="1" t="s">
         <v>52</v>
@@ -5020,58 +5061,49 @@
     </row>
     <row r="50" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E50" t="str">
+        <f t="shared" si="66"/>
+        <v>4</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="67"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="68"/>
+        <v>Isler</v>
+      </c>
+      <c r="H50" t="str">
         <f t="shared" si="69"/>
-        <v>x</v>
-      </c>
-      <c r="F50" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I50" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="G50" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H50" t="str">
-        <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I50" t="str">
-        <f t="shared" si="73"/>
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="J50" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" si="12"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_1999_References</v>
+        <f t="shared" ref="K50:K78" si="71">TRIM(_xlfn.TEXTJOIN("_",FALSE,F50,(SUBSTITUTE(SUBSTITUTE(D50," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L50" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
+        <f t="shared" ref="L50:L78" si="72">IF(ISBLANK(C50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M50" t="str">
         <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N50" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V50" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="W50" s="1" t="s">
-        <v>99</v>
+      <c r="Q50" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5079,52 +5111,52 @@
         <v>224</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>225</v>
       </c>
       <c r="E51" t="str">
+        <f t="shared" si="66"/>
+        <v>x</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H51" t="str">
         <f t="shared" si="69"/>
-        <v>x</v>
-      </c>
-      <c r="F51" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I51" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="G51" t="str">
+        <v>1999</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
+      </c>
+      <c r="K51" t="str">
         <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H51" t="str">
+        <v>Iwaniuk_etal_1999_References</v>
+      </c>
+      <c r="L51" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I51" t="str">
-        <f t="shared" si="73"/>
-        <v>1999</v>
-      </c>
-      <c r="J51" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
-      </c>
-      <c r="K51" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_1999_Table1</v>
-      </c>
-      <c r="L51" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M51" t="str">
         <f t="array" ref="M51">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>160</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="W51" s="1" t="s">
         <v>99</v>
@@ -5132,72 +5164,58 @@
     </row>
     <row r="52" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E52" t="str">
+        <f t="shared" si="66"/>
+        <v>x</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H52" t="str">
         <f t="shared" si="69"/>
-        <v>9</v>
-      </c>
-      <c r="F52" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I52" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="G52" t="str">
+        <v>1999</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
+      </c>
+      <c r="K52" t="str">
         <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H52" t="str">
+        <v>Iwaniuk_etal_1999_Table1</v>
+      </c>
+      <c r="L52" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I52" t="str">
-        <f t="shared" si="73"/>
-        <v>2001</v>
-      </c>
-      <c r="J52" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1037/0735-7036.115.1.29</v>
-      </c>
-      <c r="K52" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_2001_Table1</v>
-      </c>
-      <c r="L52" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M52" t="str">
         <f t="array" ref="M52">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R52" s="4"/>
-      <c r="T52" s="1" t="str">
-        <f>IF(S52="N", R52, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="V52" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y52" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE52" s="1" t="s">
-        <v>232</v>
+      <c r="W52" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5205,46 +5223,46 @@
         <v>228</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>194</v>
+        <v>41</v>
       </c>
       <c r="E53" t="str">
+        <f t="shared" si="66"/>
+        <v>9</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H53" t="str">
         <f t="shared" si="69"/>
-        <v>9</v>
-      </c>
-      <c r="F53" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I53" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="G53" t="str">
+        <v>2001</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1037/0735-7036.115.1.29</v>
+      </c>
+      <c r="K53" t="str">
         <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H53" t="str">
+        <v>Iwaniuk_etal_2001_Table1</v>
+      </c>
+      <c r="L53" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I53" t="str">
-        <f t="shared" si="73"/>
-        <v>2001</v>
-      </c>
-      <c r="J53" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1037/0735-7036.115.1.29</v>
-      </c>
-      <c r="K53" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_2001_Table2</v>
-      </c>
-      <c r="L53" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M53" t="str">
         <f t="array" ref="M53">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>230</v>
@@ -5275,46 +5293,46 @@
         <v>228</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E54" t="str">
+        <f t="shared" si="66"/>
+        <v>9</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H54" t="str">
         <f t="shared" si="69"/>
-        <v>9</v>
-      </c>
-      <c r="F54" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I54" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="G54" t="str">
+        <v>2001</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1037/0735-7036.115.1.29</v>
+      </c>
+      <c r="K54" t="str">
         <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H54" t="str">
+        <v>Iwaniuk_etal_2001_Table2</v>
+      </c>
+      <c r="L54" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I54" t="str">
-        <f t="shared" si="73"/>
-        <v>2001</v>
-      </c>
-      <c r="J54" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1037/0735-7036.115.1.29</v>
-      </c>
-      <c r="K54" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_2001_Table3</v>
-      </c>
-      <c r="L54" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M54" t="str">
         <f t="array" ref="M54">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>230</v>
@@ -5345,46 +5363,46 @@
         <v>228</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E55" t="str">
+        <f t="shared" si="66"/>
+        <v>9</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H55" t="str">
         <f t="shared" si="69"/>
-        <v>9</v>
-      </c>
-      <c r="F55" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I55" t="str">
         <f t="shared" si="70"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="G55" t="str">
+        <v>2001</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1037/0735-7036.115.1.29</v>
+      </c>
+      <c r="K55" t="str">
         <f t="shared" si="71"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="H55" t="str">
+        <v>Iwaniuk_etal_2001_Table3</v>
+      </c>
+      <c r="L55" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I55" t="str">
-        <f t="shared" si="73"/>
-        <v>2001</v>
-      </c>
-      <c r="J55" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1037/0735-7036.115.1.29</v>
-      </c>
-      <c r="K55" t="str">
-        <f t="shared" si="75"/>
-        <v>Iwaniuk_etal_2001_Table4</v>
-      </c>
-      <c r="L55" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M55" t="str">
         <f t="array" ref="M55">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>230</v>
@@ -5412,64 +5430,60 @@
     </row>
     <row r="56" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="E56" t="str">
+        <f t="shared" si="66"/>
+        <v>9</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="67"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="68"/>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="H56" t="str">
         <f t="shared" si="69"/>
-        <v>8</v>
-      </c>
-      <c r="F56" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I56" t="str">
         <f t="shared" si="70"/>
-        <v>JardimMesseder_etal_2017</v>
-      </c>
-      <c r="G56" t="str">
+        <v>2001</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1037/0735-7036.115.1.29</v>
+      </c>
+      <c r="K56" t="str">
         <f t="shared" si="71"/>
-        <v>JardimMesseder</v>
-      </c>
-      <c r="H56" t="str">
+        <v>Iwaniuk_etal_2001_Table4</v>
+      </c>
+      <c r="L56" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I56" t="str">
-        <f t="shared" si="73"/>
-        <v>2017</v>
-      </c>
-      <c r="J56" t="str">
-        <f t="shared" si="74"/>
-        <v>10.3389/fnana.2017.00118</v>
-      </c>
-      <c r="K56" t="str">
-        <f t="shared" si="75"/>
-        <v>JardimMesseder_etal_2017_Table1</v>
-      </c>
-      <c r="L56" t="str">
-        <f t="shared" si="76"/>
-        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M56" t="str">
         <f t="array" ref="M56">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>51</v>
+        <v>230</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R56" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>239</v>
+        <v>95</v>
+      </c>
+      <c r="R56" s="4"/>
+      <c r="T56" s="1" t="str">
+        <f>IF(S56="N", R56, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U56" s="1" t="s">
         <v>86</v>
@@ -5477,75 +5491,74 @@
       <c r="V56" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W56" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X56" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="Y56" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA56" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB56" s="1" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="AE56" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E57" t="str">
+        <f t="shared" si="66"/>
+        <v>8</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="67"/>
+        <v>JardimMesseder_etal_2017</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="68"/>
+        <v>JardimMesseder</v>
+      </c>
+      <c r="H57" t="str">
         <f t="shared" si="69"/>
-        <v>9</v>
-      </c>
-      <c r="F57" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I57" t="str">
         <f t="shared" si="70"/>
-        <v>Karl_etal_2024</v>
-      </c>
-      <c r="G57" t="str">
+        <v>2017</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="12"/>
+        <v>10.3389/fnana.2017.00118</v>
+      </c>
+      <c r="K57" t="str">
         <f t="shared" si="71"/>
-        <v>Karl</v>
-      </c>
-      <c r="H57" t="str">
+        <v>JardimMesseder_etal_2017_Table1</v>
+      </c>
+      <c r="L57" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I57" t="str">
-        <f t="shared" si="73"/>
-        <v>2024</v>
-      </c>
-      <c r="J57" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1002/cne.25669</v>
-      </c>
-      <c r="K57" t="str">
-        <f t="shared" si="75"/>
-        <v>Karl_etal_2024_TABLE1</v>
-      </c>
-      <c r="L57" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1002%2Fcne.25669_TABLE1</v>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="M57" t="str">
         <f t="array" ref="M57">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
+        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="R57" s="4"/>
+        <v>237</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="U57" s="1" t="s">
         <v>86</v>
       </c>
@@ -5553,93 +5566,88 @@
         <v>36</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="X57" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>244</v>
+        <v>135</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="AA57" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB57" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE57" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="58" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E58" t="str">
+        <f t="shared" si="66"/>
+        <v>9</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="67"/>
+        <v>Karl_etal_2024</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="68"/>
+        <v>Karl</v>
+      </c>
+      <c r="H58" t="str">
         <f t="shared" si="69"/>
-        <v>8</v>
-      </c>
-      <c r="F58" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I58" t="str">
         <f t="shared" si="70"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="G58" t="str">
+        <v>2024</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1002/cne.25669</v>
+      </c>
+      <c r="K58" t="str">
         <f t="shared" si="71"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="H58" t="str">
+        <v>Karl_etal_2024_TABLE1</v>
+      </c>
+      <c r="L58" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I58" t="str">
-        <f t="shared" si="73"/>
-        <v>2018</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1038/s41598-018-26062-8</v>
-      </c>
-      <c r="K58" t="str">
-        <f t="shared" si="75"/>
-        <v>Kverkova_etal_2018_Table1</v>
-      </c>
-      <c r="L58" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+        <v>10.1002%2Fcne.25669_TABLE1</v>
       </c>
       <c r="M58" t="str">
         <f t="array" ref="M58">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R58" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>248</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="R58" s="4"/>
       <c r="U58" s="1" t="s">
-        <v>249</v>
+        <v>86</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="W58" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="Y58" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="AB58" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE58" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5647,46 +5655,46 @@
         <v>245</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="E59" t="str">
+        <f t="shared" si="66"/>
+        <v>8</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="67"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="68"/>
+        <v>Kverkova</v>
+      </c>
+      <c r="H59" t="str">
         <f t="shared" si="69"/>
-        <v>8</v>
-      </c>
-      <c r="F59" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I59" t="str">
         <f t="shared" si="70"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="G59" t="str">
+        <v>2018</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1038/s41598-018-26062-8</v>
+      </c>
+      <c r="K59" t="str">
         <f t="shared" si="71"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="H59" t="str">
+        <v>Kverkova_etal_2018_Table1</v>
+      </c>
+      <c r="L59" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I59" t="str">
-        <f t="shared" si="73"/>
-        <v>2018</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1038/s41598-018-26062-8</v>
-      </c>
-      <c r="K59" t="str">
-        <f t="shared" si="75"/>
-        <v>Kverkova_etal_2018_TableS1</v>
-      </c>
-      <c r="L59" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M59" t="str">
         <f t="array" ref="M59">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>51</v>
@@ -5695,7 +5703,7 @@
         <v>70</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>84</v>
@@ -5709,17 +5717,11 @@
       <c r="V59" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X59" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="Y59" s="1" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>255</v>
+        <v>38</v>
       </c>
       <c r="AB59" s="1" t="s">
         <v>136</v>
@@ -5733,46 +5735,46 @@
         <v>245</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E60" t="str">
+        <f t="shared" si="66"/>
+        <v>8</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="67"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="68"/>
+        <v>Kverkova</v>
+      </c>
+      <c r="H60" t="str">
         <f t="shared" si="69"/>
-        <v>8</v>
-      </c>
-      <c r="F60" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I60" t="str">
         <f t="shared" si="70"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="G60" t="str">
+        <v>2018</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1038/s41598-018-26062-8</v>
+      </c>
+      <c r="K60" t="str">
         <f t="shared" si="71"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="H60" t="str">
+        <v>Kverkova_etal_2018_TableS1</v>
+      </c>
+      <c r="L60" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="73"/>
-        <v>2018</v>
-      </c>
-      <c r="J60" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1038/s41598-018-26062-8</v>
-      </c>
-      <c r="K60" t="str">
-        <f t="shared" si="75"/>
-        <v>Kverkova_etal_2018_TableS5</v>
-      </c>
-      <c r="L60" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M60" t="str">
         <f t="array" ref="M60">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L60, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>51</v>
@@ -5781,16 +5783,16 @@
         <v>70</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>84</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>36</v>
@@ -5802,10 +5804,10 @@
         <v>254</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
       <c r="AB60" s="1" t="s">
         <v>136</v>
@@ -5816,99 +5818,132 @@
     </row>
     <row r="61" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E61" t="str">
+        <f t="shared" si="66"/>
+        <v>8</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="67"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="68"/>
+        <v>Kverkova</v>
+      </c>
+      <c r="H61" t="str">
         <f t="shared" si="69"/>
-        <v>4</v>
-      </c>
-      <c r="F61" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I61" t="str">
         <f t="shared" si="70"/>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="G61" t="str">
+        <v>2018</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1038/s41598-018-26062-8</v>
+      </c>
+      <c r="K61" t="str">
         <f t="shared" si="71"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="H61" t="str">
+        <v>Kverkova_etal_2018_TableS5</v>
+      </c>
+      <c r="L61" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I61" t="str">
-        <f t="shared" si="73"/>
-        <v>2013</v>
-      </c>
-      <c r="J61" t="str">
-        <f t="shared" si="74"/>
-        <v>10.3389/fnhum.2013.00424</v>
-      </c>
-      <c r="K61" t="str">
-        <f t="shared" si="75"/>
-        <v>Lewitus_etal_2013_TableS2partial</v>
-      </c>
-      <c r="L61" t="str">
-        <f t="shared" si="76"/>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M61" t="str">
         <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA61" s="1" t="s">
-        <v>263</v>
+        <v>70</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y61" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE61" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>128</v>
+        <v>262</v>
       </c>
       <c r="E62" t="str">
+        <f t="shared" si="66"/>
+        <v>4</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="67"/>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="68"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H62" t="str">
         <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="F62" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I62" t="str">
         <f t="shared" si="70"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="G62" t="str">
+        <v>2013</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="12"/>
+        <v>10.3389/fnhum.2013.00424</v>
+      </c>
+      <c r="K62" t="str">
         <f t="shared" si="71"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="H62" t="str">
+        <v>Lewitus_etal_2013_TableS2partial</v>
+      </c>
+      <c r="L62" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I62" t="str">
-        <f t="shared" si="73"/>
-        <v>2014</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1371/journal.pbio.1002000</v>
-      </c>
-      <c r="K62" t="str">
-        <f t="shared" si="75"/>
-        <v>Lewitus_etal_2014_TableS1</v>
-      </c>
-      <c r="L62" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M62" t="str">
         <f t="array" ref="M62">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L62, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>265</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="Q62" s="1" t="s">
         <v>52</v>
@@ -5922,46 +5957,46 @@
         <v>264</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>266</v>
+        <v>128</v>
       </c>
       <c r="E63" t="str">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="67"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="68"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H63" t="str">
         <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="F63" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I63" t="str">
         <f t="shared" si="70"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="G63" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1371/journal.pbio.1002000</v>
+      </c>
+      <c r="K63" t="str">
         <f t="shared" si="71"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="H63" t="str">
+        <v>Lewitus_etal_2014_TableS1</v>
+      </c>
+      <c r="L63" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I63" t="str">
-        <f t="shared" si="73"/>
-        <v>2014</v>
-      </c>
-      <c r="J63" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1371/journal.pbio.1002000</v>
-      </c>
-      <c r="K63" t="str">
-        <f t="shared" si="75"/>
-        <v>Lewitus_etal_2014_TableS8</v>
-      </c>
-      <c r="L63" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M63" t="str">
         <f t="array" ref="M63">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L63, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>52</v>
@@ -5970,368 +6005,336 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
       <c r="E64" t="str">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="67"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="68"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H64" t="str">
         <f t="shared" si="69"/>
-        <v>5</v>
-      </c>
-      <c r="F64" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I64" t="str">
         <f t="shared" si="70"/>
-        <v>MacLarnon__1996</v>
-      </c>
-      <c r="G64" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1371/journal.pbio.1002000</v>
+      </c>
+      <c r="K64" t="str">
         <f t="shared" si="71"/>
-        <v>MacLarnon</v>
-      </c>
-      <c r="H64" t="str">
+        <v>Lewitus_etal_2014_TableS8</v>
+      </c>
+      <c r="L64" t="str">
         <f t="shared" si="72"/>
-        <v/>
-      </c>
-      <c r="I64" t="str">
-        <f t="shared" si="73"/>
-        <v>1996</v>
-      </c>
-      <c r="J64" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1006/jhev.1996.0005</v>
-      </c>
-      <c r="K64" t="str">
-        <f t="shared" si="75"/>
-        <v>MacLarnon__1996_Table1</v>
-      </c>
-      <c r="L64" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M64" t="str">
         <f t="array" ref="M64">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L64, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>160</v>
+        <v>267</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA64" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>271</v>
+        <v>41</v>
       </c>
       <c r="E65" t="str">
+        <f t="shared" si="66"/>
+        <v>5</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="67"/>
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="68"/>
+        <v>MacLarnon</v>
+      </c>
+      <c r="H65" t="str">
         <f t="shared" si="69"/>
-        <v>2</v>
-      </c>
-      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
         <f t="shared" si="70"/>
-        <v>ManyPrimates__2022</v>
-      </c>
-      <c r="G65" t="str">
+        <v>1996</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="12"/>
+        <v>10.1006/jhev.1996.0005</v>
+      </c>
+      <c r="K65" t="str">
         <f t="shared" si="71"/>
-        <v>ManyPrimates</v>
-      </c>
-      <c r="H65" t="str">
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="L65" t="str">
         <f t="shared" si="72"/>
-        <v/>
-      </c>
-      <c r="I65" t="str">
-        <f t="shared" si="73"/>
-        <v>2022</v>
-      </c>
-      <c r="J65" t="str">
-        <f t="shared" si="74"/>
-        <v>10.26451/abc.09.04.06.2022</v>
-      </c>
-      <c r="K65" t="str">
-        <f t="shared" si="75"/>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
-      </c>
-      <c r="L65" t="str">
-        <f t="shared" si="76"/>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M65" t="str">
         <f t="array" ref="M65">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L65, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R65" s="4"/>
-      <c r="T65" s="1" t="str">
-        <f>IF(S65="N", R65, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W65" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X65" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y65" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC65" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="AE65" s="1" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>128</v>
+        <v>271</v>
       </c>
       <c r="E66" t="str">
+        <f t="shared" si="66"/>
+        <v>2</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="67"/>
+        <v>ManyPrimates__2022</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="68"/>
+        <v>ManyPrimates</v>
+      </c>
+      <c r="H66" t="str">
         <f t="shared" si="69"/>
-        <v>1</v>
-      </c>
-      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
         <f t="shared" si="70"/>
-        <v>Mota_etal_2015</v>
-      </c>
-      <c r="G66" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="12"/>
+        <v>10.26451/abc.09.04.06.2022</v>
+      </c>
+      <c r="K66" t="str">
         <f t="shared" si="71"/>
-        <v>Mota</v>
-      </c>
-      <c r="H66" t="str">
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+      </c>
+      <c r="L66" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I66" t="str">
-        <f t="shared" si="73"/>
-        <v>2015</v>
-      </c>
-      <c r="J66" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1126/science.aaa9101</v>
-      </c>
-      <c r="K66" t="str">
-        <f t="shared" si="75"/>
-        <v>Mota_etal_2015_TableS1</v>
-      </c>
-      <c r="L66" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M66" t="str">
         <f t="array" ref="M66">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L66, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
+      </c>
+      <c r="R66" s="4"/>
+      <c r="T66" s="1" t="str">
+        <f>IF(S66="N", R66, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y66" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC66" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="AE66" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c r="E67" t="str">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" si="67"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" si="68"/>
+        <v>Mota</v>
+      </c>
+      <c r="H67" t="str">
         <f t="shared" si="69"/>
-        <v>6</v>
-      </c>
-      <c r="F67" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I67" t="str">
         <f t="shared" si="70"/>
-        <v>Mota_etal_2019</v>
-      </c>
-      <c r="G67" t="str">
+        <v>2015</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" ref="J67:J78" si="73">IF(C67&lt;&gt;"", C67, IF(C67="", _xlfn.TEXTAFTER(A67,"https://doi.org/"), C67))</f>
+        <v>10.1126/science.aaa9101</v>
+      </c>
+      <c r="K67" t="str">
         <f t="shared" si="71"/>
-        <v>Mota</v>
-      </c>
-      <c r="H67" t="str">
+        <v>Mota_etal_2015_TableS1</v>
+      </c>
+      <c r="L67" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I67" t="str">
-        <f t="shared" si="73"/>
-        <v>2019</v>
-      </c>
-      <c r="J67" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1073/pnas.1716956116</v>
-      </c>
-      <c r="K67" t="str">
-        <f t="shared" si="75"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
-      </c>
-      <c r="L67" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M67" t="str">
         <f t="array" ref="M67">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L67, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC67" s="1" t="s">
-        <v>280</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E68" t="str">
+        <f t="shared" si="66"/>
+        <v>6</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="67"/>
+        <v>Mota_etal_2019</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="68"/>
+        <v>Mota</v>
+      </c>
+      <c r="H68" t="str">
         <f t="shared" si="69"/>
-        <v>5</v>
-      </c>
-      <c r="F68" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I68" t="str">
         <f t="shared" si="70"/>
-        <v>Powell_etal_2017</v>
-      </c>
-      <c r="G68" t="str">
+        <v>2019</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1073/pnas.1716956116</v>
+      </c>
+      <c r="K68" t="str">
         <f t="shared" si="71"/>
-        <v>Powell</v>
-      </c>
-      <c r="H68" t="str">
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
+      </c>
+      <c r="L68" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I68" t="str">
-        <f t="shared" si="73"/>
-        <v>2017</v>
-      </c>
-      <c r="J68" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1098/rspb.2017.1765</v>
-      </c>
-      <c r="K68" t="str">
-        <f t="shared" si="75"/>
-        <v>Powell_etal_2017_Dataset1</v>
-      </c>
-      <c r="L68" t="str">
-        <f t="shared" si="76"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M68" t="str">
         <f t="array" ref="M68">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L68, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Q68" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R68" s="4"/>
-      <c r="T68" s="1" t="str">
-        <f>IF(S68="N", R68, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W68" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X68" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="Y68" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z68" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="AC68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE68" s="1" t="s">
-        <v>81</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="E69" t="str">
+        <f t="shared" si="66"/>
+        <v>5</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="67"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="68"/>
+        <v>Powell</v>
+      </c>
+      <c r="H69" t="str">
         <f t="shared" si="69"/>
-        <v>2</v>
-      </c>
-      <c r="F69" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I69" t="str">
         <f t="shared" si="70"/>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="G69" t="str">
+        <v>2017</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="73"/>
+        <v>10.6084/m9.figshare.c.3899422.v1</v>
+      </c>
+      <c r="K69" t="str">
         <f t="shared" si="71"/>
-        <v>Sherwood</v>
-      </c>
-      <c r="H69" t="str">
+        <v>Powell_etal_2017_Dataset1</v>
+      </c>
+      <c r="L69" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I69" t="str">
-        <f t="shared" si="73"/>
-        <v>2004</v>
-      </c>
-      <c r="J69" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159/000075672</v>
-      </c>
-      <c r="K69" t="str">
-        <f t="shared" si="75"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
-      </c>
-      <c r="L69" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M69" t="str">
         <f t="array" ref="M69">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L69, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>288</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="Q69" s="1" t="s">
         <v>95</v>
@@ -6342,16 +6345,25 @@
         <v>write file name</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>289</v>
+        <v>36</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X69" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="Z69" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
+      </c>
+      <c r="AC69" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="AE69" s="1" t="s">
         <v>81</v>
@@ -6365,46 +6377,46 @@
         <v>287</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E70" t="str">
+        <f t="shared" si="66"/>
+        <v>2</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="67"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="68"/>
+        <v>Sherwood</v>
+      </c>
+      <c r="H70" t="str">
         <f t="shared" si="69"/>
-        <v>2</v>
-      </c>
-      <c r="F70" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I70" t="str">
         <f t="shared" si="70"/>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="G70" t="str">
+        <v>2004</v>
+      </c>
+      <c r="J70" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1159/000075672</v>
+      </c>
+      <c r="K70" t="str">
         <f t="shared" si="71"/>
-        <v>Sherwood</v>
-      </c>
-      <c r="H70" t="str">
+        <v>Sherwood_etal_2004_I_Table4</v>
+      </c>
+      <c r="L70" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I70" t="str">
-        <f t="shared" si="73"/>
-        <v>2004</v>
-      </c>
-      <c r="J70" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159/000075672</v>
-      </c>
-      <c r="K70" t="str">
-        <f t="shared" si="75"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
-      </c>
-      <c r="L70" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M70" t="str">
         <f t="array" ref="M70">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L70, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>272</v>
@@ -6435,49 +6447,78 @@
     </row>
     <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>293</v>
+        <v>206</v>
       </c>
       <c r="E71" t="str">
+        <f t="shared" si="66"/>
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="67"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="68"/>
+        <v>Sherwood</v>
+      </c>
+      <c r="H71" t="str">
         <f t="shared" si="69"/>
-        <v>1</v>
-      </c>
-      <c r="F71" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I71" t="str">
         <f t="shared" si="70"/>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="G71" t="str">
+        <v>2004</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1159/000075672</v>
+      </c>
+      <c r="K71" t="str">
         <f t="shared" si="71"/>
-        <v>Smaers</v>
-      </c>
-      <c r="H71" t="str">
+        <v>Sherwood_etal_2004_I_Table5</v>
+      </c>
+      <c r="L71" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I71" t="str">
-        <f t="shared" si="73"/>
-        <v>2011</v>
-      </c>
-      <c r="J71" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159/000323671</v>
-      </c>
-      <c r="K71" t="str">
-        <f t="shared" si="75"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="L71" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M71" t="str">
         <f t="array" ref="M71">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L71, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
+      </c>
+      <c r="R71" s="4"/>
+      <c r="T71" s="1" t="str">
+        <f>IF(S71="N", R71, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y71" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Z71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE71" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6485,43 +6526,43 @@
         <v>292</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E72" t="str">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="67"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="68"/>
+        <v>Smaers</v>
+      </c>
+      <c r="H72" t="str">
         <f t="shared" si="69"/>
-        <v>1</v>
-      </c>
-      <c r="F72" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I72" t="str">
         <f t="shared" si="70"/>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="G72" t="str">
+        <v>2011</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1159/000323671</v>
+      </c>
+      <c r="K72" t="str">
         <f t="shared" si="71"/>
-        <v>Smaers</v>
-      </c>
-      <c r="H72" t="str">
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
+      </c>
+      <c r="L72" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I72" t="str">
-        <f t="shared" si="73"/>
-        <v>2011</v>
-      </c>
-      <c r="J72" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159/000323671</v>
-      </c>
-      <c r="K72" t="str">
-        <f t="shared" si="75"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
-      </c>
-      <c r="L72" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M72" t="str">
         <f t="array" ref="M72">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L72, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q72" s="1" t="s">
         <v>52</v>
@@ -6529,183 +6570,183 @@
     </row>
     <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>41</v>
+        <v>294</v>
       </c>
       <c r="E73" t="str">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="67"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="68"/>
+        <v>Smaers</v>
+      </c>
+      <c r="H73" t="str">
         <f t="shared" si="69"/>
-        <v>2</v>
-      </c>
-      <c r="F73" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I73" t="str">
         <f t="shared" si="70"/>
-        <v>Turner_etal_2016</v>
-      </c>
-      <c r="G73" t="str">
+        <v>2011</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1159/000323671</v>
+      </c>
+      <c r="K73" t="str">
         <f t="shared" si="71"/>
-        <v>Turner</v>
-      </c>
-      <c r="H73" t="str">
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="L73" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I73" t="str">
-        <f t="shared" si="73"/>
-        <v>2016</v>
-      </c>
-      <c r="J73" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1159/000446762</v>
-      </c>
-      <c r="K73" t="str">
-        <f t="shared" si="75"/>
-        <v>Turner_etal_2016_Table1</v>
-      </c>
-      <c r="L73" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M73" t="str">
         <f t="array" ref="M73">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L73, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="Y73" s="1" t="s">
-        <v>297</v>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>299</v>
+        <v>41</v>
       </c>
       <c r="E74" t="str">
+        <f t="shared" si="66"/>
+        <v>2</v>
+      </c>
+      <c r="F74" t="str">
+        <f t="shared" si="67"/>
+        <v>Turner_etal_2016</v>
+      </c>
+      <c r="G74" t="str">
+        <f t="shared" si="68"/>
+        <v>Turner</v>
+      </c>
+      <c r="H74" t="str">
         <f t="shared" si="69"/>
-        <v>1</v>
-      </c>
-      <c r="F74" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I74" t="str">
         <f t="shared" si="70"/>
-        <v>Wilman_etal_2014</v>
-      </c>
-      <c r="G74" t="str">
+        <v>2016</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1159/000446762</v>
+      </c>
+      <c r="K74" t="str">
         <f t="shared" si="71"/>
-        <v>Wilman</v>
-      </c>
-      <c r="H74" t="str">
+        <v>Turner_etal_2016_Table1</v>
+      </c>
+      <c r="L74" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I74" t="str">
-        <f t="shared" si="73"/>
-        <v>2014</v>
-      </c>
-      <c r="J74" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1890/13-1917.1</v>
-      </c>
-      <c r="K74" t="str">
-        <f t="shared" si="75"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
-      </c>
-      <c r="L74" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M74" t="str">
         <f t="array" ref="M74">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L74, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
+      <c r="N74" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E75" t="str">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="F75" t="str">
+        <f t="shared" si="67"/>
+        <v>Wilman_etal_2014</v>
+      </c>
+      <c r="G75" t="str">
+        <f t="shared" si="68"/>
+        <v>Wilman</v>
+      </c>
+      <c r="H75" t="str">
         <f t="shared" si="69"/>
-        <v>7</v>
-      </c>
-      <c r="F75" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I75" t="str">
         <f t="shared" si="70"/>
-        <v>Wimberly_etal_2021</v>
-      </c>
-      <c r="G75" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J75" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1890/13-1917.1</v>
+      </c>
+      <c r="K75" t="str">
         <f t="shared" si="71"/>
-        <v>Wimberly</v>
-      </c>
-      <c r="H75" t="str">
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+      </c>
+      <c r="L75" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I75" t="str">
-        <f t="shared" si="73"/>
-        <v>2021</v>
-      </c>
-      <c r="J75" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1098/rspb.2021.0937</v>
-      </c>
-      <c r="K75" t="str">
-        <f t="shared" si="75"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
-      </c>
-      <c r="L75" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M75" t="str">
         <f t="array" ref="M75">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L75, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E76" t="str">
+        <f t="shared" si="66"/>
+        <v>7</v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="67"/>
+        <v>Wimberly_etal_2021</v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="68"/>
+        <v>Wimberly</v>
+      </c>
+      <c r="H76" t="str">
         <f t="shared" si="69"/>
-        <v>5</v>
-      </c>
-      <c r="F76" t="str">
+        <v>etal</v>
+      </c>
+      <c r="I76" t="str">
         <f t="shared" si="70"/>
-        <v>Winkler_Bryant_2021</v>
-      </c>
-      <c r="G76" t="str">
+        <v>2021</v>
+      </c>
+      <c r="J76" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1098/rspb.2021.0937</v>
+      </c>
+      <c r="K76" t="str">
         <f t="shared" si="71"/>
-        <v>Winkler</v>
-      </c>
-      <c r="H76" t="str">
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
+      </c>
+      <c r="L76" t="str">
         <f t="shared" si="72"/>
-        <v>Bryant</v>
-      </c>
-      <c r="I76" t="str">
-        <f t="shared" si="73"/>
-        <v>2021</v>
-      </c>
-      <c r="J76" t="str">
-        <f t="shared" si="74"/>
-        <v>10.1080/09524622.2021.1905065</v>
-      </c>
-      <c r="K76" t="str">
-        <f t="shared" si="75"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
-      </c>
-      <c r="L76" t="str">
-        <f t="shared" si="76"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M76" t="str">
         <f t="array" ref="M76">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L76, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
@@ -6714,72 +6755,52 @@
       <c r="P76" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Q76" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R76" s="4"/>
-      <c r="T76" s="1" t="str">
-        <f>IF(S76="N", R76, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U76" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V76" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y76" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AE76" s="1" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>41</v>
+        <v>303</v>
       </c>
       <c r="E77" t="str">
+        <f t="shared" si="66"/>
+        <v>5</v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="67"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="68"/>
+        <v>Winkler</v>
+      </c>
+      <c r="H77" t="str">
         <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="F77" t="str">
+        <v>Bryant</v>
+      </c>
+      <c r="I77" t="str">
         <f t="shared" si="70"/>
-        <v>Young_etal_2013</v>
-      </c>
-      <c r="G77" t="str">
+        <v>2021</v>
+      </c>
+      <c r="J77" t="str">
+        <f t="shared" si="73"/>
+        <v>10.1080/09524622.2021.1905065</v>
+      </c>
+      <c r="K77" t="str">
         <f t="shared" si="71"/>
-        <v>Young</v>
-      </c>
-      <c r="H77" t="str">
+        <v>Winkler_Bryant_2021_Figure1</v>
+      </c>
+      <c r="L77" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I77" t="str">
-        <f t="shared" si="73"/>
-        <v>2013</v>
-      </c>
-      <c r="J77" t="str">
-        <f t="shared" si="74"/>
-        <v>10.3389/fncir.2013.00030</v>
-      </c>
-      <c r="K77" t="str">
-        <f t="shared" si="75"/>
-        <v>Young_etal_2013_Table1</v>
-      </c>
-      <c r="L77" t="str">
-        <f t="shared" si="76"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="M77" t="str">
         <f t="array" ref="M77">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L77, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="Q77" s="1" t="s">
         <v>95</v>
@@ -6793,15 +6814,82 @@
         <v>86</v>
       </c>
       <c r="V77" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y77" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE77" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" t="str">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="67"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="68"/>
+        <v>Young</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="69"/>
+        <v>etal</v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="70"/>
+        <v>2013</v>
+      </c>
+      <c r="J78" t="str">
+        <f t="shared" si="73"/>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="K78" t="str">
+        <f t="shared" si="71"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L78" t="str">
+        <f t="shared" si="72"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M78" t="str">
+        <f t="array" ref="M78">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L78, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R78" s="4"/>
+      <c r="T78" s="1" t="str">
+        <f>IF(S78="N", R78, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V78" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y77" s="1" t="s">
+      <c r="Y78" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="Z77" s="1" t="s">
+      <c r="Z78" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AE77" s="1" t="s">
+      <c r="AE78" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -6812,13 +6900,13 @@
     <hyperlink ref="X12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="X18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="X24" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X65" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X68" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X37" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X29:X32" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X60" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X59" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X56" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="X66" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X69" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="X38" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="X29:X33" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X61" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="X60" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X57" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="X26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="X27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
   </hyperlinks>
@@ -7322,6 +7410,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -7576,27 +7684,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7613,23 +7720,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F42699D6-E23D-4040-BEF7-F45B8BE07AC0}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA981651-3638-4A6B-8CAB-97603806A668}"/>
   <bookViews>
     <workbookView xWindow="-80" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="416">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -146,6 +146,9 @@
     <t>Andelin, A. K., Olavarria, J. F., Fine, I., Taber, E. N., Schwartz, D., Kroenke, C. D., &amp; Stevens, A. A. (2019). The Effect of Onset Age of Visual Deprivation on Visual Cortex Surface Area Across-Species. Cereb Cortex, 29(10), 4321-4333. https://doi.org/10.1093/cercor/bhy315</t>
   </si>
   <si>
+    <t>Table 4</t>
+  </si>
+  <si>
     <t>table</t>
   </si>
   <si>
@@ -159,6 +162,12 @@
   </si>
   <si>
     <t>primary</t>
+  </si>
+  <si>
+    <t>Barbeito-Andres, J., Castro-Fonseca, E., Qiu, L. R., Bernal, V., Lent, R., Henkelman, M., Lukowiak, K., Gleiser, P. M., Hallgrimsson, B., &amp; Gonzalez, P. N. (2019). Region-specific changes in Mus musculus brain size and cell composition under chronic nutrient restriction. J Exp Biol, 222(Pt 17). https://doi.org/10.1242/jeb.204651</t>
+  </si>
+  <si>
+    <t>data_figshare.xlsx</t>
   </si>
   <si>
     <t>Baron, G., Frahm, H. D., Bhatnagar, K. P., &amp; Stephan, H. (1983). Comparison of brain structure volumes in Insectivora and Primates. III. Main olfactory bulb (MOB). J Hirnforsch, 24(5), 551-568. https://www.ncbi.nlm.nih.gov/pubmed/6663055</t>
@@ -673,9 +682,6 @@
   </si>
   <si>
     <t>HerculanoHouzel_etal_2015_Table3.csv</t>
-  </si>
-  <si>
-    <t>Table 4</t>
   </si>
   <si>
     <t>Table 4. Olfactory bulb</t>
@@ -1288,7 +1294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1393,7 +1399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1413,6 +1419,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
@@ -1432,9 +1439,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1472,7 +1479,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1578,7 +1585,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1720,7 +1727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1728,41 +1735,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH83"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="42.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="1" max="1" width="42.125" customWidth="1"/>
+    <col min="2" max="2" width="5.125" customWidth="1"/>
+    <col min="3" max="3" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="34.875" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="23.625" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.125" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="31.1640625" customWidth="1"/>
+    <col min="11" max="11" width="31.125" customWidth="1"/>
     <col min="12" max="12" width="46.5" customWidth="1"/>
     <col min="13" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.375" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="20" width="14.1640625" customWidth="1"/>
-    <col min="21" max="21" width="13.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.6640625" customWidth="1"/>
-    <col min="23" max="23" width="22.1640625" customWidth="1"/>
-    <col min="24" max="24" width="14.33203125" customWidth="1"/>
+    <col min="17" max="20" width="14.125" customWidth="1"/>
+    <col min="21" max="21" width="13.875" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="22.125" customWidth="1"/>
+    <col min="24" max="24" width="14.375" customWidth="1"/>
     <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.1640625" customWidth="1"/>
+    <col min="26" max="26" width="11.125" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.6640625" customWidth="1"/>
-    <col min="30" max="30" width="10.83203125" customWidth="1"/>
+    <col min="29" max="29" width="10.625" customWidth="1"/>
+    <col min="30" max="30" width="10.875" customWidth="1"/>
     <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.83203125" customWidth="1"/>
+    <col min="32" max="34" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" ht="15.95" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1866,12 +1873,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="15.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>211</v>
+        <v>35</v>
       </c>
       <c r="E2" t="str">
         <f t="shared" ref="E2" si="0">RIGHT(A2,1)</f>
@@ -1913,17 +1920,17 @@
         <v>notfound</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="15.95" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3" si="7">RIGHT(A3,1)</f>
@@ -1953,11 +1960,11 @@
         <v>10.1002/cne.70089</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" ref="K3:K15" si="12">TRIM(_xlfn.TEXTJOIN("_",FALSE,F3,(SUBSTITUTE(SUBSTITUTE(D3," ",""), "_", ""))))</f>
+        <f t="shared" ref="K3:K16" si="12">TRIM(_xlfn.TEXTJOIN("_",FALSE,F3,(SUBSTITUTE(SUBSTITUTE(D3," ",""), "_", ""))))</f>
         <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L15" si="13">IF(ISBLANK(C3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L3:L16" si="13">IF(ISBLANK(C3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M3" t="str">
@@ -1965,36 +1972,33 @@
         <v>10.1002%2Fcne.70089_TABLE1.tsv</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="15.95" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E5" si="14">RIGHT(A4,1)</f>
-        <v>5</v>
+        <f t="shared" ref="E4" si="14">RIGHT(A4,1)</f>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" ref="F4" si="15">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
-        <v>Baron_etal_1983</v>
+        <v>BarbeitoAndres_etal_2019</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" ref="G4" si="16">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
-        <v>Baron</v>
+        <v>BarbeitoAndres</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" ref="H4" si="17">IF(ISNUMBER(FIND("&amp;", A4)),
@@ -2005,739 +2009,742 @@
       </c>
       <c r="I4" t="str">
         <f t="shared" ref="I4" si="18">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
-        <v>1983</v>
+        <v>2019</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" ref="J4:J70" si="19">IF(C4&lt;&gt;"", C4, IF(C4="", _xlfn.TEXTAFTER(A4,"https://doi.org/"), C4))</f>
-        <v>10.0000/placeholder.1</v>
+        <f>IF(C4&lt;&gt;"", C4, IF(C4="", _xlfn.TEXTAFTER(A4,"https://doi.org/"), C4))</f>
+        <v>10.1242/jeb.204651</v>
       </c>
       <c r="K4" t="str">
-        <f t="shared" si="12"/>
-        <v>Baron_etal_1983_Table1</v>
+        <f t="shared" ref="K4" si="19">TRIM(_xlfn.TEXTJOIN("_",FALSE,F4,(SUBSTITUTE(SUBSTITUTE(D4," ",""), "_", ""))))</f>
+        <v>BarbeitoAndres_etal_2019_datafigshare.xlsx</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" si="13"/>
-        <v>10.0000%2Fplaceholder.1_Table1</v>
+        <f t="shared" ref="L4" si="20">IF(ISBLANK(C4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J4, SUBSTITUTE(D4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C4, SUBSTITUTE(D4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1242%2Fjeb.204651_datafigshare.xlsx</v>
       </c>
       <c r="M4" t="str">
         <f t="array" ref="M4">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.0000%2Fplaceholder.1_Table1.tsv</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W4" s="1" t="s">
+        <v>notfound</v>
+      </c>
+      <c r="V4" s="1"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="1"/>
+    </row>
+    <row r="5" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E5" t="str">
-        <f t="shared" si="14"/>
-        <v>6</v>
+        <f t="shared" ref="E5:E6" si="21">RIGHT(A5,1)</f>
+        <v>5</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" ref="F5" si="20">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
-        <v>Baron_etal_1987</v>
+        <f t="shared" ref="F5" si="22">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
+        <v>Baron_etal_1983</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" ref="G5" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G5" si="23">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5" si="22">IF(ISNUMBER(FIND("&amp;", A5)),
+        <f t="shared" ref="H5" si="24">IF(ISNUMBER(FIND("&amp;", A5)),
     IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
-        <v>1987</v>
+        <f t="shared" ref="I5" si="25">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
+        <v>1983</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="19"/>
-        <v>10.0000/placeholder.2</v>
+        <f t="shared" ref="J5:J71" si="26">IF(C5&lt;&gt;"", C5, IF(C5="", _xlfn.TEXTAFTER(A5,"https://doi.org/"), C5))</f>
+        <v>10.0000/placeholder.1</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="12"/>
-        <v>Baron_etal_1987_Table1</v>
+        <v>Baron_etal_1983_Table1</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="13"/>
-        <v>10.0000%2Fplaceholder.2_Table1</v>
+        <v>10.0000%2Fplaceholder.1_Table1</v>
       </c>
       <c r="M5" t="str">
         <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.0000%2Fplaceholder.1_Table1.tsv</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="15.95" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" t="str">
-        <f t="shared" ref="E6:E49" si="24">RIGHT(A6,1)</f>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>6</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" ref="F6:F49" si="25">G6 &amp; IF(H6&lt;&gt;"", "_" &amp; H6, "_") &amp; IF(I6&lt;&gt;"", "_" &amp; I6, "_") &amp; IF(B6&lt;&gt;"", "_" &amp; B6, "")</f>
-        <v>Brodmann__1913</v>
+        <f t="shared" ref="F6" si="27">G6 &amp; IF(H6&lt;&gt;"", "_" &amp; H6, "_") &amp; IF(I6&lt;&gt;"", "_" &amp; I6, "_") &amp; IF(B6&lt;&gt;"", "_" &amp; B6, "")</f>
+        <v>Baron_etal_1987</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" ref="G6:G49" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A6,","), "-", ""), " ", "")</f>
-        <v>Brodmann</v>
+        <f t="shared" ref="G6" si="28">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A6,","), "-", ""), " ", "")</f>
+        <v>Baron</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H49" si="27">IF(ISNUMBER(FIND("&amp;", A6)),
+        <f t="shared" ref="H6" si="29">IF(ISNUMBER(FIND("&amp;", A6)),
     IF(LEN(A6)-LEN(SUBSTITUTE(A6, ",", ""))&gt;=6, "etal", MID(A6, SEARCH("&amp; ", A6)+2, SEARCH(",", A6, SEARCH("&amp; ", A6)+2) - SEARCH("&amp; ", A6)-2)),
     ""
 )</f>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" ref="I6:I49" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A6, "("), ")")</f>
-        <v>1913</v>
+        <f t="shared" ref="I6" si="30">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A6, "("), ")")</f>
+        <v>1987</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="19"/>
-        <v>10.0000/placeholder</v>
+        <f t="shared" si="26"/>
+        <v>10.0000/placeholder.2</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="12"/>
-        <v>Brodmann__1913_Tabelle1</v>
+        <v>Baron_etal_1987_Table1</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="13"/>
-        <v>10.0000%2Fplaceholder_Tabelle1</v>
+        <v>10.0000%2Fplaceholder.2_Table1</v>
       </c>
       <c r="M6" t="str">
         <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="15.95" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" si="24"/>
-        <v>3</v>
+        <f t="shared" ref="E7:E50" si="31">RIGHT(A7,1)</f>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="25"/>
-        <v>Burger_etal_2019</v>
+        <f t="shared" ref="F7:F50" si="32">G7 &amp; IF(H7&lt;&gt;"", "_" &amp; H7, "_") &amp; IF(I7&lt;&gt;"", "_" &amp; I7, "_") &amp; IF(B7&lt;&gt;"", "_" &amp; B7, "")</f>
+        <v>Brodmann__1913</v>
       </c>
       <c r="G7" t="str">
+        <f t="shared" ref="G7:G50" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A7,","), "-", ""), " ", "")</f>
+        <v>Brodmann</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" ref="H7:H50" si="34">IF(ISNUMBER(FIND("&amp;", A7)),
+    IF(LEN(A7)-LEN(SUBSTITUTE(A7, ",", ""))&gt;=6, "etal", MID(A7, SEARCH("&amp; ", A7)+2, SEARCH(",", A7, SEARCH("&amp; ", A7)+2) - SEARCH("&amp; ", A7)-2)),
+    ""
+)</f>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" ref="I7:I50" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A7, "("), ")")</f>
+        <v>1913</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="26"/>
-        <v>Burger</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="28"/>
-        <v>2019</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1093/jmammal/gyz043</v>
+        <v>10.0000/placeholder</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="12"/>
-        <v>Burger_etal_2019_SupplementaryDataSD1</v>
+        <v>Brodmann__1913_Tabelle1</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="13"/>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
+        <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
       <c r="M7" t="str">
         <f t="array" ref="M7">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P7" s="1" t="s">
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="17.100000000000001" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T7" s="1" t="str">
-        <f>IF(S7="N", R7, "write file name")</f>
-        <v>gyz043_suppl_Supplement_Data.csv</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E8" t="str">
-        <f t="shared" si="24"/>
-        <v>9</v>
+        <f t="shared" si="31"/>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="25"/>
-        <v>Burish_etal_2010</v>
+        <f t="shared" si="32"/>
+        <v>Burger_etal_2019</v>
       </c>
       <c r="G8" t="str">
+        <f t="shared" si="33"/>
+        <v>Burger</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="35"/>
+        <v>2019</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="26"/>
-        <v>Burish</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="28"/>
-        <v>2010</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1159/000319019</v>
+        <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="12"/>
-        <v>Burish_etal_2010_SupplementaryTable1</v>
+        <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="13"/>
-        <v>10.1159%2F000319019_SupplementaryTable1</v>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="M8" t="str">
         <f t="array" ref="M8">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="N8" s="1" t="s">
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T8" s="1" t="str">
+        <f>IF(S8="N", R8, "write file name")</f>
+        <v>gyz043_suppl_Supplement_Data.csv</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:34" ht="17.100000000000001" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="G9" t="str">
+        <f t="shared" si="33"/>
+        <v>Burish</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="35"/>
+        <v>2010</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="26"/>
-        <v>Burish</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="28"/>
-        <v>2010</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="19"/>
         <v>10.1159/000319019</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="12"/>
-        <v>Burish_etal_2010_Table1</v>
+        <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="13"/>
-        <v>10.1159%2F000319019_Table1</v>
+        <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M9" t="str">
         <f t="array" ref="M9">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_Table1.tsv</v>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+      <c r="AC9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="AE9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Z9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:34" ht="15.95" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" si="24"/>
-        <v>5</v>
+        <f t="shared" si="31"/>
+        <v>9</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="25"/>
-        <v>Caspar_etal_2022</v>
+        <f t="shared" si="32"/>
+        <v>Burish_etal_2010</v>
       </c>
       <c r="G10" t="str">
+        <f t="shared" si="33"/>
+        <v>Burish</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="35"/>
+        <v>2010</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="26"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="28"/>
-        <v>2022</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="19"/>
-        <v>10.7554/eLife.77875</v>
+        <v>10.1159/000319019</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="12"/>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
+        <v>Burish_etal_2010_Table1</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="13"/>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
+        <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M10" t="str">
         <f t="array" ref="M10">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+        <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="1" t="s">
+      <c r="AC10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="AE10" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T10" s="1" t="str">
-        <f>IF(S10="N", R10, "write file name")</f>
-        <v>elife-77875-supp3-v1.xlsx</v>
-      </c>
-      <c r="U10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E11" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="G11" t="str">
+        <f t="shared" si="33"/>
+        <v>Caspar</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="35"/>
+        <v>2022</v>
+      </c>
+      <c r="J11" t="str">
         <f t="shared" si="26"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="28"/>
-        <v>2022</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="19"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="12"/>
-        <v>Caspar_etal_2022_Table1</v>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="13"/>
-        <v>10.7554%2FeLife.77875_Table1</v>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M11" t="str">
         <f t="array" ref="M11">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Table1.tsv</v>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
       </c>
       <c r="N11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T11" s="1" t="str">
+        <f>IF(S11="N", R11, "write file name")</f>
+        <v>elife-77875-supp3-v1.xlsx</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE11" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:34" ht="15.95" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="25"/>
-        <v>Changizi__2001</v>
+        <f t="shared" si="32"/>
+        <v>Caspar_etal_2022</v>
       </c>
       <c r="G12" t="str">
+        <f t="shared" si="33"/>
+        <v>Caspar</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="35"/>
+        <v>2022</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="26"/>
-        <v>Changizi</v>
-      </c>
-      <c r="H12" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <f t="shared" si="28"/>
-        <v>2001</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1007/s004220000205</v>
+        <v>10.7554/eLife.77875</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="12"/>
-        <v>Changizi__2001_Figure3</v>
+        <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="13"/>
-        <v>10.1007%2Fs004220000205_Figure3</v>
+        <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M12" t="str">
         <f t="array" ref="M12">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+        <v>10.7554%2FeLife.77875_Table1.tsv</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="P12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD12" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="AE12" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD12" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="E13" t="str">
-        <f t="shared" si="24"/>
-        <v>3</v>
+        <f t="shared" si="31"/>
+        <v>5</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="25"/>
-        <v>Chen_Wiens_2020</v>
+        <f t="shared" si="32"/>
+        <v>Changizi__2001</v>
       </c>
       <c r="G13" t="str">
+        <f t="shared" si="33"/>
+        <v>Changizi</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="35"/>
+        <v>2001</v>
+      </c>
+      <c r="J13" t="str">
         <f t="shared" si="26"/>
-        <v>Chen</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="27"/>
-        <v>Wiens</v>
-      </c>
-      <c r="I13" t="str">
-        <f t="shared" si="28"/>
-        <v>2020</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1038/s41467-020-14356-3</v>
+        <v>10.1007/s004220000205</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="12"/>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
+        <v>Changizi__2001_Figure3</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="13"/>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
+        <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M13" t="str">
         <f t="array" ref="M13">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="R13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T13" s="1" t="str">
-        <f>IF(S13="N", R13, "write file name")</f>
-        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Y13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="Z13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE13" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E14" t="str">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <f t="shared" si="31"/>
+        <v>3</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="25"/>
-        <v>Collins_etal_2010</v>
+        <f t="shared" si="32"/>
+        <v>Chen_Wiens_2020</v>
       </c>
       <c r="G14" t="str">
+        <f t="shared" si="33"/>
+        <v>Chen</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="34"/>
+        <v>Wiens</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="35"/>
+        <v>2020</v>
+      </c>
+      <c r="J14" t="str">
         <f t="shared" si="26"/>
-        <v>Collins</v>
-      </c>
-      <c r="H14" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="28"/>
-        <v>2010</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1073/pnas.1010356107</v>
+        <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="12"/>
-        <v>Collins_etal_2010_DatasetS1</v>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="13"/>
-        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="M14" t="str">
         <f t="array" ref="M14">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T14" s="1" t="str">
+        <f>IF(S14="N", R14, "write file name")</f>
+        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="Y14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:34" ht="15.95" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>115</v>
       </c>
@@ -2745,251 +2752,230 @@
         <v>116</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>7</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" si="25"/>
-        <v>DeCasien_Higham_2019</v>
+        <f t="shared" si="32"/>
+        <v>Collins_etal_2010</v>
       </c>
       <c r="G15" t="str">
+        <f t="shared" si="33"/>
+        <v>Collins</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="35"/>
+        <v>2010</v>
+      </c>
+      <c r="J15" t="str">
         <f t="shared" si="26"/>
-        <v>DeCasien</v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" si="27"/>
-        <v>Higham</v>
-      </c>
-      <c r="I15" t="str">
-        <f t="shared" si="28"/>
-        <v>2019</v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1038/s41559-019-0969-0</v>
+        <v>10.1073/pnas.1010356107</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="12"/>
-        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
+        <v>Collins_etal_2010_DatasetS1</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="13"/>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
+        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
       <c r="M15" t="str">
         <f t="array" ref="M15">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="Y15" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="W15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="Y15" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD15" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E16" t="str">
-        <f t="shared" ref="E16" si="29">RIGHT(A16,1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" ref="F16" si="30">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
+        <f t="shared" si="32"/>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" ref="G16" si="31">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
+        <f t="shared" si="33"/>
         <v>DeCasien</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" ref="H16" si="32">IF(ISNUMBER(FIND("&amp;", A16)),
-    IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
-    ""
-)</f>
+        <f t="shared" si="34"/>
         <v>Higham</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" ref="I16" si="33">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
+        <f t="shared" si="35"/>
         <v>2019</v>
       </c>
       <c r="J16" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K16" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F16,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
-        <v>DeCasien_Higham_2019_SupplementaryData1-Diet</v>
+        <f t="shared" si="12"/>
+        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="L16" t="str">
-        <f>IF(ISBLANK(C16),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J16, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C16, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-Diet</v>
+        <f t="shared" si="13"/>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="M16" t="str">
         <f t="array" ref="M16">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="15.95" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17" si="34">RIGHT(A17,1)</f>
+        <f t="shared" ref="E17" si="36">RIGHT(A17,1)</f>
         <v>0</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" ref="F17" si="35">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <f t="shared" ref="F17" si="37">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" ref="G17" si="36">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G17" si="38">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" ref="H17" si="37">IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="H17" si="39">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" ref="I17" si="38">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <f t="shared" ref="I17" si="40">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K17" t="str">
         <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D18," ",""), "_", ""))))</f>
-        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
+        <v>DeCasien_Higham_2019_SupplementaryData1-Diet</v>
       </c>
       <c r="L17" t="str">
         <f>IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-Diet</v>
       </c>
       <c r="M17" t="str">
         <f t="array" ref="M17">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="W17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E18" t="str">
-        <f t="shared" ref="E18" si="39">RIGHT(A18,1)</f>
+        <f t="shared" ref="E18" si="41">RIGHT(A18,1)</f>
         <v>0</v>
       </c>
       <c r="F18" t="str">
-        <f t="shared" ref="F18" si="40">G18 &amp; IF(H18&lt;&gt;"", "_" &amp; H18, "_") &amp; IF(I18&lt;&gt;"", "_" &amp; I18, "_") &amp; IF(B18&lt;&gt;"", "_" &amp; B18, "")</f>
+        <f t="shared" ref="F18" si="42">G18 &amp; IF(H18&lt;&gt;"", "_" &amp; H18, "_") &amp; IF(I18&lt;&gt;"", "_" &amp; I18, "_") &amp; IF(B18&lt;&gt;"", "_" &amp; B18, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A18,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G18" si="43">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A18,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" ref="H18" si="42">IF(ISNUMBER(FIND("&amp;", A18)),
+        <f t="shared" ref="H18" si="44">IF(ISNUMBER(FIND("&amp;", A18)),
     IF(LEN(A18)-LEN(SUBSTITUTE(A18, ",", ""))&gt;=6, "etal", MID(A18, SEARCH("&amp; ", A18)+2, SEARCH(",", A18, SEARCH("&amp; ", A18)+2) - SEARCH("&amp; ", A18)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" ref="I18" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A18, "("), ")")</f>
+        <f t="shared" ref="I18" si="45">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A18, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J18" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" ref="K18:K52" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,F18,(SUBSTITUTE(SUBSTITUTE(D18," ",""), "_", ""))))</f>
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F18,(SUBSTITUTE(SUBSTITUTE(D19," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" ref="L18:L52" si="45">IF(ISBLANK(C18),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f>IF(ISBLANK(C18),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J18, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C18, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M18" t="str">
@@ -2997,799 +2983,817 @@
         <v>notfound</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>129</v>
       </c>
       <c r="E19" t="str">
-        <f t="shared" si="24"/>
-        <v>6</v>
+        <f t="shared" ref="E19" si="46">RIGHT(A19,1)</f>
+        <v>0</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" si="25"/>
-        <v>DosSantos_etal_2017</v>
+        <f t="shared" ref="F19" si="47">G19 &amp; IF(H19&lt;&gt;"", "_" &amp; H19, "_") &amp; IF(I19&lt;&gt;"", "_" &amp; I19, "_") &amp; IF(B19&lt;&gt;"", "_" &amp; B19, "")</f>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G19" t="str">
+        <f t="shared" ref="G19" si="48">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A19,","), "-", ""), " ", "")</f>
+        <v>DeCasien</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" ref="H19" si="49">IF(ISNUMBER(FIND("&amp;", A19)),
+    IF(LEN(A19)-LEN(SUBSTITUTE(A19, ",", ""))&gt;=6, "etal", MID(A19, SEARCH("&amp; ", A19)+2, SEARCH(",", A19, SEARCH("&amp; ", A19)+2) - SEARCH("&amp; ", A19)-2)),
+    ""
+)</f>
+        <v>Higham</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" ref="I19" si="50">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A19, "("), ")")</f>
+        <v>2019</v>
+      </c>
+      <c r="J19" t="str">
         <f t="shared" si="26"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="28"/>
-        <v>2017</v>
-      </c>
-      <c r="J19" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1159/000452856</v>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="44"/>
-        <v>DosSantos_etal_2017_TableS1</v>
+        <f t="shared" ref="K19:K53" si="51">TRIM(_xlfn.TEXTJOIN("_",FALSE,F19,(SUBSTITUTE(SUBSTITUTE(D19," ",""), "_", ""))))</f>
+        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000452856_TableS1</v>
+        <f t="shared" ref="L19:L53" si="52">IF(ISBLANK(C19),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J19, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C19, SUBSTITUTE(D19,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M19" t="str">
         <f t="array" ref="M19">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000452856_TableS1.tsv</v>
-      </c>
-      <c r="O19" s="1" t="s">
+        <v>notfound</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA19" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE19" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E20" t="str">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>6</v>
       </c>
       <c r="F20" t="str">
-        <f t="shared" si="25"/>
-        <v>DosSantos_etal_2020</v>
+        <f t="shared" si="32"/>
+        <v>DosSantos_etal_2017</v>
       </c>
       <c r="G20" t="str">
+        <f t="shared" si="33"/>
+        <v>DosSantos</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="35"/>
+        <v>2017</v>
+      </c>
+      <c r="J20" t="str">
         <f t="shared" si="26"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H20" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I20" t="str">
-        <f t="shared" si="28"/>
-        <v>2020</v>
-      </c>
-      <c r="J20" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+        <v>10.1159/000452856</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="44"/>
-        <v>DosSantos_etal_2020_Table1</v>
+        <f t="shared" si="51"/>
+        <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M20" t="str">
         <f t="array" ref="M20">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000452856_TableS1.tsv</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="32"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="33"/>
+        <v>DosSantos</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="35"/>
+        <v>2020</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="51"/>
+        <v>DosSantos_etal_2020_Table1</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="52"/>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="U20" s="1" t="s">
+      <c r="P21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A22" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE20" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" t="str">
-        <f t="shared" ref="E21" si="46">RIGHT(A21,1)</f>
+      <c r="D22" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" ref="E22" si="53">RIGHT(A22,1)</f>
         <v>0</v>
       </c>
-      <c r="F21" t="str">
-        <f t="shared" ref="F21" si="47">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
+      <c r="F22" t="str">
+        <f t="shared" ref="F22" si="54">G22 &amp; IF(H22&lt;&gt;"", "_" &amp; H22, "_") &amp; IF(I22&lt;&gt;"", "_" &amp; I22, "_") &amp; IF(B22&lt;&gt;"", "_" &amp; B22, "")</f>
         <v>DosSantos_etal_2020</v>
       </c>
-      <c r="G21" t="str">
-        <f t="shared" ref="G21" si="48">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
+      <c r="G22" t="str">
+        <f t="shared" ref="G22" si="55">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A22,","), "-", ""), " ", "")</f>
         <v>DosSantos</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" ref="H21" si="49">IF(ISNUMBER(FIND("&amp;", A21)),
-    IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
+      <c r="H22" t="str">
+        <f t="shared" ref="H22" si="56">IF(ISNUMBER(FIND("&amp;", A22)),
+    IF(LEN(A22)-LEN(SUBSTITUTE(A22, ",", ""))&gt;=6, "etal", MID(A22, SEARCH("&amp; ", A22)+2, SEARCH(",", A22, SEARCH("&amp; ", A22)+2) - SEARCH("&amp; ", A22)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" ref="I21" si="50">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
+      <c r="I22" t="str">
+        <f t="shared" ref="I22" si="57">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, "("), ")")</f>
         <v>2020</v>
       </c>
-      <c r="J21" t="str">
-        <f t="shared" si="19"/>
+      <c r="J22" t="str">
+        <f t="shared" si="26"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
-      <c r="K21" t="str">
-        <f t="shared" si="44"/>
+      <c r="K22" t="str">
+        <f t="shared" si="51"/>
         <v>DosSantos_etal_2020_unpublished</v>
       </c>
-      <c r="L21" t="str">
-        <f t="shared" si="45"/>
+      <c r="L22" t="str">
+        <f t="shared" si="52"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
-      <c r="M21" t="str">
-        <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+      <c r="M22" t="str">
+        <f t="array" ref="M22">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished.tsv</v>
       </c>
-      <c r="P21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z21" s="1" t="s">
+      <c r="P22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R22" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="AA21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE21" s="1" t="s">
+      <c r="S22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T22" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="22" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="U22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" t="str">
-        <f t="shared" ref="E22" si="51">RIGHT(A22,1)</f>
+      <c r="AA22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" ref="E23" si="58">RIGHT(A23,1)</f>
         <v>3</v>
       </c>
-      <c r="F22" t="str">
-        <f t="shared" ref="F22" si="52">G22 &amp; IF(H22&lt;&gt;"", "_" &amp; H22, "_") &amp; IF(I22&lt;&gt;"", "_" &amp; I22, "_") &amp; IF(B22&lt;&gt;"", "_" &amp; B22, "")</f>
+      <c r="F23" t="str">
+        <f t="shared" ref="F23" si="59">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
         <v>Eagleman_Vaughn_2021</v>
       </c>
-      <c r="G22" t="str">
-        <f t="shared" ref="G22" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A22,","), "-", ""), " ", "")</f>
+      <c r="G23" t="str">
+        <f t="shared" ref="G23" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
         <v>Eagleman</v>
       </c>
-      <c r="H22" t="str">
-        <f t="shared" ref="H22" si="54">IF(ISNUMBER(FIND("&amp;", A22)),
-    IF(LEN(A22)-LEN(SUBSTITUTE(A22, ",", ""))&gt;=6, "etal", MID(A22, SEARCH("&amp; ", A22)+2, SEARCH(",", A22, SEARCH("&amp; ", A22)+2) - SEARCH("&amp; ", A22)-2)),
+      <c r="H23" t="str">
+        <f t="shared" ref="H23" si="61">IF(ISNUMBER(FIND("&amp;", A23)),
+    IF(LEN(A23)-LEN(SUBSTITUTE(A23, ",", ""))&gt;=6, "etal", MID(A23, SEARCH("&amp; ", A23)+2, SEARCH(",", A23, SEARCH("&amp; ", A23)+2) - SEARCH("&amp; ", A23)-2)),
     ""
 )</f>
         <v>Vaughn</v>
       </c>
-      <c r="I22" t="str">
-        <f t="shared" ref="I22" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, "("), ")")</f>
+      <c r="I23" t="str">
+        <f t="shared" ref="I23" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
         <v>2021</v>
       </c>
-      <c r="J22" t="str">
-        <f t="shared" si="19"/>
+      <c r="J23" t="str">
+        <f t="shared" si="26"/>
         <v>10.3389/fnins.2021.632853</v>
       </c>
-      <c r="K22" t="str">
-        <f t="shared" si="44"/>
+      <c r="K23" t="str">
+        <f t="shared" si="51"/>
         <v>Eagleman_Vaughn_2021_TABLE1</v>
       </c>
-      <c r="L22" t="str">
-        <f t="shared" si="45"/>
+      <c r="L23" t="str">
+        <f t="shared" si="52"/>
         <v>10.3389%2Ffnins.2021.632853_TABLE1</v>
-      </c>
-      <c r="M22" t="str">
-        <f t="array" ref="M22">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="R22" s="4"/>
-      <c r="U22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" t="str">
-        <f t="shared" si="24"/>
-        <v>5</v>
-      </c>
-      <c r="F23" t="str">
-        <f t="shared" si="25"/>
-        <v>Falcone_etal_2019</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="26"/>
-        <v>Falcone</v>
-      </c>
-      <c r="H23" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I23" t="str">
-        <f t="shared" si="28"/>
-        <v>2019</v>
-      </c>
-      <c r="J23" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1002/cne.24605</v>
-      </c>
-      <c r="K23" t="str">
-        <f t="shared" si="44"/>
-        <v>Falcone_etal_2019_TABLE1</v>
-      </c>
-      <c r="L23" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M23" t="str">
         <f t="array" ref="M23">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24605_TABLE1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>151</v>
       </c>
       <c r="R23" s="4"/>
       <c r="U23" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="Y23" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="15.95" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="E24" t="str">
-        <f t="shared" ref="E24" si="56">RIGHT(A24,1)</f>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F24" t="str">
-        <f t="shared" ref="F24" si="57">G24 &amp; IF(H24&lt;&gt;"", "_" &amp; H24, "_") &amp; IF(I24&lt;&gt;"", "_" &amp; I24, "_") &amp; IF(B24&lt;&gt;"", "_" &amp; B24, "")</f>
+        <f t="shared" si="32"/>
         <v>Falcone_etal_2019</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" ref="G24" si="58">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A24,","), "-", ""), " ", "")</f>
+        <f t="shared" si="33"/>
         <v>Falcone</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" ref="H24" si="59">IF(ISNUMBER(FIND("&amp;", A24)),
-    IF(LEN(A24)-LEN(SUBSTITUTE(A24, ",", ""))&gt;=6, "etal", MID(A24, SEARCH("&amp; ", A24)+2, SEARCH(",", A24, SEARCH("&amp; ", A24)+2) - SEARCH("&amp; ", A24)-2)),
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="35"/>
+        <v>2019</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1002/cne.24605</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="51"/>
+        <v>Falcone_etal_2019_TABLE1</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="52"/>
+        <v>10.1002%2Fcne.24605_TABLE1</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="array" ref="M24">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1002%2Fcne.24605_TABLE1.tsv</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R24" s="4"/>
+      <c r="U24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" ref="E25" si="63">RIGHT(A25,1)</f>
+        <v>5</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" ref="F25" si="64">G25 &amp; IF(H25&lt;&gt;"", "_" &amp; H25, "_") &amp; IF(I25&lt;&gt;"", "_" &amp; I25, "_") &amp; IF(B25&lt;&gt;"", "_" &amp; B25, "")</f>
+        <v>Falcone_etal_2019</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" ref="G25" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A25,","), "-", ""), " ", "")</f>
+        <v>Falcone</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" ref="H25" si="66">IF(ISNUMBER(FIND("&amp;", A25)),
+    IF(LEN(A25)-LEN(SUBSTITUTE(A25, ",", ""))&gt;=6, "etal", MID(A25, SEARCH("&amp; ", A25)+2, SEARCH(",", A25, SEARCH("&amp; ", A25)+2) - SEARCH("&amp; ", A25)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I24" t="str">
-        <f t="shared" ref="I24" si="60">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A24, "("), ")")</f>
+      <c r="I25" t="str">
+        <f t="shared" ref="I25" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, "("), ")")</f>
         <v>2019</v>
       </c>
-      <c r="J24" t="str">
-        <f t="shared" si="19"/>
+      <c r="J25" t="str">
+        <f t="shared" si="26"/>
         <v>10.1002/cne.24605</v>
       </c>
-      <c r="K24" t="str">
-        <f t="shared" si="44"/>
+      <c r="K25" t="str">
+        <f t="shared" si="51"/>
         <v>Falcone_etal_2019_TABLE2</v>
       </c>
-      <c r="L24" t="str">
-        <f t="shared" si="45"/>
+      <c r="L25" t="str">
+        <f t="shared" si="52"/>
         <v>10.1002%2Fcne.24605_TABLE2</v>
-      </c>
-      <c r="M24" t="str">
-        <f t="array" ref="M24">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24605_TABLE2.tsv</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="R24" s="4"/>
-      <c r="U24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" t="str">
-        <f t="shared" si="24"/>
-        <v>6</v>
-      </c>
-      <c r="F25" t="str">
-        <f t="shared" si="25"/>
-        <v>Finlay_etal_2006</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="26"/>
-        <v>Finlay</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I25" t="str">
-        <f t="shared" si="28"/>
-        <v>2006</v>
-      </c>
-      <c r="J25" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1093/oso/9780198568742.003.0006</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="44"/>
-        <v>Finlay_etal_2006_Table6.1</v>
-      </c>
-      <c r="L25" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M25" t="str">
         <f t="array" ref="M25">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
-      </c>
-      <c r="N25" s="5"/>
-      <c r="P25" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R25" s="1" t="s">
+        <v>10.1002%2Fcne.24605_TABLE2.tsv</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T25" s="1" t="s">
+      <c r="R25" s="4"/>
+      <c r="U25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Y25" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E26" t="str">
-        <f t="shared" si="24"/>
-        <v>x</v>
+        <f t="shared" si="31"/>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" si="25"/>
-        <v>Fu_etal_2013</v>
+        <f t="shared" si="32"/>
+        <v>Finlay_etal_2006</v>
       </c>
       <c r="G26" t="str">
+        <f t="shared" si="33"/>
+        <v>Finlay</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="35"/>
+        <v>2006</v>
+      </c>
+      <c r="J26" t="str">
         <f t="shared" si="26"/>
-        <v>Fu</v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I26" t="str">
-        <f t="shared" si="28"/>
-        <v>2013</v>
-      </c>
-      <c r="J26" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1007/s00429-012-0462-x</v>
+        <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="K26" t="str">
-        <f t="shared" si="44"/>
-        <v>Fu_etal_2013_Table1</v>
+        <f t="shared" si="51"/>
+        <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
+        <f t="shared" si="52"/>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M26" t="str">
         <f t="array" ref="M26">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N26" s="1" t="s">
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+      </c>
+      <c r="N26" s="5"/>
+      <c r="P26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X26" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="Y26" s="1" t="s">
         <v>162</v>
       </c>
       <c r="Z26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AC26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="24"/>
-        <v>6</v>
+        <f t="shared" si="31"/>
+        <v>x</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="25"/>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" si="32"/>
+        <v>Fu_etal_2013</v>
       </c>
       <c r="G27" t="str">
+        <f t="shared" si="33"/>
+        <v>Fu</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="35"/>
+        <v>2013</v>
+      </c>
+      <c r="J27" t="str">
         <f t="shared" si="26"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="28"/>
-        <v>2009</v>
-      </c>
-      <c r="J27" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1073/pnas.0905777106</v>
+        <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" si="44"/>
-        <v>Garwicz_etal_2009_TableS1</v>
+        <f t="shared" si="51"/>
+        <v>Fu_etal_2013_Table1</v>
       </c>
       <c r="L27" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1073%2Fpnas.0905777106_TableS1</v>
+        <f t="shared" si="52"/>
+        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M27" t="str">
         <f t="array" ref="M27">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1073%2Fpnas.0905777106_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X27" s="1" t="s">
+      <c r="Z27" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="28" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC27" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="E28" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>6</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>Garwicz_etal_2009</v>
       </c>
       <c r="G28" t="str">
+        <f t="shared" si="33"/>
+        <v>Garwicz</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="35"/>
+        <v>2009</v>
+      </c>
+      <c r="J28" t="str">
         <f t="shared" si="26"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="28"/>
-        <v>2009</v>
-      </c>
-      <c r="J28" t="str">
-        <f t="shared" si="19"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="44"/>
-        <v>Garwicz_etal_2009_TableS2</v>
+        <f t="shared" si="51"/>
+        <v>Garwicz_etal_2009_TableS1</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1073%2Fpnas.0905777106_TableS2</v>
+        <f t="shared" si="52"/>
+        <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M28" t="str">
         <f t="array" ref="M28">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1073%2Fpnas.0905777106_TableS1.tsv</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>168</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" ht="15.95" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E29" t="str">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>6</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="25"/>
-        <v>Genoud_etal_2018</v>
+        <f t="shared" si="32"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="G29" t="str">
+        <f t="shared" si="33"/>
+        <v>Garwicz</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="35"/>
+        <v>2009</v>
+      </c>
+      <c r="J29" t="str">
         <f t="shared" si="26"/>
-        <v>Genoud</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="28"/>
-        <v>2018</v>
-      </c>
-      <c r="J29" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1111/brv.12350</v>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="44"/>
-        <v>Genoud_etal_2018_TableS2</v>
+        <f t="shared" si="51"/>
+        <v>Garwicz_etal_2009_TableS2</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1111%2Fbrv.12350_TableS2</v>
+        <f t="shared" si="52"/>
+        <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M29" t="str">
         <f t="array" ref="M29">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC29" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" ht="15.95" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="24"/>
-        <v>8</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="25"/>
-        <v>Granatosky__2018</v>
+        <f t="shared" si="32"/>
+        <v>Genoud_etal_2018</v>
       </c>
       <c r="G30" t="str">
+        <f t="shared" si="33"/>
+        <v>Genoud</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="35"/>
+        <v>2018</v>
+      </c>
+      <c r="J30" t="str">
         <f t="shared" si="26"/>
-        <v>Granatosky</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <f t="shared" si="28"/>
-        <v>2018</v>
-      </c>
-      <c r="J30" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1111/jzo.12608</v>
+        <v>10.1111/brv.12350</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="44"/>
-        <v>Granatosky__2018_TableS1</v>
+        <f t="shared" si="51"/>
+        <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="L30" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1111%2Fjzo.12608_TableS1</v>
+        <f t="shared" si="52"/>
+        <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="M30" t="str">
         <f t="array" ref="M30">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
@@ -3799,1713 +3803,1696 @@
         <v>173</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+      <c r="AC30" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" ht="15.95" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D31" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="E31" t="str">
-        <f t="shared" ref="E31" si="61">RIGHT(A31,1)</f>
+        <f t="shared" si="31"/>
+        <v>8</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="32"/>
+        <v>Granatosky__2018</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="33"/>
+        <v>Granatosky</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="35"/>
+        <v>2018</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1111/jzo.12608</v>
+      </c>
+      <c r="K31" t="str">
+        <f t="shared" si="51"/>
+        <v>Granatosky__2018_TableS1</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="52"/>
+        <v>10.1111%2Fjzo.12608_TableS1</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" t="str">
+        <f t="shared" ref="E32" si="68">RIGHT(A32,1)</f>
         <v>7</v>
       </c>
-      <c r="F31" t="str">
-        <f t="shared" ref="F31" si="62">G31 &amp; IF(H31&lt;&gt;"", "_" &amp; H31, "_") &amp; IF(I31&lt;&gt;"", "_" &amp; I31, "_") &amp; IF(B31&lt;&gt;"", "_" &amp; B31, "")</f>
+      <c r="F32" t="str">
+        <f t="shared" ref="F32" si="69">G32 &amp; IF(H32&lt;&gt;"", "_" &amp; H32, "_") &amp; IF(I32&lt;&gt;"", "_" &amp; I32, "_") &amp; IF(B32&lt;&gt;"", "_" &amp; B32, "")</f>
         <v>Haarlem_etal_2026</v>
       </c>
-      <c r="G31" t="str">
-        <f t="shared" ref="G31" si="63">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A31,","), "-", ""), " ", "")</f>
+      <c r="G32" t="str">
+        <f t="shared" ref="G32" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A32,","), "-", ""), " ", "")</f>
         <v>Haarlem</v>
       </c>
-      <c r="H31" t="str">
-        <f t="shared" ref="H31" si="64">IF(ISNUMBER(FIND("&amp;", A31)),
-    IF(LEN(A31)-LEN(SUBSTITUTE(A31, ",", ""))&gt;=6, "etal", MID(A31, SEARCH("&amp; ", A31)+2, SEARCH(",", A31, SEARCH("&amp; ", A31)+2) - SEARCH("&amp; ", A31)-2)),
+      <c r="H32" t="str">
+        <f t="shared" ref="H32" si="71">IF(ISNUMBER(FIND("&amp;", A32)),
+    IF(LEN(A32)-LEN(SUBSTITUTE(A32, ",", ""))&gt;=6, "etal", MID(A32, SEARCH("&amp; ", A32)+2, SEARCH(",", A32, SEARCH("&amp; ", A32)+2) - SEARCH("&amp; ", A32)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I31" t="str">
-        <f t="shared" ref="I31" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A31, "("), ")")</f>
+      <c r="I32" t="str">
+        <f t="shared" ref="I32" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A32, "("), ")")</f>
         <v>2026</v>
       </c>
-      <c r="J31" t="str">
-        <f t="shared" ref="J31" si="66">IF(C31&lt;&gt;"", C31, IF(C31="", _xlfn.TEXTAFTER(A31,"https://doi.org/"), C31))</f>
+      <c r="J32" t="str">
+        <f t="shared" ref="J32" si="73">IF(C32&lt;&gt;"", C32, IF(C32="", _xlfn.TEXTAFTER(A32,"https://doi.org/"), C32))</f>
         <v>10.1038/s41559-026-02994-7</v>
       </c>
-      <c r="K31" t="str">
-        <f t="shared" ref="K31" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,F31,(SUBSTITUTE(SUBSTITUTE(D31," ",""), "_", ""))))</f>
+      <c r="K32" t="str">
+        <f t="shared" ref="K32" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,F32,(SUBSTITUTE(SUBSTITUTE(D32," ",""), "_", ""))))</f>
         <v>Haarlem_etal_2026_</v>
       </c>
-      <c r="L31" t="str">
-        <f t="shared" ref="L31" si="68">IF(ISBLANK(C31),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L32" t="str">
+        <f t="shared" ref="L32" si="75">IF(ISBLANK(C32),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41559-026-02994-7_</v>
-      </c>
-      <c r="M31" t="str">
-        <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N31" s="10"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32" t="str">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="F32" t="str">
-        <f t="shared" si="25"/>
-        <v>Heffner_Masterton_1975</v>
-      </c>
-      <c r="G32" t="str">
-        <f t="shared" si="26"/>
-        <v>Heffner</v>
-      </c>
-      <c r="H32" t="str">
-        <f t="shared" si="27"/>
-        <v>Masterton</v>
-      </c>
-      <c r="I32" t="str">
-        <f t="shared" si="28"/>
-        <v>1975</v>
-      </c>
-      <c r="J32" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1159/000124401</v>
-      </c>
-      <c r="K32" t="str">
-        <f t="shared" si="44"/>
-        <v>Heffner_Masterton_1975_TableI</v>
-      </c>
-      <c r="L32" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M32" t="str">
         <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000124401_TableI.tsv</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T32" s="1" t="s">
+        <v>notfound</v>
+      </c>
+      <c r="N32" s="10"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="Z32" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC32" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE32" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E33" t="str">
-        <f t="shared" si="24"/>
-        <v>4</v>
+        <f t="shared" si="31"/>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="25"/>
-        <v>Heffner_Masterton_1983</v>
+        <f t="shared" si="32"/>
+        <v>Heffner_Masterton_1975</v>
       </c>
       <c r="G33" t="str">
+        <f t="shared" si="33"/>
+        <v>Heffner</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="34"/>
+        <v>Masterton</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="35"/>
+        <v>1975</v>
+      </c>
+      <c r="J33" t="str">
         <f t="shared" si="26"/>
-        <v>Heffner</v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="27"/>
-        <v>Masterton</v>
-      </c>
-      <c r="I33" t="str">
-        <f t="shared" si="28"/>
-        <v>1983</v>
-      </c>
-      <c r="J33" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1159/000121494</v>
+        <v>10.1159/000124401</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="44"/>
-        <v>Heffner_Masterton_1983_TableI</v>
+        <f t="shared" si="51"/>
+        <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="L33" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000121494_TableI</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000124401_TableI.tsv</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="31"/>
+        <v>4</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="32"/>
+        <v>Heffner_Masterton_1983</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="33"/>
+        <v>Heffner</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="34"/>
+        <v>Masterton</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="35"/>
+        <v>1983</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1159/000121494</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" si="51"/>
+        <v>Heffner_Masterton_1983_TableI</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000121494_TableI</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R33" s="4"/>
-      <c r="T33" s="1" t="str">
-        <f>IF(S33="N", R33, "write file name")</f>
+      <c r="P34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R34" s="4"/>
+      <c r="T34" s="1" t="str">
+        <f>IF(S34="N", R34, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE33" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" t="str">
-        <f t="shared" ref="E34" si="69">RIGHT(A34,1)</f>
+      <c r="U34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG34" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" ref="E35" si="76">RIGHT(A35,1)</f>
         <v>8</v>
       </c>
-      <c r="F34" t="str">
-        <f t="shared" ref="F34" si="70">G34 &amp; IF(H34&lt;&gt;"", "_" &amp; H34, "_") &amp; IF(I34&lt;&gt;"", "_" &amp; I34, "_") &amp; IF(B34&lt;&gt;"", "_" &amp; B34, "")</f>
+      <c r="F35" t="str">
+        <f t="shared" ref="F35" si="77">G35 &amp; IF(H35&lt;&gt;"", "_" &amp; H35, "_") &amp; IF(I35&lt;&gt;"", "_" &amp; I35, "_") &amp; IF(B35&lt;&gt;"", "_" &amp; B35, "")</f>
         <v>Heiss_etal_2004</v>
       </c>
-      <c r="G34" t="str">
-        <f t="shared" ref="G34" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A34,","), "-", ""), " ", "")</f>
+      <c r="G35" t="str">
+        <f t="shared" ref="G35" si="78">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A35,","), "-", ""), " ", "")</f>
         <v>Heiss</v>
       </c>
-      <c r="H34" t="str">
-        <f t="shared" ref="H34" si="72">IF(ISNUMBER(FIND("&amp;", A34)),
-    IF(LEN(A34)-LEN(SUBSTITUTE(A34, ",", ""))&gt;=6, "etal", MID(A34, SEARCH("&amp; ", A34)+2, SEARCH(",", A34, SEARCH("&amp; ", A34)+2) - SEARCH("&amp; ", A34)-2)),
+      <c r="H35" t="str">
+        <f t="shared" ref="H35" si="79">IF(ISNUMBER(FIND("&amp;", A35)),
+    IF(LEN(A35)-LEN(SUBSTITUTE(A35, ",", ""))&gt;=6, "etal", MID(A35, SEARCH("&amp; ", A35)+2, SEARCH(",", A35, SEARCH("&amp; ", A35)+2) - SEARCH("&amp; ", A35)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I34" t="str">
-        <f t="shared" ref="I34" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, "("), ")")</f>
+      <c r="I35" t="str">
+        <f t="shared" ref="I35" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A35, "("), ")")</f>
         <v>2004</v>
       </c>
-      <c r="J34" t="str">
-        <f t="shared" si="19"/>
+      <c r="J35" t="str">
+        <f t="shared" si="26"/>
         <v>WOS:000225086000011</v>
       </c>
-      <c r="K34" t="str">
-        <f t="shared" ref="K34" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,F34,(SUBSTITUTE(SUBSTITUTE(D34," ",""), "_", ""))))</f>
+      <c r="K35" t="str">
+        <f t="shared" ref="K35" si="81">TRIM(_xlfn.TEXTJOIN("_",FALSE,F35,(SUBSTITUTE(SUBSTITUTE(D35," ",""), "_", ""))))</f>
         <v>Heiss_etal_2004_TABLE1</v>
       </c>
-      <c r="L34" t="str">
-        <f t="shared" ref="L34" si="75">IF(ISBLANK(C34),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L35" t="str">
+        <f t="shared" ref="L35" si="82">IF(ISBLANK(C35),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J35, SUBSTITUTE(D35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C35, SUBSTITUTE(D35,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>WOS%3A000225086000011_TABLE1</v>
-      </c>
-      <c r="M34" t="str">
-        <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="4"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="10"/>
-      <c r="Y34" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AE34" s="1"/>
-      <c r="AG34" s="10"/>
-    </row>
-    <row r="35" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="str">
-        <f t="shared" si="24"/>
-        <v>8</v>
-      </c>
-      <c r="F35" t="str">
-        <f t="shared" si="25"/>
-        <v>Heldstab_etal_2016</v>
-      </c>
-      <c r="G35" t="str">
-        <f t="shared" si="26"/>
-        <v>Heldstab</v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I35" t="str">
-        <f t="shared" si="28"/>
-        <v>2016</v>
-      </c>
-      <c r="J35" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1038/srep24528</v>
-      </c>
-      <c r="K35" t="str">
-        <f t="shared" si="44"/>
-        <v>Heldstab_etal_2016_TableS1</v>
-      </c>
-      <c r="L35" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="M35" t="str">
         <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P35" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="N35" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
       <c r="R35" s="4"/>
-      <c r="T35" s="1" t="str">
-        <f>IF(S35="N", R35, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="10"/>
       <c r="Y35" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AE35" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+      <c r="AE35" s="1"/>
+      <c r="AG35" s="10"/>
+    </row>
+    <row r="36" spans="1:33" ht="15.95" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="24"/>
-        <v>3</v>
+        <f t="shared" si="31"/>
+        <v>8</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="25"/>
-        <v>HerculanoHouzel__2015</v>
+        <f t="shared" si="32"/>
+        <v>Heldstab_etal_2016</v>
       </c>
       <c r="G36" t="str">
+        <f t="shared" si="33"/>
+        <v>Heldstab</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="35"/>
+        <v>2016</v>
+      </c>
+      <c r="J36" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H36" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J36" t="str">
-        <f t="shared" ref="J36" si="76">IF(C36&lt;&gt;"", C36, IF(C36="", _xlfn.TEXTAFTER(A36,"https://doi.org/"), C36))</f>
-        <v>10.1098/rspb.2015.1853</v>
+        <v>10.1038/srep24528</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" ref="K36" si="77">TRIM(_xlfn.TEXTJOIN("_",FALSE,F36,(SUBSTITUTE(SUBSTITUTE(D36," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel__2015_Table1</v>
+        <f t="shared" si="51"/>
+        <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="L36" t="str">
-        <f t="shared" ref="L36" si="78">IF(ISBLANK(C36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1098%2Frspb.2015.1853_Table1</v>
+        <f t="shared" si="52"/>
+        <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="M36" t="str">
         <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R36" s="4"/>
+      <c r="T36" s="1" t="str">
+        <f>IF(S36="N", R36, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AE36" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="31"/>
+        <v>3</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="32"/>
+        <v>HerculanoHouzel__2015</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" ref="J37" si="83">IF(C37&lt;&gt;"", C37, IF(C37="", _xlfn.TEXTAFTER(A37,"https://doi.org/"), C37))</f>
+        <v>10.1098/rspb.2015.1853</v>
+      </c>
+      <c r="K37" t="str">
+        <f t="shared" ref="K37" si="84">TRIM(_xlfn.TEXTJOIN("_",FALSE,F37,(SUBSTITUTE(SUBSTITUTE(D37," ",""), "_", ""))))</f>
+        <v>HerculanoHouzel__2015_Table1</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" ref="L37" si="85">IF(ISBLANK(C37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J37, SUBSTITUTE(D37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C37, SUBSTITUTE(D37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1098%2Frspb.2015.1853_Table1</v>
+      </c>
+      <c r="M37" t="str">
+        <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1098%2Frspb.2015.1853_Table1.tsv</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="R36" s="4"/>
-      <c r="U36" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="V36" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
-    </row>
-    <row r="37" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E37" t="str">
-        <f t="shared" ref="E37" si="79">RIGHT(A37,1)</f>
+      <c r="N37" s="1"/>
+      <c r="R37" s="4"/>
+      <c r="U37" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="V37" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+    </row>
+    <row r="38" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" ref="E38" si="86">RIGHT(A38,1)</f>
         <v>3</v>
       </c>
-      <c r="F37" t="str">
-        <f t="shared" ref="F37" si="80">G37 &amp; IF(H37&lt;&gt;"", "_" &amp; H37, "_") &amp; IF(I37&lt;&gt;"", "_" &amp; I37, "_") &amp; IF(B37&lt;&gt;"", "_" &amp; B37, "")</f>
+      <c r="F38" t="str">
+        <f t="shared" ref="F38" si="87">G38 &amp; IF(H38&lt;&gt;"", "_" &amp; H38, "_") &amp; IF(I38&lt;&gt;"", "_" &amp; I38, "_") &amp; IF(B38&lt;&gt;"", "_" &amp; B38, "")</f>
         <v>HerculanoHouzel__2015</v>
       </c>
-      <c r="G37" t="str">
-        <f t="shared" ref="G37" si="81">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+      <c r="G38" t="str">
+        <f t="shared" ref="G38" si="88">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="H37" t="str">
-        <f t="shared" ref="H37" si="82">IF(ISNUMBER(FIND("&amp;", A37)),
-    IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=6, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
+      <c r="H38" t="str">
+        <f t="shared" ref="H38" si="89">IF(ISNUMBER(FIND("&amp;", A38)),
+    IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=6, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
     ""
 )</f>
         <v/>
       </c>
-      <c r="I37" t="str">
-        <f t="shared" ref="I37" si="83">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+      <c r="I38" t="str">
+        <f t="shared" ref="I38" si="90">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
         <v>2015</v>
       </c>
-      <c r="J37" t="str">
-        <f t="shared" si="19"/>
+      <c r="J38" t="str">
+        <f t="shared" si="26"/>
         <v>10.1098/rspb.2015.1853</v>
       </c>
-      <c r="K37" t="str">
-        <f t="shared" si="44"/>
+      <c r="K38" t="str">
+        <f t="shared" si="51"/>
         <v>HerculanoHouzel__2015_Table2</v>
       </c>
-      <c r="L37" t="str">
-        <f t="shared" si="45"/>
+      <c r="L38" t="str">
+        <f t="shared" si="52"/>
         <v>10.1098%2Frspb.2015.1853_Table2</v>
-      </c>
-      <c r="M37" t="str">
-        <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="R37" s="4"/>
-      <c r="U37" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="V37" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y37" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z37" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E38" t="str">
-        <f t="shared" si="24"/>
-        <v>5</v>
-      </c>
-      <c r="F38" t="str">
-        <f t="shared" si="25"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="G38" t="str">
-        <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H38" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I38" t="str">
-        <f t="shared" si="28"/>
-        <v>2013</v>
-      </c>
-      <c r="J38" t="str">
-        <f t="shared" si="19"/>
-        <v>10.3389/fnana.2013.00035</v>
-      </c>
-      <c r="K38" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
-      </c>
-      <c r="L38" t="str">
-        <f t="shared" si="45"/>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M38" t="str">
         <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="R38" s="4"/>
+      <c r="U38" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="V38" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z38" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" ht="15.95" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G39" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="35"/>
+        <v>2013</v>
+      </c>
+      <c r="J39" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I39" t="str">
-        <f t="shared" si="28"/>
-        <v>2013</v>
-      </c>
-      <c r="J39" t="str">
-        <f t="shared" si="19"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="L39" t="str">
-        <f t="shared" si="45"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+        <f t="shared" si="52"/>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M39" t="str">
         <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" ht="18.95" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G40" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="35"/>
+        <v>2013</v>
+      </c>
+      <c r="J40" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" si="28"/>
-        <v>2013</v>
-      </c>
-      <c r="J40" t="str">
-        <f t="shared" si="19"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K40" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="L40" t="str">
-        <f t="shared" si="45"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+        <f t="shared" si="52"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="M40" t="str">
         <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="17.100000000000001" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="24"/>
-        <v>3</v>
+        <f t="shared" si="31"/>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="25"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="32"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G41" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="35"/>
+        <v>2013</v>
+      </c>
+      <c r="J41" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I41" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1159/000437413</v>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2015_Table1</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="L41" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000437413_Table1</v>
+        <f t="shared" si="52"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="M41" t="str">
         <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>52</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T41" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" ht="17.100000000000001" customHeight="1">
+      <c r="A42" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="U41" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X41" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE41" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G42" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J42" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H42" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I42" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J42" t="str">
-        <f t="shared" si="19"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K42" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2015_Table2</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="L42" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000437413_Table2</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="M42" t="str">
         <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table2.tsv</v>
+        <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N42" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T42" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R42" s="4" t="s">
+      <c r="U42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X42" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="S42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T42" s="1" t="s">
+      <c r="Y42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE42" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="U42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y42" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA42" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB42" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE42" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:33" ht="17.100000000000001" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G43" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J43" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I43" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="19"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K43" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2015_Table3</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="L43" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000437413_Table3</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="M43" t="str">
         <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table3.tsv</v>
+        <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R43" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R43" s="4" t="s">
+      <c r="S43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T43" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="S43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T43" s="1" t="s">
+      <c r="U43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA43" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" ht="17.100000000000001" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="U43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W43" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X43" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE43" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="E44" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G44" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J44" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I44" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J44" t="str">
-        <f t="shared" si="19"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K44" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2015_Table4</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="L44" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000437413_Table4</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="M44" t="str">
         <f t="array" ref="M44">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table4.tsv</v>
+        <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R44" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R44" s="4" t="s">
+      <c r="S44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T44" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="S44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="U44" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE44" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E45" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G45" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J45" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H45" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I45" t="str">
-        <f t="shared" si="28"/>
-        <v>2015</v>
-      </c>
-      <c r="J45" t="str">
-        <f t="shared" si="19"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2015_Table5</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="L45" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1159%2F000437413_Table5</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="M45" t="str">
         <f t="array" ref="M45">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table5.tsv</v>
+        <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="N45" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T45" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R45" s="4" t="s">
+      <c r="U45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="S45" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X45" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE45" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E46" t="str">
-        <f t="shared" si="24"/>
-        <v>5</v>
+        <f t="shared" si="31"/>
+        <v>3</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="25"/>
-        <v>HerculanoHouzel_etal_2020</v>
+        <f t="shared" si="32"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G46" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="35"/>
+        <v>2015</v>
+      </c>
+      <c r="J46" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H46" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I46" t="str">
-        <f t="shared" si="28"/>
-        <v>2020</v>
-      </c>
-      <c r="J46" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1002/cne.24985</v>
+        <v>10.1159/000437413</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2020_TABLE1</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="L46" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1002%2Fcne.24985_TABLE1</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="M46" t="str">
         <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+        <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="N46" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T46" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R46" s="4" t="s">
+      <c r="U46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A47" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W46" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE46" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="E47" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="G47" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="35"/>
+        <v>2020</v>
+      </c>
+      <c r="J47" t="str">
         <f t="shared" si="26"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I47" t="str">
-        <f t="shared" si="28"/>
-        <v>2020</v>
-      </c>
-      <c r="J47" t="str">
-        <f t="shared" si="19"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="K47" t="str">
-        <f t="shared" si="44"/>
-        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L47" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1002%2Fcne.24985_TABLE2</v>
+        <f t="shared" si="52"/>
+        <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M47" t="str">
         <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y47" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R47" s="4" t="s">
+      <c r="AA47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE47" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="S47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W47" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y47" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="AA47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE47" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:33" ht="15.95" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="E48" t="str">
-        <f t="shared" si="24"/>
-        <v>4</v>
+        <f t="shared" si="31"/>
+        <v>5</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="25"/>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="32"/>
+        <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="G48" t="str">
+        <f t="shared" si="33"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="35"/>
+        <v>2020</v>
+      </c>
+      <c r="J48" t="str">
         <f t="shared" si="26"/>
-        <v>Isler</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I48" t="str">
-        <f t="shared" si="28"/>
-        <v>2008</v>
-      </c>
-      <c r="J48" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <v>10.1002/cne.24985</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="44"/>
-        <v>Isler_etal_2008_Table2</v>
+        <f t="shared" si="51"/>
+        <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="L48" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+        <f t="shared" si="52"/>
+        <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="M48" t="str">
         <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE48" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" ht="15.95" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="E49" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>4</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G49" t="str">
+        <f t="shared" si="33"/>
+        <v>Isler</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="35"/>
+        <v>2008</v>
+      </c>
+      <c r="J49" t="str">
         <f t="shared" si="26"/>
-        <v>Isler</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" si="27"/>
-        <v>etal</v>
-      </c>
-      <c r="I49" t="str">
-        <f t="shared" si="28"/>
-        <v>2008</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="19"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K49" t="str">
-        <f t="shared" si="44"/>
-        <v>Isler_etal_2008_Table7</v>
+        <f t="shared" si="51"/>
+        <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="L49" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+        <f t="shared" si="52"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="M49" t="str">
         <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="31"/>
+        <v>4</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="32"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="33"/>
+        <v>Isler</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="34"/>
+        <v>etal</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="35"/>
+        <v>2008</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="51"/>
+        <v>Isler_etal_2008_Table7</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="52"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="Q49" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E50" t="str">
-        <f t="shared" ref="E50:E82" si="84">RIGHT(A50,1)</f>
+      <c r="Q50" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A51" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" ref="E51:E83" si="91">RIGHT(A51,1)</f>
         <v>4</v>
       </c>
-      <c r="F50" t="str">
-        <f t="shared" ref="F50:F82" si="85">G50 &amp; IF(H50&lt;&gt;"", "_" &amp; H50, "_") &amp; IF(I50&lt;&gt;"", "_" &amp; I50, "_") &amp; IF(B50&lt;&gt;"", "_" &amp; B50, "")</f>
+      <c r="F51" t="str">
+        <f t="shared" ref="F51:F83" si="92">G51 &amp; IF(H51&lt;&gt;"", "_" &amp; H51, "_") &amp; IF(I51&lt;&gt;"", "_" &amp; I51, "_") &amp; IF(B51&lt;&gt;"", "_" &amp; B51, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="G50" t="str">
-        <f t="shared" ref="G50:G82" si="86">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+      <c r="G51" t="str">
+        <f t="shared" ref="G51:G83" si="93">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A51,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="H50" t="str">
-        <f t="shared" ref="H50:H82" si="87">IF(ISNUMBER(FIND("&amp;", A50)),
-    IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
+      <c r="H51" t="str">
+        <f t="shared" ref="H51:H83" si="94">IF(ISNUMBER(FIND("&amp;", A51)),
+    IF(LEN(A51)-LEN(SUBSTITUTE(A51, ",", ""))&gt;=6, "etal", MID(A51, SEARCH("&amp; ", A51)+2, SEARCH(",", A51, SEARCH("&amp; ", A51)+2) - SEARCH("&amp; ", A51)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I50" t="str">
-        <f t="shared" ref="I50:I82" si="88">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+      <c r="I51" t="str">
+        <f t="shared" ref="I51:I83" si="95">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A51, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="J50" t="str">
-        <f t="shared" si="19"/>
+      <c r="J51" t="str">
+        <f t="shared" si="26"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="K50" t="str">
-        <f t="shared" si="44"/>
+      <c r="K51" t="str">
+        <f t="shared" si="51"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="L50" t="str">
-        <f t="shared" si="45"/>
+      <c r="L51" t="str">
+        <f t="shared" si="52"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
-      </c>
-      <c r="M50" t="str">
-        <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" t="str">
-        <f t="shared" si="84"/>
-        <v>4</v>
-      </c>
-      <c r="F51" t="str">
-        <f t="shared" si="85"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G51" t="str">
-        <f t="shared" si="86"/>
-        <v>Isler</v>
-      </c>
-      <c r="H51" t="str">
-        <f t="shared" si="87"/>
-        <v>etal</v>
-      </c>
-      <c r="I51" t="str">
-        <f t="shared" si="88"/>
-        <v>2008</v>
-      </c>
-      <c r="J51" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="K51" t="str">
-        <f t="shared" si="44"/>
-        <v>Isler_etal_2008_TableS2</v>
-      </c>
-      <c r="L51" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M51" t="str">
         <f t="array" ref="M51">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" ht="15.95" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>4</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Isler</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2008</v>
       </c>
       <c r="J52" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="44"/>
-        <v>Isler_etal_2008_TableS3</v>
+        <f t="shared" si="51"/>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L52" t="str">
-        <f t="shared" si="45"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+        <f t="shared" si="52"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M52" t="str">
         <f t="array" ref="M52">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" ht="15.95" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E53" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>4</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Isler</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2008</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" ref="K53:K82" si="89">TRIM(_xlfn.TEXTJOIN("_",FALSE,F53,(SUBSTITUTE(SUBSTITUTE(D53," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
+        <f t="shared" si="51"/>
+        <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L53" t="str">
-        <f t="shared" ref="L53:L82" si="90">IF(ISBLANK(C53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
+        <f t="shared" si="52"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M53" t="str">
         <f t="array" ref="M53">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" ht="15.95" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>234</v>
       </c>
       <c r="E54" t="str">
-        <f t="shared" si="84"/>
-        <v>x</v>
+        <f t="shared" si="91"/>
+        <v>4</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="85"/>
-        <v>Iwaniuk_etal_1999</v>
+        <f t="shared" si="92"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="86"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="93"/>
+        <v>Isler</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="88"/>
-        <v>1999</v>
+        <f t="shared" si="95"/>
+        <v>2008</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" si="26"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_1999_References</v>
+        <f t="shared" ref="K54:K83" si="96">TRIM(_xlfn.TEXTJOIN("_",FALSE,F54,(SUBSTITUTE(SUBSTITUTE(D54," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L54" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
+        <f t="shared" ref="L54:L83" si="97">IF(ISBLANK(C54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J54, SUBSTITUTE(D54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C54, SUBSTITUTE(D54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M54" t="str">
         <f t="array" ref="M54">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="V54" s="1" t="s">
+      <c r="Q54" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="W54" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="D55" s="1" t="s">
-        <v>42</v>
+        <v>236</v>
       </c>
       <c r="E55" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>x</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>1999</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_1999_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_1999_References</v>
       </c>
       <c r="L55" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M55" t="str">
         <f t="array" ref="M55">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>236</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="15.95" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E56" t="str">
-        <f t="shared" si="84"/>
-        <v>9</v>
+        <f t="shared" si="91"/>
+        <v>x</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="85"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="92"/>
+        <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="88"/>
-        <v>2001</v>
+        <f t="shared" si="95"/>
+        <v>1999</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="26"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_2001_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_1999_Table1</v>
       </c>
       <c r="L56" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M56" t="str">
         <f t="array" ref="M56">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>238</v>
       </c>
       <c r="P56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A57" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="Q56" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R56" s="4"/>
-      <c r="T56" s="1" t="str">
-        <f>IF(S56="N", R56, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y56" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE56" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="E57" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>9</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2001</v>
       </c>
       <c r="J57" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_2001_Table2</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+        <f t="shared" si="97"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M57" t="str">
         <f t="array" ref="M57">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R57" s="4"/>
       <c r="T57" s="1" t="str">
@@ -5513,69 +5500,69 @@
         <v>write file name</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y57" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AE57" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" ht="15.95" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>9</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2001</v>
       </c>
       <c r="J58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K58" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_2001_Table3</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="L58" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+        <f t="shared" si="97"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M58" t="str">
         <f t="array" ref="M58">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R58" s="4"/>
       <c r="T58" s="1" t="str">
@@ -5583,69 +5570,69 @@
         <v>write file name</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AE58" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" ht="15.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>9</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2001</v>
       </c>
       <c r="J59" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" si="89"/>
-        <v>Iwaniuk_etal_2001_Table4</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="L59" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
+        <f t="shared" si="97"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M59" t="str">
         <f t="array" ref="M59">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R59" s="4"/>
       <c r="T59" s="1" t="str">
@@ -5653,1009 +5640,994 @@
         <v>write file name</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AE59" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Y59" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE59" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E60" t="str">
-        <f t="shared" si="84"/>
-        <v>8</v>
+        <f t="shared" si="91"/>
+        <v>9</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="85"/>
-        <v>JardimMesseder_etal_2017</v>
+        <f t="shared" si="92"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="86"/>
-        <v>JardimMesseder</v>
+        <f t="shared" si="93"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="88"/>
-        <v>2017</v>
+        <f t="shared" si="95"/>
+        <v>2001</v>
       </c>
       <c r="J60" t="str">
-        <f t="shared" si="19"/>
-        <v>10.3389/fnana.2017.00118</v>
+        <f t="shared" si="26"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K60" t="str">
-        <f t="shared" si="89"/>
-        <v>JardimMesseder_etal_2017_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="L60" t="str">
-        <f t="shared" si="90"/>
-        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M60" t="str">
         <f t="array" ref="M60">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L60, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>246</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R60" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="R60" s="4"/>
+      <c r="T60" s="1" t="str">
+        <f>IF(S60="N", R60, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y60" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AE60" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A61" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="S60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T60" s="1" t="s">
+      <c r="D61" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="91"/>
+        <v>8</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="92"/>
+        <v>JardimMesseder_etal_2017</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="93"/>
+        <v>JardimMesseder</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="94"/>
+        <v>etal</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="95"/>
+        <v>2017</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="26"/>
+        <v>10.3389/fnana.2017.00118</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="96"/>
+        <v>JardimMesseder_etal_2017_Table1</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="97"/>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+      </c>
+      <c r="M61" t="str">
+        <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+      </c>
+      <c r="N61" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="U60" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W60" s="1" t="s">
+      <c r="P61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="S61" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="X60" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="Y60" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z60" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA60" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB60" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE60" s="1" t="s">
+      <c r="T61" s="1" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="61" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+      <c r="U61" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X61" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E61" t="str">
-        <f t="shared" ref="E61" si="91">RIGHT(A61,1)</f>
+      <c r="Y61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE61" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" ref="E62" si="98">RIGHT(A62,1)</f>
         <v>4</v>
       </c>
-      <c r="F61" t="str">
-        <f t="shared" ref="F61" si="92">G61 &amp; IF(H61&lt;&gt;"", "_" &amp; H61, "_") &amp; IF(I61&lt;&gt;"", "_" &amp; I61, "_") &amp; IF(B61&lt;&gt;"", "_" &amp; B61, "")</f>
+      <c r="F62" t="str">
+        <f t="shared" ref="F62" si="99">G62 &amp; IF(H62&lt;&gt;"", "_" &amp; H62, "_") &amp; IF(I62&lt;&gt;"", "_" &amp; I62, "_") &amp; IF(B62&lt;&gt;"", "_" &amp; B62, "")</f>
         <v>Johansen_etal_2024</v>
       </c>
-      <c r="G61" t="str">
-        <f t="shared" ref="G61" si="93">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A61,","), "-", ""), " ", "")</f>
+      <c r="G62" t="str">
+        <f t="shared" ref="G62" si="100">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A62,","), "-", ""), " ", "")</f>
         <v>Johansen</v>
       </c>
-      <c r="H61" t="str">
-        <f t="shared" ref="H61" si="94">IF(ISNUMBER(FIND("&amp;", A61)),
-    IF(LEN(A61)-LEN(SUBSTITUTE(A61, ",", ""))&gt;=6, "etal", MID(A61, SEARCH("&amp; ", A61)+2, SEARCH(",", A61, SEARCH("&amp; ", A61)+2) - SEARCH("&amp; ", A61)-2)),
+      <c r="H62" t="str">
+        <f t="shared" ref="H62" si="101">IF(ISNUMBER(FIND("&amp;", A62)),
+    IF(LEN(A62)-LEN(SUBSTITUTE(A62, ",", ""))&gt;=6, "etal", MID(A62, SEARCH("&amp; ", A62)+2, SEARCH(",", A62, SEARCH("&amp; ", A62)+2) - SEARCH("&amp; ", A62)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I61" t="str">
-        <f t="shared" ref="I61" si="95">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A61, "("), ")")</f>
+      <c r="I62" t="str">
+        <f t="shared" ref="I62" si="102">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A62, "("), ")")</f>
         <v>2024</v>
       </c>
-      <c r="J61" t="str">
-        <f t="shared" ref="J61" si="96">IF(C61&lt;&gt;"", C61, IF(C61="", _xlfn.TEXTAFTER(A61,"https://doi.org/"), C61))</f>
+      <c r="J62" t="str">
+        <f t="shared" ref="J62" si="103">IF(C62&lt;&gt;"", C62, IF(C62="", _xlfn.TEXTAFTER(A62,"https://doi.org/"), C62))</f>
         <v>10.1523/JNEUROSCI.1750-23.2024</v>
       </c>
-      <c r="K61" t="str">
-        <f t="shared" ref="K61" si="97">TRIM(_xlfn.TEXTJOIN("_",FALSE,F61,(SUBSTITUTE(SUBSTITUTE(D61," ",""), "_", ""))))</f>
+      <c r="K62" t="str">
+        <f t="shared" ref="K62" si="104">TRIM(_xlfn.TEXTJOIN("_",FALSE,F62,(SUBSTITUTE(SUBSTITUTE(D62," ",""), "_", ""))))</f>
         <v>Johansen_etal_2024_Table2</v>
       </c>
-      <c r="L61" t="str">
-        <f t="shared" ref="L61" si="98">IF(ISBLANK(C61),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L62" t="str">
+        <f t="shared" ref="L62" si="105">IF(ISBLANK(C62),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J62, SUBSTITUTE(D62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C62, SUBSTITUTE(D62,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1523%2FJNEUROSCI.1750-23.2024_Table2</v>
-      </c>
-      <c r="M61" t="str">
-        <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z61" s="1"/>
-      <c r="AA61" s="10"/>
-      <c r="AB61" s="10"/>
-      <c r="AE61" s="10"/>
-    </row>
-    <row r="62" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E62" t="str">
-        <f t="shared" si="84"/>
-        <v>9</v>
-      </c>
-      <c r="F62" t="str">
-        <f t="shared" si="85"/>
-        <v>Karl_etal_2024</v>
-      </c>
-      <c r="G62" t="str">
-        <f t="shared" si="86"/>
-        <v>Karl</v>
-      </c>
-      <c r="H62" t="str">
-        <f t="shared" si="87"/>
-        <v>etal</v>
-      </c>
-      <c r="I62" t="str">
-        <f t="shared" si="88"/>
-        <v>2024</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1002/cne.25669</v>
-      </c>
-      <c r="K62" t="str">
-        <f t="shared" si="89"/>
-        <v>Karl_etal_2024_TABLE1</v>
-      </c>
-      <c r="L62" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1002%2Fcne.25669_TABLE1</v>
       </c>
       <c r="M62" t="str">
         <f t="array" ref="M62">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L62, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N62" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="R62" s="4"/>
-      <c r="U62" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V62" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W62" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y62" s="1" t="s">
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="10"/>
+      <c r="AE62" s="10"/>
+    </row>
+    <row r="63" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A63" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="Z62" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="84"/>
-        <v>8</v>
+        <f t="shared" si="91"/>
+        <v>9</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="85"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="92"/>
+        <v>Karl_etal_2024</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="86"/>
-        <v>Kverkova</v>
+        <f t="shared" si="93"/>
+        <v>Karl</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="88"/>
-        <v>2018</v>
+        <f t="shared" si="95"/>
+        <v>2024</v>
       </c>
       <c r="J63" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="26"/>
+        <v>10.1002/cne.25669</v>
       </c>
       <c r="K63" t="str">
-        <f t="shared" si="89"/>
-        <v>Kverkova_etal_2018_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Karl_etal_2024_TABLE1</v>
       </c>
       <c r="L63" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1002%2Fcne.25669_TABLE1</v>
       </c>
       <c r="M63" t="str">
         <f t="array" ref="M63">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L63, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
       </c>
       <c r="N63" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="R63" s="4"/>
+      <c r="U63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y63" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="P63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R63" s="4" t="s">
+      <c r="Z63" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A64" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="S63" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T63" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="U63" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="V63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y63" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="Z63" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE63" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="E64" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>8</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Kverkova</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2018</v>
       </c>
       <c r="J64" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K64" t="str">
-        <f t="shared" si="89"/>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f t="shared" si="96"/>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L64" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <f t="shared" si="97"/>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M64" t="str">
         <f t="array" ref="M64">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L64, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N64" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R64" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y64" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="P64" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R64" s="4" t="s">
+      <c r="Z64" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE64" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="S64" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="V64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W64" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X64" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y64" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z64" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB64" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE64" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:31" ht="15.95" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>268</v>
+        <v>132</v>
       </c>
       <c r="E65" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>8</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Kverkova</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2018</v>
       </c>
       <c r="J65" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K65" t="str">
-        <f t="shared" si="89"/>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <f t="shared" si="96"/>
+        <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="L65" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <f t="shared" si="97"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M65" t="str">
         <f t="array" ref="M65">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L65, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N65" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z65" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R65" s="4" t="s">
+      <c r="AB65" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE65" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A66" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="S65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W65" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X65" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y65" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z65" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB65" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE65" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E66" t="str">
-        <f t="shared" si="84"/>
-        <v>4</v>
+        <f t="shared" si="91"/>
+        <v>8</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="85"/>
-        <v>Lewitus_etal_2013</v>
+        <f t="shared" si="92"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" si="86"/>
-        <v>Lewitus</v>
+        <f t="shared" si="93"/>
+        <v>Kverkova</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="88"/>
-        <v>2013</v>
+        <f t="shared" si="95"/>
+        <v>2018</v>
       </c>
       <c r="J66" t="str">
-        <f t="shared" si="19"/>
-        <v>10.3389/fnhum.2013.00424</v>
+        <f t="shared" si="26"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K66" t="str">
-        <f t="shared" si="89"/>
-        <v>Lewitus_etal_2013_TableS2partial</v>
+        <f t="shared" si="96"/>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L66" t="str">
-        <f t="shared" si="90"/>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+        <f t="shared" si="97"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M66" t="str">
         <f t="array" ref="M66">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L66, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R66" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y66" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z66" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB66" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE66" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A67" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="67" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E67" t="str">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <f t="shared" si="91"/>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="85"/>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="92"/>
+        <v>Lewitus_etal_2013</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Lewitus</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="88"/>
-        <v>2014</v>
+        <f t="shared" si="95"/>
+        <v>2013</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="26"/>
+        <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" si="89"/>
-        <v>Lewitus_etal_2014_TableS1</v>
+        <f t="shared" si="96"/>
+        <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="L67" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <f t="shared" si="97"/>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M67" t="str">
         <f t="array" ref="M67">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L67, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="N67" s="1" t="s">
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA67" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="Q67" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA67" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:31" ht="15.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>278</v>
+        <v>132</v>
       </c>
       <c r="E68" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Lewitus</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2014</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="89"/>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <f t="shared" si="96"/>
+        <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="L68" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <f t="shared" si="97"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M68" t="str">
         <f t="array" ref="M68">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L68, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>279</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AA68" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" ht="15.95" customHeight="1">
       <c r="A69" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E69" t="str">
-        <f t="shared" si="84"/>
-        <v>5</v>
+        <f t="shared" si="91"/>
+        <v>0</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="85"/>
-        <v>MacLarnon__1996</v>
+        <f t="shared" si="92"/>
+        <v>Lewitus_etal_2014</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="86"/>
-        <v>MacLarnon</v>
+        <f t="shared" si="93"/>
+        <v>Lewitus</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="87"/>
-        <v/>
+        <f t="shared" si="94"/>
+        <v>etal</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="88"/>
-        <v>1996</v>
+        <f t="shared" si="95"/>
+        <v>2014</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="19"/>
-        <v>10.1006/jhev.1996.0005</v>
+        <f t="shared" si="26"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="89"/>
-        <v>MacLarnon__1996_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L69" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M69" t="str">
         <f t="array" ref="M69">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L69, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA69" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" si="84"/>
-        <v>2</v>
+        <f t="shared" si="91"/>
+        <v>5</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="85"/>
-        <v>ManyPrimates__2022</v>
+        <f t="shared" si="92"/>
+        <v>MacLarnon__1996</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="86"/>
-        <v>ManyPrimates</v>
+        <f t="shared" si="93"/>
+        <v>MacLarnon</v>
       </c>
       <c r="H70" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="88"/>
-        <v>2022</v>
+        <f t="shared" si="95"/>
+        <v>1996</v>
       </c>
       <c r="J70" t="str">
-        <f t="shared" si="19"/>
-        <v>10.26451/abc.09.04.06.2022</v>
+        <f t="shared" si="26"/>
+        <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="89"/>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+        <f t="shared" si="96"/>
+        <v>MacLarnon__1996_Table1</v>
       </c>
       <c r="L70" t="str">
-        <f t="shared" si="90"/>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <f t="shared" si="97"/>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M70" t="str">
         <f t="array" ref="M70">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L70, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="P70" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A71" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="Q70" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R70" s="4"/>
-      <c r="T70" s="1" t="str">
-        <f>IF(S70="N", R70, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V70" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W70" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X70" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="Y70" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="Z70" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC70" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="AE70" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E71" t="str">
-        <f t="shared" si="84"/>
-        <v>1</v>
+        <f t="shared" si="91"/>
+        <v>2</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="85"/>
-        <v>Mota_etal_2015</v>
+        <f t="shared" si="92"/>
+        <v>ManyPrimates__2022</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="86"/>
-        <v>Mota</v>
+        <f t="shared" si="93"/>
+        <v>ManyPrimates</v>
       </c>
       <c r="H71" t="str">
-        <f t="shared" si="87"/>
-        <v>etal</v>
+        <f t="shared" si="94"/>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="88"/>
-        <v>2015</v>
+        <f t="shared" si="95"/>
+        <v>2022</v>
       </c>
       <c r="J71" t="str">
-        <f t="shared" ref="J71:J82" si="99">IF(C71&lt;&gt;"", C71, IF(C71="", _xlfn.TEXTAFTER(A71,"https://doi.org/"), C71))</f>
-        <v>10.1126/science.aaa9101</v>
+        <f t="shared" si="26"/>
+        <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" si="89"/>
-        <v>Mota_etal_2015_TableS1</v>
+        <f t="shared" si="96"/>
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="L71" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <f t="shared" si="97"/>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M71" t="str">
         <f t="array" ref="M71">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L71, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="R71" s="4"/>
+      <c r="T71" s="1" t="str">
+        <f>IF(S71="N", R71, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X71" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Y71" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Z71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC71" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="AE71" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" si="84"/>
-        <v>6</v>
+        <f t="shared" si="91"/>
+        <v>1</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="85"/>
-        <v>Mota_etal_2019</v>
+        <f t="shared" si="92"/>
+        <v>Mota_etal_2015</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Mota</v>
       </c>
       <c r="H72" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="88"/>
-        <v>2019</v>
+        <f t="shared" si="95"/>
+        <v>2015</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1073/pnas.1716956116</v>
+        <f t="shared" ref="J72:J83" si="106">IF(C72&lt;&gt;"", C72, IF(C72="", _xlfn.TEXTAFTER(A72,"https://doi.org/"), C72))</f>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="89"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
+        <f t="shared" si="96"/>
+        <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="L72" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <f t="shared" si="97"/>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M72" t="str">
         <f t="array" ref="M72">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L72, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N72" s="1" t="s">
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A73" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="P72" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC72" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E73" t="str">
-        <f t="shared" si="84"/>
-        <v>5</v>
+        <f t="shared" si="91"/>
+        <v>6</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="85"/>
-        <v>Powell_etal_2017</v>
+        <f t="shared" si="92"/>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="86"/>
-        <v>Powell</v>
+        <f t="shared" si="93"/>
+        <v>Mota</v>
       </c>
       <c r="H73" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="88"/>
-        <v>2017</v>
+        <f t="shared" si="95"/>
+        <v>2019</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="99"/>
-        <v>10.6084/m9.figshare.c.3899422.v1</v>
+        <f t="shared" si="106"/>
+        <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="89"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <f t="shared" si="96"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L73" t="str">
-        <f t="shared" si="90"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <f t="shared" si="97"/>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M73" t="str">
         <f t="array" ref="M73">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L73, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R73" s="4"/>
-      <c r="T73" s="1" t="str">
-        <f>IF(S73="N", R73, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC73" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A74" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="Y73" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="Z73" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC73" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE73" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="E74" t="str">
-        <f t="shared" si="84"/>
-        <v>2</v>
+        <f t="shared" si="91"/>
+        <v>5</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="85"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="92"/>
+        <v>Powell_etal_2017</v>
       </c>
       <c r="G74" t="str">
-        <f t="shared" si="86"/>
-        <v>Sherwood</v>
+        <f t="shared" si="93"/>
+        <v>Powell</v>
       </c>
       <c r="H74" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="88"/>
-        <v>2004</v>
+        <f t="shared" si="95"/>
+        <v>2017</v>
       </c>
       <c r="J74" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="106"/>
+        <v>10.6084/m9.figshare.c.3899422.v1</v>
       </c>
       <c r="K74" t="str">
-        <f t="shared" si="89"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <f t="shared" si="96"/>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="L74" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <f t="shared" si="97"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M74" t="str">
         <f t="array" ref="M74">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L74, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>300</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R74" s="4"/>
       <c r="T74" s="1" t="str">
@@ -6663,75 +6635,84 @@
         <v>write file name</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="V74" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="X74" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE74" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="Y74" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z74" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE74" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>2</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Sherwood</v>
       </c>
       <c r="H75" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2004</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="89"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f t="shared" si="96"/>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="L75" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <f t="shared" si="97"/>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M75" t="str">
         <f t="array" ref="M75">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L75, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R75" s="4"/>
       <c r="T75" s="1" t="str">
@@ -6739,210 +6720,242 @@
         <v>write file name</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V75" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y75" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z75" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="Y75" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z75" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE75" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="76" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>305</v>
+        <v>217</v>
       </c>
       <c r="E76" t="str">
-        <f t="shared" si="84"/>
-        <v>1</v>
+        <f t="shared" si="91"/>
+        <v>2</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="85"/>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="92"/>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G76" t="str">
-        <f t="shared" si="86"/>
-        <v>Smaers</v>
+        <f t="shared" si="93"/>
+        <v>Sherwood</v>
       </c>
       <c r="H76" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="88"/>
-        <v>2011</v>
+        <f t="shared" si="95"/>
+        <v>2004</v>
       </c>
       <c r="J76" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="106"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="89"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
+        <f t="shared" si="96"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="L76" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <f t="shared" si="97"/>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M76" t="str">
         <f t="array" ref="M76">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L76, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="R76" s="4"/>
+      <c r="T76" s="1" t="str">
+        <f>IF(S76="N", R76, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y76" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z76" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE76" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E77" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>1</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>Smaers</v>
       </c>
       <c r="H77" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2011</v>
       </c>
       <c r="J77" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="89"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" si="96"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L77" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <f t="shared" si="97"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M77" t="str">
         <f t="array" ref="M77">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L77, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>42</v>
+        <v>308</v>
       </c>
       <c r="E78" t="str">
-        <f t="shared" si="84"/>
-        <v>2</v>
+        <f t="shared" si="91"/>
+        <v>1</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="85"/>
-        <v>Turner_etal_2016</v>
+        <f t="shared" si="92"/>
+        <v>Smaers_etal_2011</v>
       </c>
       <c r="G78" t="str">
-        <f t="shared" si="86"/>
-        <v>Turner</v>
+        <f t="shared" si="93"/>
+        <v>Smaers</v>
       </c>
       <c r="H78" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="88"/>
-        <v>2016</v>
+        <f t="shared" si="95"/>
+        <v>2011</v>
       </c>
       <c r="J78" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1159/000446762</v>
+        <f t="shared" si="106"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="89"/>
-        <v>Turner_etal_2016_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L78" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M78" t="str">
         <f t="array" ref="M78">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L78, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="Y78" s="1" t="s">
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A79" s="1" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="79" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="D79" s="1" t="s">
-        <v>311</v>
+        <v>45</v>
       </c>
       <c r="E79" t="str">
-        <f t="shared" si="84"/>
-        <v>1</v>
+        <f t="shared" si="91"/>
+        <v>2</v>
       </c>
       <c r="F79" t="str">
-        <f t="shared" si="85"/>
-        <v>Wilman_etal_2014</v>
+        <f t="shared" si="92"/>
+        <v>Turner_etal_2016</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" si="86"/>
-        <v>Wilman</v>
+        <f t="shared" si="93"/>
+        <v>Turner</v>
       </c>
       <c r="H79" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="88"/>
-        <v>2014</v>
+        <f t="shared" si="95"/>
+        <v>2016</v>
       </c>
       <c r="J79" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1890/13-1917.1</v>
+        <f t="shared" si="106"/>
+        <v>10.1159/000446762</v>
       </c>
       <c r="K79" t="str">
-        <f t="shared" si="89"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+        <f t="shared" si="96"/>
+        <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L79" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <f t="shared" si="97"/>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M79" t="str">
         <f t="array" ref="M79">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L79, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-    </row>
-    <row r="80" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N79" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="Y79" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>312</v>
       </c>
@@ -6950,46 +6963,43 @@
         <v>313</v>
       </c>
       <c r="E80" t="str">
-        <f t="shared" si="84"/>
-        <v>7</v>
+        <f t="shared" si="91"/>
+        <v>1</v>
       </c>
       <c r="F80" t="str">
-        <f t="shared" si="85"/>
-        <v>Wimberly_etal_2021</v>
+        <f t="shared" si="92"/>
+        <v>Wilman_etal_2014</v>
       </c>
       <c r="G80" t="str">
-        <f t="shared" si="86"/>
-        <v>Wimberly</v>
+        <f t="shared" si="93"/>
+        <v>Wilman</v>
       </c>
       <c r="H80" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>etal</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="88"/>
-        <v>2021</v>
+        <f t="shared" si="95"/>
+        <v>2014</v>
       </c>
       <c r="J80" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1098/rspb.2021.0937</v>
+        <f t="shared" si="106"/>
+        <v>10.1890/13-1917.1</v>
       </c>
       <c r="K80" t="str">
-        <f t="shared" si="89"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
+        <f t="shared" si="96"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L80" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <f t="shared" si="97"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M80" t="str">
         <f t="array" ref="M80">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L80, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P80" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:31" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>314</v>
       </c>
@@ -6997,113 +7007,93 @@
         <v>315</v>
       </c>
       <c r="E81" t="str">
-        <f t="shared" si="84"/>
-        <v>5</v>
+        <f t="shared" si="91"/>
+        <v>7</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" si="85"/>
-        <v>Winkler_Bryant_2021</v>
+        <f t="shared" si="92"/>
+        <v>Wimberly_etal_2021</v>
       </c>
       <c r="G81" t="str">
-        <f t="shared" si="86"/>
-        <v>Winkler</v>
+        <f t="shared" si="93"/>
+        <v>Wimberly</v>
       </c>
       <c r="H81" t="str">
-        <f t="shared" si="87"/>
-        <v>Bryant</v>
+        <f t="shared" si="94"/>
+        <v>etal</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>2021</v>
       </c>
       <c r="J81" t="str">
-        <f t="shared" si="99"/>
-        <v>10.1080/09524622.2021.1905065</v>
+        <f t="shared" si="106"/>
+        <v>10.1098/rspb.2021.0937</v>
       </c>
       <c r="K81" t="str">
-        <f t="shared" si="89"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <f t="shared" si="96"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L81" t="str">
-        <f t="shared" si="90"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <f t="shared" si="97"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M81" t="str">
         <f t="array" ref="M81">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L81, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R81" s="4"/>
-      <c r="T81" s="1" t="str">
-        <f>IF(S81="N", R81, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U81" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V81" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31">
+      <c r="A82" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="Y81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="AE81" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E82" t="str">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <f t="shared" si="91"/>
+        <v>5</v>
       </c>
       <c r="F82" t="str">
-        <f t="shared" si="85"/>
-        <v>Young_etal_2013</v>
+        <f t="shared" si="92"/>
+        <v>Winkler_Bryant_2021</v>
       </c>
       <c r="G82" t="str">
-        <f t="shared" si="86"/>
-        <v>Young</v>
+        <f t="shared" si="93"/>
+        <v>Winkler</v>
       </c>
       <c r="H82" t="str">
-        <f t="shared" si="87"/>
-        <v>etal</v>
+        <f t="shared" si="94"/>
+        <v>Bryant</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="88"/>
-        <v>2013</v>
+        <f t="shared" si="95"/>
+        <v>2021</v>
       </c>
       <c r="J82" t="str">
-        <f t="shared" si="99"/>
-        <v>10.3389/fncir.2013.00030</v>
+        <f t="shared" si="106"/>
+        <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="K82" t="str">
-        <f t="shared" si="89"/>
-        <v>Young_etal_2013_Table1</v>
+        <f t="shared" si="96"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="L82" t="str">
-        <f t="shared" si="90"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <f t="shared" si="97"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="M82" t="str">
         <f t="array" ref="M82">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L82, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="R82" s="4"/>
       <c r="T82" s="1" t="str">
@@ -7111,37 +7101,104 @@
         <v>write file name</v>
       </c>
       <c r="U82" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V82" s="1" t="s">
-        <v>35</v>
+        <v>318</v>
       </c>
       <c r="Y82" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="Z82" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="AE82" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31">
+      <c r="A83" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="92"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="93"/>
+        <v>Young</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="94"/>
+        <v>etal</v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="95"/>
+        <v>2013</v>
+      </c>
+      <c r="J83" t="str">
+        <f t="shared" si="106"/>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="K83" t="str">
+        <f t="shared" si="96"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L83" t="str">
+        <f t="shared" si="97"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="array" ref="M83">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L83, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R83" s="4"/>
+      <c r="T83" s="1" t="str">
+        <f>IF(S83="N", R83, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y83" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Z83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE83" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="X11" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="X10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="X13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X19" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="X25" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X70" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X73" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X41" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X30:X35" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X65" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X64" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X60" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="X28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="X12" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="X11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="X14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="X20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="X26" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="X71" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X74" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="X42" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="X31:X36" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X66" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="X65" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X61" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="X28" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="X29" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7151,104 +7208,104 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B12" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -7260,64 +7317,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="C2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -7329,311 +7386,311 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -7898,6 +7955,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
@@ -7908,55 +7974,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_473A6008124C090B9CB4C1A72041B5B084627455" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87875D7B-3FD8-434A-94A8-4184B43373F5}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_473A6008124C090B9CB4C1A72041B5B084627455" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB67C07-269C-4DF2-A6A0-428FFB93A9C3}"/>
   <bookViews>
     <workbookView xWindow="36100" yWindow="3200" windowWidth="38960" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,11 @@
     <sheet name="Conflicts" sheetId="3" r:id="rId3"/>
     <sheet name="FileList" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -233,6 +236,15 @@
     <t>Barbeito-Andres, J., Castro-Fonseca, E., Qiu, L. R., Bernal, V., Lent, R., Henkelman, M., Lukowiak, K., Gleiser, P. M., Hallgrimsson, B., &amp; Gonzalez, P. N. (2019). Region-specific changes in Mus musculus brain size and cell composition under chronic nutrient restriction. J Exp Biol, 222(Pt 17). https://doi.org/10.1242/jeb.204651</t>
   </si>
   <si>
+    <t>volumes</t>
+  </si>
+  <si>
+    <t>cell number</t>
+  </si>
+  <si>
+    <t>cell density</t>
+  </si>
+  <si>
     <t>Barger, N., Stefanacci, L., &amp; Semendeferi, K. (2007). A comparative volumetric analysis of the amygdaloid complex and basolateral division in the human and ape brain. Am J Phys Anthropol, 134(3), 392-403. https://doi.org/10.1002/ajpa.20684</t>
   </si>
   <si>
@@ -1731,6 +1743,9 @@
     <t>TABLE 6 Volume of the various components of the telencephalon in Simians (in mm3)</t>
   </si>
   <si>
+    <t>Tables 1-6</t>
+  </si>
+  <si>
     <t>Stephan, H., Baron, G., &amp; Frahm, H. D. (1982). Comparison of brain structure volumes in Insectivora and Primates. II. Accessory olfactory bulb (AOB). J Hirnforsch, 23(5), 575-591. https://www.ncbi.nlm.nih.gov/pubmed/7161483</t>
   </si>
   <si>
@@ -1986,15 +2001,6 @@
     <t xml:space="preserve">Ref last </t>
   </si>
   <si>
-    <t>cell density</t>
-  </si>
-  <si>
-    <t>volumes</t>
-  </si>
-  <si>
-    <t>cell number</t>
-  </si>
-  <si>
     <t>10.1002%2Fajpa.20684_TABLE1.tsv</t>
   </si>
   <si>
@@ -2248,16 +2254,13 @@
   </si>
   <si>
     <t>Semendeferi_etal_2001_Table2.tsv</t>
-  </si>
-  <si>
-    <t>Tables 1-6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2373,9 +2376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2413,7 +2416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2519,7 +2522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2661,7 +2664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2670,24 +2673,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="38.5" customWidth="1"/>
-    <col min="2" max="2" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="1.625" customWidth="1"/>
     <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" customWidth="1"/>
+    <col min="4" max="4" width="7.125" customWidth="1"/>
     <col min="5" max="5" width="1.5" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
-    <col min="7" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
+    <col min="7" max="8" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
     <col min="10" max="10" width="14.5" customWidth="1"/>
-    <col min="11" max="11" width="31.83203125" customWidth="1"/>
+    <col min="11" max="11" width="31.875" customWidth="1"/>
     <col min="12" max="12" width="49" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="39" width="7.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="39" width="7.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" ht="15.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" ht="15.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" ht="15.95" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -2915,7 +2918,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" ht="15.95" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -3013,12 +3016,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" ht="15.95" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>650</v>
+        <v>65</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E6" si="17">RIGHT(A5,1)</f>
@@ -3069,12 +3072,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" ht="15.95" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>651</v>
+        <v>66</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="17"/>
@@ -3125,12 +3128,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" ht="15.95" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>649</v>
+        <v>67</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -3181,9 +3184,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" ht="15.95" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>47</v>
@@ -3225,33 +3228,33 @@
         <v>10.1002%2Fajpa.20684_TABLE1.tsv</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL8" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" ht="15.95" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" ref="E9:E10" si="25">RIGHT(A9,1)</f>
@@ -3290,24 +3293,24 @@
         <v>notfound</v>
       </c>
       <c r="Y9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK9" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK9" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="AL9" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" ht="15.95" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>47</v>
@@ -3349,18 +3352,18 @@
         <v>notfound</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" ht="15.95" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -3399,42 +3402,42 @@
         <v>PMID%3A3216099_Table1.tsv</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL11" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -3476,42 +3479,42 @@
         <v>41</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL12" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -3553,42 +3556,42 @@
         <v>41</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL13" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" ht="15.95" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -3627,48 +3630,48 @@
         <v>PMID%3A2358663_Table1.tsv</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL14" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" ht="15.95" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -3707,42 +3710,42 @@
         <v>10.1016%2Fj.jhevol.2012.12.003_Table1.tsv</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK15" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.95" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -3784,36 +3787,36 @@
         <v>41</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL16" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" ht="15.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" ref="E17" si="33">RIGHT(A17,1)</f>
@@ -3855,39 +3858,39 @@
         <v>41</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" ht="15.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -3926,24 +3929,24 @@
         <v>notfound</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AL18" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM18" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" ht="15.95" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -3982,61 +3985,61 @@
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="T19" s="2" t="str">
         <f>IF(S19="N", R19, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AK19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL19" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM19" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" ht="15.95" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -4075,16 +4078,16 @@
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AA20" s="2" t="s">
         <v>59</v>
@@ -4096,13 +4099,13 @@
         <v>59</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AL20" s="2" t="s">
         <v>42</v>
@@ -4111,12 +4114,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:39" ht="15.95" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -4155,7 +4158,7 @@
         <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>49</v>
@@ -4164,10 +4167,10 @@
         <v>50</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>54</v>
@@ -4176,10 +4179,10 @@
         <v>41</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AA21" s="2" t="s">
         <v>59</v>
@@ -4191,16 +4194,16 @@
         <v>59</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AL21" s="2" t="s">
         <v>42</v>
@@ -4209,12 +4212,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:39" ht="15.95" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -4253,21 +4256,21 @@
         <v>10.1159%2F000068880_Table1.tsv</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" ht="15.95" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -4306,19 +4309,19 @@
         <v>10.1073%2Fpnas.0305760101_Table2.tsv</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>54</v>
@@ -4327,33 +4330,33 @@
         <v>41</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD23" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" ht="15.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>47</v>
@@ -4395,19 +4398,19 @@
         <v>10.1002%2Far.a.20114_Table1.tsv</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="S24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>54</v>
@@ -4416,33 +4419,33 @@
         <v>41</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AD24" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" ht="15.95" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -4481,7 +4484,7 @@
         <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>49</v>
@@ -4490,52 +4493,52 @@
         <v>50</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="T25" s="2" t="str">
         <f>IF(S25="N", R25, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL25" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM25" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" ht="15.95" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -4574,7 +4577,7 @@
         <v>10.7554%2FeLife.77875_Table1.tsv</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>49</v>
@@ -4583,13 +4586,13 @@
         <v>50</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S26" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>54</v>
@@ -4598,39 +4601,39 @@
         <v>41</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL26" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM26" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" ht="15.95" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -4669,54 +4672,54 @@
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="S27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>54</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AK27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL27" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM27" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" ht="15.95" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -4761,58 +4764,58 @@
         <v>50</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="T28" s="2" t="str">
         <f>IF(S28="N", R28, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AL28" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM28" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" ht="15.95" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -4851,30 +4854,30 @@
         <v>notfound</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL29" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM29" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" ht="15.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E30" t="str">
         <f t="shared" si="0"/>
@@ -4913,19 +4916,19 @@
         <v>notfound</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>60</v>
@@ -4934,21 +4937,21 @@
         <v>59</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM30" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" ht="15.95" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="E31" t="str">
         <f t="shared" si="0"/>
@@ -4987,19 +4990,19 @@
         <v>10.1159%2F000346495_Table1.tsv</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>54</v>
@@ -5008,42 +5011,42 @@
         <v>41</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AG31" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AL31" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM31" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" ht="15.95" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
@@ -5082,75 +5085,75 @@
         <v>notfound</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AL32" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM32" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" ht="15.95" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
@@ -5189,45 +5192,45 @@
         <v>10.1016%2Fj.jhevol.2009.11.011_Table1.tsv</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AK33" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AL33" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM33" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" ht="15.95" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E34" t="str">
         <f t="shared" si="0"/>
@@ -5266,51 +5269,51 @@
         <v>notfound</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V34" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL34" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM34" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" ht="15.95" customHeight="1">
+      <c r="A35" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="X34" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y34" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="AG34" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL34" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM34" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
@@ -5349,48 +5352,48 @@
         <v>notfound</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V35" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM35" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" ht="15" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="W35" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y35" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z35" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB35" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG35" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL35" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM35" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="36" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
@@ -5429,48 +5432,48 @@
         <v>notfound</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V36" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM36" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" ht="15.95" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="W36" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="X36" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y36" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB36" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG36" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM36" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
@@ -5509,48 +5512,48 @@
         <v>notfound</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK37" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL37" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM37" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" ht="15.95" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E38" t="str">
         <f t="shared" si="0"/>
@@ -5589,7 +5592,7 @@
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>49</v>
@@ -5598,25 +5601,25 @@
         <v>50</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>59</v>
@@ -5628,30 +5631,30 @@
         <v>59</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AK38" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL38" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM38" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="39" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" ht="15.95" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E39" t="str">
         <f t="shared" si="0"/>
@@ -5690,7 +5693,7 @@
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished.tsv</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>49</v>
@@ -5699,28 +5702,28 @@
         <v>50</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AA39" s="2" t="s">
         <v>59</v>
@@ -5732,27 +5735,27 @@
         <v>59</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AK39" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL39" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM39" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="40" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" ht="15.95" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" ref="E40:E71" si="44">RIGHT(A40,1)</f>
@@ -5791,7 +5794,7 @@
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>49</v>
@@ -5800,28 +5803,28 @@
         <v>50</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="S40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>58</v>
@@ -5836,13 +5839,13 @@
         <v>59</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AK40" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AL40" s="2" t="s">
         <v>58</v>
@@ -5851,9 +5854,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" ht="15.95" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>47</v>
@@ -5895,30 +5898,30 @@
         <v>10.3389%2Ffnins.2021.632853_TABLE1.tsv</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>54</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AK41" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL41" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL41" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM41" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="42" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" ht="15.95" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>47</v>
@@ -5960,33 +5963,33 @@
         <v>10.1002%2Fcne.24605_TABLE1.tsv</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>54</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AK42" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AL42" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM42" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="43" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:39" ht="15.95" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E43" t="str">
         <f t="shared" si="44"/>
@@ -6025,33 +6028,33 @@
         <v>10.1002%2Fcne.24605_TABLE2.tsv</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>54</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AL43" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM43" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="44" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:39" ht="15.95" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E44" t="str">
         <f t="shared" si="44"/>
@@ -6090,19 +6093,19 @@
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>54</v>
@@ -6111,42 +6114,42 @@
         <v>41</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AK44" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL44" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL44" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM44" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="45" spans="1:39" ht="15.95" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E45" t="str">
         <f t="shared" si="44"/>
@@ -6185,15 +6188,15 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="46" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:39" ht="15.95" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E46" t="str">
         <f t="shared" si="44"/>
@@ -6232,48 +6235,48 @@
         <v>PMID%3A7983368_Table1.tsv</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA46" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC46" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK46" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL46" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM46" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:39" ht="15.95" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E47" t="str">
         <f t="shared" si="44"/>
@@ -6312,48 +6315,48 @@
         <v>PMID%3A9176733_Table1.tsv</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA47" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK47" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL47" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM47" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:39" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" ht="18.95" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E48" t="str">
         <f t="shared" si="44"/>
@@ -6392,48 +6395,48 @@
         <v>PMID%3A6501869_Table1.tsv</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA48" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC48" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK48" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL48" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM48" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E49" t="str">
         <f t="shared" si="44"/>
@@ -6472,48 +6475,48 @@
         <v>PMID%3A7161477_Table2.tsv</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="V49" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA49" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK49" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL49" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM49" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E50" t="str">
         <f t="shared" si="44"/>
@@ -6552,45 +6555,45 @@
         <v>PMID%3A9672110_Table1.tsv</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA50" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC50" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK50" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL50" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM50" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E51" t="str">
         <f t="shared" si="44"/>
@@ -6629,16 +6632,16 @@
         <v>notfound</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AE51" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AK51" s="2" t="s">
         <v>42</v>
@@ -6650,12 +6653,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:39" ht="17.100000000000001" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E52" t="str">
         <f t="shared" si="44"/>
@@ -6694,33 +6697,33 @@
         <v>10.1073%2Fpnas.0905777106_TableS1.tsv</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>54</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AK52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL52" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM52" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:39" ht="17.100000000000001" customHeight="1">
+      <c r="A53" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="53" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E53" t="str">
         <f t="shared" si="44"/>
@@ -6759,33 +6762,33 @@
         <v>notfound</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="U53" s="2" t="s">
         <v>54</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AK53" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL53" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM53" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="54" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="54" spans="1:39" ht="15.95" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="44"/>
@@ -6824,13 +6827,13 @@
         <v>notfound</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AE54" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AK54" s="2" t="s">
         <v>42</v>
@@ -6842,12 +6845,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:39" ht="15.95" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="44"/>
@@ -6886,27 +6889,27 @@
         <v>notfound</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AK55" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL55" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM55" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="56" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:39" ht="15.95" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="44"/>
@@ -6945,7 +6948,7 @@
         <v>notfound</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AK56" s="2" t="s">
         <v>42</v>
@@ -6957,12 +6960,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:39" ht="15.95" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="44"/>
@@ -7001,10 +7004,10 @@
         <v>notfound</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T57" s="2" t="str">
         <f>IF(S57="N", R57, "write file name")</f>
@@ -7017,36 +7020,36 @@
         <v>41</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AG57" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AK57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL57" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM57" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="58" spans="1:39" ht="15.95" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>334</v>
-      </c>
-    </row>
-    <row r="58" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="E58" t="str">
         <f t="shared" si="44"/>
@@ -7091,13 +7094,13 @@
         <v>50</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>54</v>
@@ -7106,39 +7109,39 @@
         <v>41</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AG58" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AK58" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL58" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM58" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="59" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:39" ht="15.95" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>47</v>
@@ -7180,30 +7183,30 @@
         <v>PMID%3A15534048_TABLE1.tsv</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AK59" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AL59" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM59" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="60" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:39" ht="15.95" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E60" t="str">
         <f t="shared" si="44"/>
@@ -7242,10 +7245,10 @@
         <v>notfound</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T60" s="2" t="str">
         <f>IF(S60="N", R60, "write file name")</f>
@@ -7258,30 +7261,30 @@
         <v>41</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG60" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK60" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL60" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM60" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="61" spans="1:39" ht="15.95" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E61" t="str">
         <f t="shared" si="44"/>
@@ -7326,24 +7329,24 @@
         <v>41</v>
       </c>
       <c r="Y61" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AK61" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL61" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM61" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="62" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" spans="1:39" ht="15.95" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E62" t="str">
         <f t="shared" si="44"/>
@@ -7382,7 +7385,7 @@
         <v>notfound</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>54</v>
@@ -7391,27 +7394,27 @@
         <v>41</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Z62" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AK62" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL62" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM62" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="63" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="63" spans="1:39" ht="15.95" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E63" t="str">
         <f t="shared" si="44"/>
@@ -7450,7 +7453,7 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>49</v>
@@ -7459,13 +7462,13 @@
         <v>50</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="U63" s="2" t="s">
         <v>54</v>
@@ -7474,13 +7477,13 @@
         <v>41</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA63" s="2" t="s">
         <v>59</v>
@@ -7495,10 +7498,10 @@
         <v>61</v>
       </c>
       <c r="AH63" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AK63" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL63" s="2" t="s">
         <v>58</v>
@@ -7507,12 +7510,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:39" ht="15.95" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="44"/>
@@ -7551,7 +7554,7 @@
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>49</v>
@@ -7560,13 +7563,13 @@
         <v>50</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>54</v>
@@ -7575,13 +7578,13 @@
         <v>41</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA64" s="2" t="s">
         <v>59</v>
@@ -7596,7 +7599,7 @@
         <v>61</v>
       </c>
       <c r="AK64" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL64" s="2" t="s">
         <v>58</v>
@@ -7605,12 +7608,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:39" ht="15.95" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="44"/>
@@ -7649,7 +7652,7 @@
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>49</v>
@@ -7658,13 +7661,13 @@
         <v>50</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S65" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>54</v>
@@ -7673,13 +7676,13 @@
         <v>41</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA65" s="2" t="s">
         <v>59</v>
@@ -7694,7 +7697,7 @@
         <v>61</v>
       </c>
       <c r="AK65" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL65" s="2" t="s">
         <v>58</v>
@@ -7703,9 +7706,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:39" ht="15.95" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>40</v>
@@ -7747,7 +7750,7 @@
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>49</v>
@@ -7756,13 +7759,13 @@
         <v>50</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="S66" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="U66" s="2" t="s">
         <v>54</v>
@@ -7771,13 +7774,13 @@
         <v>41</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA66" s="2" t="s">
         <v>59</v>
@@ -7792,7 +7795,7 @@
         <v>61</v>
       </c>
       <c r="AK66" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL66" s="2" t="s">
         <v>58</v>
@@ -7801,12 +7804,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:39" ht="15.95" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E67" t="str">
         <f t="shared" si="44"/>
@@ -7845,7 +7848,7 @@
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>49</v>
@@ -7854,13 +7857,13 @@
         <v>50</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="S67" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>54</v>
@@ -7869,13 +7872,13 @@
         <v>41</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Y67" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA67" s="2" t="s">
         <v>59</v>
@@ -7890,7 +7893,7 @@
         <v>61</v>
       </c>
       <c r="AK67" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL67" s="2" t="s">
         <v>58</v>
@@ -7899,9 +7902,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:39" ht="15.95" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>47</v>
@@ -7943,7 +7946,7 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>49</v>
@@ -7952,13 +7955,13 @@
         <v>50</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="S68" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>54</v>
@@ -7967,13 +7970,13 @@
         <v>41</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AA68" s="2" t="s">
         <v>59</v>
@@ -7985,27 +7988,27 @@
         <v>59</v>
       </c>
       <c r="AG68" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AH68" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK68" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AL68" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM68" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="69" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:39" ht="15.95" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="44"/>
@@ -8044,7 +8047,7 @@
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>49</v>
@@ -8053,13 +8056,13 @@
         <v>50</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="S69" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="U69" s="2" t="s">
         <v>54</v>
@@ -8068,13 +8071,13 @@
         <v>41</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Y69" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AA69" s="2" t="s">
         <v>59</v>
@@ -8086,13 +8089,13 @@
         <v>59</v>
       </c>
       <c r="AG69" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AH69" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK69" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AL69" s="2" t="s">
         <v>58</v>
@@ -8101,12 +8104,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:39" ht="15.95" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E70" t="str">
         <f t="shared" si="44"/>
@@ -8145,10 +8148,10 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA70" s="2" t="s">
         <v>59</v>
@@ -8160,7 +8163,7 @@
         <v>59</v>
       </c>
       <c r="AK70" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL70" s="2" t="s">
         <v>58</v>
@@ -8169,12 +8172,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:39" ht="15.95" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E71" t="str">
         <f t="shared" si="44"/>
@@ -8213,10 +8216,10 @@
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y71" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA71" s="2" t="s">
         <v>59</v>
@@ -8228,7 +8231,7 @@
         <v>59</v>
       </c>
       <c r="AK71" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL71" s="2" t="s">
         <v>58</v>
@@ -8237,12 +8240,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:39" ht="15.95" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" ref="E72:E104" si="57">RIGHT(A72,1)</f>
@@ -8281,10 +8284,10 @@
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA72" s="2" t="s">
         <v>59</v>
@@ -8296,7 +8299,7 @@
         <v>59</v>
       </c>
       <c r="AK72" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL72" s="2" t="s">
         <v>58</v>
@@ -8305,12 +8308,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:39" ht="15.95" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="57"/>
@@ -8349,27 +8352,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK73" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL73" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM73" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="74" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="74" spans="1:39" ht="15.95" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="57"/>
@@ -8408,27 +8411,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK74" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL74" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM74" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="75" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="75" spans="1:39" ht="15.95" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="57"/>
@@ -8467,27 +8470,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y75" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK75" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL75" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM75" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="76" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:39" ht="15.95" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="57"/>
@@ -8526,27 +8529,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK76" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL76" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM76" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="77" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="77" spans="1:39" ht="15.95" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E77" t="str">
         <f t="shared" si="57"/>
@@ -8585,27 +8588,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK77" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL77" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM77" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="78" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:39" ht="15.95" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="57"/>
@@ -8644,27 +8647,27 @@
         <v>notfound</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AK78" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL78" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM78" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="79" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="79" spans="1:39" ht="15.75" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="57"/>
@@ -8703,13 +8706,13 @@
         <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T79" s="2" t="str">
         <f>IF(S79="N", R79, "write file name")</f>
@@ -8722,27 +8725,27 @@
         <v>41</v>
       </c>
       <c r="Y79" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="AG79" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AK79" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL79" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM79" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:39" ht="15.75" customHeight="1">
+      <c r="A80" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AG79" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AK79" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM79" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="80" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="57"/>
@@ -8781,13 +8784,13 @@
         <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T80" s="2" t="str">
         <f>IF(S80="N", R80, "write file name")</f>
@@ -8800,27 +8803,27 @@
         <v>41</v>
       </c>
       <c r="Y80" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="AG80" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AK80" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM80" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="81" spans="1:39" ht="15.75" customHeight="1">
+      <c r="A81" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AK80" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL80" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM80" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="81" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="57"/>
@@ -8859,13 +8862,13 @@
         <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T81" s="2" t="str">
         <f>IF(S81="N", R81, "write file name")</f>
@@ -8878,24 +8881,24 @@
         <v>41</v>
       </c>
       <c r="Y81" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="AG81" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AK81" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL81" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM81" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="82" spans="1:39" ht="15.75" customHeight="1">
+      <c r="A82" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="AG81" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AK81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL81" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM81" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="82" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>40</v>
@@ -8937,13 +8940,13 @@
         <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T82" s="2" t="str">
         <f>IF(S82="N", R82, "write file name")</f>
@@ -8956,27 +8959,27 @@
         <v>41</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG82" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AK82" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL82" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL82" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM82" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="83" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="83" spans="1:39" ht="15.75" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="57"/>
@@ -9015,36 +9018,36 @@
         <v>notfound</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Y83" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="AK83" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL83" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM83" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="84" spans="1:39" ht="15.75" customHeight="1">
+      <c r="A84" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="AK83" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL83" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM83" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="84" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="57"/>
@@ -9083,36 +9086,36 @@
         <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AK84" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL84" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM84" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="85" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="85" spans="1:39" ht="15.75" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="57"/>
@@ -9151,7 +9154,7 @@
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>49</v>
@@ -9160,13 +9163,13 @@
         <v>50</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="S85" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="U85" s="2" t="s">
         <v>54</v>
@@ -9175,13 +9178,13 @@
         <v>41</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z85" s="2" t="s">
         <v>58</v>
@@ -9196,10 +9199,10 @@
         <v>59</v>
       </c>
       <c r="AG85" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AK85" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AL85" s="2" t="s">
         <v>58</v>
@@ -9208,12 +9211,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:39" ht="15.75" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="57"/>
@@ -9252,27 +9255,27 @@
         <v>notfound</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AK86" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AL86" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM86" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="87" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="87" spans="1:39" ht="15.75" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="57"/>
@@ -9311,33 +9314,33 @@
         <v>notfound</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Z87" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC87" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AK87" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL87" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL87" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM87" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="88" spans="1:39">
       <c r="A88" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>47</v>
@@ -9379,7 +9382,7 @@
         <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>54</v>
@@ -9388,33 +9391,33 @@
         <v>41</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="Z88" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AK88" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL88" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM88" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="89" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="89" spans="1:39" ht="15.75" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E89" t="str">
         <f t="shared" ref="E89" si="65">RIGHT(A89,1)</f>
@@ -9456,30 +9459,30 @@
         <v>41</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="Z89" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AF89" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AK89" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL89" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL89" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM89" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="90" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="90" spans="1:39" ht="15.75" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E90" t="str">
         <f t="shared" si="57"/>
@@ -9518,7 +9521,7 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P90" s="2" t="s">
         <v>49</v>
@@ -9527,51 +9530,51 @@
         <v>50</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="S90" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="U90" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="V90" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Z90" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA90" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AD90" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG90" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AK90" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL90" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM90" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="91" spans="1:39">
       <c r="A91" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E91" t="str">
         <f t="shared" si="57"/>
@@ -9610,7 +9613,7 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>49</v>
@@ -9619,57 +9622,57 @@
         <v>50</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="S91" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="U91" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Z91" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AA91" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AD91" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG91" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AK91" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL91" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM91" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="92" spans="1:39">
       <c r="A92" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="57"/>
@@ -9708,7 +9711,7 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>49</v>
@@ -9717,46 +9720,46 @@
         <v>50</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="S92" s="2" t="s">
         <v>52</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Z92" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA92" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AC92" s="2" t="s">
         <v>60</v>
       </c>
       <c r="AD92" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG92" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AK92" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL92" s="2" t="s">
         <v>58</v>
@@ -9765,12 +9768,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:39">
       <c r="A93" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="57"/>
@@ -9809,27 +9812,27 @@
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AK93" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL93" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM93" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="94" spans="1:39">
       <c r="A94" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="57"/>
@@ -9868,30 +9871,30 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AK94" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL94" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL94" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM94" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="95" spans="1:39">
+      <c r="A95" s="2" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="D95" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="57"/>
@@ -9930,30 +9933,30 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="N95" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y95" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="Q95" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y95" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="AK95" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL95" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL95" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM95" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="96" spans="1:39">
       <c r="A96" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="57"/>
@@ -9992,30 +9995,30 @@
         <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AK96" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL96" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM96" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="97" spans="1:39">
       <c r="A97" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="57"/>
@@ -10054,42 +10057,42 @@
         <v>notfound</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="Z97" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA97" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AB97" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AC97" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD97" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AK97" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL97" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM97" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:39">
       <c r="A98" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E98" t="str">
         <f t="shared" ref="E98" si="73">RIGHT(A98,1)</f>
@@ -10128,42 +10131,42 @@
         <v>notfound</v>
       </c>
       <c r="N98" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y98" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="Y98" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="Z98" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA98" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AB98" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC98" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD98" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK98" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL98" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM98" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:39">
       <c r="A99" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E99" t="str">
         <f t="shared" si="57"/>
@@ -10202,58 +10205,58 @@
         <v>notfound</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T99" s="2" t="str">
         <f>IF(S99="N", R99, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AE99" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG99" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK99" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL99" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM99" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="100" spans="1:39">
       <c r="A100" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E100" t="str">
         <f t="shared" si="57"/>
@@ -10292,48 +10295,48 @@
         <v>10.1159%2F000156212_Table1.tsv</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="Z100" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA100" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB100" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC100" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD100" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK100" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL100" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM100" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:39">
       <c r="A101" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E101" t="str">
         <f t="shared" si="57"/>
@@ -10372,21 +10375,21 @@
         <v>10.1159%2F000156211_Table1.tsv</v>
       </c>
       <c r="AA101" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB101" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AD101" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="102" spans="1:39">
       <c r="A102" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E102" t="str">
         <f t="shared" si="57"/>
@@ -10425,27 +10428,27 @@
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AK102" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL102" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM102" s="2" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="103" spans="1:39">
       <c r="A103" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E103" t="str">
         <f t="shared" si="57"/>
@@ -10484,36 +10487,36 @@
         <v>notfound</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AE103" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AK103" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL103" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM103" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:39">
       <c r="A104" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E104" t="str">
         <f t="shared" si="57"/>
@@ -10552,56 +10555,55 @@
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T104" s="2" t="str">
         <f>IF(S104="N", R104, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="U104" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="V104" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AE104" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AG104" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK104" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL104" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM104" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="105" spans="1:39" ht="15.75">
       <c r="A105" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C105" s="3"/>
+        <v>509</v>
+      </c>
       <c r="D105" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E105" t="str">
         <f t="shared" ref="E105" si="81">RIGHT(A105,1)</f>
@@ -10640,24 +10642,24 @@
         <v>notfound</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AB105" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AC105" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD105" s="2" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="106" spans="1:39">
       <c r="A106" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E106" t="str">
         <f t="shared" ref="E106:E138" si="89">RIGHT(A106,1)</f>
@@ -10696,39 +10698,39 @@
         <v>notfound</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="Y106" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="Z106" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA106" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AB106" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC106" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK106" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL106" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM106" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" spans="1:39">
       <c r="A107" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E107" t="str">
         <f t="shared" si="89"/>
@@ -10767,39 +10769,39 @@
         <v>notfound</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z107" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA107" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AB107" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC107" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK107" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL107" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM107" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="1:39">
       <c r="A108" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E108" t="str">
         <f t="shared" si="89"/>
@@ -10838,39 +10840,39 @@
         <v>notfound</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="Z108" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA108" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AB108" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC108" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK108" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL108" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM108" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="1:39">
       <c r="A109" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E109" t="str">
         <f t="shared" si="89"/>
@@ -10909,45 +10911,45 @@
         <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="V109" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y109" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="Z109" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA109" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB109" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC109" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD109" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK109" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AL109" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM109" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" spans="1:39">
       <c r="A110" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>40</v>
@@ -10989,13 +10991,13 @@
         <v>notfound</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T110" s="2" t="str">
         <f>IF(S110="N", R110, "write file name")</f>
@@ -11005,40 +11007,40 @@
         <v>54</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="Z110" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB110" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC110" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AG110" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK110" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL110" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM110" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="111" spans="1:39">
       <c r="A111" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E111" t="str">
         <f t="shared" ref="E111" si="93">RIGHT(A111,1)</f>
@@ -11077,30 +11079,30 @@
         <v>notfound</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="Z111" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB111" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AC111" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD111" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="112" spans="1:39">
       <c r="A112" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E112" t="str">
         <f t="shared" si="89"/>
@@ -11139,13 +11141,13 @@
         <v>notfound</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T112" s="2" t="str">
         <f>IF(S112="N", R112, "write file name")</f>
@@ -11155,45 +11157,45 @@
         <v>54</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="Y112" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="Z112" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB112" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC112" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD112" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG112" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK112" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL112" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM112" s="2" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="113" spans="1:39">
       <c r="A113" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E113" t="str">
         <f t="shared" si="89"/>
@@ -11232,33 +11234,33 @@
         <v>notfound</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AB113" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC113" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AK113" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AL113" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM113" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="1:39">
       <c r="A114" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E114" t="str">
         <f t="shared" si="89"/>
@@ -11297,48 +11299,48 @@
         <v>notfound</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="V114" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="Z114" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AA114" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AB114" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC114" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD114" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AH114" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AK114" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL114" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM114" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:39">
       <c r="A115" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E115" t="str">
         <f t="shared" si="89"/>
@@ -11377,36 +11379,36 @@
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AB115" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC115" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD115" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK115" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL115" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM115" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:39">
       <c r="A116" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E116" t="str">
         <f t="shared" si="89"/>
@@ -11445,39 +11447,39 @@
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y116" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AB116" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC116" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD116" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK116" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL116" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM116" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" spans="1:39">
       <c r="A117" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E117" t="str">
         <f t="shared" si="89"/>
@@ -11516,36 +11518,36 @@
         <v>notfound</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="Y117" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AB117" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC117" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD117" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK117" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL117" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM117" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:39">
       <c r="A118" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>47</v>
@@ -11587,36 +11589,36 @@
         <v>notfound</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="AB118" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC118" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD118" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK118" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL118" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM118" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" spans="1:39">
       <c r="A119" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E119" t="str">
         <f t="shared" si="89"/>
@@ -11655,36 +11657,36 @@
         <v>notfound</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AB119" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC119" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD119" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK119" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL119" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM119" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="1:39">
       <c r="A120" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E120" t="str">
         <f t="shared" si="89"/>
@@ -11723,36 +11725,36 @@
         <v>notfound</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AB120" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC120" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD120" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK120" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL120" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM120" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" spans="1:39">
       <c r="A121" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E121" t="str">
         <f t="shared" si="89"/>
@@ -11791,36 +11793,36 @@
         <v>notfound</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AB121" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC121" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD121" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK121" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL121" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM121" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" spans="1:39">
       <c r="A122" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E122" t="str">
         <f t="shared" si="89"/>
@@ -11859,36 +11861,36 @@
         <v>notfound</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AB122" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC122" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD122" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK122" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL122" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM122" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="1:39">
       <c r="A123" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E123" t="str">
         <f t="shared" ref="E123" si="104">RIGHT(A123,1)</f>
@@ -11927,36 +11929,36 @@
         <v>notfound</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AB123" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC123" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD123" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK123" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL123" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM123" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="1:39">
       <c r="A124" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>737</v>
+        <v>567</v>
       </c>
       <c r="E124" t="str">
         <f t="shared" ref="E124" si="112">RIGHT(A124,1)</f>
@@ -11999,33 +12001,33 @@
         <v>TABLE 1 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Insectivores; TABLE 2 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Prosimians; TABLE 3 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Simians; TABLE 4 Volume of the various components of the telencephalon in Insectivores (in mm3); TABLE 5 Volume of the various components of the telencephalon in Prosimians (in mm3); TABLE 6 Volume of the various components of the telencephalon in Simians (in mm3)</v>
       </c>
       <c r="AB124" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC124" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD124" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK124" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL124" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM124" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="1:39">
       <c r="A125" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E125" t="str">
         <f t="shared" si="89"/>
@@ -12064,51 +12066,51 @@
         <v>PMID%3A7161483_Table1.tsv</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="V125" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W125" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y125" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="Z125" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA125" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB125" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC125" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD125" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK125" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL125" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM125" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="1:39">
       <c r="A126" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E126" t="str">
         <f t="shared" si="89"/>
@@ -12147,51 +12149,51 @@
         <v>PMID%3A6481154_Table1.tsv</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="V126" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W126" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y126" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="Z126" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA126" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB126" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC126" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD126" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK126" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL126" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM126" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" spans="1:39">
       <c r="A127" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E127" t="str">
         <f t="shared" si="89"/>
@@ -12230,48 +12232,48 @@
         <v>PMID%3A3693895_Table1.tsv</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="V127" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W127" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y127" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="Z127" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA127" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB127" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC127" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD127" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK127" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL127" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM127" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" spans="1:39">
       <c r="A128" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E128" t="str">
         <f t="shared" si="89"/>
@@ -12310,45 +12312,45 @@
         <v>10.1159%2F000155963_Table1.tsv</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="V128" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y128" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="Z128" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA128" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AB128" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC128" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD128" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK128" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL128" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM128" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" spans="1:39">
       <c r="A129" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E129" t="str">
         <f t="shared" ref="E129:E130" si="120">RIGHT(A129,1)</f>
@@ -12387,36 +12389,36 @@
         <v>notfound</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="V129" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA129" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AB129" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC129" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD129" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AL129" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM129" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" spans="1:39">
       <c r="A130" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E130" t="str">
         <f t="shared" si="120"/>
@@ -12455,36 +12457,36 @@
         <v>notfound</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="V130" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA130" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AB130" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC130" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD130" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AL130" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM130" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="1:39">
       <c r="A131" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="89"/>
@@ -12523,27 +12525,27 @@
         <v>notfound</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="Y131" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AK131" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AL131" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM131" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="132" spans="1:39">
       <c r="A132" s="2" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E132" t="str">
         <f t="shared" si="89"/>
@@ -12582,24 +12584,24 @@
         <v>notfound</v>
       </c>
       <c r="Y132" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AK132" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL132" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL132" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM132" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="133" spans="1:39">
       <c r="A133" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E133" t="str">
         <f t="shared" si="89"/>
@@ -12638,7 +12640,7 @@
         <v>notfound</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AK133" s="2" t="s">
         <v>42</v>
@@ -12650,12 +12652,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:39">
       <c r="A134" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E134" t="str">
         <f t="shared" si="89"/>
@@ -12694,10 +12696,10 @@
         <v>notfound</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T134" s="2" t="str">
         <f>IF(S134="N", R134, "write file name")</f>
@@ -12707,30 +12709,30 @@
         <v>54</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="Y134" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AG134" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AK134" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL134" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AL134" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="AM134" s="2" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="135" spans="1:39">
       <c r="A135" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E135" t="str">
         <f t="shared" si="89"/>
@@ -12769,10 +12771,10 @@
         <v>notfound</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T135" s="2" t="str">
         <f>IF(S135="N", R135, "write file name")</f>
@@ -12785,30 +12787,30 @@
         <v>41</v>
       </c>
       <c r="Y135" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="Z135" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AG135" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK135" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AL135" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM135" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="136" spans="1:39">
       <c r="A136" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E136" t="str">
         <f t="shared" si="89"/>
@@ -12847,42 +12849,42 @@
         <v>notfound</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="V136" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y136" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="Z136" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA136" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AC136" s="2" t="s">
         <v>60</v>
       </c>
       <c r="AK136" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AL136" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM136" s="2" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="137" spans="1:39">
       <c r="A137" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E137" t="str">
         <f t="shared" si="89"/>
@@ -12921,36 +12923,36 @@
         <v>ISBN%3A9780195043716_Table12-2.tsv</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="Y137" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AB137" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC137" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AD137" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AK137" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AL137" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM137" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" spans="1:39">
       <c r="A138" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E138" t="str">
         <f t="shared" si="89"/>
@@ -12989,31 +12991,31 @@
         <v>notfound</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="V138" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y138" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="Z138" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA138" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AC138" s="2" t="s">
         <v>42</v>
       </c>
       <c r="AK138" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AL138" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM138" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -13046,104 +13048,104 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B4" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B5" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="6" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B6" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="6" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B7" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="6" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B8" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="6" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B9" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="6" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B10" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="6" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B11" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B12" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="7" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -13155,64 +13157,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="C2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C4" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C5" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C6" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -13224,431 +13226,431 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -13658,6 +13660,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
@@ -13666,15 +13677,6 @@
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13933,45 +13935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9618AA32-17A2-485D-95FE-DE6375A1049C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FCEA2-2E70-4137-9976-F808ECC70391}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FCEA2-2E70-4137-9976-F808ECC70391}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9618AA32-17A2-485D-95FE-DE6375A1049C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A018EF-8115-45CE-8409-1523D815B368}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A018EF-8115-45CE-8409-1523D815B368}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_473A6008124C090B9CB4C1A72041B5B084627455" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB67C07-269C-4DF2-A6A0-428FFB93A9C3}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_473A6008124C090B9CB4C1A72041B5B084627455" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E361278-D137-3044-AD13-31FBD4032BF0}"/>
   <bookViews>
-    <workbookView xWindow="36100" yWindow="3200" windowWidth="38960" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="740">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -2254,13 +2254,19 @@
   </si>
   <si>
     <t>Semendeferi_etal_2001_Table2.tsv</t>
+  </si>
+  <si>
+    <t>Matano, S. (2001). Brief communication: Proportions of the ventral half of the cerebellar dentate nucleus in humans and great apes. Am J Phys Anthropol, 114(2), 163-165. https://doi.org/10.1002/1096-8644(200102)114:2&lt;163::AID-AJPA1016&gt;3.0.CO;2-F</t>
+  </si>
+  <si>
+    <t>TABLE 2. Volume of the dentate nucleus investigated (mm3)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2347,7 +2353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2358,6 +2364,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2376,9 +2383,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2416,7 +2423,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2522,7 +2529,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2664,7 +2671,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2672,25 +2679,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM138"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <dimension ref="A1:AM139"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.5" customWidth="1"/>
-    <col min="2" max="2" width="1.625" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" customWidth="1"/>
     <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" customWidth="1"/>
     <col min="5" max="5" width="1.5" customWidth="1"/>
     <col min="6" max="6" width="14.5" customWidth="1"/>
-    <col min="7" max="8" width="10.375" customWidth="1"/>
-    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" customWidth="1"/>
     <col min="10" max="10" width="14.5" customWidth="1"/>
-    <col min="11" max="11" width="31.875" customWidth="1"/>
+    <col min="11" max="11" width="31.83203125" customWidth="1"/>
     <col min="12" max="12" width="49" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
-    <col min="14" max="39" width="7.375" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="39" width="7.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15.95" customHeight="1">
+    <row r="1" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2809,7 +2816,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="15.95" customHeight="1">
+    <row r="2" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -2868,7 +2875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15.95" customHeight="1">
+    <row r="3" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -2918,7 +2925,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="15.95" customHeight="1">
+    <row r="4" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -3016,7 +3023,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15.95" customHeight="1">
+    <row r="5" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>64</v>
       </c>
@@ -3072,7 +3079,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="15.95" customHeight="1">
+    <row r="6" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="15.95" customHeight="1">
+    <row r="7" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
@@ -3184,7 +3191,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="15.95" customHeight="1">
+    <row r="8" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
@@ -3252,7 +3259,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="15.95" customHeight="1">
+    <row r="9" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
@@ -3308,7 +3315,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="15.95" customHeight="1">
+    <row r="10" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>78</v>
       </c>
@@ -3355,7 +3362,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="15.95" customHeight="1">
+    <row r="11" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -3429,7 +3436,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="12" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>87</v>
       </c>
@@ -3506,7 +3513,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="13" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>91</v>
       </c>
@@ -3583,7 +3590,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="15.95" customHeight="1">
+    <row r="14" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
@@ -3666,7 +3673,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="15.95" customHeight="1">
+    <row r="15" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>99</v>
       </c>
@@ -3740,7 +3747,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="15.95" customHeight="1">
+    <row r="16" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>99</v>
       </c>
@@ -3811,7 +3818,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="15.95" customHeight="1">
+    <row r="17" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>99</v>
       </c>
@@ -3882,7 +3889,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="15.95" customHeight="1">
+    <row r="18" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>106</v>
       </c>
@@ -3941,7 +3948,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="15.95" customHeight="1">
+    <row r="19" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>111</v>
       </c>
@@ -4034,7 +4041,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="15.95" customHeight="1">
+    <row r="20" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>125</v>
       </c>
@@ -4114,7 +4121,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="15.95" customHeight="1">
+    <row r="21" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>125</v>
       </c>
@@ -4212,7 +4219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="15.95" customHeight="1">
+    <row r="22" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>140</v>
       </c>
@@ -4262,7 +4269,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="15.95" customHeight="1">
+    <row r="23" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>143</v>
       </c>
@@ -4351,7 +4358,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="15.95" customHeight="1">
+    <row r="24" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>153</v>
       </c>
@@ -4440,7 +4447,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="15.95" customHeight="1">
+    <row r="25" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>161</v>
       </c>
@@ -4533,7 +4540,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="15.95" customHeight="1">
+    <row r="26" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>161</v>
       </c>
@@ -4628,7 +4635,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="15.95" customHeight="1">
+    <row r="27" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>179</v>
       </c>
@@ -4714,7 +4721,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="15.95" customHeight="1">
+    <row r="28" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>191</v>
       </c>
@@ -4810,7 +4817,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="15.95" customHeight="1">
+    <row r="29" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>201</v>
       </c>
@@ -4872,7 +4879,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="15.95" customHeight="1">
+    <row r="30" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>205</v>
       </c>
@@ -4946,7 +4953,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="15.95" customHeight="1">
+    <row r="31" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>210</v>
       </c>
@@ -5041,7 +5048,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="15.95" customHeight="1">
+    <row r="32" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>219</v>
       </c>
@@ -5148,7 +5155,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="15.95" customHeight="1">
+    <row r="33" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>219</v>
       </c>
@@ -5225,7 +5232,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="15.95" customHeight="1">
+    <row r="34" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>235</v>
       </c>
@@ -5308,7 +5315,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:39" ht="15.95" customHeight="1">
+    <row r="35" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>235</v>
       </c>
@@ -5388,7 +5395,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="15" customHeight="1">
+    <row r="36" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>235</v>
       </c>
@@ -5468,7 +5475,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="15.95" customHeight="1">
+    <row r="37" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>235</v>
       </c>
@@ -5548,7 +5555,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="15.95" customHeight="1">
+    <row r="38" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>251</v>
       </c>
@@ -5649,7 +5656,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="15.95" customHeight="1">
+    <row r="39" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>251</v>
       </c>
@@ -5750,7 +5757,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="15.95" customHeight="1">
+    <row r="40" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>266</v>
       </c>
@@ -5854,7 +5861,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="15.95" customHeight="1">
+    <row r="41" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>277</v>
       </c>
@@ -5919,7 +5926,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="1:39" ht="15.95" customHeight="1">
+    <row r="42" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>281</v>
       </c>
@@ -5984,7 +5991,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:39" ht="15.95" customHeight="1">
+    <row r="43" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>281</v>
       </c>
@@ -6049,7 +6056,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:39" ht="15.95" customHeight="1">
+    <row r="44" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>288</v>
       </c>
@@ -6141,7 +6148,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:39" ht="15.95" customHeight="1">
+    <row r="45" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>295</v>
       </c>
@@ -6188,7 +6195,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="46" spans="1:39" ht="15.95" customHeight="1">
+    <row r="46" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>295</v>
       </c>
@@ -6268,7 +6275,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:39" ht="15.95" customHeight="1">
+    <row r="47" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>299</v>
       </c>
@@ -6348,7 +6355,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:39" ht="18.95" customHeight="1">
+    <row r="48" spans="1:39" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>303</v>
       </c>
@@ -6428,7 +6435,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="49" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>307</v>
       </c>
@@ -6508,7 +6515,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="50" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>311</v>
       </c>
@@ -6588,7 +6595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="51" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>315</v>
       </c>
@@ -6653,7 +6660,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="52" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>319</v>
       </c>
@@ -6718,7 +6725,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="53" spans="1:39" ht="17.100000000000001" customHeight="1">
+    <row r="53" spans="1:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>319</v>
       </c>
@@ -6783,7 +6790,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="15.95" customHeight="1">
+    <row r="54" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>325</v>
       </c>
@@ -6845,7 +6852,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:39" ht="15.95" customHeight="1">
+    <row r="55" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>328</v>
       </c>
@@ -6907,7 +6914,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:39" ht="15.95" customHeight="1">
+    <row r="56" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>332</v>
       </c>
@@ -6960,7 +6967,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="1:39" ht="15.95" customHeight="1">
+    <row r="57" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>333</v>
       </c>
@@ -7044,7 +7051,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="58" spans="1:39" ht="15.95" customHeight="1">
+    <row r="58" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>338</v>
       </c>
@@ -7136,7 +7143,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="59" spans="1:39" ht="15.95" customHeight="1">
+    <row r="59" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>345</v>
       </c>
@@ -7201,7 +7208,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="60" spans="1:39" ht="15.95" customHeight="1">
+    <row r="60" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>351</v>
       </c>
@@ -7279,7 +7286,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="61" spans="1:39" ht="15.95" customHeight="1">
+    <row r="61" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>354</v>
       </c>
@@ -7341,7 +7348,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="62" spans="1:39" ht="15.95" customHeight="1">
+    <row r="62" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>354</v>
       </c>
@@ -7409,7 +7416,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="63" spans="1:39" ht="15.95" customHeight="1">
+    <row r="63" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>360</v>
       </c>
@@ -7510,7 +7517,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:39" ht="15.95" customHeight="1">
+    <row r="64" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>360</v>
       </c>
@@ -7608,7 +7615,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:39" ht="15.95" customHeight="1">
+    <row r="65" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>360</v>
       </c>
@@ -7706,7 +7713,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:39" ht="15.95" customHeight="1">
+    <row r="66" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>360</v>
       </c>
@@ -7804,7 +7811,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:39" ht="15.95" customHeight="1">
+    <row r="67" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>360</v>
       </c>
@@ -7902,7 +7909,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:39" ht="15.95" customHeight="1">
+    <row r="68" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>379</v>
       </c>
@@ -8003,7 +8010,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="69" spans="1:39" ht="15.95" customHeight="1">
+    <row r="69" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>379</v>
       </c>
@@ -8104,7 +8111,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:39" ht="15.95" customHeight="1">
+    <row r="70" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>392</v>
       </c>
@@ -8172,7 +8179,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:39" ht="15.95" customHeight="1">
+    <row r="71" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>392</v>
       </c>
@@ -8240,7 +8247,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:39" ht="15.95" customHeight="1">
+    <row r="72" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>392</v>
       </c>
@@ -8248,15 +8255,15 @@
         <v>396</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" ref="E72:E104" si="57">RIGHT(A72,1)</f>
+        <f t="shared" ref="E72:E105" si="57">RIGHT(A72,1)</f>
         <v>5</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" ref="F72:F104" si="58">G72 &amp; IF(H72&lt;&gt;"", "_" &amp; H72, "_") &amp; IF(I72&lt;&gt;"", "_" &amp; I72, "_") &amp; IF(B72&lt;&gt;"", "_" &amp; B72, "")</f>
+        <f t="shared" ref="F72:F105" si="58">G72 &amp; IF(H72&lt;&gt;"", "_" &amp; H72, "_") &amp; IF(I72&lt;&gt;"", "_" &amp; I72, "_") &amp; IF(B72&lt;&gt;"", "_" &amp; B72, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" ref="G72:G104" si="59">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A72,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G72:G105" si="59">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A72,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H72" t="str">
@@ -8264,7 +8271,7 @@
         <v>etal</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" ref="I72:I104" si="60">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A72, "("), ")")</f>
+        <f t="shared" ref="I72:I105" si="60">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A72, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="J72" t="str">
@@ -8308,7 +8315,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:39" ht="15.95" customHeight="1">
+    <row r="73" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>397</v>
       </c>
@@ -8367,7 +8374,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="74" spans="1:39" ht="15.95" customHeight="1">
+    <row r="74" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>397</v>
       </c>
@@ -8426,7 +8433,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="75" spans="1:39" ht="15.95" customHeight="1">
+    <row r="75" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>397</v>
       </c>
@@ -8485,7 +8492,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="1:39" ht="15.95" customHeight="1">
+    <row r="76" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>397</v>
       </c>
@@ -8544,7 +8551,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="77" spans="1:39" ht="15.95" customHeight="1">
+    <row r="77" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>397</v>
       </c>
@@ -8603,7 +8610,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="78" spans="1:39" ht="15.95" customHeight="1">
+    <row r="78" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>397</v>
       </c>
@@ -8631,15 +8638,15 @@
         <v>2008</v>
       </c>
       <c r="J78" t="str">
-        <f t="shared" ref="J78:J112" si="62">IF(C78&lt;&gt;"", C78, IF(C78="", _xlfn.TEXTAFTER(A78,"https://doi.org/"), C78))</f>
+        <f t="shared" ref="J78:J113" si="62">IF(C78&lt;&gt;"", C78, IF(C78="", _xlfn.TEXTAFTER(A78,"https://doi.org/"), C78))</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" ref="K78:K112" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,F78,(SUBSTITUTE(SUBSTITUTE(D78," ",""), "_", ""))))</f>
+        <f t="shared" ref="K78:K113" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,F78,(SUBSTITUTE(SUBSTITUTE(D78," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L78" t="str">
-        <f t="shared" ref="L78:L112" si="64">IF(ISBLANK(C78),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J78, SUBSTITUTE(D78,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C78, SUBSTITUTE(D78,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L78:L113" si="64">IF(ISBLANK(C78),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J78, SUBSTITUTE(D78,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C78, SUBSTITUTE(D78,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M78" t="str">
@@ -8662,7 +8669,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:39" ht="15.75" customHeight="1">
+    <row r="79" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>405</v>
       </c>
@@ -8740,7 +8747,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="80" spans="1:39" ht="15.75" customHeight="1">
+    <row r="80" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>405</v>
       </c>
@@ -8818,7 +8825,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="81" spans="1:39" ht="15.75" customHeight="1">
+    <row r="81" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>405</v>
       </c>
@@ -8896,7 +8903,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="82" spans="1:39" ht="15.75" customHeight="1">
+    <row r="82" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>405</v>
       </c>
@@ -8974,7 +8981,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="83" spans="1:39" ht="15.75" customHeight="1">
+    <row r="83" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>414</v>
       </c>
@@ -9042,7 +9049,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="84" spans="1:39" ht="15.75" customHeight="1">
+    <row r="84" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>414</v>
       </c>
@@ -9110,7 +9117,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="85" spans="1:39" ht="15.75" customHeight="1">
+    <row r="85" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>420</v>
       </c>
@@ -9211,7 +9218,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="15.75" customHeight="1">
+    <row r="86" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>427</v>
       </c>
@@ -9270,7 +9277,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="15.75" customHeight="1">
+    <row r="87" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>432</v>
       </c>
@@ -9338,7 +9345,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="88" spans="1:39">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>437</v>
       </c>
@@ -9409,7 +9416,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="89" spans="1:39" ht="15.75" customHeight="1">
+    <row r="89" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>440</v>
       </c>
@@ -9477,7 +9484,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="90" spans="1:39" ht="15.75" customHeight="1">
+    <row r="90" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>445</v>
       </c>
@@ -9497,7 +9504,7 @@
         <v>Kverkova</v>
       </c>
       <c r="H90" t="str">
-        <f t="shared" ref="H90:H138" si="72">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A90," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A90)-LEN(SUBSTITUTE(A90,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <f t="shared" ref="H90:H139" si="72">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A90," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A90)-LEN(SUBSTITUTE(A90,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
         <v>etal</v>
       </c>
       <c r="I90" t="str">
@@ -9569,7 +9576,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="91" spans="1:39">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>445</v>
       </c>
@@ -9667,7 +9674,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="92" spans="1:39">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>445</v>
       </c>
@@ -9768,7 +9775,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:39">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>464</v>
       </c>
@@ -9827,7 +9834,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="94" spans="1:39">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>468</v>
       </c>
@@ -9889,7 +9896,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="95" spans="1:39">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>468</v>
       </c>
@@ -9951,7 +9958,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="96" spans="1:39">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>474</v>
       </c>
@@ -10013,7 +10020,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="97" spans="1:39">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>478</v>
       </c>
@@ -10087,7 +10094,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:39">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>478</v>
       </c>
@@ -10161,7 +10168,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:39">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>485</v>
       </c>
@@ -10248,7 +10255,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="100" spans="1:39">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>492</v>
       </c>
@@ -10328,7 +10335,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:39">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>495</v>
       </c>
@@ -10384,79 +10391,71 @@
         <v>85</v>
       </c>
     </row>
-    <row r="102" spans="1:39">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B102" s="8"/>
+      <c r="D102" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E102" t="str">
+        <f t="shared" ref="E102" si="81">RIGHT(A102,1)</f>
+        <v>F</v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" ref="F102" si="82">G102 &amp; IF(H102&lt;&gt;"", "_" &amp; H102, "_") &amp; IF(I102&lt;&gt;"", "_" &amp; I102, "_") &amp; IF(B102&lt;&gt;"", "_" &amp; B102, "")</f>
+        <v>Matano__2001</v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" ref="G102" si="83">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A102,","), "-", ""), " ", "")</f>
+        <v>Matano</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" ref="H102" si="84">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A102," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A102)-LEN(SUBSTITUTE(A102,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <f t="shared" ref="I102" si="85">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A102, "("), ")")</f>
+        <v>2001</v>
+      </c>
+      <c r="J102" t="str">
+        <f t="shared" ref="J102" si="86">IF(C102&lt;&gt;"", C102, IF(C102="", _xlfn.TEXTAFTER(A102,"https://doi.org/"), C102))</f>
+        <v>10.1002/1096-8644(200102)114:2&lt;163::AID-AJPA1016&gt;3.0.CO;2-F</v>
+      </c>
+      <c r="K102" t="str">
+        <f t="shared" ref="K102" si="87">TRIM(_xlfn.TEXTJOIN("_",FALSE,F102,(SUBSTITUTE(SUBSTITUTE(D102," ",""), "_", ""))))</f>
+        <v>Matano__2001_TABLE2</v>
+      </c>
+      <c r="L102" t="str">
+        <f t="shared" ref="L102" si="88">IF(ISBLANK(C102),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J102, SUBSTITUTE(D102,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C102, SUBSTITUTE(D102,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2F1096-8644(200102)114%3A2&lt;163%3A%3AAID-AJPA1016&gt;3.0.CO;2-F_TABLE2</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="array" ref="M102">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L102, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N102" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="AA102" s="8"/>
+      <c r="AB102" s="8"/>
+      <c r="AD102" s="8"/>
+    </row>
+    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E103" t="str">
         <f t="shared" si="57"/>
         <v>1</v>
       </c>
-      <c r="F102" t="str">
+      <c r="F103" t="str">
         <f t="shared" si="58"/>
         <v>Mota_etal_2015</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="59"/>
-        <v>Mota</v>
-      </c>
-      <c r="H102" t="str">
-        <f t="shared" si="72"/>
-        <v>etal</v>
-      </c>
-      <c r="I102" t="str">
-        <f t="shared" si="60"/>
-        <v>2015</v>
-      </c>
-      <c r="J102" t="str">
-        <f t="shared" si="62"/>
-        <v>10.1126/science.aaa9101</v>
-      </c>
-      <c r="K102" t="str">
-        <f t="shared" si="63"/>
-        <v>Mota_etal_2015_TableS1</v>
-      </c>
-      <c r="L102" t="str">
-        <f t="shared" si="64"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
-      </c>
-      <c r="M102" t="str">
-        <f t="array" ref="M102">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L102, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
-      </c>
-      <c r="Q102" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y102" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="AK102" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL102" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="AM102" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="103" spans="1:39">
-      <c r="A103" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E103" t="str">
-        <f t="shared" si="57"/>
-        <v>6</v>
-      </c>
-      <c r="F103" t="str">
-        <f t="shared" si="58"/>
-        <v>Mota_etal_2019</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="59"/>
@@ -10468,35 +10467,29 @@
       </c>
       <c r="I103" t="str">
         <f t="shared" si="60"/>
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="J103" t="str">
         <f t="shared" si="62"/>
-        <v>10.1073/pnas.1716956116</v>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="K103" t="str">
         <f t="shared" si="63"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
+        <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="L103" t="str">
         <f t="shared" si="64"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M103" t="str">
         <f t="array" ref="M103">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L103, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="P103" s="2" t="s">
-        <v>317</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="AE103" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AK103" s="2" t="s">
         <v>123</v>
@@ -10505,30 +10498,27 @@
         <v>343</v>
       </c>
       <c r="AM103" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="104" spans="1:39">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E104" t="str">
         <f t="shared" si="57"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F104" t="str">
         <f t="shared" si="58"/>
-        <v>Powell_etal_2017</v>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="59"/>
-        <v>Powell</v>
+        <v>Mota</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="72"/>
@@ -10536,212 +10526,209 @@
       </c>
       <c r="I104" t="str">
         <f t="shared" si="60"/>
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="J104" t="str">
         <f t="shared" si="62"/>
-        <v>10.6084/m9.figshare.c.3899422.v1</v>
+        <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="K104" t="str">
         <f t="shared" si="63"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L104" t="str">
         <f t="shared" si="64"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M104" t="str">
         <f t="array" ref="M104">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L104, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="P104" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="Q104" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="T104" s="2" t="str">
-        <f>IF(S104="N", R104, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U104" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="V104" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W104" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="X104" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="Y104" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="Z104" s="2" t="s">
-        <v>120</v>
+        <v>501</v>
       </c>
       <c r="AE104" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG104" s="2" t="s">
-        <v>160</v>
+        <v>502</v>
       </c>
       <c r="AK104" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="AL104" s="2" t="s">
-        <v>120</v>
+        <v>343</v>
       </c>
       <c r="AM104" s="2" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="105" spans="1:39" ht="15.75">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>82</v>
+        <v>504</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>506</v>
       </c>
       <c r="E105" t="str">
-        <f t="shared" ref="E105" si="81">RIGHT(A105,1)</f>
+        <f t="shared" si="57"/>
         <v>5</v>
       </c>
       <c r="F105" t="str">
-        <f t="shared" ref="F105" si="82">G105 &amp; IF(H105&lt;&gt;"", "_" &amp; H105, "_") &amp; IF(I105&lt;&gt;"", "_" &amp; I105, "_") &amp; IF(B105&lt;&gt;"", "_" &amp; B105, "")</f>
-        <v>Rilling_etal_1998</v>
+        <f t="shared" si="58"/>
+        <v>Powell_etal_2017</v>
       </c>
       <c r="G105" t="str">
-        <f t="shared" ref="G105" si="83">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A105,","), "-", ""), " ", "")</f>
-        <v>Rilling</v>
+        <f t="shared" si="59"/>
+        <v>Powell</v>
       </c>
       <c r="H105" t="str">
-        <f t="shared" ref="H105" si="84">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A105," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A105)-LEN(SUBSTITUTE(A105,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I105" t="str">
-        <f t="shared" ref="I105" si="85">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A105, "("), ")")</f>
-        <v>1998</v>
+        <f t="shared" si="60"/>
+        <v>2017</v>
       </c>
       <c r="J105" t="str">
-        <f t="shared" ref="J105" si="86">IF(C105&lt;&gt;"", C105, IF(C105="", _xlfn.TEXTAFTER(A105,"https://doi.org/"), C105))</f>
-        <v>10.1159/000006575</v>
+        <f t="shared" si="62"/>
+        <v>10.6084/m9.figshare.c.3899422.v1</v>
       </c>
       <c r="K105" t="str">
-        <f t="shared" ref="K105" si="87">TRIM(_xlfn.TEXTJOIN("_",FALSE,F105,(SUBSTITUTE(SUBSTITUTE(D105," ",""), "_", ""))))</f>
-        <v>Rilling_etal_1998_Table1</v>
+        <f t="shared" si="63"/>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="L105" t="str">
-        <f t="shared" ref="L105" si="88">IF(ISBLANK(C105),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J105, SUBSTITUTE(D105,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C105, SUBSTITUTE(D105,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000006575_Table1</v>
+        <f t="shared" si="64"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M105" t="str">
         <f t="array" ref="M105">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L105, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N105" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="AB105" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC105" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD105" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="106" spans="1:39">
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="T105" s="2" t="str">
+        <f>IF(S105="N", R105, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="Y105" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="Z105" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE105" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG105" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK105" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL105" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM105" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E106" t="str">
-        <f t="shared" ref="E106:E138" si="89">RIGHT(A106,1)</f>
-        <v>L</v>
+        <f t="shared" ref="E106" si="89">RIGHT(A106,1)</f>
+        <v>5</v>
       </c>
       <c r="F106" t="str">
-        <f t="shared" ref="F106:F138" si="90">G106 &amp; IF(H106&lt;&gt;"", "_" &amp; H106, "_") &amp; IF(I106&lt;&gt;"", "_" &amp; I106, "_") &amp; IF(B106&lt;&gt;"", "_" &amp; B106, "")</f>
-        <v>Semendeferi_etal_1998</v>
+        <f t="shared" ref="F106" si="90">G106 &amp; IF(H106&lt;&gt;"", "_" &amp; H106, "_") &amp; IF(I106&lt;&gt;"", "_" &amp; I106, "_") &amp; IF(B106&lt;&gt;"", "_" &amp; B106, "")</f>
+        <v>Rilling_etal_1998</v>
       </c>
       <c r="G106" t="str">
-        <f t="shared" ref="G106:G138" si="91">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A106,","), "-", ""), " ", "")</f>
-        <v>Semendeferi</v>
+        <f t="shared" ref="G106" si="91">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A106,","), "-", ""), " ", "")</f>
+        <v>Rilling</v>
       </c>
       <c r="H106" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="H106" si="92">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A106," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A106)-LEN(SUBSTITUTE(A106,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
         <v>etal</v>
       </c>
       <c r="I106" t="str">
-        <f t="shared" ref="I106:I138" si="92">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A106, "("), ")")</f>
+        <f t="shared" ref="I106" si="93">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A106, "("), ")")</f>
         <v>1998</v>
       </c>
       <c r="J106" t="str">
-        <f t="shared" si="62"/>
-        <v>10.1002/(SICI)1096-8644(199806)106:2&lt;129::AID-AJPA3&gt;3.0.CO;2-L</v>
+        <f t="shared" ref="J106" si="94">IF(C106&lt;&gt;"", C106, IF(C106="", _xlfn.TEXTAFTER(A106,"https://doi.org/"), C106))</f>
+        <v>10.1159/000006575</v>
       </c>
       <c r="K106" t="str">
-        <f t="shared" si="63"/>
-        <v>Semendeferi_etal_1998_TABLE2</v>
+        <f t="shared" ref="K106" si="95">TRIM(_xlfn.TEXTJOIN("_",FALSE,F106,(SUBSTITUTE(SUBSTITUTE(D106," ",""), "_", ""))))</f>
+        <v>Rilling_etal_1998_Table1</v>
       </c>
       <c r="L106" t="str">
-        <f t="shared" si="64"/>
-        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2&lt;129%3A%3AAID-AJPA3&gt;3.0.CO;2-L_TABLE2</v>
+        <f t="shared" ref="L106" si="96">IF(ISBLANK(C106),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J106, SUBSTITUTE(D106,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C106, SUBSTITUTE(D106,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000006575_Table1</v>
       </c>
       <c r="M106" t="str">
         <f t="array" ref="M106">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L106, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="Y106" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="Z106" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA106" s="2" t="s">
-        <v>72</v>
+        <v>510</v>
       </c>
       <c r="AB106" s="2" t="s">
-        <v>71</v>
+        <v>482</v>
       </c>
       <c r="AC106" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AK106" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL106" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AM106" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="107" spans="1:39">
+      <c r="AD106" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>286</v>
       </c>
       <c r="E107" t="str">
-        <f t="shared" si="89"/>
-        <v>I</v>
+        <f t="shared" ref="E107:E139" si="97">RIGHT(A107,1)</f>
+        <v>L</v>
       </c>
       <c r="F107" t="str">
-        <f t="shared" si="90"/>
-        <v>Semendeferi_etal_2001</v>
+        <f t="shared" ref="F107:F139" si="98">G107 &amp; IF(H107&lt;&gt;"", "_" &amp; H107, "_") &amp; IF(I107&lt;&gt;"", "_" &amp; I107, "_") &amp; IF(B107&lt;&gt;"", "_" &amp; B107, "")</f>
+        <v>Semendeferi_etal_1998</v>
       </c>
       <c r="G107" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="G107:G139" si="99">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A107,","), "-", ""), " ", "")</f>
         <v>Semendeferi</v>
       </c>
       <c r="H107" t="str">
@@ -10749,30 +10736,30 @@
         <v>etal</v>
       </c>
       <c r="I107" t="str">
-        <f t="shared" si="92"/>
-        <v>2001</v>
+        <f t="shared" ref="I107:I139" si="100">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A107, "("), ")")</f>
+        <v>1998</v>
       </c>
       <c r="J107" t="str">
         <f t="shared" si="62"/>
-        <v>10.1002/1096-8644(200103)114:3&lt;224::AID-AJPA1022&gt;3.0.CO;2-I</v>
+        <v>10.1002/(SICI)1096-8644(199806)106:2&lt;129::AID-AJPA3&gt;3.0.CO;2-L</v>
       </c>
       <c r="K107" t="str">
         <f t="shared" si="63"/>
-        <v>Semendeferi_etal_2001_TABLE2</v>
+        <v>Semendeferi_etal_1998_TABLE2</v>
       </c>
       <c r="L107" t="str">
         <f t="shared" si="64"/>
-        <v>10.1002%2F1096-8644(200103)114%3A3&lt;224%3A%3AAID-AJPA1022&gt;3.0.CO;2-I_TABLE2</v>
+        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2&lt;129%3A%3AAID-AJPA3&gt;3.0.CO;2-L_TABLE2</v>
       </c>
       <c r="M107" t="str">
         <f t="array" ref="M107">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L107, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Z107" s="2" t="s">
         <v>58</v>
@@ -10796,23 +10783,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="108" spans="1:39">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="E108" t="str">
-        <f t="shared" si="89"/>
-        <v>4</v>
+        <f t="shared" si="97"/>
+        <v>I</v>
       </c>
       <c r="F108" t="str">
-        <f t="shared" si="90"/>
-        <v>Semendeferi_etal_2002</v>
+        <f t="shared" si="98"/>
+        <v>Semendeferi_etal_2001</v>
       </c>
       <c r="G108" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Semendeferi</v>
       </c>
       <c r="H108" t="str">
@@ -10820,30 +10807,30 @@
         <v>etal</v>
       </c>
       <c r="I108" t="str">
-        <f t="shared" si="92"/>
-        <v>2002</v>
+        <f t="shared" si="100"/>
+        <v>2001</v>
       </c>
       <c r="J108" t="str">
         <f t="shared" si="62"/>
-        <v>10.1038/nn814</v>
+        <v>10.1002/1096-8644(200103)114:3&lt;224::AID-AJPA1022&gt;3.0.CO;2-I</v>
       </c>
       <c r="K108" t="str">
         <f t="shared" si="63"/>
-        <v>Semendeferi_etal_2002_Table1</v>
+        <v>Semendeferi_etal_2001_TABLE2</v>
       </c>
       <c r="L108" t="str">
         <f t="shared" si="64"/>
-        <v>10.1038%2Fnn814_Table1</v>
+        <v>10.1002%2F1096-8644(200103)114%3A3&lt;224%3A%3AAID-AJPA1022&gt;3.0.CO;2-I_TABLE2</v>
       </c>
       <c r="M108" t="str">
         <f t="array" ref="M108">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L108, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="Z108" s="2" t="s">
         <v>58</v>
@@ -10867,63 +10854,60 @@
         <v>74</v>
       </c>
     </row>
-    <row r="109" spans="1:39">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D109" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>82</v>
       </c>
       <c r="E109" t="str">
-        <f t="shared" si="89"/>
-        <v>3</v>
+        <f t="shared" si="97"/>
+        <v>4</v>
       </c>
       <c r="F109" t="str">
-        <f t="shared" si="90"/>
-        <v>Sherwood_etal_2005</v>
+        <f t="shared" si="98"/>
+        <v>Semendeferi_etal_2002</v>
       </c>
       <c r="G109" t="str">
-        <f t="shared" si="91"/>
-        <v>Sherwood</v>
+        <f t="shared" si="99"/>
+        <v>Semendeferi</v>
       </c>
       <c r="H109" t="str">
         <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I109" t="str">
-        <f t="shared" si="92"/>
-        <v>2005</v>
+        <f t="shared" si="100"/>
+        <v>2002</v>
       </c>
       <c r="J109" t="str">
         <f t="shared" si="62"/>
-        <v>10.1016/j.jhevol.2004.10.003</v>
+        <v>10.1038/nn814</v>
       </c>
       <c r="K109" t="str">
         <f t="shared" si="63"/>
-        <v>Sherwood_etal_2005_Table1</v>
+        <v>Semendeferi_etal_2002_Table1</v>
       </c>
       <c r="L109" t="str">
         <f t="shared" si="64"/>
-        <v>10.1016%2Fj.jhevol.2004.10.003_Table1</v>
+        <v>10.1038%2Fnn814_Table1</v>
       </c>
       <c r="M109" t="str">
         <f t="array" ref="M109">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L109, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="V109" s="2" t="s">
-        <v>41</v>
+        <v>518</v>
       </c>
       <c r="Y109" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="Z109" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA109" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AB109" s="2" t="s">
         <v>71</v>
@@ -10931,11 +10915,8 @@
       <c r="AC109" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AD109" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="AK109" s="2" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AL109" s="2" t="s">
         <v>58</v>
@@ -10944,26 +10925,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110" spans="1:39">
+    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="E110" t="str">
-        <f t="shared" si="89"/>
-        <v>2</v>
+        <f t="shared" si="97"/>
+        <v>3</v>
       </c>
       <c r="F110" t="str">
-        <f t="shared" si="90"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="98"/>
+        <v>Sherwood_etal_2005</v>
       </c>
       <c r="G110" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Sherwood</v>
       </c>
       <c r="H110" t="str">
@@ -10971,273 +10949,279 @@
         <v>etal</v>
       </c>
       <c r="I110" t="str">
-        <f t="shared" si="92"/>
-        <v>2004</v>
+        <f t="shared" si="100"/>
+        <v>2005</v>
       </c>
       <c r="J110" t="str">
         <f t="shared" si="62"/>
-        <v>10.1159/000075672</v>
+        <v>10.1016/j.jhevol.2004.10.003</v>
       </c>
       <c r="K110" t="str">
         <f t="shared" si="63"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <v>Sherwood_etal_2005_Table1</v>
       </c>
       <c r="L110" t="str">
         <f t="shared" si="64"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>10.1016%2Fj.jhevol.2004.10.003_Table1</v>
       </c>
       <c r="M110" t="str">
         <f t="array" ref="M110">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L110, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="T110" s="2" t="str">
-        <f>IF(S110="N", R110, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U110" s="2" t="s">
-        <v>54</v>
+        <v>521</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>526</v>
+        <v>41</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="Z110" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="AA110" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="AB110" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AC110" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG110" s="2" t="s">
-        <v>160</v>
+        <v>98</v>
+      </c>
+      <c r="AD110" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="AK110" s="2" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="AL110" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM110" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="111" spans="1:39">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>524</v>
+      </c>
       <c r="D111" s="2" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="E111" t="str">
-        <f t="shared" ref="E111" si="93">RIGHT(A111,1)</f>
-        <v>8</v>
+        <f t="shared" si="97"/>
+        <v>2</v>
       </c>
       <c r="F111" t="str">
-        <f t="shared" ref="F111" si="94">G111 &amp; IF(H111&lt;&gt;"", "_" &amp; H111, "_") &amp; IF(I111&lt;&gt;"", "_" &amp; I111, "_") &amp; IF(B111&lt;&gt;"", "_" &amp; B111, "")</f>
-        <v>Sherwood_etal_2004</v>
+        <f t="shared" si="98"/>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G111" t="str">
-        <f t="shared" ref="G111" si="95">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A111,","), "-", ""), " ", "")</f>
+        <f t="shared" si="99"/>
         <v>Sherwood</v>
       </c>
       <c r="H111" t="str">
-        <f t="shared" ref="H111" si="96">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A111," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A111)-LEN(SUBSTITUTE(A111,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I111" t="str">
-        <f t="shared" ref="I111" si="97">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A111, "("), ")")</f>
+        <f t="shared" si="100"/>
         <v>2004</v>
       </c>
       <c r="J111" t="str">
-        <f t="shared" ref="J111" si="98">IF(C111&lt;&gt;"", C111, IF(C111="", _xlfn.TEXTAFTER(A111,"https://doi.org/"), C111))</f>
-        <v>10.1002/ajp.20048</v>
+        <f t="shared" si="62"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="K111" t="str">
-        <f t="shared" ref="K111" si="99">TRIM(_xlfn.TEXTJOIN("_",FALSE,F111,(SUBSTITUTE(SUBSTITUTE(D111," ",""), "_", ""))))</f>
-        <v>Sherwood_etal_2004_TABLEI</v>
+        <f t="shared" si="63"/>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="L111" t="str">
-        <f t="shared" ref="L111" si="100">IF(ISBLANK(C111),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J111, SUBSTITUTE(D111,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C111, SUBSTITUTE(D111,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1002%2Fajp.20048_TABLEI</v>
+        <f t="shared" si="64"/>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M111" t="str">
         <f t="array" ref="M111">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L111, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q111" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="T111" s="2" t="str">
+        <f>IF(S111="N", R111, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U111" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="Y111" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="Z111" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB111" s="2" t="s">
-        <v>482</v>
+        <v>71</v>
       </c>
       <c r="AC111" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD111" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="112" spans="1:39">
+        <v>72</v>
+      </c>
+      <c r="AG111" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK111" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL111" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM111" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>524</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="B112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>375</v>
+        <v>530</v>
       </c>
       <c r="E112" t="str">
-        <f t="shared" si="89"/>
-        <v>2</v>
+        <f t="shared" ref="E112" si="101">RIGHT(A112,1)</f>
+        <v>8</v>
       </c>
       <c r="F112" t="str">
-        <f t="shared" si="90"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" ref="F112" si="102">G112 &amp; IF(H112&lt;&gt;"", "_" &amp; H112, "_") &amp; IF(I112&lt;&gt;"", "_" &amp; I112, "_") &amp; IF(B112&lt;&gt;"", "_" &amp; B112, "")</f>
+        <v>Sherwood_etal_2004</v>
       </c>
       <c r="G112" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="G112" si="103">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A112,","), "-", ""), " ", "")</f>
         <v>Sherwood</v>
       </c>
       <c r="H112" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="H112" si="104">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A112," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A112)-LEN(SUBSTITUTE(A112,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
         <v>etal</v>
       </c>
       <c r="I112" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="I112" si="105">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A112, "("), ")")</f>
         <v>2004</v>
       </c>
       <c r="J112" t="str">
-        <f t="shared" si="62"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" ref="J112" si="106">IF(C112&lt;&gt;"", C112, IF(C112="", _xlfn.TEXTAFTER(A112,"https://doi.org/"), C112))</f>
+        <v>10.1002/ajp.20048</v>
       </c>
       <c r="K112" t="str">
-        <f t="shared" si="63"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f t="shared" ref="K112" si="107">TRIM(_xlfn.TEXTJOIN("_",FALSE,F112,(SUBSTITUTE(SUBSTITUTE(D112," ",""), "_", ""))))</f>
+        <v>Sherwood_etal_2004_TABLEI</v>
       </c>
       <c r="L112" t="str">
-        <f t="shared" si="64"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <f t="shared" ref="L112" si="108">IF(ISBLANK(C112),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J112, SUBSTITUTE(D112,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C112, SUBSTITUTE(D112,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2Fajp.20048_TABLEI</v>
       </c>
       <c r="M112" t="str">
         <f t="array" ref="M112">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L112, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="P112" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q112" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="T112" s="2" t="str">
-        <f>IF(S112="N", R112, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U112" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V112" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="Y112" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Z112" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB112" s="2" t="s">
-        <v>71</v>
+        <v>482</v>
       </c>
       <c r="AC112" s="2" t="s">
         <v>98</v>
       </c>
       <c r="AD112" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AG112" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="AK112" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL112" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AM112" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="113" spans="1:39">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>535</v>
+        <v>523</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>536</v>
+        <v>375</v>
       </c>
       <c r="E113" t="str">
-        <f t="shared" si="89"/>
-        <v>9</v>
+        <f t="shared" si="97"/>
+        <v>2</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2013</v>
+        <f t="shared" si="98"/>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G113" t="str">
-        <f t="shared" si="91"/>
-        <v>Smaers</v>
+        <f t="shared" si="99"/>
+        <v>Sherwood</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="92"/>
-        <v>2013</v>
+        <f t="shared" si="100"/>
+        <v>2004</v>
       </c>
       <c r="J113" t="str">
-        <f t="shared" ref="J113:J138" si="101">IF(C113&lt;&gt;"", C113, IF(C113="", _xlfn.TEXTAFTER(A113,"https://doi.org/"), C113))</f>
-        <v>10.1098/rspb.2013.0269</v>
+        <f t="shared" si="62"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="K113" t="str">
-        <f t="shared" ref="K113:K138" si="102">TRIM(_xlfn.TEXTJOIN("_",FALSE,F113,(SUBSTITUTE(SUBSTITUTE(D113," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2013_Supplement</v>
+        <f t="shared" si="63"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="L113" t="str">
-        <f t="shared" ref="L113:L138" si="103">IF(ISBLANK(C113),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J113, SUBSTITUTE(D113,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C113, SUBSTITUTE(D113,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1098%2Frspb.2013.0269_Supplement</v>
+        <f t="shared" si="64"/>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M113" t="str">
         <f t="array" ref="M113">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L113, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="T113" s="2" t="str">
+        <f>IF(S113="N", R113, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>538</v>
+        <v>527</v>
+      </c>
+      <c r="Z113" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="AB113" s="2" t="s">
         <v>71</v>
@@ -11245,33 +11229,42 @@
       <c r="AC113" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="AD113" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="AG113" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="AK113" s="2" t="s">
-        <v>539</v>
+        <v>103</v>
       </c>
       <c r="AL113" s="2" t="s">
-        <v>343</v>
+        <v>58</v>
       </c>
       <c r="AM113" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="114" spans="1:39">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="E114" t="str">
-        <f t="shared" si="89"/>
-        <v>0</v>
+        <f t="shared" si="97"/>
+        <v>9</v>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2017</v>
+        <f t="shared" si="98"/>
+        <v>Smaers_etal_2013</v>
       </c>
       <c r="G114" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Smaers</v>
       </c>
       <c r="H114" t="str">
@@ -11279,39 +11272,30 @@
         <v>etal</v>
       </c>
       <c r="I114" t="str">
-        <f t="shared" si="92"/>
-        <v>2017</v>
+        <f t="shared" si="100"/>
+        <v>2013</v>
       </c>
       <c r="J114" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1016/j.cub.2017.01.020</v>
+        <f t="shared" ref="J114:J139" si="109">IF(C114&lt;&gt;"", C114, IF(C114="", _xlfn.TEXTAFTER(A114,"https://doi.org/"), C114))</f>
+        <v>10.1098/rspb.2013.0269</v>
       </c>
       <c r="K114" t="str">
-        <f t="shared" si="102"/>
-        <v>Smaers_etal_2017_Table1</v>
+        <f t="shared" ref="K114:K139" si="110">TRIM(_xlfn.TEXTJOIN("_",FALSE,F114,(SUBSTITUTE(SUBSTITUTE(D114," ",""), "_", ""))))</f>
+        <v>Smaers_etal_2013_Supplement</v>
       </c>
       <c r="L114" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1016%2Fj.cub.2017.01.020_Table1</v>
+        <f t="shared" ref="L114:L139" si="111">IF(ISBLANK(C114),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J114, SUBSTITUTE(D114,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C114, SUBSTITUTE(D114,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1098%2Frspb.2013.0269_Supplement</v>
       </c>
       <c r="M114" t="str">
         <f t="array" ref="M114">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L114, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="V114" s="2" t="s">
-        <v>41</v>
+        <v>537</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="Z114" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="AA114" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="AB114" s="2" t="s">
         <v>71</v>
@@ -11319,14 +11303,8 @@
       <c r="AC114" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AD114" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AH114" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="AK114" s="2" t="s">
-        <v>103</v>
+        <v>539</v>
       </c>
       <c r="AL114" s="2" t="s">
         <v>343</v>
@@ -11335,23 +11313,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="115" spans="1:39">
+    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="E115" t="str">
-        <f t="shared" si="89"/>
-        <v>1</v>
+        <f t="shared" si="97"/>
+        <v>0</v>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="98"/>
+        <v>Smaers_etal_2017</v>
       </c>
       <c r="G115" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Smaers</v>
       </c>
       <c r="H115" t="str">
@@ -11359,30 +11337,39 @@
         <v>etal</v>
       </c>
       <c r="I115" t="str">
-        <f t="shared" si="92"/>
-        <v>2011</v>
+        <f t="shared" si="100"/>
+        <v>2017</v>
       </c>
       <c r="J115" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="109"/>
+        <v>10.1016/j.cub.2017.01.020</v>
       </c>
       <c r="K115" t="str">
-        <f t="shared" si="102"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
+        <f t="shared" si="110"/>
+        <v>Smaers_etal_2017_Table1</v>
       </c>
       <c r="L115" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <f t="shared" si="111"/>
+        <v>10.1016%2Fj.cub.2017.01.020_Table1</v>
       </c>
       <c r="M115" t="str">
         <f t="array" ref="M115">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L115, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="Q115" s="2" t="s">
-        <v>114</v>
+        <v>notfound</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
+      </c>
+      <c r="Z115" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="AA115" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="AB115" s="2" t="s">
         <v>71</v>
@@ -11393,6 +11380,9 @@
       <c r="AD115" s="2" t="s">
         <v>484</v>
       </c>
+      <c r="AH115" s="2" t="s">
+        <v>545</v>
+      </c>
       <c r="AK115" s="2" t="s">
         <v>103</v>
       </c>
@@ -11403,23 +11393,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="1:39">
+    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>546</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E116" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="G116" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Smaers</v>
       </c>
       <c r="H116" t="str">
@@ -11427,24 +11417,24 @@
         <v>etal</v>
       </c>
       <c r="I116" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>2011</v>
       </c>
       <c r="J116" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="K116" t="str">
-        <f t="shared" si="102"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" si="110"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L116" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <f t="shared" si="111"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M116" t="str">
         <f t="array" ref="M116">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L116, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q116" s="2" t="s">
         <v>114</v>
@@ -11471,26 +11461,23 @@
         <v>74</v>
       </c>
     </row>
-    <row r="117" spans="1:39">
+    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E117" t="str">
-        <f t="shared" si="89"/>
-        <v>6</v>
+        <f t="shared" si="97"/>
+        <v>1</v>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2018</v>
+        <f t="shared" si="98"/>
+        <v>Smaers_etal_2011</v>
       </c>
       <c r="G117" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Smaers</v>
       </c>
       <c r="H117" t="str">
@@ -11498,30 +11485,30 @@
         <v>etal</v>
       </c>
       <c r="I117" t="str">
-        <f t="shared" si="92"/>
-        <v>2018</v>
+        <f t="shared" si="100"/>
+        <v>2011</v>
       </c>
       <c r="J117" t="str">
-        <f t="shared" si="101"/>
-        <v>10.7554/eLife.35696</v>
+        <f t="shared" si="109"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="K117" t="str">
-        <f t="shared" si="102"/>
-        <v>Smaers_etal_2018_Figure2-data1</v>
+        <f t="shared" si="110"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L117" t="str">
-        <f t="shared" si="103"/>
-        <v>10.7554%2FeLife.35696_Figure2-data1</v>
+        <f t="shared" si="111"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M117" t="str">
         <f t="array" ref="M117">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L117, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N117" s="2" t="s">
-        <v>553</v>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="Q117" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="Y117" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="AB117" s="2" t="s">
         <v>71</v>
@@ -11533,7 +11520,7 @@
         <v>484</v>
       </c>
       <c r="AK117" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="AL117" s="2" t="s">
         <v>343</v>
@@ -11542,54 +11529,57 @@
         <v>74</v>
       </c>
     </row>
-    <row r="118" spans="1:39">
+    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>47</v>
+        <v>552</v>
       </c>
       <c r="E118" t="str">
-        <f t="shared" si="89"/>
-        <v>s</v>
+        <f t="shared" si="97"/>
+        <v>6</v>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
+        <f t="shared" si="98"/>
+        <v>Smaers_etal_2018</v>
       </c>
       <c r="G118" t="str">
-        <f t="shared" si="91"/>
-        <v>Stephan</v>
+        <f t="shared" si="99"/>
+        <v>Smaers</v>
       </c>
       <c r="H118" t="str">
         <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I118" t="str">
-        <f t="shared" si="92"/>
-        <v>1970</v>
+        <f t="shared" si="100"/>
+        <v>2018</v>
       </c>
       <c r="J118" t="str">
-        <f t="shared" si="101"/>
-        <v>ISBN: 0390672505</v>
+        <f t="shared" si="109"/>
+        <v>10.7554/eLife.35696</v>
       </c>
       <c r="K118" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1970_TABLE1</v>
+        <f t="shared" si="110"/>
+        <v>Smaers_etal_2018_Figure2-data1</v>
       </c>
       <c r="L118" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A0390672505_TABLE1</v>
+        <f t="shared" si="111"/>
+        <v>10.7554%2FeLife.35696_Figure2-data1</v>
       </c>
       <c r="M118" t="str">
         <f t="array" ref="M118">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L118, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
+      </c>
+      <c r="Y118" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="AB118" s="2" t="s">
         <v>71</v>
@@ -11598,19 +11588,19 @@
         <v>98</v>
       </c>
       <c r="AD118" s="2" t="s">
-        <v>85</v>
+        <v>484</v>
       </c>
       <c r="AK118" s="2" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="AL118" s="2" t="s">
-        <v>58</v>
+        <v>343</v>
       </c>
       <c r="AM118" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="119" spans="1:39">
+    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>555</v>
       </c>
@@ -11618,18 +11608,18 @@
         <v>556</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>286</v>
+        <v>47</v>
       </c>
       <c r="E119" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>s</v>
       </c>
       <c r="F119" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G119" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H119" t="str">
@@ -11637,27 +11627,27 @@
         <v>etal</v>
       </c>
       <c r="I119" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>1970</v>
       </c>
       <c r="J119" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>ISBN: 0390672505</v>
       </c>
       <c r="K119" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1970_TABLE2</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1970_TABLE1</v>
       </c>
       <c r="L119" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A0390672505_TABLE2</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A0390672505_TABLE1</v>
       </c>
       <c r="M119" t="str">
         <f t="array" ref="M119">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L119, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AB119" s="2" t="s">
         <v>71</v>
@@ -11678,7 +11668,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="120" spans="1:39">
+    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>555</v>
       </c>
@@ -11686,18 +11676,18 @@
         <v>556</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>559</v>
+        <v>286</v>
       </c>
       <c r="E120" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>s</v>
       </c>
       <c r="F120" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G120" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H120" t="str">
@@ -11705,27 +11695,27 @@
         <v>etal</v>
       </c>
       <c r="I120" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>1970</v>
       </c>
       <c r="J120" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>ISBN: 0390672505</v>
       </c>
       <c r="K120" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1970_TABLE3</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1970_TABLE2</v>
       </c>
       <c r="L120" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A0390672505_TABLE3</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A0390672505_TABLE2</v>
       </c>
       <c r="M120" t="str">
         <f t="array" ref="M120">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L120, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AB120" s="2" t="s">
         <v>71</v>
@@ -11746,7 +11736,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="121" spans="1:39">
+    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>555</v>
       </c>
@@ -11754,18 +11744,18 @@
         <v>556</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E121" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>s</v>
       </c>
       <c r="F121" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G121" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H121" t="str">
@@ -11773,27 +11763,27 @@
         <v>etal</v>
       </c>
       <c r="I121" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>1970</v>
       </c>
       <c r="J121" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>ISBN: 0390672505</v>
       </c>
       <c r="K121" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1970_TABLE4</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1970_TABLE3</v>
       </c>
       <c r="L121" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A0390672505_TABLE4</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A0390672505_TABLE3</v>
       </c>
       <c r="M121" t="str">
         <f t="array" ref="M121">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L121, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AB121" s="2" t="s">
         <v>71</v>
@@ -11814,7 +11804,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="122" spans="1:39">
+    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>555</v>
       </c>
@@ -11822,18 +11812,18 @@
         <v>556</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E122" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>s</v>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G122" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H122" t="str">
@@ -11841,27 +11831,27 @@
         <v>etal</v>
       </c>
       <c r="I122" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>1970</v>
       </c>
       <c r="J122" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>ISBN: 0390672505</v>
       </c>
       <c r="K122" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1970_TABLE5</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1970_TABLE4</v>
       </c>
       <c r="L122" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A0390672505_TABLE5</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A0390672505_TABLE4</v>
       </c>
       <c r="M122" t="str">
         <f t="array" ref="M122">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L122, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AB122" s="2" t="s">
         <v>71</v>
@@ -11882,7 +11872,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:39">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>555</v>
       </c>
@@ -11890,46 +11880,46 @@
         <v>556</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E123" t="str">
-        <f t="shared" ref="E123" si="104">RIGHT(A123,1)</f>
+        <f t="shared" si="97"/>
         <v>s</v>
       </c>
       <c r="F123" t="str">
-        <f t="shared" ref="F123" si="105">G123 &amp; IF(H123&lt;&gt;"", "_" &amp; H123, "_") &amp; IF(I123&lt;&gt;"", "_" &amp; I123, "_") &amp; IF(B123&lt;&gt;"", "_" &amp; B123, "")</f>
+        <f t="shared" si="98"/>
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G123" t="str">
-        <f t="shared" ref="G123" si="106">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A123,","), "-", ""), " ", "")</f>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H123" t="str">
-        <f t="shared" ref="H123" si="107">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A123," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A123)-LEN(SUBSTITUTE(A123,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I123" t="str">
-        <f t="shared" ref="I123" si="108">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A123, "("), ")")</f>
+        <f t="shared" si="100"/>
         <v>1970</v>
       </c>
       <c r="J123" t="str">
-        <f t="shared" ref="J123" si="109">IF(C123&lt;&gt;"", C123, IF(C123="", _xlfn.TEXTAFTER(A123,"https://doi.org/"), C123))</f>
+        <f t="shared" si="109"/>
         <v>ISBN: 0390672505</v>
       </c>
       <c r="K123" t="str">
-        <f t="shared" ref="K123" si="110">TRIM(_xlfn.TEXTJOIN("_",FALSE,F123,(SUBSTITUTE(SUBSTITUTE(D123," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1970_TABLE6</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1970_TABLE5</v>
       </c>
       <c r="L123" t="str">
-        <f t="shared" ref="L123" si="111">IF(ISBLANK(C123),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J123, SUBSTITUTE(D123,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C123, SUBSTITUTE(D123,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>ISBN%3A0390672505_TABLE6</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A0390672505_TABLE5</v>
       </c>
       <c r="M123" t="str">
         <f t="array" ref="M123">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L123, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AB123" s="2" t="s">
         <v>71</v>
@@ -11950,7 +11940,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:39">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>555</v>
       </c>
@@ -11958,7 +11948,7 @@
         <v>556</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E124" t="str">
         <f t="shared" ref="E124" si="112">RIGHT(A124,1)</f>
@@ -11986,19 +11976,18 @@
       </c>
       <c r="K124" t="str">
         <f t="shared" ref="K124" si="118">TRIM(_xlfn.TEXTJOIN("_",FALSE,F124,(SUBSTITUTE(SUBSTITUTE(D124," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1970_Tables1-6</v>
+        <v>Stephan_etal_1970_TABLE6</v>
       </c>
       <c r="L124" t="str">
         <f t="shared" ref="L124" si="119">IF(ISBLANK(C124),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J124, SUBSTITUTE(D124,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C124, SUBSTITUTE(D124,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>ISBN%3A0390672505_Tables1-6</v>
+        <v>ISBN%3A0390672505_TABLE6</v>
       </c>
       <c r="M124" t="str">
         <f t="array" ref="M124">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L124, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N124" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("; ",,N118,N119,N120,N121,N122,N123)</f>
-        <v>TABLE 1 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Insectivores; TABLE 2 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Prosimians; TABLE 3 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Simians; TABLE 4 Volume of the various components of the telencephalon in Insectivores (in mm3); TABLE 5 Volume of the various components of the telencephalon in Prosimians (in mm3); TABLE 6 Volume of the various components of the telencephalon in Simians (in mm3)</v>
+      <c r="N124" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="AB124" s="2" t="s">
         <v>71</v>
@@ -12019,69 +12008,55 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:39">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="E125" t="str">
-        <f t="shared" si="89"/>
-        <v>3</v>
+        <f t="shared" ref="E125" si="120">RIGHT(A125,1)</f>
+        <v>s</v>
       </c>
       <c r="F125" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1982</v>
+        <f t="shared" ref="F125" si="121">G125 &amp; IF(H125&lt;&gt;"", "_" &amp; H125, "_") &amp; IF(I125&lt;&gt;"", "_" &amp; I125, "_") &amp; IF(B125&lt;&gt;"", "_" &amp; B125, "")</f>
+        <v>Stephan_etal_1970</v>
       </c>
       <c r="G125" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="G125" si="122">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A125,","), "-", ""), " ", "")</f>
         <v>Stephan</v>
       </c>
       <c r="H125" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="H125" si="123">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A125," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A125)-LEN(SUBSTITUTE(A125,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
         <v>etal</v>
       </c>
       <c r="I125" t="str">
-        <f t="shared" si="92"/>
-        <v>1982</v>
+        <f t="shared" ref="I125" si="124">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A125, "("), ")")</f>
+        <v>1970</v>
       </c>
       <c r="J125" t="str">
-        <f t="shared" si="101"/>
-        <v>PMID:7161483</v>
+        <f t="shared" ref="J125" si="125">IF(C125&lt;&gt;"", C125, IF(C125="", _xlfn.TEXTAFTER(A125,"https://doi.org/"), C125))</f>
+        <v>ISBN: 0390672505</v>
       </c>
       <c r="K125" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1982_Table1</v>
+        <f t="shared" ref="K125" si="126">TRIM(_xlfn.TEXTJOIN("_",FALSE,F125,(SUBSTITUTE(SUBSTITUTE(D125," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1970_Tables1-6</v>
       </c>
       <c r="L125" t="str">
-        <f t="shared" si="103"/>
-        <v>PMID%3A7161483_Table1</v>
+        <f t="shared" ref="L125" si="127">IF(ISBLANK(C125),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J125, SUBSTITUTE(D125,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C125, SUBSTITUTE(D125,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>ISBN%3A0390672505_Tables1-6</v>
       </c>
       <c r="M125" t="str">
         <f t="array" ref="M125">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L125, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>PMID%3A7161483_Table1.tsv</v>
-      </c>
-      <c r="N125" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="V125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W125" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y125" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="Z125" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA125" s="2" t="s">
-        <v>85</v>
+        <v>notfound</v>
+      </c>
+      <c r="N125" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("; ",,N119,N120,N121,N122,N123,N124)</f>
+        <v>TABLE 1 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Insectivores; TABLE 2 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Prosimians; TABLE 3 Data on body and brain weight (in g and mg) and volume of the fundemental brain sections (in mm3) in Simians; TABLE 4 Volume of the various components of the telencephalon in Insectivores (in mm3); TABLE 5 Volume of the various components of the telencephalon in Prosimians (in mm3); TABLE 6 Volume of the various components of the telencephalon in Simians (in mm3)</v>
       </c>
       <c r="AB125" s="2" t="s">
         <v>71</v>
@@ -12102,26 +12077,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:39">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E126" t="str">
-        <f t="shared" si="89"/>
-        <v>4</v>
+        <f t="shared" si="97"/>
+        <v>3</v>
       </c>
       <c r="F126" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1984</v>
+        <f t="shared" si="98"/>
+        <v>Stephan_etal_1982</v>
       </c>
       <c r="G126" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H126" t="str">
@@ -12129,27 +12104,27 @@
         <v>etal</v>
       </c>
       <c r="I126" t="str">
-        <f t="shared" si="92"/>
-        <v>1984</v>
+        <f t="shared" si="100"/>
+        <v>1982</v>
       </c>
       <c r="J126" t="str">
-        <f t="shared" si="101"/>
-        <v>PMID:6481154</v>
+        <f t="shared" si="109"/>
+        <v>PMID:7161483</v>
       </c>
       <c r="K126" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1984_Table1</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1982_Table1</v>
       </c>
       <c r="L126" t="str">
-        <f t="shared" si="103"/>
-        <v>PMID%3A6481154_Table1</v>
+        <f t="shared" si="111"/>
+        <v>PMID%3A7161483_Table1</v>
       </c>
       <c r="M126" t="str">
         <f t="array" ref="M126">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L126, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>PMID%3A6481154_Table1.tsv</v>
+        <v>PMID%3A7161483_Table1.tsv</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="V126" s="2" t="s">
         <v>41</v>
@@ -12158,7 +12133,7 @@
         <v>89</v>
       </c>
       <c r="Y126" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="Z126" s="2" t="s">
         <v>58</v>
@@ -12185,26 +12160,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:39">
+    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E127" t="str">
-        <f t="shared" si="89"/>
-        <v>5</v>
+        <f t="shared" si="97"/>
+        <v>4</v>
       </c>
       <c r="F127" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1987</v>
+        <f t="shared" si="98"/>
+        <v>Stephan_etal_1984</v>
       </c>
       <c r="G127" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H127" t="str">
@@ -12212,27 +12187,27 @@
         <v>etal</v>
       </c>
       <c r="I127" t="str">
-        <f t="shared" si="92"/>
-        <v>1987</v>
+        <f t="shared" si="100"/>
+        <v>1984</v>
       </c>
       <c r="J127" t="str">
-        <f t="shared" si="101"/>
-        <v>PMID:3693895</v>
+        <f t="shared" si="109"/>
+        <v>PMID:6481154</v>
       </c>
       <c r="K127" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1987_Table1</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1984_Table1</v>
       </c>
       <c r="L127" t="str">
-        <f t="shared" si="103"/>
-        <v>PMID%3A3693895_Table1</v>
+        <f t="shared" si="111"/>
+        <v>PMID%3A6481154_Table1</v>
       </c>
       <c r="M127" t="str">
         <f t="array" ref="M127">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L127, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>PMID%3A3693895_Table1.tsv</v>
+        <v>PMID%3A6481154_Table1.tsv</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="V127" s="2" t="s">
         <v>41</v>
@@ -12241,7 +12216,7 @@
         <v>89</v>
       </c>
       <c r="Y127" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="Z127" s="2" t="s">
         <v>58</v>
@@ -12268,23 +12243,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:39">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>577</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E128" t="str">
-        <f t="shared" si="89"/>
-        <v>3</v>
+        <f t="shared" si="97"/>
+        <v>5</v>
       </c>
       <c r="F128" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1981</v>
+        <f t="shared" si="98"/>
+        <v>Stephan_etal_1987</v>
       </c>
       <c r="G128" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Stephan</v>
       </c>
       <c r="H128" t="str">
@@ -12292,33 +12270,36 @@
         <v>etal</v>
       </c>
       <c r="I128" t="str">
-        <f t="shared" si="92"/>
-        <v>1981</v>
+        <f t="shared" si="100"/>
+        <v>1987</v>
       </c>
       <c r="J128" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1159/000155963</v>
+        <f t="shared" si="109"/>
+        <v>PMID:3693895</v>
       </c>
       <c r="K128" t="str">
-        <f t="shared" si="102"/>
-        <v>Stephan_etal_1981_Table1</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1987_Table1</v>
       </c>
       <c r="L128" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1159%2F000155963_Table1</v>
+        <f t="shared" si="111"/>
+        <v>PMID%3A3693895_Table1</v>
       </c>
       <c r="M128" t="str">
         <f t="array" ref="M128">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L128, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000155963_Table1.tsv</v>
+        <v>PMID%3A3693895_Table1.tsv</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="V128" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="W128" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="Y128" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="Z128" s="2" t="s">
         <v>58</v>
@@ -12345,57 +12326,63 @@
         <v>74</v>
       </c>
     </row>
-    <row r="129" spans="1:39">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="E129" t="str">
-        <f t="shared" ref="E129:E130" si="120">RIGHT(A129,1)</f>
-        <v>8</v>
+        <f t="shared" si="97"/>
+        <v>3</v>
       </c>
       <c r="F129" t="str">
-        <f t="shared" ref="F129:F130" si="121">G129 &amp; IF(H129&lt;&gt;"", "_" &amp; H129, "_") &amp; IF(I129&lt;&gt;"", "_" &amp; I129, "_") &amp; IF(B129&lt;&gt;"", "_" &amp; B129, "")</f>
-        <v>Stimpson_etal_2015</v>
+        <f t="shared" si="98"/>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G129" t="str">
-        <f t="shared" ref="G129:G130" si="122">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A129,","), "-", ""), " ", "")</f>
-        <v>Stimpson</v>
+        <f t="shared" si="99"/>
+        <v>Stephan</v>
       </c>
       <c r="H129" t="str">
-        <f t="shared" ref="H129:H130" si="123">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A129," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A129)-LEN(SUBSTITUTE(A129,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
+        <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I129" t="str">
-        <f t="shared" ref="I129:I130" si="124">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A129, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" si="100"/>
+        <v>1981</v>
       </c>
       <c r="J129" t="str">
-        <f t="shared" ref="J129:J130" si="125">IF(C129&lt;&gt;"", C129, IF(C129="", _xlfn.TEXTAFTER(A129,"https://doi.org/"), C129))</f>
-        <v>10.1093/scan/nsv128</v>
+        <f t="shared" si="109"/>
+        <v>10.1159/000155963</v>
       </c>
       <c r="K129" t="str">
-        <f t="shared" ref="K129:K130" si="126">TRIM(_xlfn.TEXTJOIN("_",FALSE,F129,(SUBSTITUTE(SUBSTITUTE(D129," ",""), "_", ""))))</f>
-        <v>Stimpson_etal_2015_TableS1</v>
+        <f t="shared" si="110"/>
+        <v>Stephan_etal_1981_Table1</v>
       </c>
       <c r="L129" t="str">
-        <f t="shared" ref="L129:L130" si="127">IF(ISBLANK(C129),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J129, SUBSTITUTE(D129,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C129, SUBSTITUTE(D129,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
+        <f t="shared" si="111"/>
+        <v>10.1159%2F000155963_Table1</v>
       </c>
       <c r="M129" t="str">
         <f t="array" ref="M129">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L129, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000155963_Table1.tsv</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="V129" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="Y129" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="Z129" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="AA129" s="2" t="s">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="AB129" s="2" t="s">
         <v>71</v>
@@ -12404,7 +12391,10 @@
         <v>98</v>
       </c>
       <c r="AD129" s="2" t="s">
-        <v>585</v>
+        <v>85</v>
+      </c>
+      <c r="AK129" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="AL129" s="2" t="s">
         <v>58</v>
@@ -12413,51 +12403,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="130" spans="1:39">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>583</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E130" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" ref="E130:E131" si="128">RIGHT(A130,1)</f>
         <v>8</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" ref="F130:F131" si="129">G130 &amp; IF(H130&lt;&gt;"", "_" &amp; H130, "_") &amp; IF(I130&lt;&gt;"", "_" &amp; I130, "_") &amp; IF(B130&lt;&gt;"", "_" &amp; B130, "")</f>
         <v>Stimpson_etal_2015</v>
       </c>
       <c r="G130" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" ref="G130:G131" si="130">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A130,","), "-", ""), " ", "")</f>
         <v>Stimpson</v>
       </c>
       <c r="H130" t="str">
-        <f t="shared" si="123"/>
+        <f t="shared" ref="H130:H131" si="131">_xlfn.LET(_xlpm.authorPart,_xlfn.TEXTBEFORE(A130," ("),IFERROR(IF(ISNUMBER(FIND("&amp;",_xlpm.authorPart)),IF(LEN(A130)-LEN(SUBSTITUTE(A130,",",""))&gt;=6,"etal",_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authorPart,"&amp; "),",")),""),""))</f>
         <v>etal</v>
       </c>
       <c r="I130" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" ref="I130:I131" si="132">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A130, "("), ")")</f>
         <v>2015</v>
       </c>
       <c r="J130" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" ref="J130:J131" si="133">IF(C130&lt;&gt;"", C130, IF(C130="", _xlfn.TEXTAFTER(A130,"https://doi.org/"), C130))</f>
         <v>10.1093/scan/nsv128</v>
       </c>
       <c r="K130" t="str">
-        <f t="shared" si="126"/>
-        <v>Stimpson_etal_2015_TableS2</v>
+        <f t="shared" ref="K130:K131" si="134">TRIM(_xlfn.TEXTJOIN("_",FALSE,F130,(SUBSTITUTE(SUBSTITUTE(D130," ",""), "_", ""))))</f>
+        <v>Stimpson_etal_2015_TableS1</v>
       </c>
       <c r="L130" t="str">
-        <f t="shared" si="127"/>
-        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
+        <f t="shared" ref="L130:L131" si="135">IF(ISBLANK(C130),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J130, SUBSTITUTE(D130,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C130, SUBSTITUTE(D130,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
       </c>
       <c r="M130" t="str">
         <f t="array" ref="M130">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L130, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="V130" s="2" t="s">
         <v>41</v>
@@ -12481,215 +12471,227 @@
         <v>74</v>
       </c>
     </row>
-    <row r="131" spans="1:39">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="E131" t="str">
-        <f t="shared" si="89"/>
-        <v>2</v>
+        <f t="shared" si="128"/>
+        <v>8</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="90"/>
-        <v>Turner_etal_2016</v>
+        <f t="shared" si="129"/>
+        <v>Stimpson_etal_2015</v>
       </c>
       <c r="G131" t="str">
-        <f t="shared" si="91"/>
-        <v>Turner</v>
+        <f t="shared" si="130"/>
+        <v>Stimpson</v>
       </c>
       <c r="H131" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="131"/>
         <v>etal</v>
       </c>
       <c r="I131" t="str">
-        <f t="shared" si="92"/>
-        <v>2016</v>
+        <f t="shared" si="132"/>
+        <v>2015</v>
       </c>
       <c r="J131" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1159/000446762</v>
+        <f t="shared" si="133"/>
+        <v>10.1093/scan/nsv128</v>
       </c>
       <c r="K131" t="str">
-        <f t="shared" si="102"/>
-        <v>Turner_etal_2016_Table1</v>
+        <f t="shared" si="134"/>
+        <v>Stimpson_etal_2015_TableS2</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <f t="shared" si="135"/>
+        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
       </c>
       <c r="M131" t="str">
         <f t="array" ref="M131">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L131, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="Y131" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="AK131" s="2" t="s">
-        <v>123</v>
+        <v>586</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA131" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AB131" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC131" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD131" s="2" t="s">
+        <v>585</v>
       </c>
       <c r="AL131" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM131" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="132" spans="1:39">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="E132" t="str">
-        <f t="shared" si="89"/>
-        <v>1</v>
+        <f t="shared" si="97"/>
+        <v>2</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" si="90"/>
-        <v>Wilman_etal_2014</v>
+        <f t="shared" si="98"/>
+        <v>Turner_etal_2016</v>
       </c>
       <c r="G132" t="str">
-        <f t="shared" si="91"/>
-        <v>Wilman</v>
+        <f t="shared" si="99"/>
+        <v>Turner</v>
       </c>
       <c r="H132" t="str">
         <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I132" t="str">
-        <f t="shared" si="92"/>
-        <v>2014</v>
+        <f t="shared" si="100"/>
+        <v>2016</v>
       </c>
       <c r="J132" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1890/13-1917.1</v>
+        <f t="shared" si="109"/>
+        <v>10.1159/000446762</v>
       </c>
       <c r="K132" t="str">
-        <f t="shared" si="102"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+        <f t="shared" si="110"/>
+        <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L132" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <f t="shared" si="111"/>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M132" t="str">
         <f t="array" ref="M132">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L132, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
+      <c r="N132" s="2" t="s">
+        <v>588</v>
+      </c>
       <c r="Y132" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AK132" s="2" t="s">
         <v>123</v>
       </c>
       <c r="AL132" s="2" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="AM132" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="133" spans="1:39">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E133" t="str">
-        <f t="shared" si="89"/>
-        <v>7</v>
+        <f t="shared" si="97"/>
+        <v>1</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="90"/>
-        <v>Wimberly_etal_2021</v>
+        <f t="shared" si="98"/>
+        <v>Wilman_etal_2014</v>
       </c>
       <c r="G133" t="str">
-        <f t="shared" si="91"/>
-        <v>Wimberly</v>
+        <f t="shared" si="99"/>
+        <v>Wilman</v>
       </c>
       <c r="H133" t="str">
         <f t="shared" si="72"/>
         <v>etal</v>
       </c>
       <c r="I133" t="str">
-        <f t="shared" si="92"/>
-        <v>2021</v>
+        <f t="shared" si="100"/>
+        <v>2014</v>
       </c>
       <c r="J133" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1098/rspb.2021.0937</v>
+        <f t="shared" si="109"/>
+        <v>10.1890/13-1917.1</v>
       </c>
       <c r="K133" t="str">
-        <f t="shared" si="102"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
+        <f t="shared" si="110"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L133" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <f t="shared" si="111"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M133" t="str">
         <f t="array" ref="M133">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L133, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P133" s="2" t="s">
-        <v>317</v>
+      <c r="Y133" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="AK133" s="2" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="AL133" s="2" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AM133" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="134" spans="1:39">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E134" t="str">
-        <f t="shared" si="89"/>
-        <v>5</v>
+        <f t="shared" si="97"/>
+        <v>7</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="90"/>
-        <v>Winkler_Bryant_2021</v>
+        <f t="shared" si="98"/>
+        <v>Wimberly_etal_2021</v>
       </c>
       <c r="G134" t="str">
-        <f t="shared" si="91"/>
-        <v>Winkler</v>
+        <f t="shared" si="99"/>
+        <v>Wimberly</v>
       </c>
       <c r="H134" t="str">
         <f t="shared" si="72"/>
-        <v>Bryant</v>
+        <v>etal</v>
       </c>
       <c r="I134" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>2021</v>
       </c>
       <c r="J134" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1080/09524622.2021.1905065</v>
+        <f t="shared" si="109"/>
+        <v>10.1098/rspb.2021.0937</v>
       </c>
       <c r="K134" t="str">
-        <f t="shared" si="102"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <f t="shared" si="110"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L134" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <f t="shared" si="111"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M134" t="str">
         <f t="array" ref="M134">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L134, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
@@ -12698,80 +12700,61 @@
       <c r="P134" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="Q134" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="T134" s="2" t="str">
-        <f>IF(S134="N", R134, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U134" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V134" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="Y134" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="AG134" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="AK134" s="2" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="AL134" s="2" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AM134" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="135" spans="1:39">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="E135" t="str">
-        <f t="shared" si="89"/>
-        <v>0</v>
+        <f t="shared" si="97"/>
+        <v>5</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="90"/>
-        <v>Young_etal_2013</v>
+        <f t="shared" si="98"/>
+        <v>Winkler_Bryant_2021</v>
       </c>
       <c r="G135" t="str">
-        <f t="shared" si="91"/>
-        <v>Young</v>
+        <f t="shared" si="99"/>
+        <v>Winkler</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
+        <v>Bryant</v>
       </c>
       <c r="I135" t="str">
-        <f t="shared" si="92"/>
-        <v>2013</v>
+        <f t="shared" si="100"/>
+        <v>2021</v>
       </c>
       <c r="J135" t="str">
-        <f t="shared" si="101"/>
-        <v>10.3389/fncir.2013.00030</v>
+        <f t="shared" si="109"/>
+        <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="K135" t="str">
-        <f t="shared" si="102"/>
-        <v>Young_etal_2013_Table1</v>
+        <f t="shared" si="110"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="L135" t="str">
-        <f t="shared" si="103"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <f t="shared" si="111"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="M135" t="str">
         <f t="array" ref="M135">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L135, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>487</v>
+        <v>317</v>
       </c>
       <c r="Q135" s="2" t="s">
         <v>182</v>
@@ -12784,44 +12767,41 @@
         <v>54</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>41</v>
+        <v>598</v>
       </c>
       <c r="Y135" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="Z135" s="2" t="s">
-        <v>58</v>
+        <v>599</v>
       </c>
       <c r="AG135" s="2" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="AK135" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="AL135" s="2" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="AM135" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="136" spans="1:39">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E136" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>Young_etal_2013</v>
       </c>
       <c r="G136" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Young</v>
       </c>
       <c r="H136" t="str">
@@ -12829,192 +12809,270 @@
         <v>etal</v>
       </c>
       <c r="I136" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>2013</v>
       </c>
       <c r="J136" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1073/pnas.1318894110</v>
+        <f t="shared" si="109"/>
+        <v>10.3389/fncir.2013.00030</v>
       </c>
       <c r="K136" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="110"/>
         <v>Young_etal_2013_Table1</v>
       </c>
       <c r="L136" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1073%2Fpnas.1318894110_Table1</v>
+        <f t="shared" si="111"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="M136" t="str">
         <f t="array" ref="M136">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L136, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N136" s="2" t="s">
-        <v>605</v>
+      <c r="P136" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q136" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="T136" s="2" t="str">
+        <f>IF(S136="N", R136, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U136" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="V136" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y136" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="Z136" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AA136" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC136" s="2" t="s">
-        <v>60</v>
+      <c r="AG136" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="AK136" s="2" t="s">
-        <v>607</v>
+        <v>103</v>
       </c>
       <c r="AL136" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM136" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="137" spans="1:39">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="E137" t="str">
-        <f t="shared" si="89"/>
-        <v>s</v>
+        <f t="shared" si="97"/>
+        <v>0</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="90"/>
-        <v>Zilles_Rehkämper_1988</v>
+        <f t="shared" si="98"/>
+        <v>Young_etal_2013</v>
       </c>
       <c r="G137" t="str">
-        <f t="shared" si="91"/>
-        <v>Zilles</v>
+        <f t="shared" si="99"/>
+        <v>Young</v>
       </c>
       <c r="H137" t="str">
         <f t="shared" si="72"/>
-        <v>Rehkämper</v>
+        <v>etal</v>
       </c>
       <c r="I137" t="str">
-        <f t="shared" si="92"/>
-        <v>1988</v>
+        <f t="shared" si="100"/>
+        <v>2013</v>
       </c>
       <c r="J137" t="str">
-        <f t="shared" si="101"/>
-        <v>ISBN:9780195043716</v>
+        <f t="shared" si="109"/>
+        <v>10.1073/pnas.1318894110</v>
       </c>
       <c r="K137" t="str">
-        <f t="shared" si="102"/>
-        <v>Zilles_Rehkämper_1988_Table12-2</v>
+        <f t="shared" si="110"/>
+        <v>Young_etal_2013_Table1</v>
       </c>
       <c r="L137" t="str">
-        <f t="shared" si="103"/>
-        <v>ISBN%3A9780195043716_Table12-2</v>
+        <f t="shared" si="111"/>
+        <v>10.1073%2Fpnas.1318894110_Table1</v>
       </c>
       <c r="M137" t="str">
         <f t="array" ref="M137">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L137, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>ISBN%3A9780195043716_Table12-2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>612</v>
+        <v>605</v>
+      </c>
+      <c r="V137" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="Y137" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="AB137" s="2" t="s">
-        <v>71</v>
+        <v>606</v>
+      </c>
+      <c r="Z137" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA137" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="AC137" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD137" s="2" t="s">
-        <v>484</v>
+        <v>60</v>
       </c>
       <c r="AK137" s="2" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="AL137" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AM137" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="138" spans="1:39">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>610</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>206</v>
+        <v>611</v>
       </c>
       <c r="E138" t="str">
-        <f t="shared" si="89"/>
-        <v>6</v>
+        <f t="shared" si="97"/>
+        <v>s</v>
       </c>
       <c r="F138" t="str">
-        <f t="shared" si="90"/>
-        <v>Zilles_etal_2013</v>
+        <f t="shared" si="98"/>
+        <v>Zilles_Rehkämper_1988</v>
       </c>
       <c r="G138" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>Zilles</v>
       </c>
       <c r="H138" t="str">
         <f t="shared" si="72"/>
-        <v>etal</v>
+        <v>Rehkämper</v>
       </c>
       <c r="I138" t="str">
-        <f t="shared" si="92"/>
-        <v>2013</v>
+        <f t="shared" si="100"/>
+        <v>1988</v>
       </c>
       <c r="J138" t="str">
-        <f t="shared" si="101"/>
-        <v>10.1016/j.tins.2013.01.006</v>
+        <f t="shared" si="109"/>
+        <v>ISBN:9780195043716</v>
       </c>
       <c r="K138" t="str">
-        <f t="shared" si="102"/>
-        <v>Zilles_etal_2013_Table1</v>
+        <f t="shared" si="110"/>
+        <v>Zilles_Rehkämper_1988_Table12-2</v>
       </c>
       <c r="L138" t="str">
-        <f t="shared" si="103"/>
-        <v>10.1016%2Fj.tins.2013.01.006_Table1</v>
+        <f t="shared" si="111"/>
+        <v>ISBN%3A9780195043716_Table12-2</v>
       </c>
       <c r="M138" t="str">
         <f t="array" ref="M138">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L138, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>ISBN%3A9780195043716_Table12-2.tsv</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y138" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="AB138" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC138" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD138" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="AK138" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="AL138" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM138" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E139" t="str">
+        <f t="shared" si="97"/>
+        <v>6</v>
+      </c>
+      <c r="F139" t="str">
+        <f t="shared" si="98"/>
+        <v>Zilles_etal_2013</v>
+      </c>
+      <c r="G139" t="str">
+        <f t="shared" si="99"/>
+        <v>Zilles</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="72"/>
+        <v>etal</v>
+      </c>
+      <c r="I139" t="str">
+        <f t="shared" si="100"/>
+        <v>2013</v>
+      </c>
+      <c r="J139" t="str">
+        <f t="shared" si="109"/>
+        <v>10.1016/j.tins.2013.01.006</v>
+      </c>
+      <c r="K139" t="str">
+        <f t="shared" si="110"/>
+        <v>Zilles_etal_2013_Table1</v>
+      </c>
+      <c r="L139" t="str">
+        <f t="shared" si="111"/>
+        <v>10.1016%2Fj.tins.2013.01.006_Table1</v>
+      </c>
+      <c r="M139" t="str">
+        <f t="array" ref="M139">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L139, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N138" s="2" t="s">
+      <c r="N139" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="V138" s="2" t="s">
+      <c r="V139" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y138" s="2" t="s">
+      <c r="Y139" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="Z138" s="2" t="s">
+      <c r="Z139" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AA138" s="2" t="s">
+      <c r="AA139" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AC138" s="2" t="s">
+      <c r="AC139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AK138" s="2" t="s">
+      <c r="AK139" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="AL138" s="2" t="s">
+      <c r="AL139" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AM138" s="2" t="s">
+      <c r="AM139" s="2" t="s">
         <v>619</v>
       </c>
     </row>
@@ -13038,7 +13096,7 @@
     <hyperlink ref="X91" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="X92" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="X99" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="X104" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="X105" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13048,22 +13106,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>622</v>
       </c>
@@ -13071,7 +13129,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>624</v>
       </c>
@@ -13079,7 +13137,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>626</v>
       </c>
@@ -13087,7 +13145,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>628</v>
       </c>
@@ -13095,7 +13153,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>630</v>
       </c>
@@ -13103,7 +13161,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>632</v>
       </c>
@@ -13111,7 +13169,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>634</v>
       </c>
@@ -13119,7 +13177,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>636</v>
       </c>
@@ -13127,7 +13185,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>638</v>
       </c>
@@ -13135,7 +13193,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
+    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>640</v>
       </c>
@@ -13143,7 +13201,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>642</v>
       </c>
@@ -13157,23 +13215,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -13184,7 +13242,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -13195,7 +13253,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -13206,7 +13264,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -13226,429 +13284,429 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A85"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>737</v>
       </c>
@@ -13660,26 +13718,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -13934,14 +13972,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FCEA2-2E70-4137-9976-F808ECC70391}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A018EF-8115-45CE-8409-1523D815B368}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9618AA32-17A2-485D-95FE-DE6375A1049C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9618AA32-17A2-485D-95FE-DE6375A1049C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A018EF-8115-45CE-8409-1523D815B368}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FCEA2-2E70-4137-9976-F808ECC70391}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="821">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -2472,6 +2472,12 @@
   </si>
   <si>
     <t xml:space="preserve">Stimpson_etal_2015_viaDeCasien.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2015.1853_Table2.tsv</t>
   </si>
 </sst>
 </file>
@@ -13788,471 +13794,476 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>725</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>770</v>
+        <v>820</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
         <v>818</v>
       </c>
     </row>
@@ -14538,13 +14549,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2641573F-E2CB-4C6B-9A48-8FCFBB59064C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D933AD7-599E-4D90-BF28-22193BFD0FC5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A99FFF1F-0E1C-469D-8B91-E91C8C26DA65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ED6873D-DCE1-43D9-8E3D-53883F3F39AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65819F25-E4AD-4BDA-96B4-D15F15FC5142}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA97FCEF-395B-40A1-A315-662903557EE0}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -3295,6 +3295,11 @@
       <c r="P3" t="s">
         <v>48</v>
       </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>Ashwell</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3764,6 +3769,11 @@
       <c r="P10" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Barks</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -3881,6 +3891,11 @@
       <c r="P12" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>Barks</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="2" t="s">
@@ -4877,6 +4892,16 @@
       </c>
       <c r="P25" s="2" t="s">
         <v>138</v>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>Allman</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>AFIP</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -5703,8 +5728,10 @@
       <c r="V35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y35" s="2" t="s">
-        <v>209</v>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>Stephan, Zilles</t>
+        </is>
       </c>
       <c r="Z35" s="2" t="s">
         <v>210</v>
@@ -5890,8 +5917,10 @@
       <c r="V37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y37" s="2" t="s">
-        <v>209</v>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>Stephan, Zilles</t>
+        </is>
       </c>
       <c r="Z37" s="2" t="s">
         <v>210</v>
@@ -6897,6 +6926,11 @@
       <c r="Y49" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
       <c r="AF49" s="2" t="s">
         <v>70</v>
       </c>
@@ -7029,6 +7063,11 @@
       <c r="Y51" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
       <c r="AF51" s="2" t="s">
         <v>70</v>
       </c>
@@ -7109,6 +7148,11 @@
       <c r="Y52" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
       <c r="AF52" s="2" t="s">
         <v>70</v>
       </c>
@@ -7189,6 +7233,11 @@
       <c r="Y53" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
       <c r="AF53" s="2" t="s">
         <v>70</v>
       </c>
@@ -7268,6 +7317,11 @@
       </c>
       <c r="Y54" s="2" t="s">
         <v>80</v>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
       </c>
       <c r="AF54" s="2" t="s">
         <v>70</v>
@@ -11528,6 +11582,11 @@
       <c r="N111" s="2" t="s">
         <v>509</v>
       </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>Rilling</t>
+        </is>
+      </c>
       <c r="Z111" s="2" t="s">
         <v>477</v>
       </c>
@@ -11600,7 +11659,16 @@
       <c r="N112" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="Z112" s="3"/>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>Rilling</t>
+        </is>
+      </c>
+      <c r="Z112" s="3" t="inlineStr">
+        <is>
+          <t>Rilling</t>
+        </is>
+      </c>
       <c r="AF112" s="2"/>
       <c r="AG112" s="2"/>
     </row>
@@ -12095,6 +12163,11 @@
       </c>
       <c r="N119" s="2" t="s">
         <v>532</v>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>Sherwood</t>
+        </is>
       </c>
       <c r="Z119" s="2" t="s">
         <v>533</v>
@@ -13155,6 +13228,11 @@
       <c r="V133" t="s">
         <v>527</v>
       </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
+      </c>
       <c r="Z133" s="2" t="s">
         <v>80</v>
       </c>
@@ -14712,6 +14790,11 @@
       </c>
       <c r="N153" s="2" t="s">
         <v>615</v>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>Stephan</t>
+        </is>
       </c>
       <c r="Z153" s="2" t="s">
         <v>481</v>
@@ -15630,13 +15713,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B39518F-3255-430E-B06D-89EF7E71D09F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A01E55E-8F36-4629-AF30-AC2FE7E7F611}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8503C8AE-3D1F-46A4-8364-E85B5453C9CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CBFAE3B-5EB1-4C6A-AB2B-143F02A03443}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034208DB-038F-434C-89E0-35632B549C3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86082B98-D50C-43DE-800A-C7D4AA3C266F}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -2650,20 +2650,17 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
   </fonts>
@@ -15987,13 +15984,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E704AFD-2123-4302-A539-C99C4EB30B61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C84637CE-C338-4E92-A077-11B1C2434F4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E7848B-5393-4090-A955-A6FB0975F2A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA70FF9B-D0B7-4FDD-B05E-818F1221ABD1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F693454A-79C1-4017-B390-D9F8E3872128}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EE5AC0-D798-460F-8B2A-118D5EF13A39}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -15984,13 +15984,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C84637CE-C338-4E92-A077-11B1C2434F4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02B61117-EB22-44D9-840E-FA1249B5589F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA70FF9B-D0B7-4FDD-B05E-818F1221ABD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED887890-48C2-4A6D-8763-C30C56A4266C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EE5AC0-D798-460F-8B2A-118D5EF13A39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C6E5E9-C4D5-4026-A713-32AE72B17071}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_78357B0E9628B91C05C575F9D2567CD331BB03CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8C1496-A3C0-5F47-8BD5-BADE359485FA}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_78357B0E9628B91C05C575F9D2567CD331BB03CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179A3345-E4E1-DE45-8620-396672C20D16}"/>
   <bookViews>
-    <workbookView xWindow="38180" yWindow="-4040" windowWidth="46580" windowHeight="18140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-580" windowWidth="51200" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="790">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -2359,9 +2359,6 @@
     <t>Figure 3. Comparisons of the relative volumes of the parcellated brain regions among NT, EH and MH.</t>
   </si>
   <si>
-    <t>data are written in the legend (and shown in barographs as well)</t>
-  </si>
-  <si>
     <t>Table A-15: Data for Raw and Derived Variables</t>
   </si>
   <si>
@@ -2375,6 +2372,39 @@
   </si>
   <si>
     <t>UMI:3017523</t>
+  </si>
+  <si>
+    <t>Figure 3 legend</t>
+  </si>
+  <si>
+    <t>data that are written in the legend</t>
+  </si>
+  <si>
+    <t>data that are extracted from bar plots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended Data Figure 4  Comparisons of the relative volumes of the parcellated brain regions among NT, EH and MH, assuming that the variation within NT and EH was equivalent to that of MH. </t>
+  </si>
+  <si>
+    <t>Extended Data Figure 4</t>
+  </si>
+  <si>
+    <t>figure legend</t>
+  </si>
+  <si>
+    <t>figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended Data Table 1 Correspondence between the AAL atlas and the parcellated brain regions </t>
+  </si>
+  <si>
+    <t>Extended Data Table 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended Data Table 3 Statistical test results of differences in the relative volumes of the parcellated brain regions among NT, EH and MH. </t>
+  </si>
+  <si>
+    <t>Extended Data Table 3</t>
   </si>
 </sst>
 </file>
@@ -2470,7 +2500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2478,7 +2508,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2793,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM163"/>
+  <dimension ref="A1:AM167"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" customWidth="1"/>
@@ -3235,24 +3264,24 @@
         <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L5,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
       <c r="AG5" s="2"/>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
       <c r="AJ5" s="2"/>
-      <c r="AK5" s="7"/>
+      <c r="AK5" s="3"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
     </row>
@@ -3315,24 +3344,24 @@
         <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L6,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
       <c r="AG6" s="2"/>
-      <c r="AH6" s="7"/>
-      <c r="AI6" s="7"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
       <c r="AJ6" s="2"/>
-      <c r="AK6" s="7"/>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
     </row>
@@ -8468,7 +8497,7 @@
         <v>3</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" ref="F73:F144" si="90">G73 &amp; IF(H73&lt;&gt;"", "_" &amp; H73, "_") &amp; IF(I73&lt;&gt;"", "_" &amp; I73, "_") &amp; IF(B73&lt;&gt;"", "_" &amp; B73, "")</f>
+        <f t="shared" ref="F73:F148" si="90">G73 &amp; IF(H73&lt;&gt;"", "_" &amp; H73, "_") &amp; IF(I73&lt;&gt;"", "_" &amp; I73, "_") &amp; IF(B73&lt;&gt;"", "_" &amp; B73, "")</f>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G73" t="str">
@@ -8685,7 +8714,7 @@
         <v>2020</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" ref="J75:J134" si="92">_xlfn.LET(
+        <f t="shared" ref="J75:J138" si="92">_xlfn.LET(
 _xlpm.doi,IF(C75&lt;&gt;"",C75,_xlfn.TEXTAFTER(A75,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
@@ -8704,7 +8733,7 @@
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L75" t="str">
-        <f t="shared" ref="L75:L143" si="93">J75 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D75,CHAR(160),"")," ",""),"_","")</f>
+        <f t="shared" ref="L75:L147" si="93">J75 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D75,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M75" t="str">
@@ -9017,7 +9046,7 @@
         <v>392</v>
       </c>
       <c r="E79" t="str">
-        <f t="shared" ref="E79:E115" si="94">RIGHT(A79,1)</f>
+        <f t="shared" ref="E79:E119" si="94">RIGHT(A79,1)</f>
         <v>5</v>
       </c>
       <c r="F79" t="str">
@@ -9025,7 +9054,7 @@
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" ref="G79:G115" si="95">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A79,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G79:G119" si="95">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A79,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H79" t="str">
@@ -9033,7 +9062,7 @@
         <v>etal</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" ref="I79:I115" si="96">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A79, "("), ")")</f>
+        <f t="shared" ref="I79:I119" si="96">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A79, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="J79" t="str">
@@ -9291,7 +9320,7 @@
         <v>Isler</v>
       </c>
       <c r="H83" t="str">
-        <f t="shared" ref="H83:H162" si="97">_xlfn.LET(
+        <f t="shared" ref="H83:H166" si="97">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A83," ("&amp;I83&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
@@ -9432,7 +9461,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004</v>
       </c>
       <c r="K85" t="str">
-        <f t="shared" ref="K85:K115" si="98">TRIM(_xlfn.TEXTJOIN("_",FALSE,F85,(SUBSTITUTE(SUBSTITUTE(D85," ",""), "_", ""))))</f>
+        <f t="shared" ref="K85:K119" si="98">TRIM(_xlfn.TEXTJOIN("_",FALSE,F85,(SUBSTITUTE(SUBSTITUTE(D85," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L85" t="str">
@@ -10287,9 +10316,9 @@
       <c r="A97" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="C97" s="7"/>
+      <c r="C97" s="3"/>
       <c r="D97" s="2" t="s">
-        <v>176</v>
+        <v>779</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" ref="E97" si="103">RIGHT(A97,1)</f>
@@ -10333,24 +10362,26 @@
       </c>
       <c r="K97" t="str">
         <f t="shared" ref="K97" si="109">TRIM(_xlfn.TEXTJOIN("_",FALSE,F97,(SUBSTITUTE(SUBSTITUTE(D97," ",""), "_", ""))))</f>
-        <v>Kochiyama_etal_2018_Figure3</v>
+        <v>Kochiyama_etal_2018_Figure3legend</v>
       </c>
       <c r="L97" t="str">
         <f t="shared" ref="L97" si="110">J97 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D97,CHAR(160),"")," ",""),"_","")</f>
-        <v>10.1038%2Fs41598-018-24331-0_Figure3</v>
+        <v>10.1038%2Fs41598-018-24331-0_Figure3legend</v>
       </c>
       <c r="M97" t="str">
         <f t="array" ref="M97">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L97,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N97" s="7" t="s">
+      <c r="N97" s="3" t="s">
         <v>773</v>
       </c>
       <c r="O97" t="s">
-        <v>774</v>
-      </c>
-      <c r="V97" s="2"/>
-      <c r="AB97" s="7"/>
+        <v>780</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="AB97" s="3"/>
       <c r="AI97" s="2"/>
       <c r="AJ97" s="2"/>
       <c r="AK97" s="2"/>
@@ -10359,372 +10390,304 @@
     </row>
     <row r="98" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E98" t="str">
+        <f t="shared" ref="E98" si="111">RIGHT(A98,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" ref="F98" si="112">G98 &amp; IF(H98&lt;&gt;"", "_" &amp; H98, "_") &amp; IF(I98&lt;&gt;"", "_" &amp; I98, "_") &amp; IF(B98&lt;&gt;"", "_" &amp; B98, "")</f>
+        <v>Kochiyama_etal_2018</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" ref="G98" si="113">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A98,","), "-", ""), " ", "")</f>
+        <v>Kochiyama</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" ref="H98" si="114">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A98," ("&amp;I98&amp;")"),
+_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
+_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
+IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" ref="I98" si="115">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98, "("), ")")</f>
+        <v>2018</v>
+      </c>
+      <c r="J98" t="str">
+        <f t="shared" ref="J98" si="116">_xlfn.LET(
+_xlpm.doi,IF(C98&lt;&gt;"",C98,_xlfn.TEXTAFTER(A98,"https://doi.org/")),
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+_xlpm.doi,
+"/","%2F"),
+":","%3A"),
+"&lt;","%3C"),
+"&gt;","%3E")
+)</f>
+        <v>10.1038%2Fs41598-018-24331-0</v>
+      </c>
+      <c r="K98" t="str">
+        <f t="shared" ref="K98" si="117">TRIM(_xlfn.TEXTJOIN("_",FALSE,F98,(SUBSTITUTE(SUBSTITUTE(D98," ",""), "_", ""))))</f>
+        <v>Kochiyama_etal_2018_Figure3</v>
+      </c>
+      <c r="L98" t="str">
+        <f t="shared" ref="L98" si="118">J98 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D98,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1038%2Fs41598-018-24331-0_Figure3</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="array" ref="M98">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L98,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="O98" t="s">
+        <v>781</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="AB98" s="3"/>
+      <c r="AI98" s="2"/>
+      <c r="AJ98" s="2"/>
+      <c r="AK98" s="2"/>
+      <c r="AL98" s="2"/>
+      <c r="AM98" s="2"/>
+    </row>
+    <row r="99" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="E99" t="str">
+        <f t="shared" ref="E99" si="119">RIGHT(A99,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" ref="F99" si="120">G99 &amp; IF(H99&lt;&gt;"", "_" &amp; H99, "_") &amp; IF(I99&lt;&gt;"", "_" &amp; I99, "_") &amp; IF(B99&lt;&gt;"", "_" &amp; B99, "")</f>
+        <v>Kochiyama_etal_2018</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" ref="G99" si="121">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A99,","), "-", ""), " ", "")</f>
+        <v>Kochiyama</v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" ref="H99" si="122">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A99," ("&amp;I99&amp;")"),
+_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
+_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
+IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="I99" t="str">
+        <f t="shared" ref="I99" si="123">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A99, "("), ")")</f>
+        <v>2018</v>
+      </c>
+      <c r="J99" t="str">
+        <f t="shared" ref="J99" si="124">_xlfn.LET(
+_xlpm.doi,IF(C99&lt;&gt;"",C99,_xlfn.TEXTAFTER(A99,"https://doi.org/")),
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+_xlpm.doi,
+"/","%2F"),
+":","%3A"),
+"&lt;","%3C"),
+"&gt;","%3E")
+)</f>
+        <v>10.1038%2Fs41598-018-24331-0</v>
+      </c>
+      <c r="K99" t="str">
+        <f t="shared" ref="K99" si="125">TRIM(_xlfn.TEXTJOIN("_",FALSE,F99,(SUBSTITUTE(SUBSTITUTE(D99," ",""), "_", ""))))</f>
+        <v>Kochiyama_etal_2018_ExtendedDataFigure4</v>
+      </c>
+      <c r="L99" t="str">
+        <f t="shared" ref="L99" si="126">J99 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D99,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1038%2Fs41598-018-24331-0_ExtendedDataFigure4</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="array" ref="M99">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L99,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="O99" t="s">
+        <v>781</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="AB99" s="3"/>
+      <c r="AI99" s="2"/>
+      <c r="AJ99" s="2"/>
+      <c r="AK99" s="2"/>
+      <c r="AL99" s="2"/>
+      <c r="AM99" s="2"/>
+    </row>
+    <row r="100" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E100" t="str">
+        <f t="shared" ref="E100:E101" si="127">RIGHT(A100,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" ref="F100:F101" si="128">G100 &amp; IF(H100&lt;&gt;"", "_" &amp; H100, "_") &amp; IF(I100&lt;&gt;"", "_" &amp; I100, "_") &amp; IF(B100&lt;&gt;"", "_" &amp; B100, "")</f>
+        <v>Kochiyama_etal_2018</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" ref="G100:G101" si="129">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A100,","), "-", ""), " ", "")</f>
+        <v>Kochiyama</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" ref="H100:H101" si="130">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A100," ("&amp;I100&amp;")"),
+_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
+_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
+IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="I100" t="str">
+        <f t="shared" ref="I100:I101" si="131">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A100, "("), ")")</f>
+        <v>2018</v>
+      </c>
+      <c r="J100" t="str">
+        <f t="shared" ref="J100:J101" si="132">_xlfn.LET(
+_xlpm.doi,IF(C100&lt;&gt;"",C100,_xlfn.TEXTAFTER(A100,"https://doi.org/")),
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+_xlpm.doi,
+"/","%2F"),
+":","%3A"),
+"&lt;","%3C"),
+"&gt;","%3E")
+)</f>
+        <v>10.1038%2Fs41598-018-24331-0</v>
+      </c>
+      <c r="K100" t="str">
+        <f t="shared" ref="K100:K101" si="133">TRIM(_xlfn.TEXTJOIN("_",FALSE,F100,(SUBSTITUTE(SUBSTITUTE(D100," ",""), "_", ""))))</f>
+        <v>Kochiyama_etal_2018_ExtendedDataTable1</v>
+      </c>
+      <c r="L100" t="str">
+        <f t="shared" ref="L100:L101" si="134">J100 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D100,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1038%2Fs41598-018-24331-0_ExtendedDataTable1</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="array" ref="M100">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L100,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100" s="3"/>
+      <c r="AI100" s="2"/>
+      <c r="AJ100" s="2"/>
+      <c r="AK100" s="2"/>
+      <c r="AL100" s="2"/>
+      <c r="AM100" s="2"/>
+    </row>
+    <row r="101" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="E101" t="str">
+        <f t="shared" si="127"/>
+        <v>0</v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="128"/>
+        <v>Kochiyama_etal_2018</v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="129"/>
+        <v>Kochiyama</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="130"/>
+        <v>etal</v>
+      </c>
+      <c r="I101" t="str">
+        <f t="shared" si="131"/>
+        <v>2018</v>
+      </c>
+      <c r="J101" t="str">
+        <f t="shared" si="132"/>
+        <v>10.1038%2Fs41598-018-24331-0</v>
+      </c>
+      <c r="K101" t="str">
+        <f t="shared" si="133"/>
+        <v>Kochiyama_etal_2018_ExtendedDataTable3</v>
+      </c>
+      <c r="L101" t="str">
+        <f t="shared" si="134"/>
+        <v>10.1038%2Fs41598-018-24331-0_ExtendedDataTable3</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="array" ref="M101">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L101,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB101" s="3"/>
+      <c r="AI101" s="2"/>
+      <c r="AJ101" s="2"/>
+      <c r="AK101" s="2"/>
+      <c r="AL101" s="2"/>
+      <c r="AM101" s="2"/>
+    </row>
+    <row r="102" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E102" t="str">
         <f t="shared" si="94"/>
         <v>8</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F102" t="str">
         <f t="shared" si="90"/>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G102" t="str">
         <f t="shared" si="95"/>
         <v>Kverkova</v>
-      </c>
-      <c r="H98" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I98" t="str">
-        <f t="shared" si="96"/>
-        <v>2018</v>
-      </c>
-      <c r="J98" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1038%2Fs41598-018-26062-8</v>
-      </c>
-      <c r="K98" t="str">
-        <f t="shared" si="98"/>
-        <v>Kverkova_etal_2018_Table1</v>
-      </c>
-      <c r="L98" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
-      </c>
-      <c r="M98" t="str">
-        <f t="array" ref="M98">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L98,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="P98" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q98" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R98" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T98" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="U98" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="V98" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y98" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="Z98" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="AH98" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AI98" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="AJ98" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK98" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL98" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM98" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E99" t="str">
-        <f t="shared" si="94"/>
-        <v>8</v>
-      </c>
-      <c r="F99" t="str">
-        <f t="shared" si="90"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="G99" t="str">
-        <f t="shared" si="95"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="H99" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I99" t="str">
-        <f t="shared" si="96"/>
-        <v>2018</v>
-      </c>
-      <c r="J99" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1038%2Fs41598-018-26062-8</v>
-      </c>
-      <c r="K99" t="str">
-        <f t="shared" si="98"/>
-        <v>Kverkova_etal_2018_TableS1</v>
-      </c>
-      <c r="L99" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
-      </c>
-      <c r="M99" t="str">
-        <f t="array" ref="M99">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L99,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="P99" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W99" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="X99" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Y99" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="Z99" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="AH99" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AI99" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="AJ99" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK99" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="AL99" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM99" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E100" t="str">
-        <f t="shared" si="94"/>
-        <v>8</v>
-      </c>
-      <c r="F100" t="str">
-        <f t="shared" si="90"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="G100" t="str">
-        <f t="shared" si="95"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="H100" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I100" t="str">
-        <f t="shared" si="96"/>
-        <v>2018</v>
-      </c>
-      <c r="J100" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1038%2Fs41598-018-26062-8</v>
-      </c>
-      <c r="K100" t="str">
-        <f t="shared" si="98"/>
-        <v>Kverkova_etal_2018_TableS5</v>
-      </c>
-      <c r="L100" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
-      </c>
-      <c r="M100" t="str">
-        <f t="array" ref="M100">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L100,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="P100" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q100" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R100" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T100" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="U100" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="V100" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W100" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="X100" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Y100" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="Z100" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG100" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH100" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AI100" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ100" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK100" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL100" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM100" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E101" t="str">
-        <f t="shared" si="94"/>
-        <v>4</v>
-      </c>
-      <c r="F101" t="str">
-        <f t="shared" si="90"/>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="G101" t="str">
-        <f t="shared" si="95"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="H101" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I101" t="str">
-        <f t="shared" si="96"/>
-        <v>2013</v>
-      </c>
-      <c r="J101" t="str">
-        <f t="shared" si="92"/>
-        <v>10.3389%2Ffnhum.2013.00424</v>
-      </c>
-      <c r="K101" t="str">
-        <f t="shared" si="98"/>
-        <v>Lewitus_etal_2013_TableS2partial</v>
-      </c>
-      <c r="L101" t="str">
-        <f t="shared" si="93"/>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
-      </c>
-      <c r="M101" t="str">
-        <f t="array" ref="M101">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L101,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-      </c>
-      <c r="Q101" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI101" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="AJ101" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL101" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM101" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E102" t="str">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="F102" t="str">
-        <f t="shared" si="90"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="95"/>
-        <v>Lewitus</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="97"/>
@@ -10732,61 +10695,91 @@
       </c>
       <c r="I102" t="str">
         <f t="shared" si="96"/>
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="J102" t="str">
         <f t="shared" si="92"/>
-        <v>10.1371%2Fjournal.pbio.1002000</v>
+        <v>10.1038%2Fs41598-018-26062-8</v>
       </c>
       <c r="K102" t="str">
         <f t="shared" si="98"/>
-        <v>Lewitus_etal_2014_TableS1</v>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L102" t="str">
         <f t="shared" si="93"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M102" t="str">
         <f t="array" ref="M102">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L102,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>466</v>
+        <v>443</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T102" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="U102" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y102" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z102" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="AH102" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="AI102" s="2" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="AJ102" s="2" t="s">
-        <v>118</v>
+        <v>450</v>
+      </c>
+      <c r="AK102" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="AL102" s="2" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="AM102" s="2" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>469</v>
+        <v>262</v>
       </c>
       <c r="E103" t="str">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F103" t="str">
         <f t="shared" si="90"/>
-        <v>Lewitus_etal_2014</v>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="95"/>
-        <v>Lewitus</v>
+        <v>Kverkova</v>
       </c>
       <c r="H103" t="str">
         <f t="shared" si="97"/>
@@ -10794,143 +10787,463 @@
       </c>
       <c r="I103" t="str">
         <f t="shared" si="96"/>
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="J103" t="str">
         <f t="shared" si="92"/>
-        <v>10.1371%2Fjournal.pbio.1002000</v>
+        <v>10.1038%2Fs41598-018-26062-8</v>
       </c>
       <c r="K103" t="str">
         <f t="shared" si="98"/>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="L103" t="str">
         <f t="shared" si="93"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M103" t="str">
         <f t="array" ref="M103">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L103,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>470</v>
+        <v>452</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="S103" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T103" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y103" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z103" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="AH103" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="AI103" s="2" t="s">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="AJ103" s="2" t="s">
-        <v>118</v>
+        <v>450</v>
+      </c>
+      <c r="AK103" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="AL103" s="2" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="AM103" s="2" t="s">
-        <v>468</v>
+        <v>383</v>
       </c>
     </row>
     <row r="104" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="E104" t="str">
         <f t="shared" si="94"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F104" t="str">
         <f t="shared" si="90"/>
-        <v>MacLarnon__1996</v>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="95"/>
-        <v>MacLarnon</v>
+        <v>Kverkova</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="97"/>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I104" t="str">
         <f t="shared" si="96"/>
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="J104" t="str">
         <f t="shared" si="92"/>
-        <v>10.1006%2Fjhev.1996.0005</v>
+        <v>10.1038%2Fs41598-018-26062-8</v>
       </c>
       <c r="K104" t="str">
         <f t="shared" si="98"/>
-        <v>MacLarnon__1996_Table1</v>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L104" t="str">
         <f t="shared" si="93"/>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M104" t="str">
         <f t="array" ref="M104">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L104,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="P104" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="Q104" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R104" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="S104" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T104" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y104" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z104" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG104" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH104" s="2" t="s">
+        <v>448</v>
+      </c>
       <c r="AI104" s="2" t="s">
-        <v>473</v>
+        <v>387</v>
       </c>
       <c r="AJ104" s="2" t="s">
-        <v>99</v>
+        <v>450</v>
+      </c>
+      <c r="AK104" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="AL104" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AM104" s="2" t="s">
-        <v>474</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E105" t="str">
+        <f t="shared" si="94"/>
+        <v>4</v>
+      </c>
+      <c r="F105" t="str">
+        <f t="shared" si="90"/>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="G105" t="str">
+        <f t="shared" si="95"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I105" t="str">
+        <f t="shared" si="96"/>
+        <v>2013</v>
+      </c>
+      <c r="J105" t="str">
+        <f t="shared" si="92"/>
+        <v>10.3389%2Ffnhum.2013.00424</v>
+      </c>
+      <c r="K105" t="str">
+        <f t="shared" si="98"/>
+        <v>Lewitus_etal_2013_TableS2partial</v>
+      </c>
+      <c r="L105" t="str">
+        <f t="shared" si="93"/>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="array" ref="M105">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L105,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI105" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="AJ105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL105" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM105" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E106" t="str">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
+        <f t="shared" si="90"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="G106" t="str">
+        <f t="shared" si="95"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I106" t="str">
+        <f t="shared" si="96"/>
+        <v>2014</v>
+      </c>
+      <c r="J106" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1371%2Fjournal.pbio.1002000</v>
+      </c>
+      <c r="K106" t="str">
+        <f t="shared" si="98"/>
+        <v>Lewitus_etal_2014_TableS1</v>
+      </c>
+      <c r="L106" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="array" ref="M106">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L106,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI106" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ106" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL106" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM106" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E107" t="str">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="F107" t="str">
+        <f t="shared" si="90"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="G107" t="str">
+        <f t="shared" si="95"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I107" t="str">
+        <f t="shared" si="96"/>
+        <v>2014</v>
+      </c>
+      <c r="J107" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1371%2Fjournal.pbio.1002000</v>
+      </c>
+      <c r="K107" t="str">
+        <f t="shared" si="98"/>
+        <v>Lewitus_etal_2014_TableS8</v>
+      </c>
+      <c r="L107" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="array" ref="M107">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L107,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q107" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI107" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ107" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL107" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM107" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E108" t="str">
+        <f t="shared" si="94"/>
+        <v>5</v>
+      </c>
+      <c r="F108" t="str">
+        <f t="shared" si="90"/>
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="G108" t="str">
+        <f t="shared" si="95"/>
+        <v>MacLarnon</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <f t="shared" si="96"/>
+        <v>1996</v>
+      </c>
+      <c r="J108" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1006%2Fjhev.1996.0005</v>
+      </c>
+      <c r="K108" t="str">
+        <f t="shared" si="98"/>
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="L108" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="array" ref="M108">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L108,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI108" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="AJ108" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL108" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM108" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C109" t="s">
         <v>660</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E105" t="str">
-        <f t="shared" ref="E105" si="111">RIGHT(A105,1)</f>
+      <c r="E109" t="str">
+        <f t="shared" ref="E109" si="135">RIGHT(A109,1)</f>
         <v>.</v>
       </c>
-      <c r="F105" t="str">
-        <f t="shared" ref="F105" si="112">G105 &amp; IF(H105&lt;&gt;"", "_" &amp; H105, "_") &amp; IF(I105&lt;&gt;"", "_" &amp; I105, "_") &amp; IF(B105&lt;&gt;"", "_" &amp; B105, "")</f>
+      <c r="F109" t="str">
+        <f t="shared" ref="F109" si="136">G109 &amp; IF(H109&lt;&gt;"", "_" &amp; H109, "_") &amp; IF(I109&lt;&gt;"", "_" &amp; I109, "_") &amp; IF(B109&lt;&gt;"", "_" &amp; B109, "")</f>
         <v>MacLeod__2000</v>
       </c>
-      <c r="G105" t="str">
-        <f t="shared" ref="G105" si="113">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A105,","), "-", ""), " ", "")</f>
+      <c r="G109" t="str">
+        <f t="shared" ref="G109" si="137">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A109,","), "-", ""), " ", "")</f>
         <v>MacLeod</v>
       </c>
-      <c r="H105" t="str">
-        <f t="shared" ref="H105" si="114">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A105," ("&amp;I105&amp;")"),
+      <c r="H109" t="str">
+        <f t="shared" ref="H109" si="138">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A109," ("&amp;I109&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v/>
       </c>
-      <c r="I105" t="str">
-        <f t="shared" ref="I105" si="115">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A105, "("), ")")</f>
+      <c r="I109" t="str">
+        <f t="shared" ref="I109" si="139">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A109, "("), ")")</f>
         <v>2000</v>
       </c>
-      <c r="J105" t="str">
-        <f t="shared" ref="J105" si="116">_xlfn.LET(
-_xlpm.doi,IF(C105&lt;&gt;"",C105,_xlfn.TEXTAFTER(A105,"https://doi.org/")),
+      <c r="J109" t="str">
+        <f t="shared" ref="J109" si="140">_xlfn.LET(
+_xlpm.doi,IF(C109&lt;&gt;"",C109,_xlfn.TEXTAFTER(A109,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -10943,208 +11256,208 @@
 )</f>
         <v>NQ%3A61662</v>
       </c>
-      <c r="K105" t="str">
-        <f t="shared" ref="K105" si="117">TRIM(_xlfn.TEXTJOIN("_",FALSE,F105,(SUBSTITUTE(SUBSTITUTE(D105," ",""), "_", ""))))</f>
+      <c r="K109" t="str">
+        <f t="shared" ref="K109" si="141">TRIM(_xlfn.TEXTJOIN("_",FALSE,F109,(SUBSTITUTE(SUBSTITUTE(D109," ",""), "_", ""))))</f>
         <v>MacLeod__2000_APPENDIXI</v>
       </c>
-      <c r="L105" t="str">
-        <f t="shared" ref="L105" si="118">J105 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D105,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L109" t="str">
+        <f t="shared" ref="L109" si="142">J109 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D109,CHAR(160),"")," ",""),"_","")</f>
         <v>NQ%3A61662_APPENDIXI</v>
       </c>
-      <c r="M105" t="str">
-        <f t="array" ref="M105">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L105,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M109" t="str">
+        <f t="array" ref="M109">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L109,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>NQ%3A61662_APPENDIXI.tsv</v>
       </c>
-      <c r="N105" s="2" t="s">
+      <c r="N109" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="P105" s="3"/>
-      <c r="AI105" s="2"/>
-      <c r="AJ105" s="2"/>
-      <c r="AL105" s="2"/>
-      <c r="AM105" s="2"/>
-    </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
+      <c r="P109" s="3"/>
+      <c r="AI109" s="2"/>
+      <c r="AJ109" s="2"/>
+      <c r="AL109" s="2"/>
+      <c r="AM109" s="2"/>
+    </row>
+    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E110" t="str">
         <f t="shared" si="94"/>
         <v>9</v>
       </c>
-      <c r="F106" t="str">
+      <c r="F110" t="str">
         <f t="shared" si="90"/>
         <v>MacLeod_etal_2003</v>
       </c>
-      <c r="G106" t="str">
+      <c r="G110" t="str">
         <f t="shared" si="95"/>
         <v>MacLeod</v>
       </c>
-      <c r="H106" t="str">
+      <c r="H110" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I106" t="str">
+      <c r="I110" t="str">
         <f t="shared" si="96"/>
         <v>2003</v>
       </c>
-      <c r="J106" t="str">
+      <c r="J110" t="str">
         <f t="shared" si="92"/>
         <v>10.1016%2Fs0047-2484(03)00028-9</v>
       </c>
-      <c r="K106" t="str">
+      <c r="K110" t="str">
         <f t="shared" si="98"/>
         <v>MacLeod_etal_2003_Table1</v>
       </c>
-      <c r="L106" t="str">
+      <c r="L110" t="str">
         <f t="shared" si="93"/>
         <v>10.1016%2Fs0047-2484(03)00028-9_Table1</v>
       </c>
-      <c r="M106" t="str">
-        <f t="array" ref="M106">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L106,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M110" t="str">
+        <f t="array" ref="M110">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L110,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1016%2Fs0047-2484(03)00028-9_Table1.tsv</v>
       </c>
-      <c r="N106" s="2" t="s">
+      <c r="N110" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="Y106" s="2" t="s">
+      <c r="Y110" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="Z106" s="2" t="s">
+      <c r="Z110" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="AF106" s="2" t="s">
+      <c r="AF110" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AG106" s="2" t="s">
+      <c r="AG110" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI106" s="2" t="s">
+      <c r="AI110" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AJ106" s="2" t="s">
+      <c r="AJ110" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK106" s="2" t="s">
+      <c r="AK110" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL106" s="2" t="s">
+      <c r="AL110" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM106" s="2" t="s">
+      <c r="AM110" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
+    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A111" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E107" t="str">
-        <f t="shared" ref="E107:E108" si="119">RIGHT(A107,1)</f>
+      <c r="E111" t="str">
+        <f t="shared" ref="E111:E112" si="143">RIGHT(A111,1)</f>
         <v>9</v>
       </c>
-      <c r="F107" t="str">
+      <c r="F111" t="str">
         <f t="shared" si="90"/>
         <v>MacLeod_etal_2003</v>
       </c>
-      <c r="G107" t="str">
-        <f t="shared" ref="G107:G108" si="120">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A107,","), "-", ""), " ", "")</f>
+      <c r="G111" t="str">
+        <f t="shared" ref="G111:G112" si="144">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A111,","), "-", ""), " ", "")</f>
         <v>MacLeod</v>
       </c>
-      <c r="H107" t="str">
+      <c r="H111" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I107" t="str">
-        <f t="shared" ref="I107:I108" si="121">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A107, "("), ")")</f>
+      <c r="I111" t="str">
+        <f t="shared" ref="I111:I112" si="145">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A111, "("), ")")</f>
         <v>2003</v>
       </c>
-      <c r="J107" t="str">
+      <c r="J111" t="str">
         <f t="shared" si="92"/>
         <v>10.1016%2Fs0047-2484(03)00028-9</v>
       </c>
-      <c r="K107" t="str">
-        <f t="shared" ref="K107:K108" si="122">TRIM(_xlfn.TEXTJOIN("_",FALSE,F107,(SUBSTITUTE(SUBSTITUTE(D107," ",""), "_", ""))))</f>
+      <c r="K111" t="str">
+        <f t="shared" ref="K111:K112" si="146">TRIM(_xlfn.TEXTJOIN("_",FALSE,F111,(SUBSTITUTE(SUBSTITUTE(D111," ",""), "_", ""))))</f>
         <v>MacLeod_etal_2003_Table2</v>
       </c>
-      <c r="L107" t="str">
+      <c r="L111" t="str">
         <f t="shared" si="93"/>
         <v>10.1016%2Fs0047-2484(03)00028-9_Table2</v>
       </c>
-      <c r="M107" t="str">
-        <f t="array" ref="M107">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L107,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M111" t="str">
+        <f t="array" ref="M111">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L111,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1016%2Fs0047-2484(03)00028-9_Table2.tsv</v>
       </c>
-      <c r="N107" s="2" t="s">
+      <c r="N111" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="Y107" s="2" t="s">
+      <c r="Y111" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="Z107" s="2" t="s">
+      <c r="Z111" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AF107" s="2" t="s">
+      <c r="AF111" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG107" s="2" t="s">
+      <c r="AG111" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI107" s="2" t="s">
+      <c r="AI111" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AJ107" s="2" t="s">
+      <c r="AJ111" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK107" s="2" t="s">
+      <c r="AK111" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL107" s="2" t="s">
+      <c r="AL111" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM107" s="2" t="s">
+      <c r="AM111" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A108" s="2" t="s">
+    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D108" s="4"/>
-      <c r="E108" t="str">
-        <f t="shared" si="119"/>
+      <c r="D112" s="4"/>
+      <c r="E112" t="str">
+        <f t="shared" si="143"/>
         <v>2</v>
       </c>
-      <c r="F108" t="str">
-        <f t="shared" ref="F108" si="123">G108 &amp; IF(H108&lt;&gt;"", "_" &amp; H108, "_") &amp; IF(I108&lt;&gt;"", "_" &amp; I108, "_") &amp; IF(B108&lt;&gt;"", "_" &amp; B108, "")</f>
+      <c r="F112" t="str">
+        <f t="shared" ref="F112" si="147">G112 &amp; IF(H112&lt;&gt;"", "_" &amp; H112, "_") &amp; IF(I112&lt;&gt;"", "_" &amp; I112, "_") &amp; IF(B112&lt;&gt;"", "_" &amp; B112, "")</f>
         <v>ManyPrimates__2022</v>
       </c>
-      <c r="G108" t="str">
-        <f t="shared" si="120"/>
+      <c r="G112" t="str">
+        <f t="shared" si="144"/>
         <v>ManyPrimates</v>
       </c>
-      <c r="H108" t="str">
-        <f t="shared" ref="H108" si="124">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A108," ("&amp;I108&amp;")"),
+      <c r="H112" t="str">
+        <f t="shared" ref="H112" si="148">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A112," ("&amp;I112&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v/>
       </c>
-      <c r="I108" t="str">
-        <f t="shared" si="121"/>
+      <c r="I112" t="str">
+        <f t="shared" si="145"/>
         <v>2022</v>
       </c>
-      <c r="J108" t="str">
+      <c r="J112" t="str">
         <f>_xlfn.LET(
-_xlpm.doi,IF(C105&lt;&gt;"",C105,_xlfn.TEXTAFTER(A108,"https://doi.org/")),
+_xlpm.doi,IF(C109&lt;&gt;"",C109,_xlfn.TEXTAFTER(A112,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -11157,396 +11470,147 @@
 )</f>
         <v>NQ%3A61662</v>
       </c>
-      <c r="K108" t="str">
-        <f t="shared" si="122"/>
+      <c r="K112" t="str">
+        <f t="shared" si="146"/>
         <v>ManyPrimates__2022_</v>
       </c>
-      <c r="L108" t="str">
+      <c r="L112" t="str">
         <f t="shared" si="93"/>
         <v>NQ%3A61662_</v>
       </c>
-      <c r="M108" t="str">
-        <f t="array" ref="M108">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L108,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M112" t="str">
+        <f t="array" ref="M112">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L112,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P108" s="2" t="s">
+      <c r="P112" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="Q108" s="2"/>
-      <c r="T108" s="2"/>
-      <c r="U108" s="2"/>
-      <c r="V108" s="2"/>
-      <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
-      <c r="AA108" s="2"/>
-      <c r="AH108" s="2"/>
-      <c r="AI108" s="2"/>
-      <c r="AJ108" s="2" t="s">
+      <c r="Q112" s="2"/>
+      <c r="T112" s="2"/>
+      <c r="U112" s="2"/>
+      <c r="V112" s="2"/>
+      <c r="W112" s="2"/>
+      <c r="X112" s="2"/>
+      <c r="AA112" s="2"/>
+      <c r="AH112" s="2"/>
+      <c r="AI112" s="2"/>
+      <c r="AJ112" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK108" s="2"/>
-      <c r="AL108" s="2" t="s">
+      <c r="AK112" s="2"/>
+      <c r="AL112" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM108" s="2" t="s">
+      <c r="AM112" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A113" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="E109" t="str">
+      <c r="E113" t="str">
         <f t="shared" si="94"/>
         <v>2</v>
       </c>
-      <c r="F109" t="str">
+      <c r="F113" t="str">
         <f t="shared" si="90"/>
         <v>ManyPrimates__2022</v>
       </c>
-      <c r="G109" t="str">
+      <c r="G113" t="str">
         <f t="shared" si="95"/>
         <v>ManyPrimates</v>
       </c>
-      <c r="H109" t="str">
+      <c r="H113" t="str">
         <f t="shared" si="97"/>
         <v/>
       </c>
-      <c r="I109" t="str">
+      <c r="I113" t="str">
         <f t="shared" si="96"/>
         <v>2022</v>
       </c>
-      <c r="J109" t="str">
+      <c r="J113" t="str">
         <f t="shared" si="92"/>
         <v>10.26451%2Fabc.09.04.06.2022</v>
       </c>
-      <c r="K109" t="str">
+      <c r="K113" t="str">
         <f t="shared" si="98"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
-      <c r="L109" t="str">
+      <c r="L113" t="str">
         <f t="shared" si="93"/>
         <v>10.26451%2Fabc.09.04.06.2022_data/speciespredictors.xlsx</v>
       </c>
-      <c r="M109" t="str">
-        <f t="array" ref="M109">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L109,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M113" t="str">
+        <f t="array" ref="M113">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L113,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P109" s="2" t="s">
+      <c r="P113" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="Q109" s="2" t="s">
+      <c r="Q113" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T109" s="2" t="str">
-        <f>IF(S109="N", R109, "write file name")</f>
+      <c r="T113" s="2" t="str">
+        <f>IF(S113="N", R113, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U109" s="2" t="s">
+      <c r="U113" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="V109" s="2" t="s">
+      <c r="V113" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W109" s="2" t="s">
+      <c r="W113" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="X109" s="2" t="s">
+      <c r="X113" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="AA109" s="2" t="s">
+      <c r="AA113" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="AH109" s="2" t="s">
+      <c r="AH113" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AI109" s="2" t="s">
+      <c r="AI113" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="AJ109" s="2" t="s">
+      <c r="AJ113" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK109" s="2" t="s">
+      <c r="AK113" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AL109" s="2"/>
-      <c r="AM109" s="2" t="s">
+      <c r="AL113" s="2"/>
+      <c r="AM113" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A110" s="2" t="s">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A114" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E110" t="str">
+      <c r="E114" t="str">
         <f t="shared" si="94"/>
         <v>2</v>
       </c>
-      <c r="F110" t="str">
+      <c r="F114" t="str">
         <f t="shared" si="90"/>
         <v>Matano_etal_1985_a</v>
       </c>
-      <c r="G110" t="str">
+      <c r="G114" t="str">
         <f t="shared" si="95"/>
         <v>Matano</v>
-      </c>
-      <c r="H110" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I110" t="str">
-        <f t="shared" si="96"/>
-        <v>1985</v>
-      </c>
-      <c r="J110" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1159%2F000156212</v>
-      </c>
-      <c r="K110" t="str">
-        <f t="shared" si="98"/>
-        <v>Matano_etal_1985_a_Table1</v>
-      </c>
-      <c r="L110" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1159%2F000156212_Table1</v>
-      </c>
-      <c r="M110" t="str">
-        <f t="array" ref="M110">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L110,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000156212_Table1.tsv</v>
-      </c>
-      <c r="N110" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V110" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y110" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z110" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF110" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG110" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI110" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="AJ110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK110" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL110" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM110" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A111" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E111" t="str">
-        <f t="shared" si="94"/>
-        <v>1</v>
-      </c>
-      <c r="F111" t="str">
-        <f t="shared" si="90"/>
-        <v>Matano_etal_1985_b</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="95"/>
-        <v>Matano</v>
-      </c>
-      <c r="H111" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I111" t="str">
-        <f t="shared" si="96"/>
-        <v>1985</v>
-      </c>
-      <c r="J111" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1159%2F000156211</v>
-      </c>
-      <c r="K111" t="str">
-        <f t="shared" si="98"/>
-        <v>Matano_etal_1985_b_Table1</v>
-      </c>
-      <c r="L111" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1159%2F000156211_Table1</v>
-      </c>
-      <c r="M111" t="str">
-        <f t="array" ref="M111">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L111,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000156211_Table1.tsv</v>
-      </c>
-      <c r="P111" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y111" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z111" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF111" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A112" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E112" t="str">
-        <f t="shared" ref="E112" si="125">RIGHT(A112,1)</f>
-        <v>F</v>
-      </c>
-      <c r="F112" t="str">
-        <f t="shared" si="90"/>
-        <v>Matano__2001</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" ref="G112" si="126">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A112,","), "-", ""), " ", "")</f>
-        <v>Matano</v>
-      </c>
-      <c r="H112" t="str">
-        <f t="shared" si="97"/>
-        <v/>
-      </c>
-      <c r="I112" t="str">
-        <f t="shared" ref="I112" si="127">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A112, "("), ")")</f>
-        <v>2001</v>
-      </c>
-      <c r="J112" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F</v>
-      </c>
-      <c r="K112" t="str">
-        <f t="shared" ref="K112" si="128">TRIM(_xlfn.TEXTJOIN("_",FALSE,F112,(SUBSTITUTE(SUBSTITUTE(D112," ",""), "_", ""))))</f>
-        <v>Matano__2001_TABLE2</v>
-      </c>
-      <c r="L112" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2</v>
-      </c>
-      <c r="M112" t="str">
-        <f t="array" ref="M112">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L112,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="3"/>
-      <c r="AF112" s="3"/>
-    </row>
-    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A113" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E113" t="str">
-        <f t="shared" si="94"/>
-        <v>1</v>
-      </c>
-      <c r="F113" t="str">
-        <f t="shared" si="90"/>
-        <v>Mota_Herculano-Houzel_2015</v>
-      </c>
-      <c r="G113" t="str">
-        <f t="shared" si="95"/>
-        <v>Mota</v>
-      </c>
-      <c r="H113" t="str">
-        <f t="shared" si="97"/>
-        <v>Herculano-Houzel</v>
-      </c>
-      <c r="I113" t="str">
-        <f t="shared" si="96"/>
-        <v>2015</v>
-      </c>
-      <c r="J113" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1126%2Fscience.aaa9101</v>
-      </c>
-      <c r="K113" t="str">
-        <f t="shared" si="98"/>
-        <v>Mota_Herculano-Houzel_2015_TableS1</v>
-      </c>
-      <c r="L113" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
-      </c>
-      <c r="M113" t="str">
-        <f t="array" ref="M113">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L113,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
-      </c>
-      <c r="P113" s="2"/>
-      <c r="Q113" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI113" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="AJ113" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL113" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AM113" s="2" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A114" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E114" t="str">
-        <f t="shared" si="94"/>
-        <v>6</v>
-      </c>
-      <c r="F114" t="str">
-        <f t="shared" si="90"/>
-        <v>Mota_etal_2019</v>
-      </c>
-      <c r="G114" t="str">
-        <f t="shared" si="95"/>
-        <v>Mota</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="97"/>
@@ -11554,67 +11618,82 @@
       </c>
       <c r="I114" t="str">
         <f t="shared" si="96"/>
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="J114" t="str">
         <f t="shared" si="92"/>
-        <v>10.1073%2Fpnas.1716956116</v>
+        <v>10.1159%2F000156212</v>
       </c>
       <c r="K114" t="str">
         <f t="shared" si="98"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
+        <v>Matano_etal_1985_a_Table1</v>
       </c>
       <c r="L114" t="str">
         <f t="shared" si="93"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>10.1159%2F000156212_Table1</v>
       </c>
       <c r="M114" t="str">
         <f t="array" ref="M114">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L114,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1.tsv</v>
+        <v>10.1159%2F000156212_Table1.tsv</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA114" s="2" t="s">
-        <v>500</v>
+        <v>48</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y114" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z114" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF114" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG114" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="AI114" s="2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="AJ114" s="2" t="s">
-        <v>118</v>
+        <v>82</v>
+      </c>
+      <c r="AK114" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="AL114" s="2" t="s">
-        <v>339</v>
+        <v>61</v>
       </c>
       <c r="AM114" s="2" t="s">
-        <v>502</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>504</v>
+        <v>492</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="E115" t="str">
         <f t="shared" si="94"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F115" t="str">
         <f t="shared" si="90"/>
-        <v>Powell_etal_2017</v>
+        <v>Matano_etal_1985_b</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="95"/>
-        <v>Powell</v>
+        <v>Matano</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="97"/>
@@ -11622,162 +11701,396 @@
       </c>
       <c r="I115" t="str">
         <f t="shared" si="96"/>
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="J115" t="str">
         <f t="shared" si="92"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1</v>
+        <v>10.1159%2F000156211</v>
       </c>
       <c r="K115" t="str">
         <f t="shared" si="98"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <v>Matano_etal_1985_b_Table1</v>
       </c>
       <c r="L115" t="str">
         <f t="shared" si="93"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <v>10.1159%2F000156211_Table1</v>
       </c>
       <c r="M115" t="str">
         <f t="array" ref="M115">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L115,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+        <v>10.1159%2F000156211_Table1.tsv</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q115" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="T115" s="2" t="str">
-        <f>IF(S115="N", R115, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U115" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="V115" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W115" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="X115" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="AA115" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH115" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI115" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="AJ115" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK115" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL115" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM115" s="2" t="s">
-        <v>507</v>
+        <v>48</v>
+      </c>
+      <c r="Y115" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z115" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF115" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="E116" t="str">
-        <f t="shared" ref="E116" si="129">RIGHT(A116,1)</f>
-        <v>5</v>
+        <f t="shared" ref="E116" si="149">RIGHT(A116,1)</f>
+        <v>F</v>
       </c>
       <c r="F116" t="str">
         <f t="shared" si="90"/>
-        <v>Rilling_Insel_1998</v>
+        <v>Matano__2001</v>
       </c>
       <c r="G116" t="str">
-        <f t="shared" ref="G116" si="130">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A116,","), "-", ""), " ", "")</f>
-        <v>Rilling</v>
+        <f t="shared" ref="G116" si="150">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A116,","), "-", ""), " ", "")</f>
+        <v>Matano</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="97"/>
-        <v>Insel</v>
+        <v/>
       </c>
       <c r="I116" t="str">
-        <f t="shared" ref="I116" si="131">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A116, "("), ")")</f>
-        <v>1998</v>
+        <f t="shared" ref="I116" si="151">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A116, "("), ")")</f>
+        <v>2001</v>
       </c>
       <c r="J116" t="str">
         <f t="shared" si="92"/>
-        <v>10.1159%2F000006575</v>
+        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F</v>
       </c>
       <c r="K116" t="str">
-        <f t="shared" ref="K116" si="132">TRIM(_xlfn.TEXTJOIN("_",FALSE,F116,(SUBSTITUTE(SUBSTITUTE(D116," ",""), "_", ""))))</f>
-        <v>Rilling_Insel_1998_Table1</v>
+        <f t="shared" ref="K116" si="152">TRIM(_xlfn.TEXTJOIN("_",FALSE,F116,(SUBSTITUTE(SUBSTITUTE(D116," ",""), "_", ""))))</f>
+        <v>Matano__2001_TABLE2</v>
       </c>
       <c r="L116" t="str">
         <f t="shared" si="93"/>
-        <v>10.1159%2F000006575_Table1</v>
+        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2</v>
       </c>
       <c r="M116" t="str">
         <f t="array" ref="M116">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L116,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000006575_Table1.tsv</v>
-      </c>
-      <c r="N116" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="Y116" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="Z116" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="AF116" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="AG116" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="Y116" s="3"/>
+      <c r="Z116" s="3"/>
+      <c r="AF116" s="3"/>
     </row>
     <row r="117" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E117" t="str">
+        <f t="shared" si="94"/>
+        <v>1</v>
+      </c>
+      <c r="F117" t="str">
+        <f t="shared" si="90"/>
+        <v>Mota_Herculano-Houzel_2015</v>
+      </c>
+      <c r="G117" t="str">
+        <f t="shared" si="95"/>
+        <v>Mota</v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="97"/>
+        <v>Herculano-Houzel</v>
+      </c>
+      <c r="I117" t="str">
+        <f t="shared" si="96"/>
+        <v>2015</v>
+      </c>
+      <c r="J117" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1126%2Fscience.aaa9101</v>
+      </c>
+      <c r="K117" t="str">
+        <f t="shared" si="98"/>
+        <v>Mota_Herculano-Houzel_2015_TableS1</v>
+      </c>
+      <c r="L117" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="array" ref="M117">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L117,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      </c>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI117" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="AJ117" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL117" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AM117" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A118" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E118" t="str">
+        <f t="shared" si="94"/>
+        <v>6</v>
+      </c>
+      <c r="F118" t="str">
+        <f t="shared" si="90"/>
+        <v>Mota_etal_2019</v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="95"/>
+        <v>Mota</v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I118" t="str">
+        <f t="shared" si="96"/>
+        <v>2019</v>
+      </c>
+      <c r="J118" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1073%2Fpnas.1716956116</v>
+      </c>
+      <c r="K118" t="str">
+        <f t="shared" si="98"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
+      </c>
+      <c r="L118" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="array" ref="M118">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L118,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1.tsv</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="P118" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA118" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="AI118" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AJ118" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL118" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AM118" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A119" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E119" t="str">
+        <f t="shared" si="94"/>
+        <v>5</v>
+      </c>
+      <c r="F119" t="str">
+        <f t="shared" si="90"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" si="95"/>
+        <v>Powell</v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I119" t="str">
+        <f t="shared" si="96"/>
+        <v>2017</v>
+      </c>
+      <c r="J119" t="str">
+        <f t="shared" si="92"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1</v>
+      </c>
+      <c r="K119" t="str">
+        <f t="shared" si="98"/>
+        <v>Powell_etal_2017_Dataset1</v>
+      </c>
+      <c r="L119" t="str">
+        <f t="shared" si="93"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="array" ref="M119">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L119,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q119" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="T119" s="2" t="str">
+        <f>IF(S119="N", R119, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U119" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="AA119" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH119" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI119" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="AJ119" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK119" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL119" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM119" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A120" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E120" t="str">
+        <f t="shared" ref="E120" si="153">RIGHT(A120,1)</f>
+        <v>5</v>
+      </c>
+      <c r="F120" t="str">
+        <f t="shared" si="90"/>
+        <v>Rilling_Insel_1998</v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" ref="G120" si="154">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A120,","), "-", ""), " ", "")</f>
+        <v>Rilling</v>
+      </c>
+      <c r="H120" t="str">
+        <f t="shared" si="97"/>
+        <v>Insel</v>
+      </c>
+      <c r="I120" t="str">
+        <f t="shared" ref="I120" si="155">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A120, "("), ")")</f>
+        <v>1998</v>
+      </c>
+      <c r="J120" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1159%2F000006575</v>
+      </c>
+      <c r="K120" t="str">
+        <f t="shared" ref="K120" si="156">TRIM(_xlfn.TEXTJOIN("_",FALSE,F120,(SUBSTITUTE(SUBSTITUTE(D120," ",""), "_", ""))))</f>
+        <v>Rilling_Insel_1998_Table1</v>
+      </c>
+      <c r="L120" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1159%2F000006575_Table1</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="array" ref="M120">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L120,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1159%2F000006575_Table1.tsv</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="Y120" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z120" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="AF120" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="AG120" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A121" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E117" t="str">
-        <f t="shared" ref="E117" si="133">RIGHT(A117,1)</f>
+      <c r="E121" t="str">
+        <f t="shared" ref="E121" si="157">RIGHT(A121,1)</f>
         <v>3</v>
       </c>
-      <c r="F117" t="str">
-        <f t="shared" ref="F117" si="134">G117 &amp; IF(H117&lt;&gt;"", "_" &amp; H117, "_") &amp; IF(I117&lt;&gt;"", "_" &amp; I117, "_") &amp; IF(B117&lt;&gt;"", "_" &amp; B117, "")</f>
+      <c r="F121" t="str">
+        <f t="shared" ref="F121" si="158">G121 &amp; IF(H121&lt;&gt;"", "_" &amp; H121, "_") &amp; IF(I121&lt;&gt;"", "_" &amp; I121, "_") &amp; IF(B121&lt;&gt;"", "_" &amp; B121, "")</f>
         <v>Rilling_Insel_1999</v>
       </c>
-      <c r="G117" t="str">
-        <f t="shared" ref="G117" si="135">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A117,","), "-", ""), " ", "")</f>
+      <c r="G121" t="str">
+        <f t="shared" ref="G121" si="159">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A121,","), "-", ""), " ", "")</f>
         <v>Rilling</v>
       </c>
-      <c r="H117" t="str">
-        <f t="shared" ref="H117" si="136">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A117," ("&amp;I117&amp;")"),
+      <c r="H121" t="str">
+        <f t="shared" ref="H121" si="160">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A121," ("&amp;I121&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>Insel</v>
       </c>
-      <c r="I117" t="str">
-        <f t="shared" ref="I117" si="137">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A117, "("), ")")</f>
+      <c r="I121" t="str">
+        <f t="shared" ref="I121" si="161">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A121, "("), ")")</f>
         <v>1999</v>
       </c>
-      <c r="J117" t="str">
-        <f t="shared" ref="J117" si="138">_xlfn.LET(
-_xlpm.doi,IF(C117&lt;&gt;"",C117,_xlfn.TEXTAFTER(A117,"https://doi.org/")),
+      <c r="J121" t="str">
+        <f t="shared" ref="J121" si="162">_xlfn.LET(
+_xlpm.doi,IF(C121&lt;&gt;"",C121,_xlfn.TEXTAFTER(A121,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -11790,342 +12103,342 @@
 )</f>
         <v>10.1006%2Fjhev.1999.0313</v>
       </c>
-      <c r="K117" t="str">
-        <f t="shared" ref="K117" si="139">TRIM(_xlfn.TEXTJOIN("_",FALSE,F117,(SUBSTITUTE(SUBSTITUTE(D117," ",""), "_", ""))))</f>
+      <c r="K121" t="str">
+        <f t="shared" ref="K121" si="163">TRIM(_xlfn.TEXTJOIN("_",FALSE,F121,(SUBSTITUTE(SUBSTITUTE(D121," ",""), "_", ""))))</f>
         <v>Rilling_Insel_1999_Table1</v>
       </c>
-      <c r="L117" t="str">
-        <f t="shared" ref="L117" si="140">J117 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D117,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L121" t="str">
+        <f t="shared" ref="L121" si="164">J121 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D121,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1006%2Fjhev.1999.0313_Table1</v>
       </c>
-      <c r="M117" t="str">
-        <f t="array" ref="M117">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L117,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M121" t="str">
+        <f t="array" ref="M121">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L121,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1006%2Fjhev.1999.0313_Table1.tsv</v>
       </c>
-      <c r="N117" s="2" t="s">
+      <c r="N121" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="Y117" s="2" t="s">
+      <c r="Y121" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="Z117" s="3" t="s">
+      <c r="Z121" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="AF117" s="2"/>
-      <c r="AG117" s="2"/>
-    </row>
-    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A118" s="2" t="s">
+      <c r="AF121" s="2"/>
+      <c r="AG121" s="2"/>
+    </row>
+    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E118" t="str">
-        <f t="shared" ref="E118" si="141">RIGHT(A118,1)</f>
+      <c r="E122" t="str">
+        <f t="shared" ref="E122" si="165">RIGHT(A122,1)</f>
         <v>2</v>
       </c>
-      <c r="F118" t="str">
-        <f t="shared" ref="F118" si="142">G118 &amp; IF(H118&lt;&gt;"", "_" &amp; H118, "_") &amp; IF(I118&lt;&gt;"", "_" &amp; I118, "_") &amp; IF(B118&lt;&gt;"", "_" &amp; B118, "")</f>
+      <c r="F122" t="str">
+        <f t="shared" ref="F122" si="166">G122 &amp; IF(H122&lt;&gt;"", "_" &amp; H122, "_") &amp; IF(I122&lt;&gt;"", "_" &amp; I122, "_") &amp; IF(B122&lt;&gt;"", "_" &amp; B122, "")</f>
         <v>Schniter_Penaherrera-Aguirre_2026</v>
       </c>
-      <c r="G118" t="str">
-        <f t="shared" ref="G118" si="143">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A118,","), "-", ""), " ", "")</f>
+      <c r="G122" t="str">
+        <f t="shared" ref="G122" si="167">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A122,","), "-", ""), " ", "")</f>
         <v>Schniter</v>
       </c>
-      <c r="H118" t="str">
-        <f t="shared" ref="H118" si="144">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A118," ("&amp;I118&amp;")"),
+      <c r="H122" t="str">
+        <f t="shared" ref="H122" si="168">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A122," ("&amp;I122&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>Penaherrera-Aguirre</v>
       </c>
-      <c r="I118" t="str">
-        <f t="shared" ref="I118" si="145">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A118, "("), ")")</f>
+      <c r="I122" t="str">
+        <f t="shared" ref="I122" si="169">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A122, "("), ")")</f>
         <v>2026</v>
       </c>
-      <c r="J118" t="str">
+      <c r="J122" t="str">
         <f t="shared" si="92"/>
         <v>10.1007%2Fs10329-026-01271-2</v>
       </c>
-      <c r="K118" t="str">
-        <f t="shared" ref="K118" si="146">TRIM(_xlfn.TEXTJOIN("_",FALSE,F118,(SUBSTITUTE(SUBSTITUTE(D118," ",""), "_", ""))))</f>
+      <c r="K122" t="str">
+        <f t="shared" ref="K122" si="170">TRIM(_xlfn.TEXTJOIN("_",FALSE,F122,(SUBSTITUTE(SUBSTITUTE(D122," ",""), "_", ""))))</f>
         <v>Schniter_Penaherrera-Aguirre_2026_data</v>
       </c>
-      <c r="L118" t="str">
+      <c r="L122" t="str">
         <f t="shared" si="93"/>
         <v>10.1007%2Fs10329-026-01271-2_data</v>
       </c>
-      <c r="M118" t="str">
-        <f t="array" ref="M118">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L118,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M122" t="str">
+        <f t="array" ref="M122">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L122,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N118" s="2" t="s">
+      <c r="N122" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="Z118" s="3"/>
-      <c r="AF118" s="2"/>
-      <c r="AG118" s="2"/>
-    </row>
-    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A119" s="2" t="s">
+      <c r="Z122" s="3"/>
+      <c r="AF122" s="2"/>
+      <c r="AG122" s="2"/>
+    </row>
+    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D123" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E119" t="str">
-        <f t="shared" ref="E119:E163" si="147">RIGHT(A119,1)</f>
+      <c r="E123" t="str">
+        <f t="shared" ref="E123:E167" si="171">RIGHT(A123,1)</f>
         <v>L</v>
       </c>
-      <c r="F119" t="str">
+      <c r="F123" t="str">
         <f t="shared" si="90"/>
         <v>Semendeferi_etal_1998</v>
       </c>
-      <c r="G119" t="str">
-        <f t="shared" ref="G119:G162" si="148">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A119,","), "-", ""), " ", "")</f>
+      <c r="G123" t="str">
+        <f t="shared" ref="G123:G166" si="172">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A123,","), "-", ""), " ", "")</f>
         <v>Semendeferi</v>
       </c>
-      <c r="H119" t="str">
+      <c r="H123" t="str">
         <f>_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A119," ("&amp;I119&amp;")"),
+_xlpm.authors,_xlfn.TEXTBEFORE(A123," ("&amp;I123&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I119" t="str">
-        <f t="shared" ref="I119:I162" si="149">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A119, "("), ")")</f>
+      <c r="I123" t="str">
+        <f t="shared" ref="I123:I166" si="173">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A123, "("), ")")</f>
         <v>1998</v>
       </c>
-      <c r="J119" t="str">
+      <c r="J123" t="str">
         <f t="shared" si="92"/>
         <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L</v>
       </c>
-      <c r="K119" t="str">
-        <f t="shared" ref="K119:K162" si="150">TRIM(_xlfn.TEXTJOIN("_",FALSE,F119,(SUBSTITUTE(SUBSTITUTE(D119," ",""), "_", ""))))</f>
+      <c r="K123" t="str">
+        <f t="shared" ref="K123:K166" si="174">TRIM(_xlfn.TEXTJOIN("_",FALSE,F123,(SUBSTITUTE(SUBSTITUTE(D123," ",""), "_", ""))))</f>
         <v>Semendeferi_etal_1998_TABLE2</v>
       </c>
-      <c r="L119" t="str">
+      <c r="L123" t="str">
         <f t="shared" si="93"/>
         <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2</v>
       </c>
-      <c r="M119" t="str">
-        <f t="array" ref="M119">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L119,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M123" t="str">
+        <f t="array" ref="M123">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L123,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2.tsv</v>
       </c>
-      <c r="N119" s="2" t="s">
+      <c r="N123" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="P119" s="2" t="s">
+      <c r="P123" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y119" s="2" t="s">
+      <c r="Y123" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AF119" s="2" t="s">
+      <c r="AF123" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG119" s="2" t="s">
+      <c r="AG123" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI119" s="2" t="s">
+      <c r="AI123" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AJ119" s="2" t="s">
+      <c r="AJ123" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AK119" s="2" t="s">
+      <c r="AK123" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL119" s="2" t="s">
+      <c r="AL123" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM119" s="2" t="s">
+      <c r="AM123" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A120" s="2" t="s">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E120" t="str">
-        <f t="shared" si="147"/>
+      <c r="E124" t="str">
+        <f t="shared" si="171"/>
         <v>I</v>
       </c>
-      <c r="F120" t="str">
+      <c r="F124" t="str">
         <f t="shared" si="90"/>
         <v>Semendeferi_etal_2001</v>
       </c>
-      <c r="G120" t="str">
-        <f t="shared" si="148"/>
+      <c r="G124" t="str">
+        <f t="shared" si="172"/>
         <v>Semendeferi</v>
       </c>
-      <c r="H120" t="str">
+      <c r="H124" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I120" t="str">
-        <f t="shared" si="149"/>
+      <c r="I124" t="str">
+        <f t="shared" si="173"/>
         <v>2001</v>
       </c>
-      <c r="J120" t="str">
+      <c r="J124" t="str">
         <f t="shared" si="92"/>
         <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I</v>
       </c>
-      <c r="K120" t="str">
-        <f t="shared" si="150"/>
+      <c r="K124" t="str">
+        <f t="shared" si="174"/>
         <v>Semendeferi_etal_2001_TABLE2</v>
       </c>
-      <c r="L120" t="str">
+      <c r="L124" t="str">
         <f t="shared" si="93"/>
         <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2</v>
       </c>
-      <c r="M120" t="str">
-        <f t="array" ref="M120">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L120,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M124" t="str">
+        <f t="array" ref="M124">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L124,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2.tsv</v>
       </c>
-      <c r="N120" s="2" t="s">
+      <c r="N124" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="P120" s="2" t="s">
+      <c r="P124" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Y120" s="2" t="s">
+      <c r="Y124" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AF120" s="2" t="s">
+      <c r="AF124" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG120" s="2" t="s">
+      <c r="AG124" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI120" s="2" t="s">
+      <c r="AI124" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="AJ120" s="2" t="s">
+      <c r="AJ124" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AK120" s="2" t="s">
+      <c r="AK124" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL120" s="2" t="s">
+      <c r="AL124" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM120" s="2" t="s">
+      <c r="AM124" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A121" s="2" t="s">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E121" t="str">
-        <f t="shared" si="147"/>
+      <c r="E125" t="str">
+        <f t="shared" si="171"/>
         <v>4</v>
       </c>
-      <c r="F121" t="str">
+      <c r="F125" t="str">
         <f t="shared" si="90"/>
         <v>Semendeferi_etal_2002</v>
       </c>
-      <c r="G121" t="str">
-        <f t="shared" si="148"/>
+      <c r="G125" t="str">
+        <f t="shared" si="172"/>
         <v>Semendeferi</v>
       </c>
-      <c r="H121" t="str">
+      <c r="H125" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I121" t="str">
-        <f t="shared" si="149"/>
+      <c r="I125" t="str">
+        <f t="shared" si="173"/>
         <v>2002</v>
       </c>
-      <c r="J121" t="str">
+      <c r="J125" t="str">
         <f t="shared" si="92"/>
         <v>10.1038%2Fnn814</v>
       </c>
-      <c r="K121" t="str">
-        <f t="shared" si="150"/>
+      <c r="K125" t="str">
+        <f t="shared" si="174"/>
         <v>Semendeferi_etal_2002_Table1</v>
       </c>
-      <c r="L121" t="str">
+      <c r="L125" t="str">
         <f t="shared" si="93"/>
         <v>10.1038%2Fnn814_Table1</v>
       </c>
-      <c r="M121" t="str">
-        <f t="array" ref="M121">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L121,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M125" t="str">
+        <f t="array" ref="M125">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L125,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N121" s="2" t="s">
+      <c r="N125" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="Y121" s="2" t="s">
+      <c r="Y125" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AF121" s="2" t="s">
+      <c r="AF125" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG121" s="2" t="s">
+      <c r="AG125" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI121" s="2" t="s">
+      <c r="AI125" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="AJ121" s="2" t="s">
+      <c r="AJ125" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AK121" s="2" t="s">
+      <c r="AK125" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL121" s="2" t="s">
+      <c r="AL125" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM121" s="2" t="s">
+      <c r="AM125" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A122" s="2" t="s">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D122" s="2"/>
-      <c r="E122" t="str">
-        <f t="shared" ref="E122" si="151">RIGHT(A122,1)</f>
+      <c r="D126" s="2"/>
+      <c r="E126" t="str">
+        <f t="shared" ref="E126" si="175">RIGHT(A126,1)</f>
         <v>1</v>
       </c>
-      <c r="F122" t="str">
-        <f t="shared" ref="F122" si="152">G122 &amp; IF(H122&lt;&gt;"", "_" &amp; H122, "_") &amp; IF(I122&lt;&gt;"", "_" &amp; I122, "_") &amp; IF(B122&lt;&gt;"", "_" &amp; B122, "")</f>
+      <c r="F126" t="str">
+        <f t="shared" ref="F126" si="176">G126 &amp; IF(H126&lt;&gt;"", "_" &amp; H126, "_") &amp; IF(I126&lt;&gt;"", "_" &amp; I126, "_") &amp; IF(B126&lt;&gt;"", "_" &amp; B126, "")</f>
         <v>Semendeferi_Damasio_2000</v>
       </c>
-      <c r="G122" t="str">
-        <f t="shared" ref="G122" si="153">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A122,","), "-", ""), " ", "")</f>
+      <c r="G126" t="str">
+        <f t="shared" ref="G126" si="177">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A126,","), "-", ""), " ", "")</f>
         <v>Semendeferi</v>
       </c>
-      <c r="H122" t="str">
-        <f t="shared" ref="H122" si="154">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A122," ("&amp;I122&amp;")"),
+      <c r="H126" t="str">
+        <f t="shared" ref="H126" si="178">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A126," ("&amp;I126&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>Damasio</v>
       </c>
-      <c r="I122" t="str">
-        <f t="shared" ref="I122" si="155">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A122, "("), ")")</f>
+      <c r="I126" t="str">
+        <f t="shared" ref="I126" si="179">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A126, "("), ")")</f>
         <v>2000</v>
       </c>
-      <c r="J122" t="str">
-        <f t="shared" ref="J122" si="156">_xlfn.LET(
-_xlpm.doi,IF(C122&lt;&gt;"",C122,_xlfn.TEXTAFTER(A122,"https://doi.org/")),
+      <c r="J126" t="str">
+        <f t="shared" ref="J126" si="180">_xlfn.LET(
+_xlpm.doi,IF(C126&lt;&gt;"",C126,_xlfn.TEXTAFTER(A126,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -12138,233 +12451,233 @@
 )</f>
         <v>10.1006%2Fjhev.1999.0381</v>
       </c>
-      <c r="K122" t="str">
-        <f t="shared" ref="K122" si="157">TRIM(_xlfn.TEXTJOIN("_",FALSE,F122,(SUBSTITUTE(SUBSTITUTE(D122," ",""), "_", ""))))</f>
+      <c r="K126" t="str">
+        <f t="shared" ref="K126" si="181">TRIM(_xlfn.TEXTJOIN("_",FALSE,F126,(SUBSTITUTE(SUBSTITUTE(D126," ",""), "_", ""))))</f>
         <v>Semendeferi_Damasio_2000_</v>
       </c>
-      <c r="L122" t="str">
-        <f t="shared" ref="L122" si="158">J122 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D122,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L126" t="str">
+        <f t="shared" ref="L126" si="182">J126 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D126,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1006%2Fjhev.1999.0381_</v>
       </c>
-      <c r="M122" t="str">
-        <f t="array" ref="M122">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L122,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M126" t="str">
+        <f t="array" ref="M126">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L126,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N122" s="2"/>
-      <c r="Y122" s="2"/>
-      <c r="AF122" s="2"/>
-      <c r="AG122" s="2"/>
-      <c r="AI122" s="2"/>
-      <c r="AJ122" s="2"/>
-      <c r="AK122" s="2"/>
-      <c r="AL122" s="2"/>
-      <c r="AM122" s="2"/>
-    </row>
-    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
+      <c r="N126" s="2"/>
+      <c r="Y126" s="2"/>
+      <c r="AF126" s="2"/>
+      <c r="AG126" s="2"/>
+      <c r="AI126" s="2"/>
+      <c r="AJ126" s="2"/>
+      <c r="AK126" s="2"/>
+      <c r="AL126" s="2"/>
+      <c r="AM126" s="2"/>
+    </row>
+    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D127" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E123" t="str">
-        <f t="shared" si="147"/>
+      <c r="E127" t="str">
+        <f t="shared" si="171"/>
         <v>3</v>
       </c>
-      <c r="F123" t="str">
+      <c r="F127" t="str">
         <f t="shared" si="90"/>
         <v>Sherwood_etal_2005</v>
       </c>
-      <c r="G123" t="str">
-        <f t="shared" si="148"/>
+      <c r="G127" t="str">
+        <f t="shared" si="172"/>
         <v>Sherwood</v>
       </c>
-      <c r="H123" t="str">
+      <c r="H127" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I123" t="str">
-        <f t="shared" si="149"/>
+      <c r="I127" t="str">
+        <f t="shared" si="173"/>
         <v>2005</v>
       </c>
-      <c r="J123" t="str">
+      <c r="J127" t="str">
         <f t="shared" si="92"/>
         <v>10.1016%2Fj.jhevol.2004.10.003</v>
       </c>
-      <c r="K123" t="str">
-        <f t="shared" si="150"/>
+      <c r="K127" t="str">
+        <f t="shared" si="174"/>
         <v>Sherwood_etal_2005_Table1</v>
       </c>
-      <c r="L123" t="str">
+      <c r="L127" t="str">
         <f t="shared" si="93"/>
         <v>10.1016%2Fj.jhevol.2004.10.003_Table1</v>
       </c>
-      <c r="M123" t="str">
-        <f t="array" ref="M123">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L123,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M127" t="str">
+        <f t="array" ref="M127">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L127,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
       </c>
-      <c r="N123" s="2" t="s">
+      <c r="N127" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="V123" s="2" t="s">
+      <c r="V127" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y123" s="2" t="s">
+      <c r="Y127" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="Z123" s="2" t="s">
+      <c r="Z127" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AF123" s="2" t="s">
+      <c r="AF127" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG123" s="2" t="s">
+      <c r="AG127" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI123" s="2" t="s">
+      <c r="AI127" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="AJ123" s="2" t="s">
+      <c r="AJ127" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AK123" s="2" t="s">
+      <c r="AK127" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL123" s="2" t="s">
+      <c r="AL127" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM123" s="2" t="s">
+      <c r="AM127" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E124" t="str">
-        <f t="shared" si="147"/>
+      <c r="E128" t="str">
+        <f t="shared" si="171"/>
         <v>2</v>
       </c>
-      <c r="F124" t="str">
+      <c r="F128" t="str">
         <f t="shared" si="90"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="G124" t="str">
-        <f t="shared" si="148"/>
+      <c r="G128" t="str">
+        <f t="shared" si="172"/>
         <v>Sherwood</v>
       </c>
-      <c r="H124" t="str">
+      <c r="H128" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I124" t="str">
-        <f t="shared" si="149"/>
+      <c r="I128" t="str">
+        <f t="shared" si="173"/>
         <v>2004</v>
       </c>
-      <c r="J124" t="str">
+      <c r="J128" t="str">
         <f t="shared" si="92"/>
         <v>10.1159%2F000075672</v>
       </c>
-      <c r="K124" t="str">
-        <f t="shared" si="150"/>
+      <c r="K128" t="str">
+        <f t="shared" si="174"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
-      <c r="L124" t="str">
+      <c r="L128" t="str">
         <f t="shared" si="93"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
-      <c r="M124" t="str">
-        <f t="array" ref="M124">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L124,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M128" t="str">
+        <f t="array" ref="M128">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L128,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N124" s="2" t="s">
+      <c r="N128" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="P124" s="2" t="s">
+      <c r="P128" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="Q124" s="2" t="s">
+      <c r="Q128" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T124" s="2" t="str">
-        <f>IF(S124="N", R124, "write file name")</f>
+      <c r="T128" s="2" t="str">
+        <f>IF(S128="N", R128, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U124" s="2" t="s">
+      <c r="U128" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="V124" s="2" t="s">
+      <c r="V128" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="Z124" s="2" t="s">
+      <c r="Z128" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AF124" s="2" t="s">
+      <c r="AF128" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AH124" s="2" t="s">
+      <c r="AH128" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AI124" s="2" t="s">
+      <c r="AI128" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="AJ124" s="2" t="s">
+      <c r="AJ128" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK124" s="2" t="s">
+      <c r="AK128" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL124" s="2" t="s">
+      <c r="AL128" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM124" s="2" t="s">
+      <c r="AM128" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A125" s="2" t="s">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B129" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D129" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E125" t="str">
-        <f>RIGHT(A125,1)</f>
+      <c r="E129" t="str">
+        <f>RIGHT(A129,1)</f>
         <v>2</v>
       </c>
-      <c r="F125" t="str">
-        <f>G125 &amp; IF(H125&lt;&gt;"", "_" &amp; H125, "_") &amp; IF(I125&lt;&gt;"", "_" &amp; I125, "_") &amp; IF(B125&lt;&gt;"", "_" &amp; B125, "")</f>
+      <c r="F129" t="str">
+        <f>G129 &amp; IF(H129&lt;&gt;"", "_" &amp; H129, "_") &amp; IF(I129&lt;&gt;"", "_" &amp; I129, "_") &amp; IF(B129&lt;&gt;"", "_" &amp; B129, "")</f>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="G125" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A125,","), "-", ""), " ", "")</f>
+      <c r="G129" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A129,","), "-", ""), " ", "")</f>
         <v>Sherwood</v>
       </c>
-      <c r="H125" t="str">
+      <c r="H129" t="str">
         <f>_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A125," ("&amp;I125&amp;")"),
+_xlpm.authors,_xlfn.TEXTBEFORE(A129," ("&amp;I129&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I125" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A125, "("), ")")</f>
+      <c r="I129" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A129, "("), ")")</f>
         <v>2004</v>
       </c>
-      <c r="J125" t="str">
+      <c r="J129" t="str">
         <f>_xlfn.LET(
-_xlpm.doi,IF(C125&lt;&gt;"",C125,_xlfn.TEXTAFTER(A125,"https://doi.org/")),
+_xlpm.doi,IF(C129&lt;&gt;"",C129,_xlfn.TEXTAFTER(A129,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -12377,100 +12690,100 @@
 )</f>
         <v>10.1159%2F000075672</v>
       </c>
-      <c r="K125" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F125,(SUBSTITUTE(SUBSTITUTE(D125," ",""), "_", ""))))</f>
+      <c r="K129" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F129,(SUBSTITUTE(SUBSTITUTE(D129," ",""), "_", ""))))</f>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
-      <c r="L125" t="str">
-        <f>J125 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D125,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L129" t="str">
+        <f>J129 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D129,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1159%2F000075672_Table5</v>
       </c>
-      <c r="M125" t="str">
-        <f t="array" ref="M125">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L125,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M129" t="str">
+        <f t="array" ref="M129">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L129,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N125" s="2" t="s">
+      <c r="N129" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="P125" s="2" t="s">
+      <c r="P129" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="Q125" s="2" t="s">
+      <c r="Q129" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T125" s="2" t="str">
-        <f>IF(S125="N", R125, "write file name")</f>
+      <c r="T129" s="2" t="str">
+        <f>IF(S129="N", R129, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U125" s="2" t="s">
+      <c r="U129" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="V125" s="2" t="s">
+      <c r="V129" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="Z125" s="2" t="s">
+      <c r="Z129" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AF125" s="2" t="s">
+      <c r="AF129" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG125" s="2" t="s">
+      <c r="AG129" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AH125" s="2" t="s">
+      <c r="AH129" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AI125" s="2" t="s">
+      <c r="AI129" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="AJ125" s="2" t="s">
+      <c r="AJ129" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK125" s="2" t="s">
+      <c r="AK129" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL125" s="2" t="s">
+      <c r="AL129" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM125" s="2" t="s">
+      <c r="AM129" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A130" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E126" t="str">
-        <f t="shared" ref="E126" si="159">RIGHT(A126,1)</f>
+      <c r="E130" t="str">
+        <f t="shared" ref="E130" si="183">RIGHT(A130,1)</f>
         <v>8</v>
       </c>
-      <c r="F126" t="str">
-        <f t="shared" ref="F126" si="160">G126 &amp; IF(H126&lt;&gt;"", "_" &amp; H126, "_") &amp; IF(I126&lt;&gt;"", "_" &amp; I126, "_") &amp; IF(B126&lt;&gt;"", "_" &amp; B126, "")</f>
+      <c r="F130" t="str">
+        <f t="shared" ref="F130" si="184">G130 &amp; IF(H130&lt;&gt;"", "_" &amp; H130, "_") &amp; IF(I130&lt;&gt;"", "_" &amp; I130, "_") &amp; IF(B130&lt;&gt;"", "_" &amp; B130, "")</f>
         <v>Sherwood_etal_2004</v>
       </c>
-      <c r="G126" t="str">
-        <f t="shared" ref="G126" si="161">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A126,","), "-", ""), " ", "")</f>
+      <c r="G130" t="str">
+        <f t="shared" ref="G130" si="185">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A130,","), "-", ""), " ", "")</f>
         <v>Sherwood</v>
       </c>
-      <c r="H126" t="str">
-        <f t="shared" ref="H126" si="162">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A126," ("&amp;I126&amp;")"),
+      <c r="H130" t="str">
+        <f t="shared" ref="H130" si="186">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A130," ("&amp;I130&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I126" t="str">
-        <f t="shared" ref="I126" si="163">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A126, "("), ")")</f>
+      <c r="I130" t="str">
+        <f t="shared" ref="I130" si="187">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A130, "("), ")")</f>
         <v>2004</v>
       </c>
-      <c r="J126" t="str">
-        <f t="shared" ref="J126" si="164">_xlfn.LET(
-_xlpm.doi,IF(C126&lt;&gt;"",C126,_xlfn.TEXTAFTER(A126,"https://doi.org/")),
+      <c r="J130" t="str">
+        <f t="shared" ref="J130" si="188">_xlfn.LET(
+_xlpm.doi,IF(C130&lt;&gt;"",C130,_xlfn.TEXTAFTER(A130,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -12483,664 +12796,664 @@
 )</f>
         <v>10.1002%2Fajp.20048</v>
       </c>
-      <c r="K126" t="str">
-        <f t="shared" ref="K126" si="165">TRIM(_xlfn.TEXTJOIN("_",FALSE,F126,(SUBSTITUTE(SUBSTITUTE(D126," ",""), "_", ""))))</f>
+      <c r="K130" t="str">
+        <f t="shared" ref="K130" si="189">TRIM(_xlfn.TEXTJOIN("_",FALSE,F130,(SUBSTITUTE(SUBSTITUTE(D130," ",""), "_", ""))))</f>
         <v>Sherwood_etal_2004_TABLEI</v>
       </c>
-      <c r="L126" t="str">
-        <f t="shared" ref="L126" si="166">J126 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D126,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L130" t="str">
+        <f t="shared" ref="L130" si="190">J130 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D130,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1002%2Fajp.20048_TABLEI</v>
       </c>
-      <c r="M126" t="str">
-        <f t="array" ref="M126">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L126,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M130" t="str">
+        <f t="array" ref="M130">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L130,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1002%2Fajp.20048_TABLEI.tsv</v>
       </c>
-      <c r="N126" s="2" t="s">
+      <c r="N130" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="Y126" s="2" t="s">
+      <c r="Y130" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="Z126" s="2" t="s">
+      <c r="Z130" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AF126" s="2" t="s">
+      <c r="AF130" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AG126" s="2" t="s">
+      <c r="AG130" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AK126" s="2" t="s">
+      <c r="AK130" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A127" s="2" t="s">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E127" t="str">
-        <f t="shared" ref="E127" si="167">RIGHT(A127,1)</f>
+      <c r="E131" t="str">
+        <f t="shared" ref="E131" si="191">RIGHT(A131,1)</f>
         <v>8</v>
       </c>
-      <c r="F127" t="str">
+      <c r="F131" t="str">
         <f t="shared" si="90"/>
         <v>Sherwood_etal_2004</v>
       </c>
-      <c r="G127" t="str">
-        <f t="shared" si="148"/>
+      <c r="G131" t="str">
+        <f t="shared" si="172"/>
         <v>Sherwood</v>
       </c>
-      <c r="H127" t="str">
+      <c r="H131" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I127" t="str">
-        <f t="shared" si="149"/>
+      <c r="I131" t="str">
+        <f t="shared" si="173"/>
         <v>2004</v>
       </c>
-      <c r="J127" t="str">
+      <c r="J131" t="str">
         <f t="shared" si="92"/>
         <v>10.1002%2Fajp.20048</v>
       </c>
-      <c r="K127" t="str">
-        <f t="shared" si="150"/>
+      <c r="K131" t="str">
+        <f t="shared" si="174"/>
         <v>Sherwood_etal_2004_unpublishedviaDeCasien</v>
       </c>
-      <c r="L127" t="str">
+      <c r="L131" t="str">
         <f t="shared" si="93"/>
         <v>10.1002%2Fajp.20048_unpublishedviaDeCasien</v>
       </c>
-      <c r="M127" t="str">
-        <f t="array" ref="M127">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L127,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M131" t="str">
+        <f t="array" ref="M131">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L131,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1002%2Fajp.20048_unpublishedviaDeCasien.tsv</v>
       </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s">
+      <c r="N131" s="2"/>
+      <c r="O131" t="s">
         <v>658</v>
       </c>
-      <c r="Y127" s="2" t="s">
+      <c r="Y131" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="Z127" s="2" t="s">
+      <c r="Z131" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AF127" s="2" t="s">
+      <c r="AF131" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AG127" s="2" t="s">
+      <c r="AG131" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AK127" s="2" t="s">
+      <c r="AK131" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
+    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="E128" t="str">
-        <f t="shared" si="147"/>
+      <c r="E132" t="str">
+        <f t="shared" si="171"/>
         <v>9</v>
       </c>
-      <c r="F128" t="str">
+      <c r="F132" t="str">
         <f t="shared" si="90"/>
         <v>Smaers_Soligo_2013</v>
       </c>
-      <c r="G128" t="str">
-        <f t="shared" si="148"/>
+      <c r="G132" t="str">
+        <f t="shared" si="172"/>
         <v>Smaers</v>
       </c>
-      <c r="H128" t="str">
+      <c r="H132" t="str">
         <f t="shared" si="97"/>
         <v>Soligo</v>
       </c>
-      <c r="I128" t="str">
-        <f t="shared" si="149"/>
+      <c r="I132" t="str">
+        <f t="shared" si="173"/>
         <v>2013</v>
       </c>
-      <c r="J128" t="str">
+      <c r="J132" t="str">
         <f t="shared" si="92"/>
         <v>10.1098%2Frspb.2013.0269</v>
       </c>
-      <c r="K128" t="str">
-        <f t="shared" si="150"/>
+      <c r="K132" t="str">
+        <f t="shared" si="174"/>
         <v>Smaers_Soligo_2013_Supplement</v>
       </c>
-      <c r="L128" t="str">
+      <c r="L132" t="str">
         <f t="shared" si="93"/>
         <v>10.1098%2Frspb.2013.0269_Supplement</v>
       </c>
-      <c r="M128" t="str">
-        <f t="array" ref="M128">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L128,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M132" t="str">
+        <f t="array" ref="M132">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L132,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N128" s="2" t="s">
+      <c r="N132" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="AF128" s="2" t="s">
+      <c r="AF132" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG128" s="2" t="s">
+      <c r="AG132" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI128" s="2" t="s">
+      <c r="AI132" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="AJ128" s="2" t="s">
+      <c r="AJ132" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="AL128" s="2" t="s">
+      <c r="AL132" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="AM128" s="2" t="s">
+      <c r="AM132" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
+    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A133" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D133" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E129" t="str">
-        <f t="shared" si="147"/>
+      <c r="E133" t="str">
+        <f t="shared" si="171"/>
         <v>0</v>
       </c>
-      <c r="F129" t="str">
+      <c r="F133" t="str">
         <f t="shared" si="90"/>
         <v>Smaers_etal_2017</v>
       </c>
-      <c r="G129" t="str">
-        <f t="shared" si="148"/>
+      <c r="G133" t="str">
+        <f t="shared" si="172"/>
         <v>Smaers</v>
       </c>
-      <c r="H129" t="str">
+      <c r="H133" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I129" t="str">
-        <f t="shared" si="149"/>
+      <c r="I133" t="str">
+        <f t="shared" si="173"/>
         <v>2017</v>
       </c>
-      <c r="J129" t="str">
+      <c r="J133" t="str">
         <f t="shared" si="92"/>
         <v>10.1016%2Fj.cub.2017.01.020</v>
       </c>
-      <c r="K129" t="str">
-        <f t="shared" si="150"/>
+      <c r="K133" t="str">
+        <f t="shared" si="174"/>
         <v>Smaers_etal_2017_TableS1part1</v>
       </c>
-      <c r="L129" t="str">
+      <c r="L133" t="str">
         <f t="shared" si="93"/>
         <v>10.1016%2Fj.cub.2017.01.020_TableS1part1</v>
       </c>
-      <c r="M129" t="str">
-        <f t="array" ref="M129">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L129,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M133" t="str">
+        <f t="array" ref="M133">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L133,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1016%2Fj.cub.2017.01.020_TableS1part1.tsv</v>
       </c>
-      <c r="N129" s="2" t="s">
+      <c r="N133" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="O129" t="s">
+      <c r="O133" t="s">
         <v>544</v>
       </c>
-      <c r="P129" s="2" t="s">
+      <c r="P133" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="V129" s="2" t="s">
+      <c r="V133" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y129" s="2" t="s">
+      <c r="Y133" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="Z129" s="2" t="s">
+      <c r="Z133" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AC129" s="2" t="s">
+      <c r="AC133" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="AF129" s="2" t="s">
+      <c r="AF133" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG129" s="2" t="s">
+      <c r="AG133" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI129" s="2" t="s">
+      <c r="AI133" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="AJ129" s="2" t="s">
+      <c r="AJ133" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK129" s="2" t="s">
+      <c r="AK133" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="AL129" s="2" t="s">
+      <c r="AL133" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="AM129" s="2" t="s">
+      <c r="AM133" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
+    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="E130" t="str">
-        <f t="shared" ref="E130" si="168">RIGHT(A130,1)</f>
+      <c r="E134" t="str">
+        <f t="shared" ref="E134" si="192">RIGHT(A134,1)</f>
         <v>0</v>
       </c>
-      <c r="F130" t="str">
-        <f t="shared" ref="F130" si="169">G130 &amp; IF(H130&lt;&gt;"", "_" &amp; H130, "_") &amp; IF(I130&lt;&gt;"", "_" &amp; I130, "_") &amp; IF(B130&lt;&gt;"", "_" &amp; B130, "")</f>
+      <c r="F134" t="str">
+        <f t="shared" ref="F134" si="193">G134 &amp; IF(H134&lt;&gt;"", "_" &amp; H134, "_") &amp; IF(I134&lt;&gt;"", "_" &amp; I134, "_") &amp; IF(B134&lt;&gt;"", "_" &amp; B134, "")</f>
         <v>Smaers_etal_2017</v>
       </c>
-      <c r="G130" t="str">
-        <f t="shared" ref="G130" si="170">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A130,","), "-", ""), " ", "")</f>
+      <c r="G134" t="str">
+        <f t="shared" ref="G134" si="194">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A134,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="H130" t="str">
-        <f t="shared" ref="H130" si="171">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A130," ("&amp;I130&amp;")"),
+      <c r="H134" t="str">
+        <f t="shared" ref="H134" si="195">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A134," ("&amp;I134&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I130" t="str">
-        <f t="shared" ref="I130" si="172">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A130, "("), ")")</f>
+      <c r="I134" t="str">
+        <f t="shared" ref="I134" si="196">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A134, "("), ")")</f>
         <v>2017</v>
       </c>
-      <c r="J130" t="str">
+      <c r="J134" t="str">
         <f t="shared" si="92"/>
         <v>10.1016%2Fj.cub.2017.01.020</v>
       </c>
-      <c r="K130" t="str">
-        <f t="shared" ref="K130" si="173">TRIM(_xlfn.TEXTJOIN("_",FALSE,F130,(SUBSTITUTE(SUBSTITUTE(D130," ",""), "_", ""))))</f>
+      <c r="K134" t="str">
+        <f t="shared" ref="K134" si="197">TRIM(_xlfn.TEXTJOIN("_",FALSE,F134,(SUBSTITUTE(SUBSTITUTE(D134," ",""), "_", ""))))</f>
         <v>Smaers_etal_2017_TableS1part2</v>
       </c>
-      <c r="L130" t="str">
+      <c r="L134" t="str">
         <f t="shared" si="93"/>
         <v>10.1016%2Fj.cub.2017.01.020_TableS1part2</v>
       </c>
-      <c r="M130" t="str">
-        <f t="array" ref="M130">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L130,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M134" t="str">
+        <f t="array" ref="M134">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L134,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>10.1016%2Fj.cub.2017.01.020_TableS1part2.tsv</v>
       </c>
-      <c r="N130" s="2" t="s">
+      <c r="N134" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="O130" t="s">
+      <c r="O134" t="s">
         <v>550</v>
       </c>
-      <c r="P130" s="2" t="s">
+      <c r="P134" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="V130" s="2" t="s">
+      <c r="V134" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y130" s="2" t="s">
+      <c r="Y134" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="Z130" s="2" t="s">
+      <c r="Z134" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AC130" s="2" t="s">
+      <c r="AC134" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="AF130" s="2" t="s">
+      <c r="AF134" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG130" s="2" t="s">
+      <c r="AG134" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI130" s="2" t="s">
+      <c r="AI134" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="AJ130" s="2" t="s">
+      <c r="AJ134" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK130" s="2" t="s">
+      <c r="AK134" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="AL130" s="2" t="s">
+      <c r="AL134" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="AM130" s="2" t="s">
+      <c r="AM134" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A131" s="2" t="s">
+    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D135" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E131" t="str">
-        <f t="shared" si="147"/>
+      <c r="E135" t="str">
+        <f t="shared" si="171"/>
         <v>1</v>
       </c>
-      <c r="F131" t="str">
+      <c r="F135" t="str">
         <f t="shared" si="90"/>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="G131" t="str">
-        <f t="shared" si="148"/>
+      <c r="G135" t="str">
+        <f t="shared" si="172"/>
         <v>Smaers</v>
-      </c>
-      <c r="H131" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I131" t="str">
-        <f t="shared" si="149"/>
-        <v>2011</v>
-      </c>
-      <c r="J131" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1159%2F000323671</v>
-      </c>
-      <c r="K131" t="str">
-        <f t="shared" si="150"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="L131" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
-      </c>
-      <c r="M131" t="str">
-        <f t="array" ref="M131">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L131,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="P131" s="2"/>
-      <c r="Q131" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="V131" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z131" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="AF131" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG131" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI131" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="AJ131" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL131" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AM131" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A132" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E132" t="str">
-        <f t="shared" si="147"/>
-        <v>1</v>
-      </c>
-      <c r="F132" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="G132" t="str">
-        <f t="shared" si="148"/>
-        <v>Smaers</v>
-      </c>
-      <c r="H132" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I132" t="str">
-        <f t="shared" si="149"/>
-        <v>2011</v>
-      </c>
-      <c r="J132" t="str">
-        <f t="shared" si="92"/>
-        <v>10.1159%2F000323671</v>
-      </c>
-      <c r="K132" t="str">
-        <f t="shared" si="150"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
-      </c>
-      <c r="L132" t="str">
-        <f t="shared" si="93"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
-      </c>
-      <c r="M132" t="str">
-        <f t="array" ref="M132">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L132,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
-      </c>
-      <c r="P132" s="2"/>
-      <c r="Q132" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="V132" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z132" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="AF132" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG132" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI132" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="AJ132" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL132" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AM132" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E133" t="str">
-        <f t="shared" si="147"/>
-        <v>6</v>
-      </c>
-      <c r="F133" t="str">
-        <f t="shared" si="90"/>
-        <v>Smaers_etal_2018</v>
-      </c>
-      <c r="G133" t="str">
-        <f t="shared" si="148"/>
-        <v>Smaers</v>
-      </c>
-      <c r="H133" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I133" t="str">
-        <f t="shared" si="149"/>
-        <v>2018</v>
-      </c>
-      <c r="J133" t="str">
-        <f t="shared" si="92"/>
-        <v>10.7554%2FeLife.35696</v>
-      </c>
-      <c r="K133" t="str">
-        <f t="shared" si="150"/>
-        <v>Smaers_etal_2018_Figure2-data1</v>
-      </c>
-      <c r="L133" t="str">
-        <f t="shared" si="93"/>
-        <v>10.7554%2FeLife.35696_Figure2-data1</v>
-      </c>
-      <c r="M133" t="str">
-        <f t="array" ref="M133">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L133,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N133" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="Z133" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="AF133" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG133" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI133" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="AJ133" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL133" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AM133" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A134" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E134" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
-      </c>
-      <c r="F134" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G134" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H134" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I134" t="str">
-        <f t="shared" si="149"/>
-        <v>1970</v>
-      </c>
-      <c r="J134" t="str">
-        <f t="shared" si="92"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K134" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_TABLE1</v>
-      </c>
-      <c r="L134" t="str">
-        <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_TABLE1</v>
-      </c>
-      <c r="M134" t="str">
-        <f t="array" ref="M134">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L134,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N134" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="V134" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z134" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF134" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG134" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ134" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="AL134" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM134" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A135" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E135" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
-      </c>
-      <c r="F135" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G135" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
       <c r="I135" t="str">
-        <f t="shared" si="149"/>
+        <f t="shared" si="173"/>
+        <v>2011</v>
+      </c>
+      <c r="J135" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1159%2F000323671</v>
+      </c>
+      <c r="K135" t="str">
+        <f t="shared" si="174"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
+      </c>
+      <c r="L135" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
+      </c>
+      <c r="M135" t="str">
+        <f t="array" ref="M135">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L135,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="P135" s="2"/>
+      <c r="Q135" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="V135" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z135" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AF135" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG135" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI135" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="AJ135" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL135" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AM135" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A136" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E136" t="str">
+        <f t="shared" si="171"/>
+        <v>1</v>
+      </c>
+      <c r="F136" t="str">
+        <f t="shared" si="90"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="G136" t="str">
+        <f t="shared" si="172"/>
+        <v>Smaers</v>
+      </c>
+      <c r="H136" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I136" t="str">
+        <f t="shared" si="173"/>
+        <v>2011</v>
+      </c>
+      <c r="J136" t="str">
+        <f t="shared" si="92"/>
+        <v>10.1159%2F000323671</v>
+      </c>
+      <c r="K136" t="str">
+        <f t="shared" si="174"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="L136" t="str">
+        <f t="shared" si="93"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
+      </c>
+      <c r="M136" t="str">
+        <f t="array" ref="M136">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L136,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="P136" s="2"/>
+      <c r="Q136" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="V136" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z136" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AF136" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG136" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI136" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="AJ136" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL136" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AM136" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E137" t="str">
+        <f t="shared" si="171"/>
+        <v>6</v>
+      </c>
+      <c r="F137" t="str">
+        <f t="shared" si="90"/>
+        <v>Smaers_etal_2018</v>
+      </c>
+      <c r="G137" t="str">
+        <f t="shared" si="172"/>
+        <v>Smaers</v>
+      </c>
+      <c r="H137" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I137" t="str">
+        <f t="shared" si="173"/>
+        <v>2018</v>
+      </c>
+      <c r="J137" t="str">
+        <f t="shared" si="92"/>
+        <v>10.7554%2FeLife.35696</v>
+      </c>
+      <c r="K137" t="str">
+        <f t="shared" si="174"/>
+        <v>Smaers_etal_2018_Figure2-data1</v>
+      </c>
+      <c r="L137" t="str">
+        <f t="shared" si="93"/>
+        <v>10.7554%2FeLife.35696_Figure2-data1</v>
+      </c>
+      <c r="M137" t="str">
+        <f t="array" ref="M137">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L137,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="Z137" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AF137" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG137" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI137" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="AJ137" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL137" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AM137" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E138" t="str">
+        <f t="shared" si="171"/>
+        <v>s</v>
+      </c>
+      <c r="F138" t="str">
+        <f t="shared" si="90"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G138" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H138" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I138" t="str">
+        <f t="shared" si="173"/>
         <v>1970</v>
       </c>
-      <c r="J135" t="str">
-        <f t="shared" ref="J135:J163" si="174">_xlfn.LET(
-_xlpm.doi,IF(C135&lt;&gt;"",C135,_xlfn.TEXTAFTER(A135,"https://doi.org/")),
+      <c r="J138" t="str">
+        <f t="shared" si="92"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K138" t="str">
+        <f t="shared" si="174"/>
+        <v>Stephan_etal_1970_TABLE1</v>
+      </c>
+      <c r="L138" t="str">
+        <f t="shared" si="93"/>
+        <v>ISBN%3A0390672505_TABLE1</v>
+      </c>
+      <c r="M138" t="str">
+        <f t="array" ref="M138">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L138,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="V138" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z138" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF138" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG138" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ138" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="AL138" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM138" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E139" t="str">
+        <f t="shared" si="171"/>
+        <v>s</v>
+      </c>
+      <c r="F139" t="str">
+        <f t="shared" si="90"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G139" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I139" t="str">
+        <f t="shared" si="173"/>
+        <v>1970</v>
+      </c>
+      <c r="J139" t="str">
+        <f t="shared" ref="J139:J167" si="198">_xlfn.LET(
+_xlpm.doi,IF(C139&lt;&gt;"",C139,_xlfn.TEXTAFTER(A139,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -13153,304 +13466,20 @@
 )</f>
         <v>ISBN%3A0390672505</v>
       </c>
-      <c r="K135" t="str">
-        <f t="shared" si="150"/>
+      <c r="K139" t="str">
+        <f t="shared" si="174"/>
         <v>Stephan_etal_1970_TABLE2</v>
       </c>
-      <c r="L135" t="str">
+      <c r="L139" t="str">
         <f t="shared" si="93"/>
         <v>ISBN%3A0390672505_TABLE2</v>
-      </c>
-      <c r="M135" t="str">
-        <f t="array" ref="M135">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L135,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N135" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="V135" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z135" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF135" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG135" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ135" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL135" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM135" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A136" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="E136" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
-      </c>
-      <c r="F136" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G136" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H136" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I136" t="str">
-        <f t="shared" si="149"/>
-        <v>1970</v>
-      </c>
-      <c r="J136" t="str">
-        <f t="shared" si="174"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K136" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_TABLE3</v>
-      </c>
-      <c r="L136" t="str">
-        <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_TABLE3</v>
-      </c>
-      <c r="M136" t="str">
-        <f t="array" ref="M136">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L136,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="V136" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z136" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF136" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG136" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ136" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL136" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM136" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E137" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
-      </c>
-      <c r="F137" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G137" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H137" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I137" t="str">
-        <f t="shared" si="149"/>
-        <v>1970</v>
-      </c>
-      <c r="J137" t="str">
-        <f t="shared" si="174"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K137" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_TABLE4</v>
-      </c>
-      <c r="L137" t="str">
-        <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_TABLE4</v>
-      </c>
-      <c r="M137" t="str">
-        <f t="array" ref="M137">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L137,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N137" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="V137" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z137" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF137" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG137" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ137" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="AL137" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM137" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E138" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
-      </c>
-      <c r="F138" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G138" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H138" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I138" t="str">
-        <f t="shared" si="149"/>
-        <v>1970</v>
-      </c>
-      <c r="J138" t="str">
-        <f t="shared" si="174"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K138" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_TABLE5</v>
-      </c>
-      <c r="L138" t="str">
-        <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_TABLE5</v>
-      </c>
-      <c r="M138" t="str">
-        <f t="array" ref="M138">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L138,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N138" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="V138" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z138" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF138" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG138" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ138" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL138" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM138" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A139" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E139" t="str">
-        <f t="shared" ref="E139" si="175">RIGHT(A139,1)</f>
-        <v>s</v>
-      </c>
-      <c r="F139" t="str">
-        <f t="shared" si="90"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G139" t="str">
-        <f t="shared" si="148"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H139" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
-      </c>
-      <c r="I139" t="str">
-        <f t="shared" si="149"/>
-        <v>1970</v>
-      </c>
-      <c r="J139" t="str">
-        <f t="shared" si="174"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K139" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_TABLE6</v>
-      </c>
-      <c r="L139" t="str">
-        <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_TABLE6</v>
       </c>
       <c r="M139" t="str">
         <f t="array" ref="M139">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L139,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="V139" t="s">
         <v>40</v>
@@ -13482,10 +13511,10 @@
         <v>624</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E140" t="str">
-        <f t="shared" ref="E140" si="176">RIGHT(A140,1)</f>
+        <f t="shared" si="171"/>
         <v>s</v>
       </c>
       <c r="F140" t="str">
@@ -13493,7 +13522,7 @@
         <v>Stephan_etal_1970</v>
       </c>
       <c r="G140" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="172"/>
         <v>Stephan</v>
       </c>
       <c r="H140" t="str">
@@ -13501,37 +13530,30 @@
         <v>etal</v>
       </c>
       <c r="I140" t="str">
-        <f t="shared" si="149"/>
+        <f t="shared" si="173"/>
         <v>1970</v>
       </c>
       <c r="J140" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K140" t="str">
         <f t="shared" si="174"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K140" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1970_Tables1-6</v>
+        <v>Stephan_etal_1970_TABLE3</v>
       </c>
       <c r="L140" t="str">
         <f t="shared" si="93"/>
-        <v>ISBN%3A0390672505_Tables1-6</v>
+        <v>ISBN%3A0390672505_TABLE3</v>
       </c>
       <c r="M140" t="str">
         <f t="array" ref="M140">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L140,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>ISBN%3A0390672505_Tables1-6.tsv</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" t="s">
-        <v>645</v>
-      </c>
-      <c r="P140" s="2" t="s">
-        <v>48</v>
+        <v>notfound</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>564</v>
       </c>
       <c r="V140" t="s">
-        <v>527</v>
-      </c>
-      <c r="Y140" s="2" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z140" s="2" t="s">
         <v>80</v>
@@ -13543,7 +13565,7 @@
         <v>93</v>
       </c>
       <c r="AJ140" s="2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AL140" s="2" t="s">
         <v>61</v>
@@ -13554,24 +13576,24 @@
     </row>
     <row r="141" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>573</v>
+        <v>624</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="E141" t="str">
-        <f t="shared" si="147"/>
-        <v>3</v>
+        <f t="shared" si="171"/>
+        <v>s</v>
       </c>
       <c r="F141" t="str">
         <f t="shared" si="90"/>
-        <v>Stephan_etal_1982</v>
+        <v>Stephan_etal_1970</v>
       </c>
       <c r="G141" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="172"/>
         <v>Stephan</v>
       </c>
       <c r="H141" t="str">
@@ -13579,39 +13601,30 @@
         <v>etal</v>
       </c>
       <c r="I141" t="str">
-        <f t="shared" si="149"/>
-        <v>1982</v>
+        <f t="shared" si="173"/>
+        <v>1970</v>
       </c>
       <c r="J141" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K141" t="str">
         <f t="shared" si="174"/>
-        <v>PMID%3A7161483</v>
-      </c>
-      <c r="K141" t="str">
-        <f t="shared" si="150"/>
-        <v>Stephan_etal_1982_Table1</v>
+        <v>Stephan_etal_1970_TABLE4</v>
       </c>
       <c r="L141" t="str">
         <f t="shared" si="93"/>
-        <v>PMID%3A7161483_Table1</v>
+        <v>ISBN%3A0390672505_TABLE4</v>
       </c>
       <c r="M141" t="str">
         <f t="array" ref="M141">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L141,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="P141" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V141" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="V141" t="s">
         <v>40</v>
-      </c>
-      <c r="W141" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y141" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="Z141" s="2" t="s">
         <v>80</v>
@@ -13622,14 +13635,8 @@
       <c r="AG141" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI141" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="AJ141" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK141" s="2" t="s">
-        <v>61</v>
+        <v>625</v>
       </c>
       <c r="AL141" s="2" t="s">
         <v>61</v>
@@ -13640,294 +13647,600 @@
     </row>
     <row r="142" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="E142" t="str">
-        <f t="shared" si="147"/>
-        <v>4</v>
+        <f t="shared" si="171"/>
+        <v>s</v>
       </c>
       <c r="F142" t="str">
         <f t="shared" si="90"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G142" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H142" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I142" t="str">
+        <f t="shared" si="173"/>
+        <v>1970</v>
+      </c>
+      <c r="J142" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K142" t="str">
+        <f t="shared" si="174"/>
+        <v>Stephan_etal_1970_TABLE5</v>
+      </c>
+      <c r="L142" t="str">
+        <f t="shared" si="93"/>
+        <v>ISBN%3A0390672505_TABLE5</v>
+      </c>
+      <c r="M142" t="str">
+        <f t="array" ref="M142">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L142,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N142" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="V142" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z142" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF142" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG142" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ142" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL142" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM142" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E143" t="str">
+        <f t="shared" ref="E143" si="199">RIGHT(A143,1)</f>
+        <v>s</v>
+      </c>
+      <c r="F143" t="str">
+        <f t="shared" si="90"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G143" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H143" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I143" t="str">
+        <f t="shared" si="173"/>
+        <v>1970</v>
+      </c>
+      <c r="J143" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K143" t="str">
+        <f t="shared" si="174"/>
+        <v>Stephan_etal_1970_TABLE6</v>
+      </c>
+      <c r="L143" t="str">
+        <f t="shared" si="93"/>
+        <v>ISBN%3A0390672505_TABLE6</v>
+      </c>
+      <c r="M143" t="str">
+        <f t="array" ref="M143">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L143,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="V143" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z143" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF143" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG143" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ143" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL143" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM143" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E144" t="str">
+        <f t="shared" ref="E144" si="200">RIGHT(A144,1)</f>
+        <v>s</v>
+      </c>
+      <c r="F144" t="str">
+        <f t="shared" si="90"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G144" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H144" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I144" t="str">
+        <f t="shared" si="173"/>
+        <v>1970</v>
+      </c>
+      <c r="J144" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
+      <c r="K144" t="str">
+        <f t="shared" si="174"/>
+        <v>Stephan_etal_1970_Tables1-6</v>
+      </c>
+      <c r="L144" t="str">
+        <f t="shared" si="93"/>
+        <v>ISBN%3A0390672505_Tables1-6</v>
+      </c>
+      <c r="M144" t="str">
+        <f t="array" ref="M144">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L144,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>ISBN%3A0390672505_Tables1-6.tsv</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s">
+        <v>645</v>
+      </c>
+      <c r="P144" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V144" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y144" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z144" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF144" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG144" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ144" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL144" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM144" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="145" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E145" t="str">
+        <f t="shared" si="171"/>
+        <v>3</v>
+      </c>
+      <c r="F145" t="str">
+        <f t="shared" si="90"/>
+        <v>Stephan_etal_1982</v>
+      </c>
+      <c r="G145" t="str">
+        <f t="shared" si="172"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H145" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I145" t="str">
+        <f t="shared" si="173"/>
+        <v>1982</v>
+      </c>
+      <c r="J145" t="str">
+        <f t="shared" si="198"/>
+        <v>PMID%3A7161483</v>
+      </c>
+      <c r="K145" t="str">
+        <f t="shared" si="174"/>
+        <v>Stephan_etal_1982_Table1</v>
+      </c>
+      <c r="L145" t="str">
+        <f t="shared" si="93"/>
+        <v>PMID%3A7161483_Table1</v>
+      </c>
+      <c r="M145" t="str">
+        <f t="array" ref="M145">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L145,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="P145" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V145" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W145" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y145" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z145" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF145" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG145" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI145" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="AJ145" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK145" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL145" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM145" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="146" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E146" t="str">
+        <f t="shared" si="171"/>
+        <v>4</v>
+      </c>
+      <c r="F146" t="str">
+        <f t="shared" si="90"/>
         <v>Stephan_etal_1984</v>
       </c>
-      <c r="G142" t="str">
-        <f t="shared" si="148"/>
+      <c r="G146" t="str">
+        <f t="shared" si="172"/>
         <v>Stephan</v>
       </c>
-      <c r="H142" t="str">
+      <c r="H146" t="str">
         <f>_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A142," ("&amp;I142&amp;")"),
+_xlpm.authors,_xlfn.TEXTBEFORE(A146," ("&amp;I146&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I142" t="str">
-        <f t="shared" si="149"/>
+      <c r="I146" t="str">
+        <f t="shared" si="173"/>
         <v>1984</v>
       </c>
-      <c r="J142" t="str">
+      <c r="J146" t="str">
+        <f t="shared" si="198"/>
+        <v>PMID%3A6481154</v>
+      </c>
+      <c r="K146" t="str">
         <f t="shared" si="174"/>
-        <v>PMID%3A6481154</v>
-      </c>
-      <c r="K142" t="str">
-        <f t="shared" si="150"/>
         <v>Stephan_etal_1984_Table1</v>
       </c>
-      <c r="L142" t="str">
+      <c r="L146" t="str">
         <f t="shared" si="93"/>
         <v>PMID%3A6481154_Table1</v>
       </c>
-      <c r="M142" t="str">
-        <f t="array" ref="M142">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L142,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M146" t="str">
+        <f t="array" ref="M146">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L146,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>PMID%3A6481154_Table1.tsv</v>
       </c>
-      <c r="N142" s="2" t="s">
+      <c r="N146" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="P142" s="2" t="s">
+      <c r="P146" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="V142" s="2" t="s">
+      <c r="V146" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W142" s="2" t="s">
+      <c r="W146" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="Y142" s="2" t="s">
+      <c r="Y146" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="Z142" s="2" t="s">
+      <c r="Z146" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AF142" s="2" t="s">
+      <c r="AF146" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG142" s="2" t="s">
+      <c r="AG146" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI142" s="2" t="s">
+      <c r="AI146" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="AJ142" s="2" t="s">
+      <c r="AJ146" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AK142" s="2" t="s">
+      <c r="AK146" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL142" s="2" t="s">
+      <c r="AL146" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM142" s="2" t="s">
+      <c r="AM146" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A143" s="2" t="s">
+    <row r="147" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E143" t="str">
-        <f t="shared" si="147"/>
+      <c r="E147" t="str">
+        <f t="shared" si="171"/>
         <v>5</v>
       </c>
-      <c r="F143" t="str">
+      <c r="F147" t="str">
         <f t="shared" si="90"/>
         <v>Stephan_etal_1987</v>
       </c>
-      <c r="G143" t="str">
-        <f t="shared" si="148"/>
+      <c r="G147" t="str">
+        <f t="shared" si="172"/>
         <v>Stephan</v>
       </c>
-      <c r="H143" t="str">
+      <c r="H147" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I143" t="str">
-        <f t="shared" si="149"/>
+      <c r="I147" t="str">
+        <f t="shared" si="173"/>
         <v>1987</v>
       </c>
-      <c r="J143" t="str">
+      <c r="J147" t="str">
+        <f t="shared" si="198"/>
+        <v>PMID%3A3693895</v>
+      </c>
+      <c r="K147" t="str">
         <f t="shared" si="174"/>
-        <v>PMID%3A3693895</v>
-      </c>
-      <c r="K143" t="str">
-        <f t="shared" si="150"/>
         <v>Stephan_etal_1987_Table1</v>
       </c>
-      <c r="L143" t="str">
+      <c r="L147" t="str">
         <f t="shared" si="93"/>
         <v>PMID%3A3693895_Table1</v>
       </c>
-      <c r="M143" t="str">
-        <f t="array" ref="M143">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L143,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M147" t="str">
+        <f t="array" ref="M147">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L147,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>PMID%3A3693895_Table1.tsv</v>
       </c>
-      <c r="N143" s="2" t="s">
+      <c r="N147" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="P143" s="2" t="s">
+      <c r="P147" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="V143" s="2" t="s">
+      <c r="V147" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W143" s="2" t="s">
+      <c r="W147" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="Y143" s="2" t="s">
+      <c r="Y147" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="Z143" s="2" t="s">
+      <c r="Z147" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AF143" s="2" t="s">
+      <c r="AF147" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG143" s="2" t="s">
+      <c r="AG147" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI143" s="2" t="s">
+      <c r="AI147" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="AJ143" s="2" t="s">
+      <c r="AJ147" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AK143" s="2" t="s">
+      <c r="AK147" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL143" s="2" t="s">
+      <c r="AL147" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM143" s="2" t="s">
+      <c r="AM147" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A144" s="2" t="s">
+    <row r="148" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E144" t="str">
-        <f t="shared" si="147"/>
+      <c r="E148" t="str">
+        <f t="shared" si="171"/>
         <v>3</v>
       </c>
-      <c r="F144" t="str">
+      <c r="F148" t="str">
         <f t="shared" si="90"/>
         <v>Stephan_etal_1981</v>
       </c>
-      <c r="G144" t="str">
-        <f t="shared" si="148"/>
+      <c r="G148" t="str">
+        <f t="shared" si="172"/>
         <v>Stephan</v>
       </c>
-      <c r="H144" t="str">
+      <c r="H148" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
-      <c r="I144" t="str">
-        <f t="shared" si="149"/>
+      <c r="I148" t="str">
+        <f t="shared" si="173"/>
         <v>1981</v>
       </c>
-      <c r="J144" t="str">
+      <c r="J148" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1159%2F000155963</v>
+      </c>
+      <c r="K148" t="str">
         <f t="shared" si="174"/>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K144" t="str">
-        <f t="shared" si="150"/>
         <v>Stephan_etal_1981_TableI</v>
       </c>
-      <c r="L144" t="str">
-        <f t="shared" ref="L144:L163" si="177">J144 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D144,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L148" t="str">
+        <f t="shared" ref="L148:L167" si="201">J148 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D148,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1159%2F000155963_TableI</v>
       </c>
-      <c r="M144" t="str">
-        <f t="array" ref="M144">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L144,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+      <c r="M148" t="str">
+        <f t="array" ref="M148">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L148,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N144" s="2" t="s">
+      <c r="N148" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="P144" s="2"/>
-      <c r="V144" s="2" t="s">
+      <c r="P148" s="2"/>
+      <c r="V148" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y144" s="2" t="s">
+      <c r="Y148" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="Z144" s="2" t="s">
+      <c r="Z148" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AF144" s="2" t="s">
+      <c r="AF148" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AG144" s="2" t="s">
+      <c r="AG148" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AI144" s="2" t="s">
+      <c r="AI148" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="AJ144" s="2" t="s">
+      <c r="AJ148" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AK144" s="2" t="s">
+      <c r="AK148" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AL144" s="2" t="s">
+      <c r="AL148" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AM144" s="2" t="s">
+      <c r="AM148" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="145" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A145" s="2" t="s">
+    <row r="149" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D149" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="E145" t="str">
-        <f t="shared" ref="E145" si="178">RIGHT(A145,1)</f>
+      <c r="E149" t="str">
+        <f t="shared" ref="E149" si="202">RIGHT(A149,1)</f>
         <v>3</v>
       </c>
-      <c r="F145" t="str">
-        <f t="shared" ref="F145" si="179">G145 &amp; IF(H145&lt;&gt;"", "_" &amp; H145, "_") &amp; IF(I145&lt;&gt;"", "_" &amp; I145, "_") &amp; IF(B145&lt;&gt;"", "_" &amp; B145, "")</f>
+      <c r="F149" t="str">
+        <f t="shared" ref="F149" si="203">G149 &amp; IF(H149&lt;&gt;"", "_" &amp; H149, "_") &amp; IF(I149&lt;&gt;"", "_" &amp; I149, "_") &amp; IF(B149&lt;&gt;"", "_" &amp; B149, "")</f>
         <v>Stephan_etal_1981</v>
       </c>
-      <c r="G145" t="str">
-        <f t="shared" ref="G145" si="180">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A145,","), "-", ""), " ", "")</f>
+      <c r="G149" t="str">
+        <f t="shared" ref="G149" si="204">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A149,","), "-", ""), " ", "")</f>
         <v>Stephan</v>
       </c>
-      <c r="H145" t="str">
-        <f t="shared" ref="H145" si="181">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A145," ("&amp;I145&amp;")"),
+      <c r="H149" t="str">
+        <f t="shared" ref="H149" si="205">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A149," ("&amp;I149&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I145" t="str">
-        <f t="shared" ref="I145" si="182">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A145, "("), ")")</f>
+      <c r="I149" t="str">
+        <f t="shared" ref="I149" si="206">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A149, "("), ")")</f>
         <v>1981</v>
       </c>
-      <c r="J145" t="str">
-        <f t="shared" ref="J145" si="183">_xlfn.LET(
-_xlpm.doi,IF(C145&lt;&gt;"",C145,_xlfn.TEXTAFTER(A145,"https://doi.org/")),
+      <c r="J149" t="str">
+        <f t="shared" ref="J149" si="207">_xlfn.LET(
+_xlpm.doi,IF(C149&lt;&gt;"",C149,_xlfn.TEXTAFTER(A149,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -13940,364 +14253,20 @@
 )</f>
         <v>10.1159%2F000155963</v>
       </c>
-      <c r="K145" t="str">
-        <f t="shared" ref="K145" si="184">TRIM(_xlfn.TEXTJOIN("_",FALSE,F145,(SUBSTITUTE(SUBSTITUTE(D145," ",""), "_", ""))))</f>
+      <c r="K149" t="str">
+        <f t="shared" ref="K149" si="208">TRIM(_xlfn.TEXTJOIN("_",FALSE,F149,(SUBSTITUTE(SUBSTITUTE(D149," ",""), "_", ""))))</f>
         <v>Stephan_etal_1981_TableII</v>
       </c>
-      <c r="L145" t="str">
-        <f t="shared" ref="L145" si="185">J145 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D145,CHAR(160),"")," ",""),"_","")</f>
+      <c r="L149" t="str">
+        <f t="shared" ref="L149" si="209">J149 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D149,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1159%2F000155963_TableII</v>
-      </c>
-      <c r="M145" t="str">
-        <f t="array" ref="M145">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L145,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N145" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="P145" s="2"/>
-      <c r="V145" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y145" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z145" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF145" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG145" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI145" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="AJ145" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK145" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL145" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM145" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="146" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A146" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E146" t="str">
-        <f t="shared" ref="E146" si="186">RIGHT(A146,1)</f>
-        <v>3</v>
-      </c>
-      <c r="F146" t="str">
-        <f t="shared" ref="F146" si="187">G146 &amp; IF(H146&lt;&gt;"", "_" &amp; H146, "_") &amp; IF(I146&lt;&gt;"", "_" &amp; I146, "_") &amp; IF(B146&lt;&gt;"", "_" &amp; B146, "")</f>
-        <v>Stephan_etal_1981</v>
-      </c>
-      <c r="G146" t="str">
-        <f t="shared" ref="G146" si="188">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A146,","), "-", ""), " ", "")</f>
-        <v>Stephan</v>
-      </c>
-      <c r="H146" t="str">
-        <f t="shared" ref="H146" si="189">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A146," ("&amp;I146&amp;")"),
-_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
-_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
-IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="I146" t="str">
-        <f t="shared" ref="I146" si="190">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A146, "("), ")")</f>
-        <v>1981</v>
-      </c>
-      <c r="J146" t="str">
-        <f t="shared" ref="J146" si="191">_xlfn.LET(
-_xlpm.doi,IF(C146&lt;&gt;"",C146,_xlfn.TEXTAFTER(A146,"https://doi.org/")),
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-_xlpm.doi,
-"/","%2F"),
-":","%3A"),
-"&lt;","%3C"),
-"&gt;","%3E")
-)</f>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K146" t="str">
-        <f t="shared" ref="K146" si="192">TRIM(_xlfn.TEXTJOIN("_",FALSE,F146,(SUBSTITUTE(SUBSTITUTE(D146," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1981_TableIII</v>
-      </c>
-      <c r="L146" t="str">
-        <f t="shared" ref="L146" si="193">J146 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D146,CHAR(160),"")," ",""),"_","")</f>
-        <v>10.1159%2F000155963_TableIII</v>
-      </c>
-      <c r="M146" t="str">
-        <f t="array" ref="M146">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L146,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N146" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="P146" s="2"/>
-      <c r="V146" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y146" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z146" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF146" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG146" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI146" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="AJ146" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK146" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL146" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM146" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="147" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A147" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="E147" t="str">
-        <f t="shared" ref="E147:E149" si="194">RIGHT(A147,1)</f>
-        <v>3</v>
-      </c>
-      <c r="F147" t="str">
-        <f t="shared" ref="F147:F149" si="195">G147 &amp; IF(H147&lt;&gt;"", "_" &amp; H147, "_") &amp; IF(I147&lt;&gt;"", "_" &amp; I147, "_") &amp; IF(B147&lt;&gt;"", "_" &amp; B147, "")</f>
-        <v>Stephan_etal_1981</v>
-      </c>
-      <c r="G147" t="str">
-        <f t="shared" ref="G147:G149" si="196">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A147,","), "-", ""), " ", "")</f>
-        <v>Stephan</v>
-      </c>
-      <c r="H147" t="str">
-        <f t="shared" ref="H147:H149" si="197">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A147," ("&amp;I147&amp;")"),
-_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
-_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
-IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="I147" t="str">
-        <f t="shared" ref="I147:I149" si="198">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A147, "("), ")")</f>
-        <v>1981</v>
-      </c>
-      <c r="J147" t="str">
-        <f t="shared" ref="J147:J149" si="199">_xlfn.LET(
-_xlpm.doi,IF(C147&lt;&gt;"",C147,_xlfn.TEXTAFTER(A147,"https://doi.org/")),
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-_xlpm.doi,
-"/","%2F"),
-":","%3A"),
-"&lt;","%3C"),
-"&gt;","%3E")
-)</f>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K147" t="str">
-        <f t="shared" ref="K147:K149" si="200">TRIM(_xlfn.TEXTJOIN("_",FALSE,F147,(SUBSTITUTE(SUBSTITUTE(D147," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1981_TableIV</v>
-      </c>
-      <c r="L147" t="str">
-        <f t="shared" ref="L147:L149" si="201">J147 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D147,CHAR(160),"")," ",""),"_","")</f>
-        <v>10.1159%2F000155963_TableIV</v>
-      </c>
-      <c r="M147" t="str">
-        <f t="array" ref="M147">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L147,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N147" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="P147" s="2"/>
-      <c r="V147" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y147" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z147" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF147" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG147" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI147" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="AJ147" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK147" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL147" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM147" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="148" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A148" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E148" t="str">
-        <f t="shared" si="194"/>
-        <v>3</v>
-      </c>
-      <c r="F148" t="str">
-        <f t="shared" si="195"/>
-        <v>Stephan_etal_1981</v>
-      </c>
-      <c r="G148" t="str">
-        <f t="shared" si="196"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H148" t="str">
-        <f t="shared" si="197"/>
-        <v>etal</v>
-      </c>
-      <c r="I148" t="str">
-        <f t="shared" si="198"/>
-        <v>1981</v>
-      </c>
-      <c r="J148" t="str">
-        <f t="shared" si="199"/>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K148" t="str">
-        <f t="shared" si="200"/>
-        <v>Stephan_etal_1981_TableV</v>
-      </c>
-      <c r="L148" t="str">
-        <f t="shared" si="201"/>
-        <v>10.1159%2F000155963_TableV</v>
-      </c>
-      <c r="M148" t="str">
-        <f t="array" ref="M148">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L148,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N148" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="P148" s="2"/>
-      <c r="V148" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y148" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z148" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF148" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG148" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI148" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="AJ148" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK148" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL148" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM148" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="149" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A149" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E149" t="str">
-        <f t="shared" si="194"/>
-        <v>3</v>
-      </c>
-      <c r="F149" t="str">
-        <f t="shared" si="195"/>
-        <v>Stephan_etal_1981</v>
-      </c>
-      <c r="G149" t="str">
-        <f t="shared" si="196"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H149" t="str">
-        <f t="shared" si="197"/>
-        <v>etal</v>
-      </c>
-      <c r="I149" t="str">
-        <f t="shared" si="198"/>
-        <v>1981</v>
-      </c>
-      <c r="J149" t="str">
-        <f t="shared" si="199"/>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K149" t="str">
-        <f t="shared" si="200"/>
-        <v>Stephan_etal_1981_TableVI</v>
-      </c>
-      <c r="L149" t="str">
-        <f t="shared" si="201"/>
-        <v>10.1159%2F000155963_TableVI</v>
       </c>
       <c r="M149" t="str">
         <f t="array" ref="M149">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L149,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="P149" s="2"/>
       <c r="V149" s="2" t="s">
@@ -14336,22 +14305,22 @@
         <v>584</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="E150" t="str">
-        <f t="shared" ref="E150" si="202">RIGHT(A150,1)</f>
+        <f t="shared" ref="E150" si="210">RIGHT(A150,1)</f>
         <v>3</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" ref="F150" si="203">G150 &amp; IF(H150&lt;&gt;"", "_" &amp; H150, "_") &amp; IF(I150&lt;&gt;"", "_" &amp; I150, "_") &amp; IF(B150&lt;&gt;"", "_" &amp; B150, "")</f>
+        <f t="shared" ref="F150" si="211">G150 &amp; IF(H150&lt;&gt;"", "_" &amp; H150, "_") &amp; IF(I150&lt;&gt;"", "_" &amp; I150, "_") &amp; IF(B150&lt;&gt;"", "_" &amp; B150, "")</f>
         <v>Stephan_etal_1981</v>
       </c>
       <c r="G150" t="str">
-        <f t="shared" ref="G150" si="204">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A150,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G150" si="212">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A150,","), "-", ""), " ", "")</f>
         <v>Stephan</v>
       </c>
       <c r="H150" t="str">
-        <f t="shared" ref="H150" si="205">_xlfn.LET(
+        <f t="shared" ref="H150" si="213">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A150," ("&amp;I150&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
@@ -14360,11 +14329,11 @@
         <v>etal</v>
       </c>
       <c r="I150" t="str">
-        <f t="shared" ref="I150" si="206">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A150, "("), ")")</f>
+        <f t="shared" ref="I150" si="214">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A150, "("), ")")</f>
         <v>1981</v>
       </c>
       <c r="J150" t="str">
-        <f t="shared" ref="J150" si="207">_xlfn.LET(
+        <f t="shared" ref="J150" si="215">_xlfn.LET(
 _xlpm.doi,IF(C150&lt;&gt;"",C150,_xlfn.TEXTAFTER(A150,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
@@ -14379,24 +14348,21 @@
         <v>10.1159%2F000155963</v>
       </c>
       <c r="K150" t="str">
-        <f t="shared" ref="K150" si="208">TRIM(_xlfn.TEXTJOIN("_",FALSE,F150,(SUBSTITUTE(SUBSTITUTE(D150," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1981_TablesI-VI</v>
+        <f t="shared" ref="K150" si="216">TRIM(_xlfn.TEXTJOIN("_",FALSE,F150,(SUBSTITUTE(SUBSTITUTE(D150," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1981_TableIII</v>
       </c>
       <c r="L150" t="str">
-        <f t="shared" ref="L150" si="209">J150 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D150,CHAR(160),"")," ",""),"_","")</f>
-        <v>10.1159%2F000155963_TablesI-VI</v>
+        <f t="shared" ref="L150" si="217">J150 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D150,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1159%2F000155963_TableIII</v>
       </c>
       <c r="M150" t="str">
         <f t="array" ref="M150">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L150,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TablesI-VI.tsv</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s">
-        <v>647</v>
-      </c>
-      <c r="P150" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>notfound</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="P150" s="2"/>
       <c r="V150" s="2" t="s">
         <v>40</v>
       </c>
@@ -14430,28 +14396,25 @@
     </row>
     <row r="151" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>46</v>
+        <v>639</v>
       </c>
       <c r="E151" t="str">
-        <f t="shared" ref="E151" si="210">RIGHT(A151,1)</f>
-        <v>.</v>
+        <f t="shared" ref="E151:E153" si="218">RIGHT(A151,1)</f>
+        <v>3</v>
       </c>
       <c r="F151" t="str">
-        <f t="shared" ref="F151" si="211">G151 &amp; IF(H151&lt;&gt;"", "_" &amp; H151, "_") &amp; IF(I151&lt;&gt;"", "_" &amp; I151, "_") &amp; IF(B151&lt;&gt;"", "_" &amp; B151, "")</f>
-        <v>Stephan_etal_1988</v>
+        <f t="shared" ref="F151:F153" si="219">G151 &amp; IF(H151&lt;&gt;"", "_" &amp; H151, "_") &amp; IF(I151&lt;&gt;"", "_" &amp; I151, "_") &amp; IF(B151&lt;&gt;"", "_" &amp; B151, "")</f>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G151" t="str">
-        <f t="shared" ref="G151" si="212">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A151,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G151:G153" si="220">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A151,","), "-", ""), " ", "")</f>
         <v>Stephan</v>
       </c>
       <c r="H151" t="str">
-        <f t="shared" ref="H151" si="213">_xlfn.LET(
+        <f t="shared" ref="H151:H153" si="221">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A151," ("&amp;I151&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
@@ -14460,11 +14423,11 @@
         <v>etal</v>
       </c>
       <c r="I151" t="str">
-        <f t="shared" ref="I151" si="214">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A151, "("), ")")</f>
-        <v>1988</v>
+        <f t="shared" ref="I151:I153" si="222">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A151, "("), ")")</f>
+        <v>1981</v>
       </c>
       <c r="J151" t="str">
-        <f t="shared" ref="J151" si="215">_xlfn.LET(
+        <f t="shared" ref="J151:J153" si="223">_xlfn.LET(
 _xlpm.doi,IF(C151&lt;&gt;"",C151,_xlfn.TEXTAFTER(A151,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
@@ -14476,92 +14439,110 @@
 "&lt;","%3C"),
 "&gt;","%3E")
 )</f>
-        <v>ISBN%3A0845140000</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K151" t="str">
-        <f t="shared" ref="K151" si="216">TRIM(_xlfn.TEXTJOIN("_",FALSE,F151,(SUBSTITUTE(SUBSTITUTE(D151," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1988_TABLE1</v>
+        <f t="shared" ref="K151:K153" si="224">TRIM(_xlfn.TEXTJOIN("_",FALSE,F151,(SUBSTITUTE(SUBSTITUTE(D151," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1981_TableIV</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" ref="L151" si="217">J151 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D151,CHAR(160),"")," ",""),"_","")</f>
-        <v>ISBN%3A0845140000_TABLE1</v>
+        <f t="shared" ref="L151:L153" si="225">J151 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D151,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1159%2F000155963_TableIV</v>
       </c>
       <c r="M151" t="str">
         <f t="array" ref="M151">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L151,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>ISBN%3A0845140000_TABLE1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="P151" s="2"/>
-      <c r="V151" s="2"/>
-      <c r="Y151" s="2"/>
-      <c r="Z151" s="2"/>
-      <c r="AF151" s="2"/>
-      <c r="AG151" s="2"/>
-      <c r="AI151" s="3"/>
-      <c r="AJ151" s="3"/>
-      <c r="AK151" s="3"/>
-      <c r="AL151" s="2"/>
-      <c r="AM151" s="2"/>
+      <c r="V151" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y151" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z151" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF151" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG151" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI151" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AJ151" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK151" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL151" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM151" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="152" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="E152" t="str">
-        <f t="shared" ref="E152:E153" si="218">RIGHT(A152,1)</f>
-        <v>8</v>
+        <f t="shared" si="218"/>
+        <v>3</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" ref="F152:F163" si="219">G152 &amp; IF(H152&lt;&gt;"", "_" &amp; H152, "_") &amp; IF(I152&lt;&gt;"", "_" &amp; I152, "_") &amp; IF(B152&lt;&gt;"", "_" &amp; B152, "")</f>
-        <v>Stimpson_etal_2015</v>
+        <f t="shared" si="219"/>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G152" t="str">
-        <f t="shared" si="148"/>
-        <v>Stimpson</v>
+        <f t="shared" si="220"/>
+        <v>Stephan</v>
       </c>
       <c r="H152" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="221"/>
         <v>etal</v>
       </c>
       <c r="I152" t="str">
-        <f t="shared" si="149"/>
-        <v>2015</v>
+        <f t="shared" si="222"/>
+        <v>1981</v>
       </c>
       <c r="J152" t="str">
-        <f t="shared" si="174"/>
-        <v>10.1093%2Fscan%2Fnsv128</v>
+        <f t="shared" si="223"/>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K152" t="str">
-        <f t="shared" si="150"/>
-        <v>Stimpson_etal_2015_TableS1</v>
+        <f t="shared" si="224"/>
+        <v>Stephan_etal_1981_TableV</v>
       </c>
       <c r="L152" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
+        <f t="shared" si="225"/>
+        <v>10.1159%2F000155963_TableV</v>
       </c>
       <c r="M152" t="str">
         <f t="array" ref="M152">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L152,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1093%2Fscan%2Fnsv128_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="P152" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="P152" s="2"/>
       <c r="V152" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y152" s="2" t="s">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="Z152" s="2" t="s">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AF152" s="2" t="s">
         <v>70</v>
@@ -14569,6 +14550,15 @@
       <c r="AG152" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="AI152" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AJ152" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK152" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="AL152" s="2" t="s">
         <v>61</v>
       </c>
@@ -14578,61 +14568,59 @@
     </row>
     <row r="153" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="E153" t="str">
         <f t="shared" si="218"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F153" t="str">
         <f t="shared" si="219"/>
-        <v>Stimpson_etal_2015</v>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G153" t="str">
-        <f t="shared" si="148"/>
-        <v>Stimpson</v>
+        <f t="shared" si="220"/>
+        <v>Stephan</v>
       </c>
       <c r="H153" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="221"/>
         <v>etal</v>
       </c>
       <c r="I153" t="str">
-        <f t="shared" si="149"/>
-        <v>2015</v>
+        <f t="shared" si="222"/>
+        <v>1981</v>
       </c>
       <c r="J153" t="str">
-        <f t="shared" si="174"/>
-        <v>10.1093%2Fscan%2Fnsv128</v>
+        <f t="shared" si="223"/>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K153" t="str">
-        <f t="shared" si="150"/>
-        <v>Stimpson_etal_2015_TableS2</v>
+        <f t="shared" si="224"/>
+        <v>Stephan_etal_1981_TableVI</v>
       </c>
       <c r="L153" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
+        <f t="shared" si="225"/>
+        <v>10.1159%2F000155963_TableVI</v>
       </c>
       <c r="M153" t="str">
         <f t="array" ref="M153">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L153,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>10.1093%2Fscan%2Fnsv128_TableS2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="P153" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="P153" s="2"/>
       <c r="V153" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y153" s="2" t="s">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="Z153" s="2" t="s">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AF153" s="2" t="s">
         <v>70</v>
@@ -14640,6 +14628,15 @@
       <c r="AG153" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="AI153" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AJ153" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK153" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="AL153" s="2" t="s">
         <v>61</v>
       </c>
@@ -14649,100 +14646,138 @@
     </row>
     <row r="154" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>78</v>
+        <v>649</v>
       </c>
       <c r="E154" t="str">
-        <f t="shared" si="147"/>
-        <v>2</v>
+        <f t="shared" ref="E154" si="226">RIGHT(A154,1)</f>
+        <v>3</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="219"/>
-        <v>Turner_etal_2016</v>
+        <f t="shared" ref="F154" si="227">G154 &amp; IF(H154&lt;&gt;"", "_" &amp; H154, "_") &amp; IF(I154&lt;&gt;"", "_" &amp; I154, "_") &amp; IF(B154&lt;&gt;"", "_" &amp; B154, "")</f>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G154" t="str">
-        <f t="shared" si="148"/>
-        <v>Turner</v>
+        <f t="shared" ref="G154" si="228">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A154,","), "-", ""), " ", "")</f>
+        <v>Stephan</v>
       </c>
       <c r="H154" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="H154" si="229">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A154," ("&amp;I154&amp;")"),
+_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
+_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
+IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
+)</f>
         <v>etal</v>
       </c>
       <c r="I154" t="str">
-        <f t="shared" si="149"/>
-        <v>2016</v>
+        <f t="shared" ref="I154" si="230">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A154, "("), ")")</f>
+        <v>1981</v>
       </c>
       <c r="J154" t="str">
-        <f t="shared" si="174"/>
-        <v>10.1159%2F000446762</v>
+        <f t="shared" ref="J154" si="231">_xlfn.LET(
+_xlpm.doi,IF(C154&lt;&gt;"",C154,_xlfn.TEXTAFTER(A154,"https://doi.org/")),
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+_xlpm.doi,
+"/","%2F"),
+":","%3A"),
+"&lt;","%3C"),
+"&gt;","%3E")
+)</f>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K154" t="str">
-        <f t="shared" si="150"/>
-        <v>Turner_etal_2016_Table1</v>
+        <f t="shared" ref="K154" si="232">TRIM(_xlfn.TEXTJOIN("_",FALSE,F154,(SUBSTITUTE(SUBSTITUTE(D154," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1981_TablesI-VI</v>
       </c>
       <c r="L154" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <f t="shared" ref="L154" si="233">J154 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D154,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1159%2F000155963_TablesI-VI</v>
       </c>
       <c r="M154" t="str">
         <f t="array" ref="M154">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L154,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N154" s="2" t="s">
-        <v>591</v>
+        <v>10.1159%2F000155963_TablesI-VI.tsv</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" t="s">
+        <v>647</v>
+      </c>
+      <c r="P154" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V154" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y154" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z154" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF154" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG154" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="AI154" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="AJ154" s="2" t="s">
-        <v>118</v>
+        <v>82</v>
+      </c>
+      <c r="AK154" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="AL154" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AM154" s="2" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C155" t="s">
-        <v>779</v>
+        <v>629</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>630</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>777</v>
+        <v>46</v>
       </c>
       <c r="E155" t="str">
-        <f t="shared" ref="E155:E156" si="220">RIGHT(A155,1)</f>
+        <f t="shared" ref="E155" si="234">RIGHT(A155,1)</f>
         <v>.</v>
       </c>
       <c r="F155" t="str">
-        <f t="shared" ref="F155:F156" si="221">G155 &amp; IF(H155&lt;&gt;"", "_" &amp; H155, "_") &amp; IF(I155&lt;&gt;"", "_" &amp; I155, "_") &amp; IF(B155&lt;&gt;"", "_" &amp; B155, "")</f>
-        <v>Weaver__2001</v>
+        <f t="shared" ref="F155" si="235">G155 &amp; IF(H155&lt;&gt;"", "_" &amp; H155, "_") &amp; IF(I155&lt;&gt;"", "_" &amp; I155, "_") &amp; IF(B155&lt;&gt;"", "_" &amp; B155, "")</f>
+        <v>Stephan_etal_1988</v>
       </c>
       <c r="G155" t="str">
-        <f t="shared" ref="G155:G156" si="222">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A155,","), "-", ""), " ", "")</f>
-        <v>Weaver</v>
+        <f t="shared" ref="G155" si="236">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A155,","), "-", ""), " ", "")</f>
+        <v>Stephan</v>
       </c>
       <c r="H155" t="str">
-        <f t="shared" ref="H155:H156" si="223">_xlfn.LET(
+        <f t="shared" ref="H155" si="237">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A155," ("&amp;I155&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I155" t="str">
-        <f t="shared" ref="I155:I156" si="224">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A155, "("), ")")</f>
-        <v>2001</v>
+        <f t="shared" ref="I155" si="238">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A155, "("), ")")</f>
+        <v>1988</v>
       </c>
       <c r="J155" t="str">
-        <f t="shared" ref="J155:J156" si="225">_xlfn.LET(
+        <f t="shared" ref="J155" si="239">_xlfn.LET(
 _xlpm.doi,IF(C155&lt;&gt;"",C155,_xlfn.TEXTAFTER(A155,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
@@ -14754,565 +14789,843 @@
 "&lt;","%3C"),
 "&gt;","%3E")
 )</f>
-        <v>UMI%3A3017523</v>
+        <v>ISBN%3A0845140000</v>
       </c>
       <c r="K155" t="str">
-        <f t="shared" ref="K155:K156" si="226">TRIM(_xlfn.TEXTJOIN("_",FALSE,F155,(SUBSTITUTE(SUBSTITUTE(D155," ",""), "_", ""))))</f>
-        <v>Weaver__2001_TableA-15</v>
+        <f t="shared" ref="K155" si="240">TRIM(_xlfn.TEXTJOIN("_",FALSE,F155,(SUBSTITUTE(SUBSTITUTE(D155," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1988_TABLE1</v>
       </c>
       <c r="L155" t="str">
-        <f t="shared" ref="L155:L156" si="227">J155 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D155,CHAR(160),"")," ",""),"_","")</f>
-        <v>UMI%3A3017523_TableA-15</v>
+        <f t="shared" ref="L155" si="241">J155 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D155,CHAR(160),"")," ",""),"_","")</f>
+        <v>ISBN%3A0845140000_TABLE1</v>
       </c>
       <c r="M155" t="str">
         <f t="array" ref="M155">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L155,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N155" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="AI155" s="2"/>
-      <c r="AJ155" s="2"/>
+        <v>ISBN%3A0845140000_TABLE1.tsv</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="P155" s="2"/>
+      <c r="V155" s="2"/>
+      <c r="Y155" s="2"/>
+      <c r="Z155" s="2"/>
+      <c r="AF155" s="2"/>
+      <c r="AG155" s="2"/>
+      <c r="AI155" s="3"/>
+      <c r="AJ155" s="3"/>
+      <c r="AK155" s="3"/>
       <c r="AL155" s="2"/>
       <c r="AM155" s="2"/>
     </row>
     <row r="156" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C156" t="s">
-        <v>779</v>
+        <v>586</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>776</v>
+        <v>587</v>
       </c>
       <c r="E156" t="str">
-        <f t="shared" si="220"/>
-        <v>.</v>
+        <f t="shared" ref="E156:E157" si="242">RIGHT(A156,1)</f>
+        <v>8</v>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="221"/>
-        <v>Weaver__2001</v>
+        <f t="shared" ref="F156:F167" si="243">G156 &amp; IF(H156&lt;&gt;"", "_" &amp; H156, "_") &amp; IF(I156&lt;&gt;"", "_" &amp; I156, "_") &amp; IF(B156&lt;&gt;"", "_" &amp; B156, "")</f>
+        <v>Stimpson_etal_2015</v>
       </c>
       <c r="G156" t="str">
-        <f t="shared" si="222"/>
-        <v>Weaver</v>
+        <f t="shared" si="172"/>
+        <v>Stimpson</v>
       </c>
       <c r="H156" t="str">
-        <f t="shared" si="223"/>
-        <v/>
+        <f t="shared" si="97"/>
+        <v>etal</v>
       </c>
       <c r="I156" t="str">
-        <f t="shared" si="224"/>
-        <v>2001</v>
+        <f t="shared" si="173"/>
+        <v>2015</v>
       </c>
       <c r="J156" t="str">
-        <f t="shared" si="225"/>
-        <v>UMI%3A3017523</v>
+        <f t="shared" si="198"/>
+        <v>10.1093%2Fscan%2Fnsv128</v>
       </c>
       <c r="K156" t="str">
-        <f t="shared" si="226"/>
-        <v>Weaver__2001_NotesforTableA-15</v>
+        <f t="shared" si="174"/>
+        <v>Stimpson_etal_2015_TableS1</v>
       </c>
       <c r="L156" t="str">
-        <f t="shared" si="227"/>
-        <v>UMI%3A3017523_NotesforTableA-15</v>
+        <f t="shared" si="201"/>
+        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
       </c>
       <c r="M156" t="str">
         <f t="array" ref="M156">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L156,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N156" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="AI156" s="2"/>
-      <c r="AJ156" s="2"/>
-      <c r="AL156" s="2"/>
-      <c r="AM156" s="2"/>
+        <v>10.1093%2Fscan%2Fnsv128_TableS1.tsv</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V156" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y156" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="Z156" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="AF156" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG156" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL156" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM156" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="157" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E157" t="str">
-        <f t="shared" si="147"/>
-        <v>1</v>
+        <f t="shared" si="242"/>
+        <v>8</v>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="219"/>
-        <v>Wilman_etal_2014</v>
+        <f t="shared" si="243"/>
+        <v>Stimpson_etal_2015</v>
       </c>
       <c r="G157" t="str">
-        <f t="shared" si="148"/>
-        <v>Wilman</v>
+        <f t="shared" si="172"/>
+        <v>Stimpson</v>
       </c>
       <c r="H157" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
       <c r="I157" t="str">
-        <f t="shared" si="149"/>
-        <v>2014</v>
+        <f t="shared" si="173"/>
+        <v>2015</v>
       </c>
       <c r="J157" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1093%2Fscan%2Fnsv128</v>
+      </c>
+      <c r="K157" t="str">
         <f t="shared" si="174"/>
-        <v>10.1890%2F13-1917.1</v>
-      </c>
-      <c r="K157" t="str">
-        <f t="shared" si="150"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+        <v>Stimpson_etal_2015_TableS2</v>
       </c>
       <c r="L157" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <f t="shared" si="201"/>
+        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
       </c>
       <c r="M157" t="str">
         <f t="array" ref="M157">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L157,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="AI157" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="AJ157" s="2" t="s">
-        <v>118</v>
+        <v>10.1093%2Fscan%2Fnsv128_TableS2.tsv</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V157" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y157" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="Z157" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="AF157" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG157" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="AL157" s="2" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="AM157" s="2" t="s">
-        <v>596</v>
+        <v>73</v>
       </c>
     </row>
     <row r="158" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>598</v>
+        <v>78</v>
       </c>
       <c r="E158" t="str">
-        <f t="shared" si="147"/>
-        <v>7</v>
+        <f t="shared" si="171"/>
+        <v>2</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="219"/>
-        <v>Wimberly_etal_2021</v>
+        <f t="shared" si="243"/>
+        <v>Turner_etal_2016</v>
       </c>
       <c r="G158" t="str">
-        <f t="shared" si="148"/>
-        <v>Wimberly</v>
+        <f t="shared" si="172"/>
+        <v>Turner</v>
       </c>
       <c r="H158" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
       <c r="I158" t="str">
-        <f t="shared" si="149"/>
-        <v>2021</v>
+        <f t="shared" si="173"/>
+        <v>2016</v>
       </c>
       <c r="J158" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1159%2F000446762</v>
+      </c>
+      <c r="K158" t="str">
         <f t="shared" si="174"/>
-        <v>10.1098%2Frspb.2021.0937</v>
-      </c>
-      <c r="K158" t="str">
-        <f t="shared" si="150"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
+        <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L158" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <f t="shared" si="201"/>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M158" t="str">
         <f t="array" ref="M158">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L158,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P158" s="2" t="s">
-        <v>312</v>
+      <c r="N158" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="AI158" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="AJ158" s="2" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="AL158" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="AM158" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="159" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>599</v>
+        <v>777</v>
+      </c>
+      <c r="C159" t="s">
+        <v>778</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>600</v>
+        <v>776</v>
       </c>
       <c r="E159" t="str">
-        <f t="shared" si="147"/>
-        <v>5</v>
+        <f t="shared" ref="E159:E160" si="244">RIGHT(A159,1)</f>
+        <v>.</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="219"/>
-        <v>Winkler_Bryant_2021</v>
+        <f t="shared" ref="F159:F160" si="245">G159 &amp; IF(H159&lt;&gt;"", "_" &amp; H159, "_") &amp; IF(I159&lt;&gt;"", "_" &amp; I159, "_") &amp; IF(B159&lt;&gt;"", "_" &amp; B159, "")</f>
+        <v>Weaver__2001</v>
       </c>
       <c r="G159" t="str">
-        <f t="shared" si="148"/>
-        <v>Winkler</v>
+        <f t="shared" ref="G159:G160" si="246">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A159,","), "-", ""), " ", "")</f>
+        <v>Weaver</v>
       </c>
       <c r="H159" t="str">
-        <f t="shared" si="97"/>
-        <v>Bryant</v>
+        <f t="shared" ref="H159:H160" si="247">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A159," ("&amp;I159&amp;")"),
+_xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
+_xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
+IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
+)</f>
+        <v/>
       </c>
       <c r="I159" t="str">
-        <f t="shared" si="149"/>
-        <v>2021</v>
+        <f t="shared" ref="I159:I160" si="248">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A159, "("), ")")</f>
+        <v>2001</v>
       </c>
       <c r="J159" t="str">
-        <f t="shared" si="174"/>
-        <v>10.1080%2F09524622.2021.1905065</v>
+        <f t="shared" ref="J159:J160" si="249">_xlfn.LET(
+_xlpm.doi,IF(C159&lt;&gt;"",C159,_xlfn.TEXTAFTER(A159,"https://doi.org/")),
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+SUBSTITUTE(
+_xlpm.doi,
+"/","%2F"),
+":","%3A"),
+"&lt;","%3C"),
+"&gt;","%3E")
+)</f>
+        <v>UMI%3A3017523</v>
       </c>
       <c r="K159" t="str">
-        <f t="shared" si="150"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <f t="shared" ref="K159:K160" si="250">TRIM(_xlfn.TEXTJOIN("_",FALSE,F159,(SUBSTITUTE(SUBSTITUTE(D159," ",""), "_", ""))))</f>
+        <v>Weaver__2001_TableA-15</v>
       </c>
       <c r="L159" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <f t="shared" ref="L159:L160" si="251">J159 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D159,CHAR(160),"")," ",""),"_","")</f>
+        <v>UMI%3A3017523_TableA-15</v>
       </c>
       <c r="M159" t="str">
         <f t="array" ref="M159">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L159,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q159" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="T159" s="2" t="str">
-        <f>IF(S159="N", R159, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U159" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V159" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="AH159" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI159" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="AJ159" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL159" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM159" s="2" t="s">
-        <v>603</v>
-      </c>
+      <c r="N159" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="AI159" s="2"/>
+      <c r="AJ159" s="2"/>
+      <c r="AL159" s="2"/>
+      <c r="AM159" s="2"/>
     </row>
     <row r="160" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>604</v>
+        <v>777</v>
+      </c>
+      <c r="C160" t="s">
+        <v>778</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>78</v>
+        <v>775</v>
       </c>
       <c r="E160" t="str">
-        <f t="shared" si="147"/>
-        <v>0</v>
+        <f t="shared" si="244"/>
+        <v>.</v>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="219"/>
-        <v>Young_etal_2013</v>
+        <f t="shared" si="245"/>
+        <v>Weaver__2001</v>
       </c>
       <c r="G160" t="str">
-        <f t="shared" si="148"/>
-        <v>Young</v>
+        <f t="shared" si="246"/>
+        <v>Weaver</v>
       </c>
       <c r="H160" t="str">
-        <f t="shared" si="97"/>
-        <v>etal</v>
+        <f t="shared" si="247"/>
+        <v/>
       </c>
       <c r="I160" t="str">
-        <f t="shared" si="149"/>
-        <v>2013</v>
+        <f t="shared" si="248"/>
+        <v>2001</v>
       </c>
       <c r="J160" t="str">
-        <f t="shared" si="174"/>
-        <v>10.3389%2Ffncir.2013.00030</v>
+        <f t="shared" si="249"/>
+        <v>UMI%3A3017523</v>
       </c>
       <c r="K160" t="str">
-        <f t="shared" si="150"/>
-        <v>Young_etal_2013_Table1</v>
+        <f t="shared" si="250"/>
+        <v>Weaver__2001_NotesforTableA-15</v>
       </c>
       <c r="L160" t="str">
-        <f t="shared" si="177"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <f t="shared" si="251"/>
+        <v>UMI%3A3017523_NotesforTableA-15</v>
       </c>
       <c r="M160" t="str">
         <f t="array" ref="M160">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L160,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P160" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q160" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="T160" s="2" t="str">
-        <f>IF(S160="N", R160, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U160" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V160" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH160" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AI160" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="AJ160" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK160" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL160" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM160" s="2" t="s">
-        <v>606</v>
-      </c>
+      <c r="N160" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="AI160" s="2"/>
+      <c r="AJ160" s="2"/>
+      <c r="AL160" s="2"/>
+      <c r="AM160" s="2"/>
     </row>
     <row r="161" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>78</v>
+        <v>594</v>
       </c>
       <c r="E161" t="str">
-        <f t="shared" si="147"/>
-        <v>0</v>
+        <f t="shared" si="171"/>
+        <v>1</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="219"/>
-        <v>Young_etal_2013</v>
+        <f t="shared" si="243"/>
+        <v>Wilman_etal_2014</v>
       </c>
       <c r="G161" t="str">
-        <f t="shared" si="148"/>
-        <v>Young</v>
+        <f t="shared" si="172"/>
+        <v>Wilman</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="97"/>
         <v>etal</v>
       </c>
       <c r="I161" t="str">
-        <f t="shared" si="149"/>
-        <v>2013</v>
+        <f t="shared" si="173"/>
+        <v>2014</v>
       </c>
       <c r="J161" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1890%2F13-1917.1</v>
+      </c>
+      <c r="K161" t="str">
         <f t="shared" si="174"/>
-        <v>10.1073%2Fpnas.1318894110</v>
-      </c>
-      <c r="K161" t="str">
-        <f t="shared" si="150"/>
-        <v>Young_etal_2013_Table1</v>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L161" t="str">
-        <f t="shared" si="177"/>
-        <v>10.1073%2Fpnas.1318894110_Table1</v>
+        <f t="shared" si="201"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M161" t="str">
         <f t="array" ref="M161">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L161,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N161" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="V161" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y161" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG161" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="AI161" s="2" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="AJ161" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="AK161" s="2" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="AL161" s="2" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="AM161" s="2" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
     </row>
     <row r="162" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="E162" t="str">
-        <f t="shared" si="147"/>
-        <v>s</v>
+        <f t="shared" si="171"/>
+        <v>7</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" si="219"/>
-        <v>Zilles_Rehkämper_1988</v>
+        <f t="shared" si="243"/>
+        <v>Wimberly_etal_2021</v>
       </c>
       <c r="G162" t="str">
-        <f t="shared" si="148"/>
-        <v>Zilles</v>
+        <f t="shared" si="172"/>
+        <v>Wimberly</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="97"/>
-        <v>Rehkämper</v>
+        <v>etal</v>
       </c>
       <c r="I162" t="str">
-        <f t="shared" si="149"/>
-        <v>1988</v>
+        <f t="shared" si="173"/>
+        <v>2021</v>
       </c>
       <c r="J162" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1098%2Frspb.2021.0937</v>
+      </c>
+      <c r="K162" t="str">
         <f t="shared" si="174"/>
-        <v>ISBN%3A9780195043716</v>
-      </c>
-      <c r="K162" t="str">
-        <f t="shared" si="150"/>
-        <v>Zilles_Rehkämper_1988_Table12-2</v>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L162" t="str">
-        <f t="shared" si="177"/>
-        <v>ISBN%3A9780195043716_Table12-2</v>
+        <f t="shared" si="201"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M162" t="str">
         <f t="array" ref="M162">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L162,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
-        <v>ISBN%3A9780195043716_Table12-2.tsv</v>
-      </c>
-      <c r="N162" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="Y162" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z162" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="AF162" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG162" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI162" s="2" t="s">
-        <v>616</v>
+        <v>notfound</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="AJ162" s="2" t="s">
-        <v>617</v>
+        <v>41</v>
       </c>
       <c r="AL162" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AM162" s="2" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="163" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E163" t="str">
+        <f t="shared" si="171"/>
+        <v>5</v>
+      </c>
+      <c r="F163" t="str">
+        <f t="shared" si="243"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="G163" t="str">
+        <f t="shared" si="172"/>
+        <v>Winkler</v>
+      </c>
+      <c r="H163" t="str">
+        <f t="shared" si="97"/>
+        <v>Bryant</v>
+      </c>
+      <c r="I163" t="str">
+        <f t="shared" si="173"/>
+        <v>2021</v>
+      </c>
+      <c r="J163" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1080%2F09524622.2021.1905065</v>
+      </c>
+      <c r="K163" t="str">
+        <f t="shared" si="174"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
+      </c>
+      <c r="L163" t="str">
+        <f t="shared" si="201"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+      </c>
+      <c r="M163" t="str">
+        <f t="array" ref="M163">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L163,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P163" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q163" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="T163" s="2" t="str">
+        <f>IF(S163="N", R163, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U163" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V163" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="AH163" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI163" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="AJ163" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL163" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM163" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="164" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A164" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E164" t="str">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+      <c r="F164" t="str">
+        <f t="shared" si="243"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="G164" t="str">
+        <f t="shared" si="172"/>
+        <v>Young</v>
+      </c>
+      <c r="H164" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I164" t="str">
+        <f t="shared" si="173"/>
+        <v>2013</v>
+      </c>
+      <c r="J164" t="str">
+        <f t="shared" si="198"/>
+        <v>10.3389%2Ffncir.2013.00030</v>
+      </c>
+      <c r="K164" t="str">
+        <f t="shared" si="174"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L164" t="str">
+        <f t="shared" si="201"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M164" t="str">
+        <f t="array" ref="M164">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L164,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P164" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q164" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="T164" s="2" t="str">
+        <f>IF(S164="N", R164, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U164" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V164" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH164" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI164" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="AJ164" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK164" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL164" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM164" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="165" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A165" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E165" t="str">
+        <f t="shared" si="171"/>
+        <v>0</v>
+      </c>
+      <c r="F165" t="str">
+        <f t="shared" si="243"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="G165" t="str">
+        <f t="shared" si="172"/>
+        <v>Young</v>
+      </c>
+      <c r="H165" t="str">
+        <f t="shared" si="97"/>
+        <v>etal</v>
+      </c>
+      <c r="I165" t="str">
+        <f t="shared" si="173"/>
+        <v>2013</v>
+      </c>
+      <c r="J165" t="str">
+        <f t="shared" si="198"/>
+        <v>10.1073%2Fpnas.1318894110</v>
+      </c>
+      <c r="K165" t="str">
+        <f t="shared" si="174"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L165" t="str">
+        <f t="shared" si="201"/>
+        <v>10.1073%2Fpnas.1318894110_Table1</v>
+      </c>
+      <c r="M165" t="str">
+        <f t="array" ref="M165">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L165,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="V165" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y165" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AG165" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI165" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="AJ165" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="AK165" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL165" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM165" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="166" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A166" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E166" t="str">
+        <f t="shared" si="171"/>
+        <v>s</v>
+      </c>
+      <c r="F166" t="str">
+        <f t="shared" si="243"/>
+        <v>Zilles_Rehkämper_1988</v>
+      </c>
+      <c r="G166" t="str">
+        <f t="shared" si="172"/>
+        <v>Zilles</v>
+      </c>
+      <c r="H166" t="str">
+        <f t="shared" si="97"/>
+        <v>Rehkämper</v>
+      </c>
+      <c r="I166" t="str">
+        <f t="shared" si="173"/>
+        <v>1988</v>
+      </c>
+      <c r="J166" t="str">
+        <f t="shared" si="198"/>
+        <v>ISBN%3A9780195043716</v>
+      </c>
+      <c r="K166" t="str">
+        <f t="shared" si="174"/>
+        <v>Zilles_Rehkämper_1988_Table12-2</v>
+      </c>
+      <c r="L166" t="str">
+        <f t="shared" si="201"/>
+        <v>ISBN%3A9780195043716_Table12-2</v>
+      </c>
+      <c r="M166" t="str">
+        <f t="array" ref="M166">IFERROR(INDEX(FileList!$A$1:$A$100,MATCH(TRUE,EXACT(L166,_xlfn.TEXTBEFORE(FileList!$A$1:$A$100,".tsv")),0)),"notfound")</f>
+        <v>ISBN%3A9780195043716_Table12-2.tsv</v>
+      </c>
+      <c r="N166" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="Y166" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z166" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="AF166" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG166" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI166" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="AJ166" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="AL166" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM166" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="167" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A167" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E163" t="str">
-        <f t="shared" si="147"/>
+      <c r="E167" t="str">
+        <f t="shared" si="171"/>
         <v>6</v>
       </c>
-      <c r="F163" t="str">
-        <f t="shared" si="219"/>
+      <c r="F167" t="str">
+        <f t="shared" si="243"/>
         <v>Zilles_etal_2013</v>
       </c>
-      <c r="G163" t="str">
-        <f t="shared" ref="G163" si="228">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A163,","), "-", ""), " ", "")</f>
+      <c r="G167" t="str">
+        <f t="shared" ref="G167" si="252">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A167,","), "-", ""), " ", "")</f>
         <v>Zilles</v>
       </c>
-      <c r="H163" t="str">
-        <f t="shared" ref="H163" si="229">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A163," ("&amp;I163&amp;")"),
+      <c r="H167" t="str">
+        <f t="shared" ref="H167" si="253">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A167," ("&amp;I167&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
-      <c r="I163" t="str">
-        <f t="shared" ref="I163" si="230">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A163, "("), ")")</f>
+      <c r="I167" t="str">
+        <f t="shared" ref="I167" si="254">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A167, "("), ")")</f>
         <v>2013</v>
       </c>
-      <c r="J163" t="str">
-        <f t="shared" si="174"/>
+      <c r="J167" t="str">
+        <f t="shared" si="198"/>
         <v>10.1016%2Fj.tins.2013.01.006</v>
       </c>
-      <c r